--- a/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE12"/>
+  <dimension ref="A1:BE14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,84 +515,84 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_interceptions</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions_against</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions_against</t>
-        </is>
-      </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
@@ -615,97 +615,97 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
           <t>dif_sum_val_player_miss</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_pot_player_miss</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -717,32 +717,32 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ld9fFUZA</t>
+          <t>raSHWV4o</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45462.89583333334</v>
+        <v>45463.10416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mendoza r 
+          <t xml:space="preserve">de oliveira m 
   usa </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">toyota stadium
-  frisco  tx </t>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>bm8usLzB</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -759,141 +759,141 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>WWvwigh</t>
+          <t>Onn3tCA</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>UFWZoX9</t>
+          <t>EqKWmJf</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="n">
-        <v>0.5999999999999996</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.166666666666667</v>
-      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>0.3333333333333335</v>
+        <v>0.2626262626262625</v>
       </c>
       <c r="U2" t="n">
-        <v>-1</v>
+        <v>0.898989898989899</v>
       </c>
       <c r="V2" t="n">
-        <v>5.5</v>
+        <v>3.595959595959597</v>
       </c>
       <c r="W2" t="n">
-        <v>-5.5</v>
+        <v>1.858585858585858</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.833333333333332</v>
+        <v>0.3535353535353538</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.833333333333334</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.833333333333332</v>
+        <v>-3.171717171717169</v>
       </c>
       <c r="AA2" t="n">
-        <v>-2.5</v>
+        <v>3.171717171717169</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.166666666666667</v>
+        <v>1</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1.333333333333333</v>
+        <v>-0.8888888888888888</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.333333333333333</v>
+        <v>-0.2222222222222223</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.9999999999999996</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
+        <v>0.2626262626262625</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-2.252525252525253</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.1616161616161627</v>
+      </c>
       <c r="AH2" t="n">
-        <v>0.6825000000000001</v>
+        <v>0.04194444444444434</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.1699999999999999</v>
+        <v>0.5097222222222222</v>
       </c>
       <c r="AJ2" t="n">
-        <v>68.06545454545454</v>
+        <v>69.12300785634119</v>
       </c>
       <c r="AK2" t="n">
-        <v>69.52575757575758</v>
+        <v>68.8347923681257</v>
       </c>
       <c r="AL2" t="n">
-        <v>-4150000</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.75151515151515</v>
+        <v>67</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.4234132503846979</v>
+        <v>-0.4028099173553699</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.9970538342136734</v>
+        <v>-342395.0413223137</v>
       </c>
       <c r="AP2" t="n">
-        <v>183828.1830317387</v>
+        <v>-97693.16988605889</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.295477855477856</v>
+        <v>-1.430705719134792</v>
       </c>
       <c r="AR2" t="n">
-        <v>13</v>
+        <v>1725000</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.188111888111877</v>
+        <v>-2</v>
       </c>
       <c r="AT2" t="n">
-        <v>-1</v>
+        <v>-1.497603010983312</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.07627039627040233</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.05757575757575761</v>
+        <v>-0.02603305785124022</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>0.4427272727272822</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.07729108967270903</v>
+        <v>0.9150975335763007</v>
       </c>
       <c r="AY2" t="n">
-        <v>11</v>
+        <v>2.436363636363609</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-4</v>
+        <v>1.190089171499537</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0.3333333333333333</v>
+        <v>3.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0.7582586897641477</v>
+        <v>76</v>
       </c>
       <c r="BC2" t="n">
-        <v>1242345.221445221</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.04196178852929444</v>
+        <v>1</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -902,32 +902,32 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vo27CSJT</t>
+          <t>tflZ7nSp</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45462.89583333334</v>
+        <v>45463.10416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">badawi m 
+          <t xml:space="preserve">vazquez r 
   usa </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">citypark
-  st  louis  mo </t>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
+          <t>U3ebh62R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>jmBZNRn8</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -944,19 +944,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>WWvwigh</t>
+          <t>2PIEeC7</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>KtuTuMN</t>
+          <t>zoZ995a</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -967,112 +967,118 @@
       <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="n">
-        <v>-0.9285714285714288</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.1190476190476186</v>
-      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>-0.8571428571428572</v>
+        <v>-0.325</v>
       </c>
       <c r="U3" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.4499999999999993</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.5250000000000004</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.8499999999999996</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-1.875</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-0.6499999999999999</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.07499999999999929</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-0.08269841269841249</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.2631746031746032</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>67.43797979797981</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>67.75795454545454</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.03008195307108363</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-47</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>4.020185185185198</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1870618.827160494</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>107926.4038381416</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.940570576191426</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1550000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2.420357680278659</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>3.697037037037038</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.626543209876544</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-3.326350641100845</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>-2.449691358024694</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-1.173925619940178</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>-72</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0.05333333333333323</v>
+      </c>
+      <c r="BD3" t="n">
         <v>-1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>9.285714285714285</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-9.285714285714285</v>
-      </c>
-      <c r="X3" t="n">
-        <v>5.428571428571429</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.5714285714285712</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>6.714285714285714</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-9.285714285714286</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.2857142857142858</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-0.5714285714285714</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.8571428571428577</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="n">
-        <v>0.3585714285714285</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-0.5228571428571429</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>68.67474747474748</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>68.09058441558442</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>-2240000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>2.025957375957375</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2.70051410940593</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>4.828878390367628</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>551924.9061463359</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0.447236097236086</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-143</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1.538855588855625</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="n">
-        <v>1.369352869352866</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0.186013986013986</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>2.171066651444942</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>-118</v>
-      </c>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="n">
-        <v>0.5997181431661289</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>318748.4737484739</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
@@ -1085,12 +1091,12 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45462.89583333334</v>
+        <v>45463.02083333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">dujic f 
-  can </t>
+          <t xml:space="preserve">allatin m 
+  usa </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1147,121 +1153,121 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.1428571428571432</v>
+        <v>2.5</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1071428571428568</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3611111111111112</v>
+        <v>-0.7545454545454544</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.4090909090909092</v>
       </c>
       <c r="V4" t="n">
-        <v>2.041666666666664</v>
+        <v>-0.545454545454545</v>
       </c>
       <c r="W4" t="n">
-        <v>-2.152777777777779</v>
+        <v>-3.345454545454546</v>
       </c>
       <c r="X4" t="n">
-        <v>2.638888888888889</v>
+        <v>-2.045454545454546</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.541666666666666</v>
+        <v>-0.8818181818181818</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.486111111111111</v>
+        <v>-0.1454545454545482</v>
       </c>
       <c r="AA4" t="n">
-        <v>-4.541666666666666</v>
+        <v>0.04545454545454675</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.5555555555555556</v>
+        <v>0.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8611111111111112</v>
+        <v>0.0777777777777775</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.6805555555555554</v>
+        <v>-1.081818181818182</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.9722222222222223</v>
+        <v>1.481818181818182</v>
       </c>
       <c r="AF4" t="n">
-        <v>-2</v>
+        <v>0.2545454545454557</v>
       </c>
       <c r="AG4" t="n">
-        <v>-2</v>
+        <v>0.009090909090907928</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.1442857142857144</v>
+        <v>-1.0175</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.2114285714285715</v>
+        <v>0.3162499999999999</v>
       </c>
       <c r="AJ4" t="n">
-        <v>70.20490620490621</v>
+        <v>67.67474747474746</v>
       </c>
       <c r="AK4" t="n">
-        <v>69.22449494949495</v>
+        <v>68.35274971941638</v>
       </c>
       <c r="AL4" t="n">
+        <v>0.06822406257188884</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-69</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.075757575757564</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-351615.9320477503</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-237250.1451158914</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.2159380095328132</v>
+      </c>
+      <c r="AR4" t="n">
         <v>-1000000</v>
       </c>
-      <c r="AM4" t="n">
-        <v>1.217344276094281</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.220368276550289</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>-0.6143121265220088</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>-309224.3048984734</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>-2.577159090909092</v>
-      </c>
-      <c r="AR4" t="n">
+      <c r="AS4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.9216304664403978</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>3.187511478420568</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-3.087213039485775</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.360066830133945</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.9619834710744044</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-2.544909440602893</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.8333333333333428</v>
+      </c>
+      <c r="BB4" t="n">
         <v>-70</v>
       </c>
-      <c r="AS4" t="n">
-        <v>0.8916161616161844</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.985441919191924</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.05965909090909083</v>
-      </c>
-      <c r="AW4" t="n">
+      <c r="BC4" t="n">
+        <v>0.06287878787878776</v>
+      </c>
+      <c r="BD4" t="n">
         <v>-1</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0.3240183603338984</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>-69</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.8333333333333428</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>-3.0368769992795</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>-256128.0303030305</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0.06366804692891659</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -1270,32 +1276,32 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WKbaElkH</t>
+          <t>ld9fFUZA</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45462.89583333334</v>
+        <v>45463.02083333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">mendoza r 
+          <t xml:space="preserve">demianchuk s 
   usa </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">shell energy stadium
-  houston  tx </t>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>6P5S63Ah</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1312,7 +1318,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>l6eEjGl</t>
+          <t>WWvwigh</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1321,136 +1327,132 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>-0.3454545454545455</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.1272727272727272</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-1.227272727272727</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4.254545454545454</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.3545454545454545</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.063636363636363</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>6.609090909090909</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-6.609090909090909</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-1.175</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0.1636363636363636</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.1909090909090908</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-2.054545454545455</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.6363636363636367</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.3330555555555557</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.3750000000000004</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>67.86172839506172</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>68.50272727272727</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.03578556899495111</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>2.149242424242431</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1452213.636363636</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>240261.9703904029</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.8104192670411123</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-4150000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.06015999319775389</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-0.1880303030302954</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.75181818181818</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-0.7003194332999954</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.9160606060605971</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-0.6211603097830221</v>
+      </c>
+      <c r="BA5" t="n">
         <v>-4</v>
       </c>
-      <c r="P5" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-0.708333333333333</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-0.125</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.2777777777777777</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-0.2222222222222223</v>
-      </c>
-      <c r="V5" t="n">
-        <v>15.27777777777778</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-15.27777777777778</v>
-      </c>
-      <c r="X5" t="n">
-        <v>5.388888888888889</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-1.833333333333334</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>7.722222222222221</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-4.777777777777779</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.2222222222222221</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-0.4444444444444444</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>4.166666666666666</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-0.3888888888888893</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-0.0126666666666666</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-0.3542222222222219</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>66.90727272727273</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>68.20314253647587</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>150000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-1.530308972073698</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0.9439872842343107</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0.9238107683599495</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-64258.88568673003</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-1.935668449197877</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>-0.04173499702912409</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>-8</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>-0.2108793820558503</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-0.1381224004753414</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.5869257127022</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-9</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
       <c r="BB5" t="n">
-        <v>-0.8321183314105411</v>
+        <v>13</v>
       </c>
       <c r="BC5" t="n">
-        <v>-373248.90077243</v>
+        <v>0.07196969696969702</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.02123744365388802</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -1459,32 +1461,32 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>zg5jGAK4</t>
+          <t>WKbaElkH</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45462.89583333334</v>
+        <v>45463.02083333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">vazquez r 
-  usa </t>
+          <t xml:space="preserve">fischer d 
+  can </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">q2 stadium
-  austin  tx </t>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IeT6JBE3</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>txUJt9AR</t>
+          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1501,135 +1503,145 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>lAVQ9RG</t>
+          <t>l6eEjGl</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>UL7r7du</t>
+          <t>UFWZoX9</t>
         </is>
       </c>
       <c r="M6" t="n">
+        <v>-12</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-12</v>
+      </c>
+      <c r="O6" t="n">
         <v>-4</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>-4</v>
       </c>
-      <c r="O6" t="n">
-        <v>-3</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-3</v>
-      </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.9047619047619042</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1714285714285708</v>
+        <v>3.333333333333334</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.09523809523809534</v>
+        <v>0.3500000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>4.69047619047619</v>
+        <v>1.949999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>-4.69047619047619</v>
+        <v>-0.3833333333333346</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.023809523809524</v>
+        <v>2.433333333333333</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.047619047619047</v>
+        <v>0.6833333333333327</v>
       </c>
       <c r="Z6" t="n">
-        <v>-1.690476190476192</v>
+        <v>6.433333333333337</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.2619047619047628</v>
+        <v>-6.433333333333337</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6428571428571428</v>
+        <v>-1.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.5</v>
+        <v>0.5795454545454541</v>
       </c>
       <c r="AD6" t="n">
-        <v>-1.738095238095238</v>
+        <v>-0.75</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.428571428571428</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.133333333333335</v>
+      </c>
       <c r="AH6" t="n">
-        <v>0.5383333333333333</v>
+        <v>0.08111111111111113</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.01566666666666694</v>
+        <v>0.1236111111111111</v>
       </c>
       <c r="AJ6" t="n">
-        <v>68.37744107744108</v>
+        <v>68.06745230078565</v>
       </c>
       <c r="AK6" t="n">
-        <v>68.7026936026936</v>
+        <v>67.82363636363637</v>
       </c>
       <c r="AL6" t="n">
-        <v>-2200000</v>
+        <v>0.04465949165774163</v>
       </c>
       <c r="AM6" t="n">
-        <v>-4.813352573352574</v>
+        <v>-4</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.508653595048372</v>
+        <v>-1.155015186833381</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1.302378084878086</v>
+        <v>-247223.3877233877</v>
       </c>
       <c r="AP6" t="n">
-        <v>-578888.9336597307</v>
+        <v>56628.67746394081</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-6.355348725348719</v>
+        <v>1.532199086307671</v>
       </c>
       <c r="AR6" t="n">
-        <v>-149</v>
+        <v>150000</v>
       </c>
       <c r="AS6" t="n">
-        <v>-1.0614911014911</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
+        <v>-8</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.060589312383268</v>
+      </c>
       <c r="AU6" t="n">
-        <v>0.4006974506974572</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.2332515632515637</v>
+        <v>-0.04740764286218635</v>
       </c>
       <c r="AW6" t="n">
-        <v>-2</v>
+        <v>-1.870449247721965</v>
       </c>
       <c r="AX6" t="n">
-        <v>2.745448867693284</v>
+        <v>1.053068944601819</v>
       </c>
       <c r="AY6" t="n">
-        <v>-123</v>
-      </c>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
+        <v>0.1639189093733933</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-0.9906079080769103</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-9</v>
+      </c>
       <c r="BB6" t="n">
-        <v>-5.226437710398756</v>
+        <v>6</v>
       </c>
       <c r="BC6" t="n">
-        <v>-1941721.981721981</v>
+        <v>-0.08282121918485541</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.3112994485869609</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -1638,32 +1650,32 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>MTkoJCzn</t>
+          <t>vo27CSJT</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45462.86458333334</v>
+        <v>45463.02083333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">pekmic i 
+          <t xml:space="preserve">gonzales g 
   usa </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">tql stadium
-  cincinnati  oh </t>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Szrwix67</t>
+          <t>jmBZNRn8</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1680,135 +1692,135 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Onn3tCA</t>
+          <t>WWvwigh</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>6gpXy3v</t>
+          <t>KtuTuMN</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
-      <c r="R7" t="n">
-        <v>0.4000000000000004</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.6000000000000005</v>
-      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="n">
-        <v>-0.6666666666666667</v>
+        <v>-0.7777777777777777</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.375</v>
       </c>
       <c r="V7" t="n">
-        <v>9.333333333333336</v>
+        <v>3.527777777777779</v>
       </c>
       <c r="W7" t="n">
-        <v>-9.333333333333336</v>
+        <v>-1.055555555555555</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6666666666666661</v>
+        <v>-0.5972222222222223</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5</v>
+        <v>0.04166666666666696</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.833333333333332</v>
+        <v>-1.416666666666664</v>
       </c>
       <c r="AA7" t="n">
-        <v>-3.833333333333332</v>
+        <v>1.416666666666664</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="AC7" t="n">
         <v>0.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.833333333333333</v>
+        <v>-0.3611111111111112</v>
       </c>
       <c r="AE7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
+        <v>0.09722222222222232</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>5.763888888888889</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-2.333333333333334</v>
+      </c>
       <c r="AH7" t="n">
-        <v>0.1983333333333333</v>
+        <v>-0.3023214285714286</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.4983333333333332</v>
+        <v>-0.1466071428571429</v>
       </c>
       <c r="AJ7" t="n">
-        <v>67.69747474747474</v>
+        <v>70.00909090909092</v>
       </c>
       <c r="AK7" t="n">
-        <v>66.85454545454546</v>
+        <v>68.0300505050505</v>
       </c>
       <c r="AL7" t="n">
-        <v>-1055000</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.2553946053946134</v>
+        <v>-118</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.5110979414009194</v>
+        <v>2.305454545454552</v>
       </c>
       <c r="AO7" t="n">
-        <v>-3.257138532870705</v>
+        <v>419510.1010101011</v>
       </c>
       <c r="AP7" t="n">
-        <v>-208663.8446564553</v>
+        <v>564914.1408153626</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.1778721278721349</v>
+        <v>4.187607629280123</v>
       </c>
       <c r="AR7" t="n">
-        <v>-195</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>-4.500449550449503</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="n">
-        <v>-0.009490509490497345</v>
-      </c>
+        <v>-2240000</v>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>1.795966420359676</v>
+      </c>
+      <c r="AU7" t="inlineStr"/>
       <c r="AV7" t="n">
-        <v>-0.0792207792207793</v>
+        <v>1.464646464646464</v>
       </c>
       <c r="AW7" t="n">
-        <v>-3</v>
+        <v>0.5289898989899058</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.4049311096396124</v>
+        <v>3.424817838717445</v>
       </c>
       <c r="AY7" t="n">
-        <v>-181</v>
-      </c>
-      <c r="AZ7" t="inlineStr"/>
+        <v>1.863939393939404</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.7048921109999355</v>
+      </c>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="n">
-        <v>-3.314666278610787</v>
+        <v>-143</v>
       </c>
       <c r="BC7" t="n">
-        <v>1034613.886113886</v>
+        <v>0.187878787878788</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.09826603718410443</v>
+        <v>-2</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -1817,32 +1829,32 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hK8xvrmh</t>
+          <t>zg5jGAK4</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45462.85416666666</v>
+        <v>45463.02083333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gonzalez g  jr 
+          <t xml:space="preserve">unkel t 
   usa </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">saputo stadium
-  montreal  qc </t>
+          <t xml:space="preserve">q2 stadium
+  austin  tx </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>IeT6JBE3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1859,141 +1871,135 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>K4FYmLD</t>
+          <t>lAVQ9RG</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>EgT3xN3</t>
+          <t>UL7r7du</t>
         </is>
       </c>
       <c r="M8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.8555555555555556</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-4.555555555555555</v>
+      </c>
+      <c r="W8" t="n">
+        <v>4.166666666666668</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-3.644444444444445</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.277777777777778</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-1.833333333333336</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.833333333333336</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-1.477777777777778</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.255555555555556</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.04444444444444429</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.3777777777777782</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-0.2687500000000003</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.7980357142857142</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>68.84556677890012</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>68.96704545454546</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.2736270683295856</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-123</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-4.696767676767678</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-1943471.533516988</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-751937.8030542501</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-1.902009704173736</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-2200000</v>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>2.23185083036984</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="n">
+        <v>0.2333241505968786</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>-6.217364554637271</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.348215444556985</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-0.9138751147841901</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>-5.246404047971893</v>
+      </c>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="n">
+        <v>-149</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>-0.2211753902662996</v>
+      </c>
+      <c r="BD8" t="n">
         <v>-2</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.7142857142857144</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.8571428571428577</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.1428571428571428</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-0.4285714285714286</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6.428571428571431</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-6.428571428571431</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.142857142857144</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.7142857142857135</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.142857142857142</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>-2.428571428571429</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0.142857142857143</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-0.2857142857142856</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>-0.5714285714285712</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>-0.1428571428571432</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="n">
-        <v>0.03761904761904766</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>-0.2783333333333335</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>70.20418470418471</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>69.62481962481962</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>3175000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>-2.436563436563432</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0.05145036272708126</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0.9631942559952691</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>-572375.0173666463</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>-3.148351648351664</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>-0.8141858141858336</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>5.333333333333336</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0.7887112887112835</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>-0.08891108891108912</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0.4238012946133196</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>2.666666666666657</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>-0.8701065061679003</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>-1670804.195804196</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0.02050562694660174</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -2002,32 +2008,32 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>rwisKhLu</t>
+          <t>MTkoJCzn</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45462.85416666666</v>
+        <v>45462.98958333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">vazquez r 
+          <t xml:space="preserve">marrufo j 
   usa </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">bank of america stadium
-  charlotte  nc </t>
+          <t xml:space="preserve">tql stadium
+  cincinnati  oh </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>rsHkUNCo</t>
+          <t>Szrwix67</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2044,19 +2050,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>022mBmS</t>
+          <t>Onn3tCA</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>UL7r7du</t>
+          <t>6gpXy3v</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -2067,112 +2073,118 @@
       <c r="Q9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="n">
-        <v>-0.04166666666666696</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-0.791666666666667</v>
-      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="n">
-        <v>-0.5555555555555556</v>
+        <v>0.7250000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.3500000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2222222222222214</v>
+        <v>-2.800000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.2222222222222214</v>
+        <v>1.025</v>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>0.4500000000000002</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.5</v>
+        <v>-0.5750000000000002</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.444444444444445</v>
+        <v>0.3500000000000014</v>
       </c>
       <c r="AA9" t="n">
-        <v>-6.722222222222223</v>
+        <v>-0.3500000000000014</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.1666666666666667</v>
+        <v>-1</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.1666666666666667</v>
+        <v>0.06349206349206327</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.1111111111111112</v>
+        <v>1.925</v>
       </c>
       <c r="AE9" t="n">
-        <v>-1.277777777777778</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
+        <v>-1.525</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.175000000000001</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0.2249999999999996</v>
+      </c>
       <c r="AH9" t="n">
-        <v>-0.1708333333333332</v>
+        <v>-0.1244444444444446</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.4495833333333332</v>
+        <v>-0.2927777777777777</v>
       </c>
       <c r="AJ9" t="n">
-        <v>68.0074074074074</v>
+        <v>67.95214646464646</v>
       </c>
       <c r="AK9" t="n">
-        <v>68.59696969696971</v>
+        <v>67.24305555555556</v>
       </c>
       <c r="AL9" t="n">
-        <v>-615000</v>
+        <v>-0.08492216117216111</v>
       </c>
       <c r="AM9" t="n">
-        <v>-3.692607392607385</v>
+        <v>-215</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.235235870390568</v>
+        <v>0.06929292929292785</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.151453021520012</v>
+        <v>938550.5050505055</v>
       </c>
       <c r="AP9" t="n">
-        <v>-777775.32304301</v>
+        <v>-281183.6538757256</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.542757242757247</v>
+        <v>-4.236279370435376</v>
       </c>
       <c r="AR9" t="n">
-        <v>-143</v>
+        <v>-11950000</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.552147852147868</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
+        <v>-2.300000000000001</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>-0.4794390523514558</v>
+      </c>
       <c r="AU9" t="n">
-        <v>-1.119480519480526</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.2135864135864136</v>
+        <v>-0.2510101010100954</v>
       </c>
       <c r="AW9" t="n">
-        <v>-2</v>
+        <v>0.07919191919191348</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.078388061870502</v>
+        <v>-0.2319192549659022</v>
       </c>
       <c r="AY9" t="n">
-        <v>-106</v>
-      </c>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
+        <v>-4.084141414141413</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>-3.999212850590723</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4</v>
+      </c>
       <c r="BB9" t="n">
-        <v>0.78958369958589</v>
+        <v>-219</v>
       </c>
       <c r="BC9" t="n">
-        <v>-1377012.987012987</v>
+        <v>-0.07363636363636372</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.07429587036737084</v>
+        <v>-3</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
@@ -2181,32 +2193,32 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>WA7tw22b</t>
+          <t>hK8xvrmh</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45462.85416666666</v>
+        <v>45462.97916666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">gonzalez g  jr 
+          <t xml:space="preserve">szpala l 
   usa </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">bmo field
-  toronto  on </t>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>84yIDQMe</t>
+          <t>zV5YmQAr</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2223,7 +2235,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>xA45kov</t>
+          <t>K4FYmLD</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -2232,10 +2244,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="N10" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -2246,118 +2258,118 @@
       <c r="Q10" t="n">
         <v>0</v>
       </c>
-      <c r="R10" t="n">
-        <v>-0.1714285714285708</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-1.057142857142857</v>
-      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="n">
-        <v>1.75</v>
+        <v>-0.5777777777777777</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5</v>
+        <v>0.5111111111111111</v>
       </c>
       <c r="V10" t="n">
-        <v>3.583333333333336</v>
+        <v>-2.855555555555556</v>
       </c>
       <c r="W10" t="n">
-        <v>-3.583333333333336</v>
+        <v>3.077777777777779</v>
       </c>
       <c r="X10" t="n">
-        <v>2.958333333333334</v>
+        <v>-1.833333333333333</v>
       </c>
       <c r="Y10" t="n">
-        <v>-3.791666666666666</v>
+        <v>1.733333333333333</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.666666666666666</v>
+        <v>1.533333333333339</v>
       </c>
       <c r="AA10" t="n">
-        <v>-3.958333333333332</v>
+        <v>-1.533333333333339</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.6666666666666666</v>
+        <v>-0.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.3333333333333333</v>
+        <v>0.291666666666667</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.583333333333333</v>
+        <v>-0.7222222222222222</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.375</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
+        <v>0.5777777777777777</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.522222222222222</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.277777777777779</v>
+      </c>
       <c r="AH10" t="n">
-        <v>0.8974285714285716</v>
+        <v>0.003888888888888831</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.390857142857143</v>
+        <v>0.4968055555555555</v>
       </c>
       <c r="AJ10" t="n">
-        <v>66.65353535353535</v>
+        <v>68.50145903479236</v>
       </c>
       <c r="AK10" t="n">
-        <v>69.35151515151516</v>
+        <v>68.91373737373738</v>
       </c>
       <c r="AL10" t="n">
-        <v>-350000</v>
+        <v>-0.01634548424459581</v>
       </c>
       <c r="AM10" t="n">
-        <v>-4.314635364635365</v>
+        <v>88</v>
       </c>
       <c r="AN10" t="n">
-        <v>-3.539431719332839</v>
+        <v>-2.872727272727261</v>
       </c>
       <c r="AO10" t="n">
-        <v>-2.733733001909506</v>
+        <v>-1809318.181818182</v>
       </c>
       <c r="AP10" t="n">
-        <v>225263.7663936641</v>
+        <v>-643721.2870449799</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-2.700299700299723</v>
+        <v>0.349051794905705</v>
       </c>
       <c r="AR10" t="n">
-        <v>3</v>
+        <v>3900000</v>
       </c>
       <c r="AS10" t="n">
-        <v>-1.155244755244723</v>
+        <v>6.166666666666668</v>
       </c>
       <c r="AT10" t="n">
+        <v>-0.348921077501636</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.663636363636364</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-3.527272727272731</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-0.1661124952506725</v>
+      </c>
+      <c r="AY10" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AU10" t="n">
-        <v>-1.38826173826174</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0.01403596403596397</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>-4.570051268474586</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>-2</v>
-      </c>
       <c r="AZ10" t="n">
-        <v>4.5</v>
+        <v>-0.5812456859707709</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.125038301486114</v>
+        <v>65</v>
       </c>
       <c r="BC10" t="n">
-        <v>-1265650.0999001</v>
+        <v>-0.1090909090909093</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.06207467480759421</v>
+        <v>1</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -2366,32 +2378,32 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>tW5nHj5b</t>
+          <t>rwisKhLu</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45462.85416666666</v>
+        <v>45462.97916666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">da silva a 
+          <t xml:space="preserve">chapman a 
   usa </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">chase stadium
-  fort lauderdale  fl </t>
+          <t xml:space="preserve">bank of america stadium
+  charlotte  nc </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0AheRyBg</t>
+          <t>QJF7WTFB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2408,141 +2420,135 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>6BusaLE</t>
+          <t>022mBmS</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>zoZ995a</t>
+          <t>UL7r7du</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
-      <c r="R11" t="n">
-        <v>0.833333333333333</v>
-      </c>
-      <c r="S11" t="n">
-        <v>-0.1428571428571432</v>
-      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
       <c r="T11" t="n">
-        <v>0.5714285714285712</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5714285714285714</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.7222222222222214</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-1.044444444444444</v>
       </c>
       <c r="X11" t="n">
-        <v>1.571428571428571</v>
+        <v>-0.02222222222222214</v>
       </c>
       <c r="Y11" t="n">
-        <v>-5.428571428571427</v>
+        <v>0.2666666666666666</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.571428571428571</v>
+        <v>0.4555555555555557</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.714285714285714</v>
+        <v>-0.4555555555555557</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.2857142857142858</v>
+        <v>0.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.428571428571428</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
+        <v>-0.7888888888888888</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.177777777777779</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-0.2777777777777786</v>
+      </c>
       <c r="AH11" t="n">
-        <v>0.5664285714285717</v>
+        <v>-0.133015873015873</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.1504761904761904</v>
+        <v>-0.4138095238095236</v>
       </c>
       <c r="AJ11" t="n">
-        <v>67.7988455988456</v>
+        <v>67.93348484848484</v>
       </c>
       <c r="AK11" t="n">
-        <v>67.34992784992787</v>
+        <v>69.72615039281706</v>
       </c>
       <c r="AL11" t="n">
-        <v>22875000</v>
+        <v>-0.05941304182722917</v>
       </c>
       <c r="AM11" t="n">
-        <v>6.054125672307478</v>
+        <v>-106</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.542498202188682</v>
+        <v>-4.063636363636377</v>
       </c>
       <c r="AO11" t="n">
-        <v>3.798211220625248</v>
+        <v>-1397295.454545455</v>
       </c>
       <c r="AP11" t="n">
-        <v>1465002.294738205</v>
+        <v>-994706.7418216155</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.628945297127103</v>
+        <v>0.7719452947256116</v>
       </c>
       <c r="AR11" t="n">
-        <v>399</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1.975672307490527</v>
-      </c>
+        <v>-615000</v>
+      </c>
+      <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
-        <v>-15.16666666666667</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.600295159386068</v>
-      </c>
+        <v>0.8827118686043107</v>
+      </c>
+      <c r="AU11" t="inlineStr"/>
       <c r="AV11" t="n">
-        <v>0.7597402597402596</v>
+        <v>-1.008181818181825</v>
       </c>
       <c r="AW11" t="n">
-        <v>5</v>
+        <v>-2.050000000000011</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.2081055775636784</v>
+        <v>1.288532794436691</v>
       </c>
       <c r="AY11" t="n">
-        <v>350</v>
+        <v>2.655454545454546</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-3.333333333333343</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
+        <v>0.7957790556760784</v>
+      </c>
+      <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="n">
-        <v>3.59580077345899</v>
+        <v>-143</v>
       </c>
       <c r="BC11" t="n">
-        <v>3835338.941361669</v>
+        <v>-0.2245454545454546</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.2196158563759951</v>
+        <v>-2</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -2551,185 +2557,555 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
+          <t>WA7tw22b</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">penso c 
+  usa </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo field
+  toronto  on </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>167</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>xA45kov</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>EgT3xN3</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="n">
+        <v>0.7777777777777777</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.3333333333333339</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.8888888888888875</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.444444444444445</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.333333333333329</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-1.333333333333329</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.4027777777777777</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0.2222222222222221</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-2.555555555555555</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.18875</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>67.32233445566779</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>66.43636363636364</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.08236542443064176</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-4.72999999999999</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-1372686.363636364</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>355790.9539735627</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-2.717002001939079</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-275000</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>3.199999999999999</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-4.527757604714125</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-1.564545454545453</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-3.172727272727272</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-4.171239658510899</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-1.396363636363617</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>2.297501334160373</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.866666666666646</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-64</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-0.002727272727272911</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
           <t>2u7rIWkh</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
-        <v>45462.85416666666</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rivas v 
-  usa </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="B13" s="2" t="n">
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lauziere p 
+  can </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t xml:space="preserve">audi field
   washington  dc </t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>O6hjfSXE</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>EPngUvhk</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="G13" t="n">
         <v>167</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H13" t="n">
         <v>1671</v>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
         <v>2024</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>022mBmS</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>86yPt28</t>
         </is>
       </c>
-      <c r="M12" t="n">
+      <c r="M13" t="n">
         <v>-2</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N13" t="n">
         <v>-2</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O13" t="n">
         <v>-4</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P13" t="n">
         <v>-4</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>-1.523809523809524</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="U12" t="n">
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="n">
+        <v>0.08080808080808088</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-1.919191919191919</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-1.353535353535353</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.6161616161616168</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0.858585858585859</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-6.313131313131315</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>6.222222222222221</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.4444444444444446</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.09090909090909083</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.03030303030303028</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.979797979797981</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.3838383838383841</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.3387500000000001</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.2412500000000002</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>68.46767676767678</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>69.37171717171718</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-0.0242621778805987</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-23</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-0.6547348484848499</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-2286657.765151515</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-1495568.488132506</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-4.55477572440212</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-5600000</v>
+      </c>
+      <c r="AS13" t="n">
         <v>1</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.714285714285715</v>
-      </c>
-      <c r="W12" t="n">
-        <v>-1.714285714285715</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.142857142857144</v>
-      </c>
-      <c r="Y12" t="n">
+      <c r="AT13" t="n">
+        <v>-2.581541002312047</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.8952651515151544</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-1.995909090909095</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>3.52288087967392</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>4.891363636363593</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.3151883361991565</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-15</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-0.05575757575757589</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>tW5nHj5b</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chase stadium
+  fort lauderdale  fl </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>167</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>6BusaLE</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>zoZ995a</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="Z12" t="n">
-        <v>2.714285714285714</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.857142857142857</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>-0.5714285714285712</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="n">
-        <v>0.5019047619047619</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0.0302380952380954</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>68.2012987012987</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>69.19949494949495</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>4050000</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>-0.3858022186147139</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>3.072711922629367</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>-4.230160244770921</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>-1212899.469320801</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>-2.004356060606057</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>134</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>4.983369408369384</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>8.666666666666668</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0.9771577380952401</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>-0.07172619047619055</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>-2.30203476969584</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>143</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>11.66666666666666</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0.2638736863545859</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>-2464098.563762627</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>-0.01878142873208666</v>
-      </c>
-      <c r="BE12" t="n">
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="n">
+        <v>0.4444444444444446</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-1.277777777777777</v>
+      </c>
+      <c r="W14" t="n">
+        <v>5.166666666666666</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.1666666666666661</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0.1111111111111116</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-2.833333333333336</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.833333333333336</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.6749999999999998</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.0555555555555558</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-0.111111111111111</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.777777777777779</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-5.888888888888888</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.2230000000000003</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.03624999999999989</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>68.75353535353536</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>67.85067340067341</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.1449621989263936</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>524</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>6.454747474747478</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>4332307.359307359</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>854239.4360754334</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>2.935769558659587</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>78375000</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-11.625</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-0.254230160291538</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.839884559884556</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>5.882799422799408</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>2.973119712768039</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.48486291486293</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>3.466078197165146</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-5.125</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>573</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0.7909090909090906</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE14" t="n">
         <v>0</v>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
@@ -515,94 +515,94 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_interceptions</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions_against</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -615,97 +615,97 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -782,31 +782,31 @@
       <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>0.2626262626262625</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.898989898989899</v>
+      </c>
       <c r="T2" t="n">
-        <v>0.2626262626262625</v>
+        <v>3.595959595959597</v>
       </c>
       <c r="U2" t="n">
-        <v>0.898989898989899</v>
+        <v>1.858585858585858</v>
       </c>
       <c r="V2" t="n">
-        <v>3.595959595959597</v>
+        <v>0.04194444444444434</v>
       </c>
       <c r="W2" t="n">
-        <v>1.858585858585858</v>
-      </c>
-      <c r="X2" t="n">
+        <v>0.5097222222222222</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
         <v>0.3535353535353538</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AA2" t="n">
         <v>1.333333333333333</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-3.171717171717169</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3.171717171717169</v>
       </c>
       <c r="AB2" t="n">
         <v>1</v>
@@ -815,22 +815,22 @@
         <v>-0.8888888888888888</v>
       </c>
       <c r="AD2" t="n">
+        <v>-2.252525252525253</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.1616161616161627</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-3.171717171717169</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>3.171717171717169</v>
+      </c>
+      <c r="AH2" t="n">
         <v>-0.2222222222222223</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AI2" t="n">
         <v>0.2626262626262625</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-2.252525252525253</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.1616161616161627</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0.04194444444444434</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.5097222222222222</v>
       </c>
       <c r="AJ2" t="n">
         <v>69.12300785634119</v>
@@ -839,61 +839,61 @@
         <v>68.8347923681257</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>0.9150975335763007</v>
       </c>
       <c r="AM2" t="n">
-        <v>67</v>
+        <v>-342395.0413223137</v>
       </c>
       <c r="AN2" t="n">
+        <v>1.190089171499537</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-0.02603305785124022</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>2.436363636363609</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>76</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.4427272727272822</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>78</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-1.430705719134792</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>-1.497603010983312</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>6025000</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>-97693.16988605889</v>
+      </c>
+      <c r="BD2" t="n">
         <v>-0.4028099173553699</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-342395.0413223137</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-97693.16988605889</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-1.430705719134792</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1725000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>-1.497603010983312</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>-0.02603305785124022</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.4427272727272822</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0.9150975335763007</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>2.436363636363609</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1.190089171499537</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>76</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -967,31 +967,31 @@
       <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>-0.325</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.125</v>
+      </c>
       <c r="T3" t="n">
-        <v>-0.325</v>
+        <v>0.4499999999999993</v>
       </c>
       <c r="U3" t="n">
-        <v>0.125</v>
+        <v>0.5250000000000004</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4499999999999993</v>
+        <v>-0.08269841269841249</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5250000000000004</v>
-      </c>
-      <c r="X3" t="n">
+        <v>0.2631746031746032</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
         <v>0.8499999999999996</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AA3" t="n">
         <v>-1.7</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.875</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-1.875</v>
       </c>
       <c r="AB3" t="n">
         <v>1</v>
@@ -1000,22 +1000,22 @@
         <v>1.625</v>
       </c>
       <c r="AD3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.07499999999999929</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-1.875</v>
+      </c>
+      <c r="AH3" t="n">
         <v>-0.6499999999999999</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AI3" t="n">
         <v>0.25</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.07499999999999929</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-0.08269841269841249</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0.2631746031746032</v>
       </c>
       <c r="AJ3" t="n">
         <v>67.43797979797981</v>
@@ -1024,61 +1024,61 @@
         <v>67.75795454545454</v>
       </c>
       <c r="AL3" t="n">
+        <v>-3.326350641100845</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1870618.827160494</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-1.173925619940178</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.05333333333333323</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>3.697037037037038</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-2.449691358024694</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-47</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.626543209876544</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-72</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.940570576191426</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>0.03008195307108363</v>
       </c>
-      <c r="AM3" t="n">
-        <v>-47</v>
-      </c>
-      <c r="AN3" t="n">
+      <c r="BA3" t="n">
+        <v>2.420357680278659</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1550000</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>107926.4038381416</v>
+      </c>
+      <c r="BD3" t="n">
         <v>4.020185185185198</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1870618.827160494</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>107926.4038381416</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.940570576191426</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1550000</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2.420357680278659</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>3.697037037037038</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.626543209876544</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>-3.326350641100845</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>-2.449691358024694</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-1.173925619940178</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>-72</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0.05333333333333323</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>-1</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
@@ -1153,34 +1153,34 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
+        <v>-0.7545454545454544</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.4090909090909092</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.545454545454545</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-3.345454545454546</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-1.0175</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.3162499999999999</v>
+      </c>
+      <c r="X4" t="n">
         <v>2.5</v>
       </c>
-      <c r="S4" t="n">
+      <c r="Y4" t="n">
         <v>4</v>
       </c>
-      <c r="T4" t="n">
-        <v>-0.7545454545454544</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.4090909090909092</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-0.545454545454545</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-3.345454545454546</v>
-      </c>
-      <c r="X4" t="n">
+      <c r="Z4" t="n">
         <v>-2.045454545454546</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AA4" t="n">
         <v>-0.8818181818181818</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-0.1454545454545482</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.04545454545454675</v>
       </c>
       <c r="AB4" t="n">
         <v>0.5</v>
@@ -1189,22 +1189,22 @@
         <v>0.0777777777777775</v>
       </c>
       <c r="AD4" t="n">
+        <v>0.2545454545454557</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.009090909090907928</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-0.1454545454545482</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.04545454545454675</v>
+      </c>
+      <c r="AH4" t="n">
         <v>-1.081818181818182</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AI4" t="n">
         <v>1.481818181818182</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.2545454545454557</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.009090909090907928</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-1.0175</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.3162499999999999</v>
       </c>
       <c r="AJ4" t="n">
         <v>67.67474747474746</v>
@@ -1213,61 +1213,61 @@
         <v>68.35274971941638</v>
       </c>
       <c r="AL4" t="n">
+        <v>1.360066830133945</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-351615.9320477503</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-2.544909440602893</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.06287878787878776</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3.187511478420568</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.9619834710744044</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-69</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-3.087213039485775</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.8333333333333428</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-70</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.2159380095328132</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>0.06822406257188884</v>
       </c>
-      <c r="AM4" t="n">
-        <v>-69</v>
-      </c>
-      <c r="AN4" t="n">
+      <c r="BA4" t="n">
+        <v>0.9216304664403978</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-237250.1451158914</v>
+      </c>
+      <c r="BD4" t="n">
         <v>1.075757575757564</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>-351615.9320477503</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>-237250.1451158914</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0.2159380095328132</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>-1000000</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0.9216304664403978</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>3.187511478420568</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>-3.087213039485775</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.360066830133945</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0.9619834710744044</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>-2.544909440602893</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0.8333333333333428</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>-70</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0.06287878787878776</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>-1</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -1341,31 +1341,31 @@
       <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>-0.3454545454545455</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.1272727272727272</v>
+      </c>
       <c r="T5" t="n">
-        <v>-0.3454545454545455</v>
+        <v>-1.227272727272727</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1272727272727272</v>
+        <v>4.254545454545454</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.227272727272727</v>
+        <v>-0.3330555555555557</v>
       </c>
       <c r="W5" t="n">
-        <v>4.254545454545454</v>
-      </c>
-      <c r="X5" t="n">
+        <v>0.3750000000000004</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
         <v>-0.3545454545454545</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AA5" t="n">
         <v>2.063636363636363</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>6.609090909090909</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-6.609090909090909</v>
       </c>
       <c r="AB5" t="n">
         <v>0.5</v>
@@ -1374,22 +1374,22 @@
         <v>-1.175</v>
       </c>
       <c r="AD5" t="n">
+        <v>-2.054545454545455</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.6363636363636367</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>6.609090909090909</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-6.609090909090909</v>
+      </c>
+      <c r="AH5" t="n">
         <v>-0.1636363636363636</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AI5" t="n">
         <v>0.1909090909090908</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-2.054545454545455</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0.6363636363636367</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-0.3330555555555557</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0.3750000000000004</v>
       </c>
       <c r="AJ5" t="n">
         <v>67.86172839506172</v>
@@ -1398,61 +1398,61 @@
         <v>68.50272727272727</v>
       </c>
       <c r="AL5" t="n">
+        <v>-0.7003194332999954</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1452213.636363636</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-0.6211603097830221</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.07196969696969702</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.1880303030302954</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.9160606060605971</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.75181818181818</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-0.8104192670411123</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>0.03578556899495111</v>
       </c>
-      <c r="AM5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AN5" t="n">
+      <c r="BA5" t="n">
+        <v>0.06015999319775389</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-4150000</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>240261.9703904029</v>
+      </c>
+      <c r="BD5" t="n">
         <v>2.149242424242431</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1452213.636363636</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>240261.9703904029</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-0.8104192670411123</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>-4150000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0.06015999319775389</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-0.1880303030302954</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.75181818181818</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>-0.7003194332999954</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0.9160606060605971</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-0.6211603097830221</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>-4</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0.07196969696969702</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -1527,34 +1527,34 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
+        <v>-0.1000000000000001</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.3500000000000001</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.949999999999999</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.3833333333333346</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.08111111111111113</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.1236111111111111</v>
+      </c>
+      <c r="X6" t="n">
         <v>3</v>
       </c>
-      <c r="S6" t="n">
+      <c r="Y6" t="n">
         <v>3.333333333333334</v>
       </c>
-      <c r="T6" t="n">
-        <v>-0.1000000000000001</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.3500000000000001</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.949999999999999</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-0.3833333333333346</v>
-      </c>
-      <c r="X6" t="n">
+      <c r="Z6" t="n">
         <v>2.433333333333333</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AA6" t="n">
         <v>0.6833333333333327</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>6.433333333333337</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>-6.433333333333337</v>
       </c>
       <c r="AB6" t="n">
         <v>-1.5</v>
@@ -1563,22 +1563,22 @@
         <v>0.5795454545454541</v>
       </c>
       <c r="AD6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.133333333333335</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>6.433333333333337</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-6.433333333333337</v>
+      </c>
+      <c r="AH6" t="n">
         <v>-0.75</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AI6" t="n">
         <v>0.6000000000000001</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.133333333333335</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.08111111111111113</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0.1236111111111111</v>
       </c>
       <c r="AJ6" t="n">
         <v>68.06745230078565</v>
@@ -1587,61 +1587,61 @@
         <v>67.82363636363637</v>
       </c>
       <c r="AL6" t="n">
+        <v>1.053068944601819</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-247223.3877233877</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-0.9906079080769103</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.08282121918485541</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0.04740764286218635</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.1639189093733933</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-1.870449247721965</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.532199086307671</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>0.04465949165774163</v>
       </c>
-      <c r="AM6" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AN6" t="n">
+      <c r="BA6" t="n">
+        <v>2.060589312383268</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>150000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>56628.67746394081</v>
+      </c>
+      <c r="BD6" t="n">
         <v>-1.155015186833381</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>-247223.3877233877</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>56628.67746394081</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.532199086307671</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>150000</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>-8</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.060589312383268</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>-0.04740764286218635</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>-1.870449247721965</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.053068944601819</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0.1639189093733933</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>-0.9906079080769103</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>-9</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>-0.08282121918485541</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -1715,31 +1715,31 @@
       <c r="Q7" t="n">
         <v>0</v>
       </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>-0.7777777777777777</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.375</v>
+      </c>
       <c r="T7" t="n">
-        <v>-0.7777777777777777</v>
+        <v>3.527777777777779</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.375</v>
+        <v>-1.055555555555555</v>
       </c>
       <c r="V7" t="n">
-        <v>3.527777777777779</v>
+        <v>-0.3023214285714286</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.055555555555555</v>
-      </c>
-      <c r="X7" t="n">
+        <v>-0.1466071428571429</v>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="n">
         <v>-0.5972222222222223</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AA7" t="n">
         <v>0.04166666666666696</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-1.416666666666664</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.416666666666664</v>
       </c>
       <c r="AB7" t="n">
         <v>-0.5</v>
@@ -1748,22 +1748,22 @@
         <v>0.5</v>
       </c>
       <c r="AD7" t="n">
+        <v>5.763888888888889</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-2.333333333333334</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-1.416666666666664</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.416666666666664</v>
+      </c>
+      <c r="AH7" t="n">
         <v>-0.3611111111111112</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AI7" t="n">
         <v>0.09722222222222232</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>5.763888888888889</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>-2.333333333333334</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-0.3023214285714286</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>-0.1466071428571429</v>
       </c>
       <c r="AJ7" t="n">
         <v>70.00909090909092</v>
@@ -1772,55 +1772,55 @@
         <v>68.0300505050505</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>3.424817838717445</v>
       </c>
       <c r="AM7" t="n">
+        <v>419510.1010101011</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.7048921109999355</v>
+      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="n">
+        <v>0.187878787878788</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.464646464646464</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.863939393939404</v>
+      </c>
+      <c r="AS7" t="n">
         <v>-118</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AT7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.5289898989899058</v>
+      </c>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="n">
+        <v>-143</v>
+      </c>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="n">
+        <v>4.187607629280123</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.795966420359676</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>-2240000</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>564914.1408153626</v>
+      </c>
+      <c r="BD7" t="n">
         <v>2.305454545454552</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>419510.1010101011</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>564914.1408153626</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>4.187607629280123</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>-2240000</v>
-      </c>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="n">
-        <v>1.795966420359676</v>
-      </c>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="n">
-        <v>1.464646464646464</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.5289898989899058</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>3.424817838717445</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.863939393939404</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.7048921109999355</v>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="n">
-        <v>-143</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0.187878787878788</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>-2</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -1894,31 +1894,31 @@
       <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.8555555555555556</v>
+      </c>
       <c r="T8" t="n">
-        <v>-1.2</v>
+        <v>-4.555555555555555</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8555555555555556</v>
+        <v>4.166666666666668</v>
       </c>
       <c r="V8" t="n">
-        <v>-4.555555555555555</v>
+        <v>-0.2687500000000003</v>
       </c>
       <c r="W8" t="n">
-        <v>4.166666666666668</v>
-      </c>
-      <c r="X8" t="n">
+        <v>0.7980357142857142</v>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="n">
         <v>-3.644444444444445</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AA8" t="n">
         <v>2.277777777777778</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>-1.833333333333336</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.833333333333336</v>
       </c>
       <c r="AB8" t="n">
         <v>-1</v>
@@ -1927,22 +1927,22 @@
         <v>0</v>
       </c>
       <c r="AD8" t="n">
+        <v>0.04444444444444429</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.3777777777777782</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-1.833333333333336</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.833333333333336</v>
+      </c>
+      <c r="AH8" t="n">
         <v>-1.477777777777778</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AI8" t="n">
         <v>1.255555555555556</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0.04444444444444429</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.3777777777777782</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>-0.2687500000000003</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0.7980357142857142</v>
       </c>
       <c r="AJ8" t="n">
         <v>68.84556677890012</v>
@@ -1951,55 +1951,55 @@
         <v>68.96704545454546</v>
       </c>
       <c r="AL8" t="n">
+        <v>1.348215444556985</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-1943471.533516988</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-5.246404047971893</v>
+      </c>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="n">
+        <v>-0.2211753902662996</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.2333241505968786</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-0.9138751147841901</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>-123</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-6.217364554637271</v>
+      </c>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="n">
+        <v>-149</v>
+      </c>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="n">
+        <v>-1.902009704173736</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>0.2736270683295856</v>
       </c>
-      <c r="AM8" t="n">
-        <v>-123</v>
-      </c>
-      <c r="AN8" t="n">
+      <c r="BA8" t="n">
+        <v>2.23185083036984</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-2200000</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>-751937.8030542501</v>
+      </c>
+      <c r="BD8" t="n">
         <v>-4.696767676767678</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>-1943471.533516988</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>-751937.8030542501</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>-1.902009704173736</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>-2200000</v>
-      </c>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="n">
-        <v>2.23185083036984</v>
-      </c>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="n">
-        <v>0.2333241505968786</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>-6.217364554637271</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.348215444556985</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>-0.9138751147841901</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>-5.246404047971893</v>
-      </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="n">
-        <v>-149</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>-0.2211753902662996</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>-2</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -2073,31 +2073,31 @@
       <c r="Q9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+      <c r="R9" t="n">
+        <v>0.7250000000000001</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.3500000000000001</v>
+      </c>
       <c r="T9" t="n">
-        <v>0.7250000000000001</v>
+        <v>-2.800000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3500000000000001</v>
+        <v>1.025</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.800000000000001</v>
+        <v>-0.1244444444444446</v>
       </c>
       <c r="W9" t="n">
-        <v>1.025</v>
-      </c>
-      <c r="X9" t="n">
+        <v>-0.2927777777777777</v>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="n">
         <v>0.4500000000000002</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AA9" t="n">
         <v>-0.5750000000000002</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.3500000000000014</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>-0.3500000000000014</v>
       </c>
       <c r="AB9" t="n">
         <v>-1</v>
@@ -2106,22 +2106,22 @@
         <v>0.06349206349206327</v>
       </c>
       <c r="AD9" t="n">
+        <v>2.175000000000001</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.2249999999999996</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.3500000000000014</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0.3500000000000014</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.925</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AI9" t="n">
         <v>-1.525</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.175000000000001</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>-0.2249999999999996</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-0.1244444444444446</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>-0.2927777777777777</v>
       </c>
       <c r="AJ9" t="n">
         <v>67.95214646464646</v>
@@ -2130,61 +2130,61 @@
         <v>67.24305555555556</v>
       </c>
       <c r="AL9" t="n">
+        <v>-0.2319192549659022</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>938550.5050505055</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-3.999212850590723</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>-0.3999999999999999</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-0.07363636363636372</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0.2510101010100954</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-4.084141414141413</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-212</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.07919191919191348</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-216</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-2.699999999999999</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-4.236279370435376</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>-0.08492216117216111</v>
       </c>
-      <c r="AM9" t="n">
-        <v>-215</v>
-      </c>
-      <c r="AN9" t="n">
+      <c r="BA9" t="n">
+        <v>-0.4794390523514558</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-7550000</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>-281183.6538757256</v>
+      </c>
+      <c r="BD9" t="n">
         <v>0.06929292929292785</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>938550.5050505055</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>-281183.6538757256</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>-4.236279370435376</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>-11950000</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>-2.300000000000001</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>-0.4794390523514558</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>-0.3999999999999999</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>-0.2510101010100954</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.07919191919191348</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>-0.2319192549659022</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>-4.084141414141413</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>-3.999212850590723</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>-219</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>-0.07363636363636372</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>-3</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
@@ -2258,31 +2258,31 @@
       <c r="Q10" t="n">
         <v>0</v>
       </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>-0.5777777777777777</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.5111111111111111</v>
+      </c>
       <c r="T10" t="n">
-        <v>-0.5777777777777777</v>
+        <v>-2.855555555555556</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5111111111111111</v>
+        <v>3.077777777777779</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.855555555555556</v>
+        <v>0.003888888888888831</v>
       </c>
       <c r="W10" t="n">
-        <v>3.077777777777779</v>
-      </c>
-      <c r="X10" t="n">
+        <v>0.4968055555555555</v>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="n">
         <v>-1.833333333333333</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AA10" t="n">
         <v>1.733333333333333</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.533333333333339</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-1.533333333333339</v>
       </c>
       <c r="AB10" t="n">
         <v>-0.5</v>
@@ -2291,22 +2291,22 @@
         <v>0.291666666666667</v>
       </c>
       <c r="AD10" t="n">
+        <v>1.522222222222222</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.277777777777779</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.533333333333339</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-1.533333333333339</v>
+      </c>
+      <c r="AH10" t="n">
         <v>-0.7222222222222222</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AI10" t="n">
         <v>0.5777777777777777</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.522222222222222</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.277777777777779</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0.003888888888888831</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0.4968055555555555</v>
       </c>
       <c r="AJ10" t="n">
         <v>68.50145903479236</v>
@@ -2315,61 +2315,61 @@
         <v>68.91373737373738</v>
       </c>
       <c r="AL10" t="n">
+        <v>-0.1661124952506725</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-1809318.181818182</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-0.5812456859707709</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-0.1090909090909093</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.663636363636364</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>88</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-3.527272727272731</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>6.166666666666668</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0.349051794905705</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>-0.01634548424459581</v>
       </c>
-      <c r="AM10" t="n">
-        <v>88</v>
-      </c>
-      <c r="AN10" t="n">
+      <c r="BA10" t="n">
+        <v>-0.348921077501636</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>3900000</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-643721.2870449799</v>
+      </c>
+      <c r="BD10" t="n">
         <v>-2.872727272727261</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>-1809318.181818182</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>-643721.2870449799</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0.349051794905705</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>3900000</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>6.166666666666668</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>-0.348921077501636</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0.663636363636364</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>-3.527272727272731</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>-0.1661124952506725</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>-0.5812456859707709</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>65</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>-0.1090909090909093</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>1</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -2443,31 +2443,31 @@
       <c r="Q11" t="n">
         <v>0</v>
       </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
       <c r="T11" t="n">
-        <v>0.2222222222222222</v>
+        <v>-0.7222222222222214</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-1.044444444444444</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7222222222222214</v>
+        <v>-0.133015873015873</v>
       </c>
       <c r="W11" t="n">
-        <v>-1.044444444444444</v>
-      </c>
-      <c r="X11" t="n">
+        <v>-0.4138095238095236</v>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="n">
         <v>-0.02222222222222214</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AA11" t="n">
         <v>0.2666666666666666</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0.4555555555555557</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>-0.4555555555555557</v>
       </c>
       <c r="AB11" t="n">
         <v>0.5</v>
@@ -2476,22 +2476,22 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
+        <v>2.177777777777779</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0.2777777777777786</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.4555555555555557</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-0.4555555555555557</v>
+      </c>
+      <c r="AH11" t="n">
         <v>0.8111111111111111</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AI11" t="n">
         <v>-0.7888888888888888</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.177777777777779</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>-0.2777777777777786</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>-0.133015873015873</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>-0.4138095238095236</v>
       </c>
       <c r="AJ11" t="n">
         <v>67.93348484848484</v>
@@ -2500,55 +2500,55 @@
         <v>69.72615039281706</v>
       </c>
       <c r="AL11" t="n">
+        <v>1.288532794436691</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-1397295.454545455</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.7957790556760784</v>
+      </c>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="n">
+        <v>-0.2245454545454546</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-1.008181818181825</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.655454545454546</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-106</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-2.050000000000011</v>
+      </c>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="n">
+        <v>-143</v>
+      </c>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="n">
+        <v>0.7719452947256116</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>-0.05941304182722917</v>
       </c>
-      <c r="AM11" t="n">
-        <v>-106</v>
-      </c>
-      <c r="AN11" t="n">
+      <c r="BA11" t="n">
+        <v>0.8827118686043107</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-615000</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-994706.7418216155</v>
+      </c>
+      <c r="BD11" t="n">
         <v>-4.063636363636377</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>-1397295.454545455</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>-994706.7418216155</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0.7719452947256116</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>-615000</v>
-      </c>
-      <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="n">
-        <v>0.8827118686043107</v>
-      </c>
-      <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="n">
-        <v>-1.008181818181825</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>-2.050000000000011</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.288532794436691</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>2.655454545454546</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.7957790556760784</v>
-      </c>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="n">
-        <v>-143</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>-0.2245454545454546</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>-2</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -2622,31 +2622,31 @@
       <c r="Q12" t="n">
         <v>0</v>
       </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+      <c r="R12" t="n">
+        <v>0.7777777777777777</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.333333333333333</v>
+      </c>
       <c r="T12" t="n">
-        <v>0.7777777777777777</v>
+        <v>0.3333333333333339</v>
       </c>
       <c r="U12" t="n">
-        <v>1.333333333333333</v>
+        <v>-0.8888888888888875</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3333333333333339</v>
+        <v>0.18875</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.8888888888888875</v>
-      </c>
-      <c r="X12" t="n">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="n">
         <v>1.444444444444445</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AA12" t="n">
         <v>0.8888888888888888</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.333333333333329</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>-1.333333333333329</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -2655,22 +2655,22 @@
         <v>0.4027777777777777</v>
       </c>
       <c r="AD12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-2.555555555555555</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.333333333333329</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-1.333333333333329</v>
+      </c>
+      <c r="AH12" t="n">
         <v>-0.2222222222222221</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AI12" t="n">
         <v>0.4444444444444444</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>-2.555555555555555</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0.18875</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0.6900000000000001</v>
       </c>
       <c r="AJ12" t="n">
         <v>67.32233445566779</v>
@@ -2679,61 +2679,61 @@
         <v>66.43636363636364</v>
       </c>
       <c r="AL12" t="n">
+        <v>-4.171239658510899</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-1372686.363636364</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>2.297501334160373</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-0.002727272727272911</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-1.564545454545453</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-1.396363636363617</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-3.172727272727272</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.866666666666646</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-64</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>3.199999999999999</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-2.717002001939079</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>0.08236542443064176</v>
       </c>
-      <c r="AM12" t="n">
-        <v>-50</v>
-      </c>
-      <c r="AN12" t="n">
+      <c r="BA12" t="n">
+        <v>-4.527757604714125</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-275000</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>355790.9539735627</v>
+      </c>
+      <c r="BD12" t="n">
         <v>-4.72999999999999</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>-1372686.363636364</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>355790.9539735627</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>-2.717002001939079</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>-275000</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>3.199999999999999</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>-4.527757604714125</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>-1.564545454545453</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>-3.172727272727272</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>-4.171239658510899</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>-1.396363636363617</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>2.297501334160373</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>1.866666666666646</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>-64</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>-0.002727272727272911</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>-1</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -2807,31 +2807,31 @@
       <c r="Q13" t="n">
         <v>0</v>
       </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>0.08080808080808088</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.7272727272727273</v>
+      </c>
       <c r="T13" t="n">
-        <v>0.08080808080808088</v>
+        <v>-1.919191919191919</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7272727272727273</v>
+        <v>-1.353535353535353</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.919191919191919</v>
+        <v>0.3387500000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>-1.353535353535353</v>
-      </c>
-      <c r="X13" t="n">
+        <v>0.2412500000000002</v>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="n">
         <v>0.6161616161616168</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AA13" t="n">
         <v>-0.858585858585859</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>-6.313131313131315</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>6.222222222222221</v>
       </c>
       <c r="AB13" t="n">
         <v>-1</v>
@@ -2840,22 +2840,22 @@
         <v>-0.4444444444444446</v>
       </c>
       <c r="AD13" t="n">
+        <v>1.979797979797981</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.3838383838383841</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-6.313131313131315</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>6.222222222222221</v>
+      </c>
+      <c r="AH13" t="n">
         <v>-0.09090909090909083</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AI13" t="n">
         <v>0.03030303030303028</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.979797979797981</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0.3838383838383841</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0.3387500000000001</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0.2412500000000002</v>
       </c>
       <c r="AJ13" t="n">
         <v>68.46767676767678</v>
@@ -2864,61 +2864,61 @@
         <v>69.37171717171718</v>
       </c>
       <c r="AL13" t="n">
+        <v>3.52288087967392</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-2286657.765151515</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.3151883361991565</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-0.05575757575757589</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0.8952651515151544</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4.891363636363593</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-23</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-1.995909090909095</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-15</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-4.55477572440212</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>-0.0242621778805987</v>
       </c>
-      <c r="AM13" t="n">
-        <v>-23</v>
-      </c>
-      <c r="AN13" t="n">
+      <c r="BA13" t="n">
+        <v>-2.581541002312047</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-5600000</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-1495568.488132506</v>
+      </c>
+      <c r="BD13" t="n">
         <v>-0.6547348484848499</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>-2286657.765151515</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>-1495568.488132506</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>-4.55477572440212</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>-5600000</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>-2.581541002312047</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0.8952651515151544</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>-1.995909090909095</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>3.52288087967392</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>4.891363636363593</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.3151883361991565</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>-15</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>-0.05575757575757589</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -2992,31 +2992,31 @@
       <c r="Q14" t="n">
         <v>0</v>
       </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
+      <c r="R14" t="n">
+        <v>0.4444444444444446</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.4444444444444444</v>
+      </c>
       <c r="T14" t="n">
-        <v>0.4444444444444446</v>
+        <v>-1.277777777777777</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4444444444444444</v>
+        <v>5.166666666666666</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.277777777777777</v>
+        <v>0.2230000000000003</v>
       </c>
       <c r="W14" t="n">
-        <v>5.166666666666666</v>
-      </c>
-      <c r="X14" t="n">
+        <v>0.03624999999999989</v>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="n">
         <v>-0.1666666666666661</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AA14" t="n">
         <v>-0.1111111111111116</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>-2.833333333333336</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.833333333333336</v>
       </c>
       <c r="AB14" t="n">
         <v>1.5</v>
@@ -3025,22 +3025,22 @@
         <v>0.6749999999999998</v>
       </c>
       <c r="AD14" t="n">
+        <v>1.777777777777779</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-5.888888888888888</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-2.833333333333336</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.833333333333336</v>
+      </c>
+      <c r="AH14" t="n">
         <v>0.0555555555555558</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AI14" t="n">
         <v>-0.111111111111111</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.777777777777779</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>-5.888888888888888</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0.2230000000000003</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0.03624999999999989</v>
       </c>
       <c r="AJ14" t="n">
         <v>68.75353535353536</v>
@@ -3049,61 +3049,61 @@
         <v>67.85067340067341</v>
       </c>
       <c r="AL14" t="n">
+        <v>2.973119712768039</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>4332307.359307359</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>3.466078197165146</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.7909090909090906</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.839884559884556</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.48486291486293</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>524</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>5.882799422799408</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-5.125</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>573</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-11.625</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>2.935769558659587</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>0.1449621989263936</v>
       </c>
-      <c r="AM14" t="n">
-        <v>524</v>
-      </c>
-      <c r="AN14" t="n">
+      <c r="BA14" t="n">
+        <v>-0.254230160291538</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>78375000</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>854239.4360754334</v>
+      </c>
+      <c r="BD14" t="n">
         <v>6.454747474747478</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>4332307.359307359</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>854239.4360754334</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>2.935769558659587</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>78375000</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>-11.625</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>-0.254230160291538</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>1.839884559884556</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>5.882799422799408</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>2.973119712768039</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.48486291486293</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>3.466078197165146</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>-5.125</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>573</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>0.7909090909090906</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>7</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>

--- a/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE14"/>
+  <dimension ref="A1:BE15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,94 +515,94 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_interceptions</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions_against</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -615,97 +615,97 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_start</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -717,32 +717,32 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>raSHWV4o</t>
+          <t>8K42rT3c</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45463.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">de oliveira m 
+          <t xml:space="preserve">badawi m 
   usa </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">paypal park
-  san jose  ca </t>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>bm8usLzB</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -759,141 +759,139 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Onn3tCA</t>
+          <t>86yPt28</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>EqKWmJf</t>
+          <t>UFWZoX9</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>-11</v>
+        <v>9</v>
       </c>
       <c r="N2" t="n">
-        <v>-11</v>
+        <v>9</v>
       </c>
       <c r="O2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.333333333333336</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-3.333333333333336</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.4173333333333333</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-0.6193333333333333</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-4.833333333333332</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.3333333333333339</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-7.333333333333334</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-0.8333333333333334</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>2.666666666666666</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>67.39545454545454</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>68.14565656565655</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.3731085978061515</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-2.060411810411836</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-109254.0965385477</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.7264763014762963</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.9790209790209587</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-206</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-15450000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.05693617135769502</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="n">
         <v>-3</v>
       </c>
-      <c r="P2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="n">
-        <v>0.2626262626262625</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.898989898989899</v>
-      </c>
-      <c r="V2" t="n">
-        <v>3.595959595959597</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.858585858585858</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.3535353535353538</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-3.171717171717169</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3.171717171717169</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-0.8888888888888888</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-0.2222222222222223</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0.2626262626262625</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-2.252525252525253</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.1616161616161627</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0.04194444444444434</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.5097222222222222</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>69.12300785634119</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>68.8347923681257</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>67</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-0.4028099173553699</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-342395.0413223137</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-97693.16988605889</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-1.430705719134792</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1725000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>-1.497603010983312</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>-0.02603305785124022</v>
-      </c>
+      <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="n">
-        <v>0.4427272727272822</v>
+        <v>-229</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.9150975335763007</v>
+        <v>-757832.5563325565</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.436363636363609</v>
+        <v>-0.8809675693206387</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.190089171499537</v>
+        <v>-0.0842319001685965</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.5</v>
+        <v>0.1370435120435118</v>
       </c>
       <c r="BB2" t="n">
-        <v>76</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
+        <v>0.7532828282828241</v>
+      </c>
+      <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="n">
-        <v>1</v>
+        <v>-1.135349536645123</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -902,32 +900,32 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>tflZ7nSp</t>
+          <t>Ma0gz0nH</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45463.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">vazquez r 
+          <t xml:space="preserve">unkel t 
   usa </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">dignity health sports park
-  carson  ca </t>
+          <t xml:space="preserve">providence park
+  portland  or </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>U3ebh62R</t>
+          <t>bm8usLzB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -944,141 +942,141 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2PIEeC7</t>
+          <t>Onn3tCA</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>zoZ995a</t>
+          <t>Sd7snoa</t>
         </is>
       </c>
       <c r="M3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.8333333333333333</v>
+      </c>
+      <c r="T3" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-7.25</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.5779999999999998</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-0.9330000000000001</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.8499999999999996</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-7.083333333333334</v>
+      </c>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.08333333333333326</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>3.666666666666666</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-2.833333333333334</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>70.03282828282829</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>68.10151515151516</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-0.2282825099466947</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.439393939393966</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>550487.0562760041</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.6612121212121167</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.3835353535353505</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-525000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>96916.16161616147</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>2.01695216398743</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>2.192552960420159</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.117676767676773</v>
+      </c>
+      <c r="BC3" t="n">
         <v>-2</v>
       </c>
-      <c r="N3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="n">
-        <v>-0.325</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.4499999999999993</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.5250000000000004</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.8499999999999996</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.875</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-1.875</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.625</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-0.6499999999999999</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.07499999999999929</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-0.08269841269841249</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0.2631746031746032</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>67.43797979797981</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>67.75795454545454</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0.03008195307108363</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>-47</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>4.020185185185198</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1870618.827160494</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>107926.4038381416</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.940570576191426</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1550000</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2.420357680278659</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>3.697037037037038</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.626543209876544</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>-3.326350641100845</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>-2.449691358024694</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-1.173925619940178</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>-72</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0.05333333333333323</v>
-      </c>
       <c r="BD3" t="n">
-        <v>-1</v>
+        <v>1.979606226529341</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
@@ -1087,32 +1085,32 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ABc3D84N</t>
+          <t>UT5bq9li</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">allatin m 
-  usa </t>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">children s mercy park
-  kansas city  mo </t>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>W0ealpQl</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1129,19 +1127,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2PIEeC7</t>
+          <t>KtuTuMN</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>rXawJi8</t>
+          <t>EqKWmJf</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
         <v>-2</v>
@@ -1153,121 +1151,121 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7545454545454544</v>
+        <v>10.8</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4090909090909092</v>
+        <v>-10.8</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.545454545454545</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>-3.345454545454546</v>
+        <v>-1.58</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.045454545454546</v>
+        <v>4.199999999999999</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.8818181818181818</v>
+        <v>-3.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.1454545454545482</v>
+        <v>0.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.04545454545454675</v>
+        <v>1.25</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5</v>
+        <v>4.600000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0777777777777775</v>
+        <v>-6.800000000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>-1.081818181818182</v>
+        <v>-8</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.481818181818182</v>
+        <v>-16</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.2545454545454557</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.009090909090907928</v>
+        <v>-2.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>-1.0175</v>
+        <v>2.6</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.3162499999999999</v>
+        <v>-2.199999999999999</v>
       </c>
       <c r="AJ4" t="n">
-        <v>67.67474747474746</v>
+        <v>69.02727272727273</v>
       </c>
       <c r="AK4" t="n">
-        <v>68.35274971941638</v>
+        <v>67.45454545454547</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.06822406257188884</v>
+        <v>2.269865289110825</v>
       </c>
       <c r="AM4" t="n">
-        <v>-69</v>
+        <v>-0.5095959595959414</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.075757575757564</v>
+        <v>387315.8130431876</v>
       </c>
       <c r="AO4" t="n">
-        <v>-351615.9320477503</v>
+        <v>2.614026629935722</v>
       </c>
       <c r="AP4" t="n">
-        <v>-237250.1451158914</v>
+        <v>2.33617998163453</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.2159380095328132</v>
+        <v>63</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1000000</v>
+        <v>2600000</v>
       </c>
       <c r="AS4" t="n">
+        <v>0.01154401154401152</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.3333333333333428</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1746940.541781451</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.627110436441118</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.698697829732765</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.3266299357208451</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.4556703397612409</v>
+      </c>
+      <c r="BC4" t="n">
         <v>-3</v>
       </c>
-      <c r="AT4" t="n">
-        <v>0.9216304664403978</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>3.187511478420568</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>-3.087213039485775</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.360066830133945</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0.9619834710744044</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>-2.544909440602893</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0.8333333333333428</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>-70</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0.06287878787878776</v>
-      </c>
       <c r="BD4" t="n">
-        <v>-1</v>
+        <v>-0.987187028162964</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -1276,32 +1274,32 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ld9fFUZA</t>
+          <t>Sx1kytXA</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.9375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">demianchuk s 
+          <t xml:space="preserve">mendoza r 
   usa </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">toyota stadium
-  frisco  tx </t>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
+          <t>jmBZNRn8</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1318,141 +1316,137 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>WWvwigh</t>
+          <t>z9ZXDy6</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>UFWZoX9</t>
+          <t>rJ9D8rz</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-1</v>
+      </c>
       <c r="T5" t="n">
-        <v>-0.3454545454545455</v>
+        <v>13.25</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1272727272727272</v>
+        <v>-13.25</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.227272727272727</v>
+        <v>1.016666666666666</v>
       </c>
       <c r="W5" t="n">
-        <v>4.254545454545454</v>
+        <v>-1.228333333333333</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3545454545454545</v>
+        <v>2.75</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.063636363636363</v>
+        <v>-4.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.609090909090909</v>
+        <v>-0.1666666666666665</v>
       </c>
       <c r="AA5" t="n">
-        <v>-6.609090909090909</v>
+        <v>-0.1666666666666665</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.5</v>
+        <v>6.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.175</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-0.1636363636363636</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0.1909090909090908</v>
-      </c>
+        <v>-8.25</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>-2.054545454545455</v>
+        <v>1</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.6363636363636367</v>
+        <v>-1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.3330555555555557</v>
+        <v>-4.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.3750000000000004</v>
+        <v>2.25</v>
       </c>
       <c r="AJ5" t="n">
-        <v>67.86172839506172</v>
+        <v>67.7590909090909</v>
       </c>
       <c r="AK5" t="n">
-        <v>68.50272727272727</v>
+        <v>66.84595959595958</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.03578556899495111</v>
+        <v>-2.270556856471174</v>
       </c>
       <c r="AM5" t="n">
-        <v>11</v>
+        <v>0.7657575757575614</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.149242424242431</v>
+        <v>-484968.2158682763</v>
       </c>
       <c r="AO5" t="n">
-        <v>1452213.636363636</v>
+        <v>-0.004141414141415112</v>
       </c>
       <c r="AP5" t="n">
-        <v>240261.9703904029</v>
+        <v>-0.4399999999999977</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.8104192670411123</v>
+        <v>-2</v>
       </c>
       <c r="AR5" t="n">
-        <v>-4150000</v>
+        <v>1240000</v>
       </c>
       <c r="AS5" t="n">
-        <v>-1</v>
+        <v>-0.0935099111414901</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.06015999319775389</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.1880303030302954</v>
+        <v>-3.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.75181818181818</v>
+        <v>15</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.7003194332999954</v>
+        <v>426972.2222222225</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.9160606060605971</v>
+        <v>-0.8062073696408696</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.6211603097830221</v>
+        <v>-3.844034424878735</v>
       </c>
       <c r="BA5" t="n">
-        <v>-4</v>
+        <v>-0.01818181818181808</v>
       </c>
       <c r="BB5" t="n">
-        <v>13</v>
+        <v>0.298787878787877</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.07196969696969702</v>
+        <v>-5</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>-1.907425065511973</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -1461,32 +1455,32 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WKbaElkH</t>
+          <t>2NHGKPBj</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.9375</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">fischer d 
-  can </t>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">shell energy stadium
-  houston  tx </t>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>W0ealpQl</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>6P5S63Ah</t>
+          <t>U3ebh62R</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1503,145 +1497,141 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>l6eEjGl</t>
+          <t>jBBpU7Y</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>UFWZoX9</t>
+          <t>dp6AQn9</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>-12</v>
+        <v>-3</v>
       </c>
       <c r="N6" t="n">
-        <v>-12</v>
+        <v>-3</v>
       </c>
       <c r="O6" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4.350000000000001</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-4.350000000000001</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.0445</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.2875000000000001</v>
+      </c>
+      <c r="X6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0.3499999999999996</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0.09999999999999964</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>66.60606060606061</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>67.58181818181818</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0.156779640507267</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.05932047750229685</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-169459.6924007819</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-5.064462809917359</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-2.163728191000928</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>192</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-0.03167623439362566</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
         <v>3</v>
       </c>
-      <c r="S6" t="n">
-        <v>3.333333333333334</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-0.1000000000000001</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.3500000000000001</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.949999999999999</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-0.3833333333333346</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.433333333333333</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.6833333333333327</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>6.433333333333337</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>-6.433333333333337</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.5795454545454541</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0.6000000000000001</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.133333333333335</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.08111111111111113</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0.1236111111111111</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>68.06745230078565</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>67.82363636363637</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0.04465949165774163</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>-1.155015186833381</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>-247223.3877233877</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>56628.67746394081</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.532199086307671</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>150000</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>-8</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.060589312383268</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
       <c r="AV6" t="n">
-        <v>-0.04740764286218635</v>
+        <v>5.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>-1.870449247721965</v>
+        <v>208</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.053068944601819</v>
+        <v>-2029589.531680441</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.1639189093733933</v>
+        <v>0.9160045139701047</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.9906079080769103</v>
+        <v>-0.6763872304037335</v>
       </c>
       <c r="BA6" t="n">
-        <v>-9</v>
+        <v>-0.04848484848484835</v>
       </c>
       <c r="BB6" t="n">
-        <v>6</v>
+        <v>-2.21643709825528</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.08282121918485541</v>
+        <v>-3</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>0.9865515423118438</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -1650,32 +1640,32 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vo27CSJT</t>
+          <t>4nxtRRYM</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">gonzales g 
-  usa </t>
+          <t xml:space="preserve">fischer d 
+  can </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">citypark
-  st  louis  mo </t>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>jmBZNRn8</t>
+          <t>IeT6JBE3</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1697,130 +1687,136 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>KtuTuMN</t>
+          <t>UL7r7du</t>
         </is>
       </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-5.200000000000003</v>
+      </c>
+      <c r="U7" t="n">
+        <v>5.200000000000003</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.5115000000000001</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-1.2215</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.1499999999999999</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.5999999999999996</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>6.600000000000001</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-8.600000000000001</v>
+      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-0.1999999999999993</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>67.93818181818182</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>68.78909090909092</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.949961315009958</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.996611570247921</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>114934.7891752978</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-1.97999999999999</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.018925619834718</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>68</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>17950000</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>-0.2947686030934114</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AU7" t="n">
         <v>1</v>
       </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="n">
-        <v>-0.7777777777777777</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-0.375</v>
-      </c>
-      <c r="V7" t="n">
-        <v>3.527777777777779</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-1.055555555555555</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.5972222222222223</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.04166666666666696</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-1.416666666666664</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.416666666666664</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-0.3611111111111112</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0.09722222222222232</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>5.763888888888889</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>-2.333333333333334</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-0.3023214285714286</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>-0.1466071428571429</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>70.00909090909092</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>68.0300505050505</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>-118</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>2.305454545454552</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>419510.1010101011</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>564914.1408153626</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>4.187607629280123</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>-2240000</v>
-      </c>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="n">
-        <v>1.795966420359676</v>
-      </c>
-      <c r="AU7" t="inlineStr"/>
       <c r="AV7" t="n">
-        <v>1.464646464646464</v>
+        <v>12.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.5289898989899058</v>
+        <v>74</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.424817838717445</v>
+        <v>-1051148.760330579</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.863939393939404</v>
+        <v>-3.447196393292771</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.7048921109999355</v>
-      </c>
-      <c r="BA7" t="inlineStr"/>
+        <v>-0.9274582059059355</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-0.1054545454545455</v>
+      </c>
       <c r="BB7" t="n">
-        <v>-143</v>
+        <v>-1.830661157024792</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.187878787878788</v>
+        <v>-2</v>
       </c>
       <c r="BD7" t="n">
-        <v>-2</v>
+        <v>-0.9158559660160677</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -1829,32 +1825,32 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>zg5jGAK4</t>
+          <t>IktpQolT</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unkel t 
+          <t xml:space="preserve">rivas v 
   usa </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">q2 stadium
-  austin  tx </t>
+          <t xml:space="preserve">geodis park
+  nashville  tn </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IeT6JBE3</t>
+          <t>84yIDQMe</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>txUJt9AR</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1871,135 +1867,141 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>lAVQ9RG</t>
+          <t>xA45kov</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>UL7r7du</t>
+          <t>dp6AQn9</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>-0.6499999999999999</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.25</v>
+      </c>
       <c r="T8" t="n">
-        <v>-1.2</v>
+        <v>5.950000000000003</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8555555555555556</v>
+        <v>-5.950000000000003</v>
       </c>
       <c r="V8" t="n">
-        <v>-4.555555555555555</v>
+        <v>0.2593333333333332</v>
       </c>
       <c r="W8" t="n">
-        <v>4.166666666666668</v>
+        <v>-0.7086666666666667</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.644444444444445</v>
+        <v>0.25</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.277777777777778</v>
+        <v>-4.05</v>
       </c>
       <c r="Z8" t="n">
-        <v>-1.833333333333336</v>
+        <v>0.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.833333333333336</v>
+        <v>-0.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1</v>
+        <v>2.65</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>-1.477777777777778</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.255555555555556</v>
-      </c>
+        <v>-6.199999999999999</v>
+      </c>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="n">
-        <v>0.04444444444444429</v>
+        <v>0.3</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.3777777777777782</v>
+        <v>-0.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0.2687500000000003</v>
+        <v>-0.5999999999999996</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.7980357142857142</v>
+        <v>-2.199999999999999</v>
       </c>
       <c r="AJ8" t="n">
-        <v>68.84556677890012</v>
+        <v>65.88727272727272</v>
       </c>
       <c r="AK8" t="n">
-        <v>68.96704545454546</v>
+        <v>68.55227272727272</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.2736270683295856</v>
+        <v>-4.935305472327045</v>
       </c>
       <c r="AM8" t="n">
-        <v>-123</v>
+        <v>2.505050505050519</v>
       </c>
       <c r="AN8" t="n">
-        <v>-4.696767676767678</v>
+        <v>-262377.6618656204</v>
       </c>
       <c r="AO8" t="n">
-        <v>-1943471.533516988</v>
+        <v>3.15970819304151</v>
       </c>
       <c r="AP8" t="n">
-        <v>-751937.8030542501</v>
+        <v>-1.412991021324345</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.902009704173736</v>
+        <v>334</v>
       </c>
       <c r="AR8" t="n">
-        <v>-2200000</v>
-      </c>
-      <c r="AS8" t="inlineStr"/>
+        <v>5675000</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.05126811594202896</v>
+      </c>
       <c r="AT8" t="n">
-        <v>2.23185083036984</v>
-      </c>
-      <c r="AU8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>5</v>
+      </c>
       <c r="AV8" t="n">
-        <v>0.2333241505968786</v>
+        <v>-5.666666666666657</v>
       </c>
       <c r="AW8" t="n">
-        <v>-6.217364554637271</v>
+        <v>346</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.348215444556985</v>
+        <v>1470414.562289563</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.9138751147841901</v>
+        <v>6.045468885853413</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-5.246404047971893</v>
-      </c>
-      <c r="BA8" t="inlineStr"/>
+        <v>2.71180243292519</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0.1636363636363638</v>
+      </c>
       <c r="BB8" t="n">
-        <v>-149</v>
+        <v>5.129040404040403</v>
       </c>
       <c r="BC8" t="n">
-        <v>-0.2211753902662996</v>
+        <v>3</v>
       </c>
       <c r="BD8" t="n">
-        <v>-2</v>
+        <v>2.131452263226976</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -2008,32 +2010,32 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>MTkoJCzn</t>
+          <t>OWICL5dp</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45462.98958333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">marrufo j 
-  usa </t>
+          <t xml:space="preserve">dujic f 
+  can </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">tql stadium
-  cincinnati  oh </t>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Szrwix67</t>
+          <t>EPngUvhk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2050,141 +2052,127 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Onn3tCA</t>
+          <t>z9ZXDy6</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>6gpXy3v</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
+          <t>l6eEjGl</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+      <c r="R9" t="n">
+        <v>-1.033333333333333</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.166666666666667</v>
+      </c>
       <c r="T9" t="n">
-        <v>0.7250000000000001</v>
+        <v>1.200000000000003</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3500000000000001</v>
+        <v>-1.200000000000003</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.800000000000001</v>
+        <v>0.165</v>
       </c>
       <c r="W9" t="n">
-        <v>1.025</v>
+        <v>-0.0525000000000001</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4500000000000002</v>
+        <v>1.933333333333333</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.5750000000000002</v>
+        <v>-0.9666666666666668</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.3500000000000014</v>
+        <v>-2.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.3500000000000014</v>
+        <v>0.7999999999999998</v>
       </c>
       <c r="AB9" t="n">
-        <v>-1</v>
+        <v>5.766666666666667</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.06349206349206327</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.925</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>-1.525</v>
-      </c>
+        <v>-3.966666666666667</v>
+      </c>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
-        <v>2.175000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.2249999999999996</v>
+        <v>1.1</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.1244444444444446</v>
+        <v>3.333333333333334</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.2927777777777777</v>
+        <v>0.9000000000000004</v>
       </c>
       <c r="AJ9" t="n">
-        <v>67.95214646464646</v>
+        <v>68.88545454545455</v>
       </c>
       <c r="AK9" t="n">
-        <v>67.24305555555556</v>
+        <v>69.91818181818181</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.08492216117216111</v>
+        <v>-0.4962656232363685</v>
       </c>
       <c r="AM9" t="n">
-        <v>-215</v>
+        <v>2.90681818181821</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.06929292929292785</v>
+        <v>-749698.4368223345</v>
       </c>
       <c r="AO9" t="n">
-        <v>938550.5050505055</v>
+        <v>0.7770833333333371</v>
       </c>
       <c r="AP9" t="n">
-        <v>-281183.6538757256</v>
+        <v>-0.5128787878787762</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-4.236279370435376</v>
+        <v>-279</v>
       </c>
       <c r="AR9" t="n">
-        <v>-11950000</v>
+        <v>-8600000</v>
       </c>
       <c r="AS9" t="n">
-        <v>-2.300000000000001</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>-0.4794390523514558</v>
-      </c>
+        <v>-0.04063644688644685</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
       <c r="AU9" t="n">
-        <v>-0.3999999999999999</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>-0.2510101010100954</v>
-      </c>
+        <v>-4</v>
+      </c>
+      <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="n">
-        <v>0.07919191919191348</v>
+        <v>-292</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.2319192549659022</v>
+        <v>-1412476.957070707</v>
       </c>
       <c r="AY9" t="n">
-        <v>-4.084141414141413</v>
+        <v>-1.665747722029273</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-3.999212850590723</v>
+        <v>-0.8646347583700305</v>
       </c>
       <c r="BA9" t="n">
-        <v>4</v>
+        <v>0.0368686868686865</v>
       </c>
       <c r="BB9" t="n">
-        <v>-219</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>-0.07363636363636372</v>
-      </c>
+        <v>-0.4830176767676804</v>
+      </c>
+      <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="n">
-        <v>-3</v>
+        <v>2.629907805276702</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
@@ -2193,32 +2181,32 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hK8xvrmh</t>
+          <t>z7pPU9Zc</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">szpala l 
+          <t xml:space="preserve">de oliveira m 
   usa </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">saputo stadium
-  montreal  qc </t>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2235,12 +2223,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>K4FYmLD</t>
+          <t>6gpXy3v</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>EgT3xN3</t>
+          <t>rXawJi8</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -2258,118 +2246,118 @@
       <c r="Q10" t="n">
         <v>0</v>
       </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>0.07142857142857145</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0.5714285714285716</v>
+      </c>
       <c r="T10" t="n">
-        <v>-0.5777777777777777</v>
+        <v>5.642857142857146</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5111111111111111</v>
+        <v>-5.642857142857146</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.855555555555556</v>
+        <v>0.3809999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>3.077777777777779</v>
+        <v>-0.8159999999999997</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.833333333333333</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.733333333333333</v>
+        <v>-1.214285714285714</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.533333333333339</v>
+        <v>-3.333333333333333</v>
       </c>
       <c r="AA10" t="n">
-        <v>-1.533333333333339</v>
+        <v>-1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.5</v>
+        <v>-0.3571428571428577</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.291666666666667</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>-0.7222222222222222</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0.5777777777777777</v>
-      </c>
+        <v>-2.5</v>
+      </c>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="n">
-        <v>1.522222222222222</v>
+        <v>-0.7857142857142858</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.277777777777779</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.003888888888888831</v>
+        <v>-3.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.4968055555555555</v>
+        <v>5.285714285714286</v>
       </c>
       <c r="AJ10" t="n">
-        <v>68.50145903479236</v>
+        <v>68.14090909090909</v>
       </c>
       <c r="AK10" t="n">
-        <v>68.91373737373738</v>
+        <v>66.93333333333334</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.01634548424459581</v>
+        <v>2.882642728589019</v>
       </c>
       <c r="AM10" t="n">
-        <v>88</v>
+        <v>0.567171717171675</v>
       </c>
       <c r="AN10" t="n">
-        <v>-2.872727272727261</v>
+        <v>760376.2857075199</v>
       </c>
       <c r="AO10" t="n">
-        <v>-1809318.181818182</v>
+        <v>1.856421356421365</v>
       </c>
       <c r="AP10" t="n">
-        <v>-643721.2870449799</v>
+        <v>3.170598845598846</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.349051794905705</v>
+        <v>-66</v>
       </c>
       <c r="AR10" t="n">
-        <v>3900000</v>
+        <v>-1950000</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.166666666666668</v>
+        <v>-0.06822406257188884</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0.348921077501636</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.25</v>
+        <v>-1</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.663636363636364</v>
+        <v>4.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>-3.527272727272731</v>
+        <v>-74</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.1661124952506725</v>
+        <v>1667378.246753247</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.5</v>
+        <v>-0.7562135820511777</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0.5812456859707709</v>
+        <v>1.507395550007423</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.5</v>
+        <v>-0.05454545454545445</v>
       </c>
       <c r="BB10" t="n">
-        <v>65</v>
+        <v>-1.733044733044732</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0.1090909090909093</v>
+        <v>12</v>
       </c>
       <c r="BD10" t="n">
-        <v>1</v>
+        <v>1.031940604744307</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -2378,32 +2366,32 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>rwisKhLu</t>
+          <t>EcqTTTl4</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapman a 
+          <t xml:space="preserve">ford t 
   usa </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">bank of america stadium
-  charlotte  nc </t>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>O6hjfSXE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>rsHkUNCo</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2420,135 +2408,141 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>022mBmS</t>
+          <t>nJ01AhX</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>UL7r7du</t>
+          <t>tOpyQa2</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>0.1666666666666666</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
       <c r="T11" t="n">
-        <v>0.2222222222222222</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-2.5</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7222222222222214</v>
+        <v>0.7020000000000002</v>
       </c>
       <c r="W11" t="n">
-        <v>-1.044444444444444</v>
+        <v>-0.07399999999999984</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.02222222222222214</v>
+        <v>0.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.2666666666666666</v>
+        <v>-0.833333333333333</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.4555555555555557</v>
+        <v>-1</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.4555555555555557</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.5</v>
+        <v>3.166666666666666</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0.8111111111111111</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>-0.7888888888888888</v>
-      </c>
+        <v>-3.5</v>
+      </c>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="n">
-        <v>2.177777777777779</v>
+        <v>0.1666666666666665</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.2777777777777786</v>
+        <v>0.1666666666666665</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0.133015873015873</v>
+        <v>-1.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.4138095238095236</v>
+        <v>-3.833333333333332</v>
       </c>
       <c r="AJ11" t="n">
-        <v>67.93348484848484</v>
+        <v>67.4590909090909</v>
       </c>
       <c r="AK11" t="n">
-        <v>69.72615039281706</v>
+        <v>68.87239057239057</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.05941304182722917</v>
+        <v>2.443193316865049</v>
       </c>
       <c r="AM11" t="n">
-        <v>-106</v>
+        <v>3.854876033057849</v>
       </c>
       <c r="AN11" t="n">
-        <v>-4.063636363636377</v>
+        <v>-383308.3381888666</v>
       </c>
       <c r="AO11" t="n">
-        <v>-1397295.454545455</v>
+        <v>-0.8647107438016377</v>
       </c>
       <c r="AP11" t="n">
-        <v>-994706.7418216155</v>
+        <v>-0.588512396694199</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.7719452947256116</v>
+        <v>194</v>
       </c>
       <c r="AR11" t="n">
-        <v>-615000</v>
-      </c>
-      <c r="AS11" t="inlineStr"/>
+        <v>2125000</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-0.07760590540910872</v>
+      </c>
       <c r="AT11" t="n">
-        <v>0.8827118686043107</v>
-      </c>
-      <c r="AU11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3</v>
+      </c>
       <c r="AV11" t="n">
-        <v>-1.008181818181825</v>
+        <v>10.75</v>
       </c>
       <c r="AW11" t="n">
-        <v>-2.050000000000011</v>
+        <v>205</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.288532794436691</v>
+        <v>-472622.7272727271</v>
       </c>
       <c r="AY11" t="n">
-        <v>2.655454545454546</v>
+        <v>-2.505192864482446</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.7957790556760784</v>
-      </c>
-      <c r="BA11" t="inlineStr"/>
+        <v>-2.440674125125952</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>-0.05404958677685956</v>
+      </c>
       <c r="BB11" t="n">
-        <v>-143</v>
+        <v>0.135206611570247</v>
       </c>
       <c r="BC11" t="n">
-        <v>-0.2245454545454546</v>
+        <v>6.25</v>
       </c>
       <c r="BD11" t="n">
-        <v>-2</v>
+        <v>2.314807860470381</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -2557,32 +2551,32 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>WA7tw22b</t>
+          <t>APxxS7JG</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">penso c 
+          <t xml:space="preserve">da silva a 
   usa </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">bmo field
-  toronto  on </t>
+          <t xml:space="preserve">subaru park
+  chester  pa </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
+          <t>Szrwix67</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>84yIDQMe</t>
+          <t>QJF7WTFB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2599,141 +2593,141 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>xA45kov</t>
+          <t>roEEsq7</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>EgT3xN3</t>
+          <t>K4zRMgT</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+      <c r="R12" t="n">
+        <v>-1.214285714285714</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.9285714285714284</v>
+      </c>
       <c r="T12" t="n">
-        <v>0.7777777777777777</v>
+        <v>11.03571428571428</v>
       </c>
       <c r="U12" t="n">
-        <v>1.333333333333333</v>
+        <v>-11.03571428571428</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3333333333333339</v>
+        <v>1.2225</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.8888888888888875</v>
+        <v>0.02083333333333348</v>
       </c>
       <c r="X12" t="n">
-        <v>1.444444444444445</v>
+        <v>2.392857142857143</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.8888888888888888</v>
+        <v>-1.464285714285714</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.333333333333329</v>
+        <v>-0.666666666666667</v>
       </c>
       <c r="AA12" t="n">
-        <v>-1.333333333333329</v>
+        <v>-1.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>11.53571428571428</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.4027777777777777</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>-0.2222222222222221</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0.4444444444444444</v>
-      </c>
+        <v>-5.392857142857142</v>
+      </c>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>-0.2142857142857142</v>
       </c>
       <c r="AG12" t="n">
-        <v>-2.555555555555555</v>
+        <v>0.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.18875</v>
+        <v>-2.071428571428571</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.6900000000000001</v>
+        <v>-2.357142857142858</v>
       </c>
       <c r="AJ12" t="n">
-        <v>67.32233445566779</v>
+        <v>67.826443001443</v>
       </c>
       <c r="AK12" t="n">
-        <v>66.43636363636364</v>
+        <v>68.34886363636363</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.08236542443064176</v>
+        <v>0.9971293183424024</v>
       </c>
       <c r="AM12" t="n">
-        <v>-50</v>
+        <v>1.033884297520672</v>
       </c>
       <c r="AN12" t="n">
-        <v>-4.72999999999999</v>
+        <v>-4788.900603129761</v>
       </c>
       <c r="AO12" t="n">
-        <v>-1372686.363636364</v>
+        <v>3.031404958677683</v>
       </c>
       <c r="AP12" t="n">
-        <v>355790.9539735627</v>
+        <v>2.138842975206614</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-2.717002001939079</v>
+        <v>285</v>
       </c>
       <c r="AR12" t="n">
-        <v>-275000</v>
+        <v>15025000</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.199999999999999</v>
+        <v>-0.01503092318309718</v>
       </c>
       <c r="AT12" t="n">
-        <v>-4.527757604714125</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV12" t="n">
-        <v>-1.564545454545453</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-3.172727272727272</v>
+        <v>292</v>
       </c>
       <c r="AX12" t="n">
-        <v>-4.171239658510899</v>
+        <v>1283008.26446281</v>
       </c>
       <c r="AY12" t="n">
-        <v>-1.396363636363617</v>
+        <v>-1.476742500763073</v>
       </c>
       <c r="AZ12" t="n">
-        <v>2.297501334160373</v>
+        <v>0.2312362351539292</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.866666666666646</v>
+        <v>0.05867768595041323</v>
       </c>
       <c r="BB12" t="n">
-        <v>-64</v>
+        <v>-0.2966942148760374</v>
       </c>
       <c r="BC12" t="n">
-        <v>-0.002727272727272911</v>
+        <v>-5.199999999999999</v>
       </c>
       <c r="BD12" t="n">
-        <v>-1</v>
+        <v>-0.004013450511394012</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -2742,32 +2736,32 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2u7rIWkh</t>
+          <t>tpoLVkKi</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">lauziere p 
-  can </t>
+          <t xml:space="preserve">simon n 
+  usa </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi field
-  washington  dc </t>
+          <t xml:space="preserve">tql stadium
+  cincinnati  oh </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2784,141 +2778,141 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>022mBmS</t>
+          <t>roEEsq7</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>86yPt28</t>
+          <t>Sd7snoa</t>
         </is>
       </c>
       <c r="M13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O13" t="n">
         <v>-2</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>-2</v>
       </c>
-      <c r="O13" t="n">
-        <v>-4</v>
-      </c>
-      <c r="P13" t="n">
-        <v>-4</v>
-      </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.4</v>
+      </c>
       <c r="T13" t="n">
-        <v>0.08080808080808088</v>
+        <v>2.200000000000003</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7272727272727273</v>
+        <v>-2.200000000000003</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.919191919191919</v>
+        <v>0.7549999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>-1.353535353535353</v>
+        <v>-1.794166666666666</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6161616161616168</v>
+        <v>2.533333333333333</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.858585858585859</v>
+        <v>-1.866666666666667</v>
       </c>
       <c r="Z13" t="n">
-        <v>-6.313131313131315</v>
+        <v>1.416666666666667</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.222222222222221</v>
+        <v>1</v>
       </c>
       <c r="AB13" t="n">
-        <v>-1</v>
+        <v>7.266666666666667</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.4444444444444446</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>-0.09090909090909083</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0.03030303030303028</v>
-      </c>
+        <v>-9.4</v>
+      </c>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="n">
-        <v>1.979797979797981</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.3838383838383841</v>
+        <v>-0.2666666666666668</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.3387500000000001</v>
+        <v>-2.666666666666666</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.2412500000000002</v>
+        <v>1.933333333333333</v>
       </c>
       <c r="AJ13" t="n">
-        <v>68.46767676767678</v>
+        <v>67.79050505050505</v>
       </c>
       <c r="AK13" t="n">
-        <v>69.37171717171718</v>
+        <v>69.42424242424242</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0.0242621778805987</v>
+        <v>-4.7376721554471</v>
       </c>
       <c r="AM13" t="n">
-        <v>-23</v>
+        <v>-1.547727272727229</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.6547348484848499</v>
+        <v>-30191.94156434387</v>
       </c>
       <c r="AO13" t="n">
-        <v>-2286657.765151515</v>
+        <v>0.2032828282828376</v>
       </c>
       <c r="AP13" t="n">
-        <v>-1495568.488132506</v>
+        <v>1.628282828282835</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-4.55477572440212</v>
+        <v>-139</v>
       </c>
       <c r="AR13" t="n">
-        <v>-5600000</v>
+        <v>-7650000</v>
       </c>
       <c r="AS13" t="n">
+        <v>-0.08890100912159737</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-144</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>728231.060606061</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-0.9438040970289983</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-4.450771461269383</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-0.09545454545454568</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-1.377525252525249</v>
+      </c>
+      <c r="BC13" t="n">
         <v>1</v>
       </c>
-      <c r="AT13" t="n">
-        <v>-2.581541002312047</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0.8952651515151544</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>-1.995909090909095</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>3.52288087967392</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>4.891363636363593</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.3151883361991565</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>-15</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>-0.05575757575757589</v>
-      </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>0.01656441074203485</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -2927,32 +2921,32 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>tW5nHj5b</t>
+          <t>WYwYSm4A</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
+          <t xml:space="preserve">simon n 
+  usa </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">chase stadium
-  fort lauderdale  fl </t>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0AheRyBg</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2969,143 +2963,328 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>6BusaLE</t>
+          <t>022mBmS</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>zoZ995a</t>
+          <t>Uw6sTk0</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
+      <c r="R14" t="n">
+        <v>-1.133333333333333</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.266666666666667</v>
+      </c>
       <c r="T14" t="n">
-        <v>0.4444444444444446</v>
+        <v>-0.3999999999999986</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.3999999999999986</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.277777777777777</v>
+        <v>0.08166666666666678</v>
       </c>
       <c r="W14" t="n">
-        <v>5.166666666666666</v>
+        <v>-0.5183333333333333</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1666666666666661</v>
+        <v>-2</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.1111111111111116</v>
+        <v>-1.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>-2.833333333333336</v>
+        <v>-0.4166666666666665</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.833333333333336</v>
+        <v>-0.3333333333333335</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>0.1999999999999993</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.6749999999999998</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0.0555555555555558</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>-0.111111111111111</v>
-      </c>
+        <v>-8.466666666666669</v>
+      </c>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="n">
-        <v>1.777777777777779</v>
+        <v>-1.6</v>
       </c>
       <c r="AG14" t="n">
-        <v>-5.888888888888888</v>
+        <v>-0.06666666666666665</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.2230000000000003</v>
+        <v>-2.066666666666666</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.03624999999999989</v>
+        <v>1.133333333333335</v>
       </c>
       <c r="AJ14" t="n">
-        <v>68.75353535353536</v>
+        <v>69.91797979797981</v>
       </c>
       <c r="AK14" t="n">
-        <v>67.85067340067341</v>
+        <v>66.59090909090908</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.1449621989263936</v>
+        <v>-0.02280751835671424</v>
       </c>
       <c r="AM14" t="n">
-        <v>524</v>
+        <v>-2.27555555555557</v>
       </c>
       <c r="AN14" t="n">
-        <v>6.454747474747478</v>
+        <v>1165322.2044186</v>
       </c>
       <c r="AO14" t="n">
-        <v>4332307.359307359</v>
+        <v>1.982020202020195</v>
       </c>
       <c r="AP14" t="n">
-        <v>854239.4360754334</v>
+        <v>1.087070707070708</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.935769558659587</v>
+        <v>-95</v>
       </c>
       <c r="AR14" t="n">
-        <v>78375000</v>
+        <v>-2660000</v>
       </c>
       <c r="AS14" t="n">
-        <v>-11.625</v>
+        <v>-0.01730930587337931</v>
       </c>
       <c r="AT14" t="n">
-        <v>-0.254230160291538</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.875</v>
+        <v>-1</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.839884559884556</v>
+        <v>2.833333333333343</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.882799422799408</v>
+        <v>-61</v>
       </c>
       <c r="AX14" t="n">
-        <v>2.973119712768039</v>
+        <v>532786.8686868688</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.48486291486293</v>
+        <v>-1.282047355983284</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3.466078197165146</v>
+        <v>-1.641670340211519</v>
       </c>
       <c r="BA14" t="n">
-        <v>-5.125</v>
+        <v>0.1622222222222225</v>
       </c>
       <c r="BB14" t="n">
-        <v>573</v>
+        <v>1.180707070707072</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.7909090909090906</v>
+        <v>-9</v>
       </c>
       <c r="BD14" t="n">
-        <v>7</v>
+        <v>-0.751210450918677</v>
       </c>
       <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ln2oxMH4</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45465.85416666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>167</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>K4FYmLD</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>EgT3xN3</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>12</v>
+      </c>
+      <c r="N15" t="n">
+        <v>12</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.9500000000000002</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0.6499999999999986</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.6499999999999986</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.3524999999999998</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.4099999999999999</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0.916666666666667</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>4.949999999999999</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-2.699999999999999</v>
+      </c>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>68.31272727272727</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>68.5409090909091</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.787371215927536</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-2.30545454545458</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>190353.8610155566</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>3.599999999999994</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>6.488181818181829</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-172</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-4175000</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-0.06943696430101065</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-1.199999999999989</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-137</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>852163.6363636365</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0.002499866273925733</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.8899904743145726</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-0.07363636363636372</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-2.955454545454547</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-9.866666666666667</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>2.321211952896533</v>
+      </c>
+      <c r="BE15" t="n">
         <v>0</v>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
@@ -515,34 +515,34 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal</t>
@@ -555,54 +555,54 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_interceptions</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -615,97 +615,97 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -783,22 +783,22 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
+        <v>3.333333333333336</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-3.333333333333336</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.4173333333333333</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-0.6193333333333333</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.166666666666667</v>
       </c>
-      <c r="S2" t="n">
+      <c r="W2" t="n">
         <v>-1.333333333333333</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.333333333333336</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-3.333333333333336</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.4173333333333333</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-0.6193333333333333</v>
       </c>
       <c r="X2" t="n">
         <v>0.6666666666666665</v>
@@ -807,22 +807,22 @@
         <v>-4.833333333333332</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.3333333333333339</v>
+        <v>-0.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="AB2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.666666666666666</v>
+      </c>
+      <c r="AD2" t="n">
         <v>8.5</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AE2" t="n">
         <v>-7.333333333333334</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-0.5</v>
       </c>
       <c r="AF2" t="n">
         <v>0.5</v>
@@ -831,10 +831,10 @@
         <v>-0.8333333333333334</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333339</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.666666666666666</v>
+        <v>-1</v>
       </c>
       <c r="AJ2" t="n">
         <v>67.39545454545454</v>
@@ -843,56 +843,56 @@
         <v>68.14565656565655</v>
       </c>
       <c r="AL2" t="n">
+        <v>-229</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.9790209790209587</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.7532828282828241</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>-1.135349536645123</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.7264763014762963</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-0.8809675693206387</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-0.0842319001685965</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>-757832.5563325565</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.05693617135769502</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>-15450000</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>-206</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="n">
+        <v>-109254.0965385477</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>-2.060411810411836</v>
+      </c>
+      <c r="BB2" t="n">
         <v>0.3731085978061515</v>
       </c>
-      <c r="AM2" t="n">
-        <v>-2.060411810411836</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-109254.0965385477</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0.7264763014762963</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0.9790209790209587</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-206</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-15450000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0.05693617135769502</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="n">
-        <v>-229</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>-757832.5563325565</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>-0.8809675693206387</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-0.0842319001685965</v>
-      </c>
-      <c r="BA2" t="n">
+      <c r="BC2" t="n">
         <v>0.1370435120435118</v>
       </c>
-      <c r="BB2" t="n">
-        <v>0.7532828282828241</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="n">
-        <v>-1.135349536645123</v>
-      </c>
+      <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -966,22 +966,22 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-7.25</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.5779999999999998</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-0.9330000000000001</v>
+      </c>
+      <c r="V3" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="S3" t="n">
+      <c r="W3" t="n">
         <v>-0.8333333333333333</v>
-      </c>
-      <c r="T3" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-7.25</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.5779999999999998</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-0.9330000000000001</v>
       </c>
       <c r="X3" t="n">
         <v>1.083333333333333</v>
@@ -989,20 +989,20 @@
       <c r="Y3" t="n">
         <v>-2.333333333333333</v>
       </c>
-      <c r="Z3" t="n">
-        <v>0.3999999999999999</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.8499999999999996</v>
-      </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
+        <v>3.666666666666666</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-2.833333333333334</v>
+      </c>
+      <c r="AD3" t="n">
         <v>2.75</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AE3" t="n">
         <v>-7.083333333333334</v>
       </c>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
         <v>1.25</v>
       </c>
@@ -1010,10 +1010,10 @@
         <v>0.08333333333333326</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.666666666666666</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="AI3" t="n">
-        <v>-2.833333333333334</v>
+        <v>0.8499999999999996</v>
       </c>
       <c r="AJ3" t="n">
         <v>70.03282828282829</v>
@@ -1022,61 +1022,61 @@
         <v>68.10151515151516</v>
       </c>
       <c r="AL3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.3835353535353505</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.117676767676773</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1.979606226529341</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.6612121212121167</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>2.01695216398743</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2.192552960420159</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>96916.16161616147</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-525000</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>550487.0562760041</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.439393939393966</v>
+      </c>
+      <c r="BB3" t="n">
         <v>-0.2282825099466947</v>
       </c>
-      <c r="AM3" t="n">
-        <v>1.439393939393966</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>550487.0562760041</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0.6612121212121167</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0.3835353535353505</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-525000</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>96916.16161616147</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>2.01695216398743</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>2.192552960420159</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.117676767676773</v>
-      </c>
       <c r="BC3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.979606226529341</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1151,22 +1151,22 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-10.8</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="V4" t="n">
         <v>2.2</v>
       </c>
-      <c r="S4" t="n">
+      <c r="W4" t="n">
         <v>-2</v>
-      </c>
-      <c r="T4" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-10.8</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-1.58</v>
       </c>
       <c r="X4" t="n">
         <v>4.199999999999999</v>
@@ -1175,22 +1175,22 @@
         <v>-3.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.25</v>
+        <v>-8</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.25</v>
+        <v>-16</v>
       </c>
       <c r="AB4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-2.199999999999999</v>
+      </c>
+      <c r="AD4" t="n">
         <v>4.600000000000001</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AE4" t="n">
         <v>-6.800000000000001</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-16</v>
       </c>
       <c r="AF4" t="n">
         <v>0.3999999999999999</v>
@@ -1199,10 +1199,10 @@
         <v>-2.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.6</v>
+        <v>0.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>-2.199999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="AJ4" t="n">
         <v>69.02727272727273</v>
@@ -1211,61 +1211,61 @@
         <v>67.45454545454547</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.269865289110825</v>
+        <v>90</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.5095959595959414</v>
+        <v>2.296786042240583</v>
       </c>
       <c r="AN4" t="n">
-        <v>387315.8130431876</v>
+        <v>0.5262626262626142</v>
       </c>
       <c r="AO4" t="n">
-        <v>2.614026629935722</v>
+        <v>-0.8689361731038048</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.33617998163453</v>
+        <v>2.602387511478426</v>
       </c>
       <c r="AQ4" t="n">
-        <v>63</v>
+        <v>0.6431171330671468</v>
       </c>
       <c r="AR4" t="n">
-        <v>2600000</v>
+        <v>1.732702993162775</v>
       </c>
       <c r="AS4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1706640.955004592</v>
+      </c>
+      <c r="AV4" t="n">
         <v>0.01154401154401152</v>
       </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.3333333333333428</v>
-      </c>
       <c r="AW4" t="n">
-        <v>80</v>
+        <v>3700000</v>
       </c>
       <c r="AX4" t="n">
-        <v>1746940.541781451</v>
+        <v>68</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.627110436441118</v>
+        <v>1.833333333333343</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.698697829732765</v>
+        <v>365763.7921170387</v>
       </c>
       <c r="BA4" t="n">
+        <v>-0.4331496786042237</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>2.287032299445116</v>
+      </c>
+      <c r="BC4" t="n">
         <v>0.3266299357208451</v>
       </c>
-      <c r="BB4" t="n">
-        <v>0.4556703397612409</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>-3</v>
-      </c>
       <c r="BD4" t="n">
-        <v>-0.987187028162964</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45465.9375</v>
+        <v>45466.0625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1336,22 +1336,22 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-13.25</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.016666666666666</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-1.228333333333333</v>
+      </c>
+      <c r="V5" t="n">
         <v>1.25</v>
       </c>
-      <c r="S5" t="n">
+      <c r="W5" t="n">
         <v>-1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-13.25</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.016666666666666</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-1.228333333333333</v>
       </c>
       <c r="X5" t="n">
         <v>2.75</v>
@@ -1359,20 +1359,20 @@
       <c r="Y5" t="n">
         <v>-4.25</v>
       </c>
-      <c r="Z5" t="n">
-        <v>-0.1666666666666665</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-0.1666666666666665</v>
-      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD5" t="n">
         <v>6.25</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AE5" t="n">
         <v>-8.25</v>
       </c>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
         <v>1</v>
       </c>
@@ -1380,10 +1380,10 @@
         <v>-1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>-4.25</v>
+        <v>-0.1666666666666665</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.25</v>
+        <v>-0.1666666666666665</v>
       </c>
       <c r="AJ5" t="n">
         <v>67.7590909090909</v>
@@ -1392,61 +1392,61 @@
         <v>66.84595959595958</v>
       </c>
       <c r="AL5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-0.4399999999999977</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.298787878787877</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-1.907425065511973</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-0.004141414141415112</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.8062073696408696</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-3.844034424878735</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>426972.2222222225</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-0.0935099111414901</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1240000</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-484968.2158682763</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0.7657575757575614</v>
+      </c>
+      <c r="BB5" t="n">
         <v>-2.270556856471174</v>
       </c>
-      <c r="AM5" t="n">
-        <v>0.7657575757575614</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-484968.2158682763</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>-0.004141414141415112</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-0.4399999999999977</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1240000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>-0.0935099111414901</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>426972.2222222225</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>-0.8062073696408696</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-3.844034424878735</v>
-      </c>
-      <c r="BA5" t="n">
+      <c r="BC5" t="n">
         <v>-0.01818181818181808</v>
       </c>
-      <c r="BB5" t="n">
-        <v>0.298787878787877</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>-5</v>
-      </c>
       <c r="BD5" t="n">
-        <v>-1.907425065511973</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45465.9375</v>
+        <v>45466.0625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1521,22 +1521,22 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
+        <v>4.350000000000001</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-4.350000000000001</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.0445</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.2875000000000001</v>
+      </c>
+      <c r="V6" t="n">
         <v>2.4</v>
       </c>
-      <c r="S6" t="n">
+      <c r="W6" t="n">
         <v>-1.8</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4.350000000000001</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-4.350000000000001</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.0445</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-0.2875000000000001</v>
       </c>
       <c r="X6" t="n">
         <v>4.1</v>
@@ -1544,20 +1544,20 @@
       <c r="Y6" t="n">
         <v>-0.3499999999999996</v>
       </c>
-      <c r="Z6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.09999999999999964</v>
+      </c>
+      <c r="AD6" t="n">
         <v>5.9</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AE6" t="n">
         <v>-4.5</v>
       </c>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
         <v>2.65</v>
       </c>
@@ -1565,10 +1565,10 @@
         <v>-0.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.9</v>
+        <v>0.75</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.09999999999999964</v>
+        <v>0.5</v>
       </c>
       <c r="AJ6" t="n">
         <v>66.60606060606061</v>
@@ -1577,61 +1577,61 @@
         <v>67.58181818181818</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.156779640507267</v>
+        <v>208</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.05932047750229685</v>
+        <v>-2.117061524334261</v>
       </c>
       <c r="AN6" t="n">
-        <v>-169459.6924007819</v>
+        <v>-2.124214876033058</v>
       </c>
       <c r="AO6" t="n">
-        <v>-5.064462809917359</v>
+        <v>1.003418932878077</v>
       </c>
       <c r="AP6" t="n">
-        <v>-2.163728191000928</v>
+        <v>-4.911331496786048</v>
       </c>
       <c r="AQ6" t="n">
+        <v>1.003045009351396</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.7248012897033504</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-1944304.178145088</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-0.0306771911663215</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AX6" t="n">
         <v>192</v>
       </c>
-      <c r="AR6" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>-0.03167623439362566</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV6" t="n">
+      <c r="AY6" t="n">
         <v>5.5</v>
       </c>
-      <c r="AW6" t="n">
-        <v>208</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>-2029589.531680441</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0.9160045139701047</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>-0.6763872304037335</v>
+        <v>-184865.2815633246</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.04848484848484835</v>
+        <v>-0.04542699724518684</v>
       </c>
       <c r="BB6" t="n">
-        <v>-2.21643709825528</v>
+        <v>-0.3235549889865723</v>
       </c>
       <c r="BC6" t="n">
-        <v>-3</v>
+        <v>-0.04222222222222216</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.9865515423118438</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1706,22 +1706,22 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
+        <v>-5.200000000000003</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5.200000000000003</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.5115000000000001</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-1.2215</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.8</v>
       </c>
-      <c r="S7" t="n">
+      <c r="W7" t="n">
         <v>-1.8</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-5.200000000000003</v>
-      </c>
-      <c r="U7" t="n">
-        <v>5.200000000000003</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.5115000000000001</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-1.2215</v>
       </c>
       <c r="X7" t="n">
         <v>3.6</v>
@@ -1729,20 +1729,20 @@
       <c r="Y7" t="n">
         <v>-3.4</v>
       </c>
-      <c r="Z7" t="n">
-        <v>0.1499999999999999</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.5999999999999996</v>
-      </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-0.1999999999999993</v>
+      </c>
+      <c r="AD7" t="n">
         <v>6.600000000000001</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AE7" t="n">
         <v>-8.600000000000001</v>
       </c>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="n">
         <v>1.4</v>
       </c>
@@ -1750,10 +1750,10 @@
         <v>-0.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.4</v>
+        <v>0.1499999999999999</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.1999999999999993</v>
+        <v>0.5999999999999996</v>
       </c>
       <c r="AJ7" t="n">
         <v>67.93818181818182</v>
@@ -1762,61 +1762,61 @@
         <v>68.78909090909092</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.949961315009958</v>
+        <v>74</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.996611570247921</v>
+        <v>1.124545454545455</v>
       </c>
       <c r="AN7" t="n">
-        <v>114934.7891752978</v>
+        <v>-1.863636363636363</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1.97999999999999</v>
+        <v>-0.8621562542914489</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.018925619834718</v>
+        <v>-1.952727272727273</v>
       </c>
       <c r="AQ7" t="n">
+        <v>-3.502215123272801</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-1.104131745410186</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-1039872.727272728</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-0.2947686030934114</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>17950000</v>
+      </c>
+      <c r="AX7" t="n">
         <v>68</v>
       </c>
-      <c r="AR7" t="n">
-        <v>17950000</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>-0.2947686030934114</v>
-      </c>
-      <c r="AT7" t="n">
+      <c r="AY7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>84859.6771782008</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>2.030000000000001</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>2.815060032472886</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-0.1054545454545455</v>
+      </c>
+      <c r="BD7" t="n">
         <v>0.5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>74</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>-1051148.760330579</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>-3.447196393292771</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>-0.9274582059059355</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>-0.1054545454545455</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>-1.830661157024792</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>-0.9158559660160677</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1891,22 +1891,22 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
+        <v>5.950000000000003</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-5.950000000000003</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.2593333333333332</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.7086666666666667</v>
+      </c>
+      <c r="V8" t="n">
         <v>-0.6499999999999999</v>
       </c>
-      <c r="S8" t="n">
+      <c r="W8" t="n">
         <v>0.25</v>
-      </c>
-      <c r="T8" t="n">
-        <v>5.950000000000003</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-5.950000000000003</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.2593333333333332</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-0.7086666666666667</v>
       </c>
       <c r="X8" t="n">
         <v>0.25</v>
@@ -1914,20 +1914,20 @@
       <c r="Y8" t="n">
         <v>-4.05</v>
       </c>
-      <c r="Z8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>-0.25</v>
-      </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="n">
+        <v>-0.5999999999999996</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-2.199999999999999</v>
+      </c>
+      <c r="AD8" t="n">
         <v>2.65</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AE8" t="n">
         <v>-6.199999999999999</v>
       </c>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="n">
         <v>0.3</v>
       </c>
@@ -1935,10 +1935,10 @@
         <v>-0.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0.5999999999999996</v>
+        <v>0.25</v>
       </c>
       <c r="AI8" t="n">
-        <v>-2.199999999999999</v>
+        <v>-0.25</v>
       </c>
       <c r="AJ8" t="n">
         <v>65.88727272727272</v>
@@ -1947,61 +1947,61 @@
         <v>68.55227272727272</v>
       </c>
       <c r="AL8" t="n">
+        <v>346</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-1.412991021324345</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>5.129040404040403</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>2.131452263226976</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>3.15970819304151</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>6.045468885853413</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.71180243292519</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1470414.562289563</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.05126811594202896</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>5675000</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>334</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-5.666666666666657</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>-262377.6618656204</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>2.505050505050519</v>
+      </c>
+      <c r="BB8" t="n">
         <v>-4.935305472327045</v>
       </c>
-      <c r="AM8" t="n">
-        <v>2.505050505050519</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>-262377.6618656204</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>3.15970819304151</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>-1.412991021324345</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>334</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>5675000</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0.05126811594202896</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>-5.666666666666657</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>346</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1470414.562289563</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>6.045468885853413</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>2.71180243292519</v>
-      </c>
-      <c r="BA8" t="n">
+      <c r="BC8" t="n">
         <v>0.1636363636363638</v>
       </c>
-      <c r="BB8" t="n">
-        <v>5.129040404040403</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>3</v>
-      </c>
       <c r="BD8" t="n">
-        <v>2.131452263226976</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2068,22 +2068,22 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
+        <v>1.200000000000003</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-1.200000000000003</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.0525000000000001</v>
+      </c>
+      <c r="V9" t="n">
         <v>-1.033333333333333</v>
       </c>
-      <c r="S9" t="n">
+      <c r="W9" t="n">
         <v>1.166666666666667</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.200000000000003</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-1.200000000000003</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-0.0525000000000001</v>
       </c>
       <c r="X9" t="n">
         <v>1.933333333333333</v>
@@ -2091,20 +2091,20 @@
       <c r="Y9" t="n">
         <v>-0.9666666666666668</v>
       </c>
-      <c r="Z9" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.7999999999999998</v>
-      </c>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="n">
+        <v>3.333333333333334</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.9000000000000004</v>
+      </c>
+      <c r="AD9" t="n">
         <v>5.766666666666667</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AE9" t="n">
         <v>-3.966666666666667</v>
       </c>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
         <v>-0.2</v>
       </c>
@@ -2112,10 +2112,10 @@
         <v>1.1</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.333333333333334</v>
+        <v>-2.2</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.9000000000000004</v>
+        <v>0.7999999999999998</v>
       </c>
       <c r="AJ9" t="n">
         <v>68.88545454545455</v>
@@ -2124,56 +2124,56 @@
         <v>69.91818181818181</v>
       </c>
       <c r="AL9" t="n">
+        <v>-380</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-0.5128787878787762</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.4830176767676804</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>2.629907805276702</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.7770833333333371</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-1.665747722029273</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0.8646347583700305</v>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>-1412476.957070707</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-0.04063644688644685</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-56100000</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-359</v>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="n">
+        <v>-749698.4368223345</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>2.90681818181821</v>
+      </c>
+      <c r="BB9" t="n">
         <v>-0.4962656232363685</v>
       </c>
-      <c r="AM9" t="n">
-        <v>2.90681818181821</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>-749698.4368223345</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0.7770833333333371</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>-0.5128787878787762</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>-279</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>-8600000</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>-0.04063644688644685</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="n">
-        <v>-292</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>-1412476.957070707</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>-1.665747722029273</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>-0.8646347583700305</v>
-      </c>
-      <c r="BA9" t="n">
+      <c r="BC9" t="n">
         <v>0.0368686868686865</v>
       </c>
-      <c r="BB9" t="n">
-        <v>-0.4830176767676804</v>
-      </c>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="n">
-        <v>2.629907805276702</v>
-      </c>
+      <c r="BD9" t="inlineStr"/>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2247,22 +2247,22 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
+        <v>5.642857142857146</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-5.642857142857146</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.3809999999999999</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.8159999999999997</v>
+      </c>
+      <c r="V10" t="n">
         <v>0.07142857142857145</v>
       </c>
-      <c r="S10" t="n">
+      <c r="W10" t="n">
         <v>-0.5714285714285716</v>
-      </c>
-      <c r="T10" t="n">
-        <v>5.642857142857146</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-5.642857142857146</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.3809999999999999</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-0.8159999999999997</v>
       </c>
       <c r="X10" t="n">
         <v>1.142857142857143</v>
@@ -2270,20 +2270,20 @@
       <c r="Y10" t="n">
         <v>-1.214285714285714</v>
       </c>
-      <c r="Z10" t="n">
-        <v>-3.333333333333333</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-1.8</v>
-      </c>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>5.285714285714286</v>
+      </c>
+      <c r="AD10" t="n">
         <v>-0.3571428571428577</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AE10" t="n">
         <v>-2.5</v>
       </c>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="n">
         <v>-0.7857142857142858</v>
       </c>
@@ -2291,10 +2291,10 @@
         <v>-1.285714285714286</v>
       </c>
       <c r="AH10" t="n">
-        <v>-3.5</v>
+        <v>-3.333333333333333</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.285714285714286</v>
+        <v>-1.8</v>
       </c>
       <c r="AJ10" t="n">
         <v>68.14090909090909</v>
@@ -2303,61 +2303,61 @@
         <v>66.93333333333334</v>
       </c>
       <c r="AL10" t="n">
+        <v>-74</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>3.170598845598846</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-1.733044733044732</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1.031940604744307</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.856421356421365</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0.7562135820511777</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.507395550007423</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1667378.246753247</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-0.06822406257188884</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-1950000</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-66</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>760376.2857075199</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0.567171717171675</v>
+      </c>
+      <c r="BB10" t="n">
         <v>2.882642728589019</v>
       </c>
-      <c r="AM10" t="n">
-        <v>0.567171717171675</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>760376.2857075199</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1.856421356421365</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>3.170598845598846</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>-66</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>-1950000</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>-0.06822406257188884</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>-74</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1667378.246753247</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>-0.7562135820511777</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.507395550007423</v>
-      </c>
-      <c r="BA10" t="n">
+      <c r="BC10" t="n">
         <v>-0.05454545454545445</v>
       </c>
-      <c r="BB10" t="n">
-        <v>-1.733044733044732</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>12</v>
-      </c>
       <c r="BD10" t="n">
-        <v>1.031940604744307</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2432,22 +2432,22 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.7020000000000002</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.07399999999999984</v>
+      </c>
+      <c r="V11" t="n">
         <v>0.1666666666666666</v>
       </c>
-      <c r="S11" t="n">
+      <c r="W11" t="n">
         <v>-0.3333333333333333</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.7020000000000002</v>
-      </c>
-      <c r="W11" t="n">
-        <v>-0.07399999999999984</v>
       </c>
       <c r="X11" t="n">
         <v>0.5</v>
@@ -2455,20 +2455,20 @@
       <c r="Y11" t="n">
         <v>-0.833333333333333</v>
       </c>
-      <c r="Z11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>-0.2000000000000002</v>
-      </c>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-3.833333333333332</v>
+      </c>
+      <c r="AD11" t="n">
         <v>3.166666666666666</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AE11" t="n">
         <v>-3.5</v>
       </c>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="n">
         <v>0.1666666666666665</v>
       </c>
@@ -2476,10 +2476,10 @@
         <v>0.1666666666666665</v>
       </c>
       <c r="AH11" t="n">
-        <v>-1.5</v>
+        <v>-1</v>
       </c>
       <c r="AI11" t="n">
-        <v>-3.833333333333332</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="AJ11" t="n">
         <v>67.4590909090909</v>
@@ -2488,61 +2488,61 @@
         <v>68.87239057239057</v>
       </c>
       <c r="AL11" t="n">
+        <v>205</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0.588512396694199</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.135206611570247</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>2.314807860470381</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-0.8647107438016377</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-2.505192864482446</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-2.440674125125952</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-472622.7272727271</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-0.07760590540910872</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>2125000</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>194</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-383308.3381888666</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>3.854876033057849</v>
+      </c>
+      <c r="BB11" t="n">
         <v>2.443193316865049</v>
       </c>
-      <c r="AM11" t="n">
-        <v>3.854876033057849</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>-383308.3381888666</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>-0.8647107438016377</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>-0.588512396694199</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>194</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>2125000</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>-0.07760590540910872</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>205</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>-472622.7272727271</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>-2.505192864482446</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>-2.440674125125952</v>
-      </c>
-      <c r="BA11" t="n">
+      <c r="BC11" t="n">
         <v>-0.05404958677685956</v>
       </c>
-      <c r="BB11" t="n">
-        <v>0.135206611570247</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>6.25</v>
-      </c>
       <c r="BD11" t="n">
-        <v>2.314807860470381</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2617,22 +2617,22 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
+        <v>11.03571428571428</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-11.03571428571428</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.2225</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.02083333333333348</v>
+      </c>
+      <c r="V12" t="n">
         <v>-1.214285714285714</v>
       </c>
-      <c r="S12" t="n">
+      <c r="W12" t="n">
         <v>0.9285714285714284</v>
-      </c>
-      <c r="T12" t="n">
-        <v>11.03571428571428</v>
-      </c>
-      <c r="U12" t="n">
-        <v>-11.03571428571428</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.2225</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0.02083333333333348</v>
       </c>
       <c r="X12" t="n">
         <v>2.392857142857143</v>
@@ -2640,20 +2640,20 @@
       <c r="Y12" t="n">
         <v>-1.464285714285714</v>
       </c>
-      <c r="Z12" t="n">
-        <v>-0.666666666666667</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>-1.5</v>
-      </c>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="n">
+        <v>-2.071428571428571</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-2.357142857142858</v>
+      </c>
+      <c r="AD12" t="n">
         <v>11.53571428571428</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AE12" t="n">
         <v>-5.392857142857142</v>
       </c>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="n">
         <v>-0.2142857142857142</v>
       </c>
@@ -2661,10 +2661,10 @@
         <v>0.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>-2.071428571428571</v>
+        <v>-0.666666666666667</v>
       </c>
       <c r="AI12" t="n">
-        <v>-2.357142857142858</v>
+        <v>-1.5</v>
       </c>
       <c r="AJ12" t="n">
         <v>67.826443001443</v>
@@ -2673,61 +2673,61 @@
         <v>68.34886363636363</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.9971293183424024</v>
+        <v>286</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.033884297520672</v>
+        <v>2.278016528925619</v>
       </c>
       <c r="AN12" t="n">
-        <v>-4788.900603129761</v>
+        <v>-0.2416528925619872</v>
       </c>
       <c r="AO12" t="n">
-        <v>3.031404958677683</v>
+        <v>0.2800701513087915</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.138842975206614</v>
+        <v>3.291074380165284</v>
       </c>
       <c r="AQ12" t="n">
-        <v>285</v>
+        <v>-1.647175696439238</v>
       </c>
       <c r="AR12" t="n">
-        <v>15025000</v>
+        <v>0.009777622723447621</v>
       </c>
       <c r="AS12" t="n">
-        <v>-0.01503092318309718</v>
+        <v>-4.800000000000001</v>
       </c>
       <c r="AT12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1366474.380165289</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-0.02425421197160338</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>12325000</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>279</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>2.400000000000006</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-56348.01347093843</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0.7838016528925777</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0.8869191051398531</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0.05785123966942152</v>
+      </c>
+      <c r="BD12" t="n">
         <v>-0.6000000000000001</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>292</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1283008.26446281</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>-1.476742500763073</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0.2312362351539292</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0.05867768595041323</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>-0.2966942148760374</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>-5.199999999999999</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>-0.004013450511394012</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2802,22 +2802,22 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
+        <v>2.200000000000003</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-2.200000000000003</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.7549999999999999</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-1.794166666666666</v>
+      </c>
+      <c r="V13" t="n">
         <v>0.3999999999999999</v>
       </c>
-      <c r="S13" t="n">
+      <c r="W13" t="n">
         <v>-0.4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.200000000000003</v>
-      </c>
-      <c r="U13" t="n">
-        <v>-2.200000000000003</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.7549999999999999</v>
-      </c>
-      <c r="W13" t="n">
-        <v>-1.794166666666666</v>
       </c>
       <c r="X13" t="n">
         <v>2.533333333333333</v>
@@ -2825,20 +2825,20 @@
       <c r="Y13" t="n">
         <v>-1.866666666666667</v>
       </c>
-      <c r="Z13" t="n">
-        <v>1.416666666666667</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1</v>
-      </c>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.933333333333333</v>
+      </c>
+      <c r="AD13" t="n">
         <v>7.266666666666667</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AE13" t="n">
         <v>-9.4</v>
       </c>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="n">
         <v>0.3333333333333333</v>
       </c>
@@ -2846,10 +2846,10 @@
         <v>-0.2666666666666668</v>
       </c>
       <c r="AH13" t="n">
-        <v>-2.666666666666666</v>
+        <v>1.416666666666667</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.933333333333333</v>
+        <v>1</v>
       </c>
       <c r="AJ13" t="n">
         <v>67.79050505050505</v>
@@ -2858,61 +2858,61 @@
         <v>69.42424242424242</v>
       </c>
       <c r="AL13" t="n">
+        <v>-144</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.628282828282835</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-1.377525252525249</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.01656441074203485</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.2032828282828376</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-0.9438040970289983</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-4.450771461269383</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>728231.060606061</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-0.08890100912159737</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-7650000</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-139</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-30191.94156434387</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-1.547727272727229</v>
+      </c>
+      <c r="BB13" t="n">
         <v>-4.7376721554471</v>
       </c>
-      <c r="AM13" t="n">
-        <v>-1.547727272727229</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>-30191.94156434387</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0.2032828282828376</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.628282828282835</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>-139</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>-7650000</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>-0.08890100912159737</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>-144</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>728231.060606061</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>-0.9438040970289983</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>-4.450771461269383</v>
-      </c>
-      <c r="BA13" t="n">
+      <c r="BC13" t="n">
         <v>-0.09545454545454568</v>
       </c>
-      <c r="BB13" t="n">
-        <v>-1.377525252525249</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1</v>
-      </c>
       <c r="BD13" t="n">
-        <v>0.01656441074203485</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2987,22 +2987,22 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
+        <v>-0.3999999999999986</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.3999999999999986</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.08166666666666678</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.5183333333333333</v>
+      </c>
+      <c r="V14" t="n">
         <v>-1.133333333333333</v>
       </c>
-      <c r="S14" t="n">
+      <c r="W14" t="n">
         <v>1.266666666666667</v>
-      </c>
-      <c r="T14" t="n">
-        <v>-0.3999999999999986</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.3999999999999986</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.08166666666666678</v>
-      </c>
-      <c r="W14" t="n">
-        <v>-0.5183333333333333</v>
       </c>
       <c r="X14" t="n">
         <v>-2</v>
@@ -3010,20 +3010,20 @@
       <c r="Y14" t="n">
         <v>-1.8</v>
       </c>
-      <c r="Z14" t="n">
-        <v>-0.4166666666666665</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>-0.3333333333333335</v>
-      </c>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="n">
+        <v>-2.066666666666666</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.133333333333335</v>
+      </c>
+      <c r="AD14" t="n">
         <v>0.1999999999999993</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AE14" t="n">
         <v>-8.466666666666669</v>
       </c>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="n">
         <v>-1.6</v>
       </c>
@@ -3031,10 +3031,10 @@
         <v>-0.06666666666666665</v>
       </c>
       <c r="AH14" t="n">
-        <v>-2.066666666666666</v>
+        <v>-0.4166666666666665</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.133333333333335</v>
+        <v>-0.3333333333333335</v>
       </c>
       <c r="AJ14" t="n">
         <v>69.91797979797981</v>
@@ -3043,61 +3043,61 @@
         <v>66.59090909090908</v>
       </c>
       <c r="AL14" t="n">
+        <v>-61</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.087070707070708</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.180707070707072</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.751210450918677</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.982020202020195</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-1.282047355983284</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-1.641670340211519</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>532786.8686868688</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-0.01730930587337931</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>-2660000</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-95</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>2.833333333333343</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1165322.2044186</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-2.27555555555557</v>
+      </c>
+      <c r="BB14" t="n">
         <v>-0.02280751835671424</v>
       </c>
-      <c r="AM14" t="n">
-        <v>-2.27555555555557</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1165322.2044186</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1.982020202020195</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.087070707070708</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>-95</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>-2660000</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>-0.01730930587337931</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.833333333333343</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>-61</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>532786.8686868688</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>-1.282047355983284</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>-1.641670340211519</v>
-      </c>
-      <c r="BA14" t="n">
+      <c r="BC14" t="n">
         <v>0.1622222222222225</v>
       </c>
-      <c r="BB14" t="n">
-        <v>1.180707070707072</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>-9</v>
-      </c>
       <c r="BD14" t="n">
-        <v>-0.751210450918677</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -3172,22 +3172,22 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
+        <v>-0.6499999999999986</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.6499999999999986</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.3524999999999998</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.4099999999999999</v>
+      </c>
+      <c r="V15" t="n">
         <v>0.9500000000000002</v>
       </c>
-      <c r="S15" t="n">
+      <c r="W15" t="n">
         <v>-0.85</v>
-      </c>
-      <c r="T15" t="n">
-        <v>-0.6499999999999986</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.6499999999999986</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.3524999999999998</v>
-      </c>
-      <c r="W15" t="n">
-        <v>-0.4099999999999999</v>
       </c>
       <c r="X15" t="n">
         <v>3.15</v>
@@ -3195,20 +3195,20 @@
       <c r="Y15" t="n">
         <v>0.25</v>
       </c>
-      <c r="Z15" t="n">
-        <v>-0.916666666666667</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>-0.75</v>
-      </c>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD15" t="n">
         <v>4.949999999999999</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AE15" t="n">
         <v>-2.699999999999999</v>
       </c>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="n">
         <v>0.8</v>
       </c>
@@ -3216,10 +3216,10 @@
         <v>-0.45</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.1</v>
+        <v>-0.916666666666667</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.1</v>
+        <v>-0.75</v>
       </c>
       <c r="AJ15" t="n">
         <v>68.31272727272727</v>
@@ -3228,61 +3228,61 @@
         <v>68.5409090909091</v>
       </c>
       <c r="AL15" t="n">
+        <v>-137</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>6.488181818181829</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-2.955454545454547</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>2.321211952896533</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>3.599999999999994</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.002499866273925733</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.8899904743145726</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-9.866666666666667</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>852163.6363636365</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-0.06943696430101065</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-4175000</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-172</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-1.199999999999989</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>190353.8610155566</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-2.30545454545458</v>
+      </c>
+      <c r="BB15" t="n">
         <v>2.787371215927536</v>
       </c>
-      <c r="AM15" t="n">
-        <v>-2.30545454545458</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>190353.8610155566</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>3.599999999999994</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>6.488181818181829</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>-172</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>-4175000</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>-0.06943696430101065</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>-1.199999999999989</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>-137</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>852163.6363636365</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0.002499866273925733</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0.8899904743145726</v>
-      </c>
-      <c r="BA15" t="n">
+      <c r="BC15" t="n">
         <v>-0.07363636363636372</v>
       </c>
-      <c r="BB15" t="n">
-        <v>-2.955454545454547</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>-9.866666666666667</v>
-      </c>
       <c r="BD15" t="n">
-        <v>2.321211952896533</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>

--- a/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
@@ -515,94 +515,94 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -615,97 +615,97 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
           <t>dif_sum_pot_player_miss</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -783,34 +783,34 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-0.8333333333333334</v>
+      </c>
+      <c r="T2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-7.333333333333334</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.4173333333333333</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-0.6193333333333333</v>
+      </c>
+      <c r="X2" t="n">
         <v>3.333333333333336</v>
       </c>
-      <c r="S2" t="n">
+      <c r="Y2" t="n">
         <v>-3.333333333333336</v>
       </c>
-      <c r="T2" t="n">
-        <v>0.4173333333333333</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-0.6193333333333333</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.6666666666666665</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-4.833333333333332</v>
-      </c>
       <c r="Z2" t="n">
-        <v>-0.5</v>
+        <v>0.3333333333333339</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="AB2" t="n">
         <v>0.5</v>
@@ -819,22 +819,22 @@
         <v>2.666666666666666</v>
       </c>
       <c r="AD2" t="n">
-        <v>8.5</v>
+        <v>-0.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>-7.333333333333334</v>
+        <v>-0.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.5</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.3333333333333339</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1</v>
+        <v>-4.833333333333332</v>
       </c>
       <c r="AJ2" t="n">
         <v>67.39545454545454</v>
@@ -843,56 +843,56 @@
         <v>68.14565656565655</v>
       </c>
       <c r="AL2" t="n">
+        <v>-0.0842319001685965</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.7532828282828241</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.05693617135769502</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>-2.060411810411836</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.9790209790209587</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.3731085978061515</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.7264763014762963</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>-109254.0965385477</v>
+      </c>
+      <c r="AT2" t="n">
         <v>-229</v>
       </c>
-      <c r="AM2" t="n">
-        <v>0.9790209790209587</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0.7532828282828241</v>
-      </c>
-      <c r="AO2" t="n">
+      <c r="AU2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.1370435120435118</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="n">
+        <v>-15450000</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-206</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>-757832.5563325565</v>
+      </c>
+      <c r="BB2" t="n">
         <v>-1.135349536645123</v>
       </c>
-      <c r="AP2" t="n">
-        <v>0.7264763014762963</v>
-      </c>
-      <c r="AQ2" t="n">
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="n">
         <v>-0.8809675693206387</v>
       </c>
-      <c r="AR2" t="n">
-        <v>-0.0842319001685965</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>-757832.5563325565</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.05693617135769502</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>-15450000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>-206</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="n">
-        <v>-109254.0965385477</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>-2.060411810411836</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0.3731085978061515</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0.1370435120435118</v>
-      </c>
-      <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
@@ -966,54 +966,54 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.08333333333333326</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-7.083333333333334</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.5779999999999998</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-0.9330000000000001</v>
+      </c>
+      <c r="X3" t="n">
         <v>7.25</v>
       </c>
-      <c r="S3" t="n">
+      <c r="Y3" t="n">
         <v>-7.25</v>
       </c>
-      <c r="T3" t="n">
-        <v>0.5779999999999998</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-0.9330000000000001</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-0.8333333333333333</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.083333333333333</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-2.333333333333333</v>
-      </c>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.8499999999999996</v>
+      </c>
       <c r="AB3" t="n">
         <v>3.666666666666666</v>
       </c>
       <c r="AC3" t="n">
         <v>-2.833333333333334</v>
       </c>
-      <c r="AD3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-7.083333333333334</v>
-      </c>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>1.25</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.08333333333333326</v>
+        <v>-0.8333333333333333</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.3999999999999999</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.8499999999999996</v>
+        <v>-2.333333333333333</v>
       </c>
       <c r="AJ3" t="n">
         <v>70.03282828282829</v>
@@ -1022,61 +1022,61 @@
         <v>68.10151515151516</v>
       </c>
       <c r="AL3" t="n">
+        <v>2.192552960420159</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.117676767676773</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1.439393939393966</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.3835353535353505</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-0.2282825099466947</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.6612121212121167</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>550487.0562760041</v>
+      </c>
+      <c r="AT3" t="n">
         <v>-4</v>
       </c>
-      <c r="AM3" t="n">
-        <v>0.3835353535353505</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.117676767676773</v>
-      </c>
-      <c r="AO3" t="n">
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>-525000</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>96916.16161616147</v>
+      </c>
+      <c r="BB3" t="n">
         <v>1.979606226529341</v>
       </c>
-      <c r="AP3" t="n">
-        <v>0.6612121212121167</v>
-      </c>
-      <c r="AQ3" t="n">
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="n">
         <v>2.01695216398743</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>2.192552960420159</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>96916.16161616147</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>-525000</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>550487.0562760041</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.439393939393966</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>-0.2282825099466947</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
@@ -1151,34 +1151,34 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4.600000000000001</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-6.800000000000001</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="X4" t="n">
         <v>10.8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="Y4" t="n">
         <v>-10.8</v>
       </c>
-      <c r="T4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-1.58</v>
-      </c>
-      <c r="V4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X4" t="n">
-        <v>4.199999999999999</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-3.2</v>
-      </c>
       <c r="Z4" t="n">
-        <v>-8</v>
+        <v>0.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>-16</v>
+        <v>1.25</v>
       </c>
       <c r="AB4" t="n">
         <v>2.6</v>
@@ -1187,22 +1187,22 @@
         <v>-2.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>4.600000000000001</v>
+        <v>-8</v>
       </c>
       <c r="AE4" t="n">
-        <v>-6.800000000000001</v>
+        <v>-16</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3999999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>-2.8</v>
+        <v>-2</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.25</v>
+        <v>4.199999999999999</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.25</v>
+        <v>-3.2</v>
       </c>
       <c r="AJ4" t="n">
         <v>69.02727272727273</v>
@@ -1211,61 +1211,61 @@
         <v>67.45454545454547</v>
       </c>
       <c r="AL4" t="n">
-        <v>90</v>
+        <v>1.732702993162775</v>
       </c>
       <c r="AM4" t="n">
+        <v>0.5262626262626142</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.01154401154401152</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.4331496786042237</v>
+      </c>
+      <c r="AP4" t="n">
         <v>2.296786042240583</v>
       </c>
-      <c r="AN4" t="n">
-        <v>0.5262626262626142</v>
-      </c>
-      <c r="AO4" t="n">
+      <c r="AQ4" t="n">
+        <v>2.287032299445116</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2.602387511478426</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>365763.7921170387</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>157</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.3266299357208451</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-4.666666666666657</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>128</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1706640.955004592</v>
+      </c>
+      <c r="BB4" t="n">
         <v>-0.8689361731038048</v>
       </c>
-      <c r="AP4" t="n">
-        <v>2.602387511478426</v>
-      </c>
-      <c r="AQ4" t="n">
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
         <v>0.6431171330671468</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.732702993162775</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1706640.955004592</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.01154401154401152</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>3700000</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>68</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.833333333333343</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>365763.7921170387</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>-0.4331496786042237</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>2.287032299445116</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0.3266299357208451</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -1336,54 +1336,54 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="T5" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-8.25</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.016666666666666</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-1.228333333333333</v>
+      </c>
+      <c r="X5" t="n">
         <v>13.25</v>
       </c>
-      <c r="S5" t="n">
+      <c r="Y5" t="n">
         <v>-13.25</v>
       </c>
-      <c r="T5" t="n">
-        <v>1.016666666666666</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-1.228333333333333</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-4.25</v>
-      </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>-0.1666666666666665</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-0.1666666666666665</v>
+      </c>
       <c r="AB5" t="n">
         <v>-4.25</v>
       </c>
       <c r="AC5" t="n">
         <v>2.25</v>
       </c>
-      <c r="AD5" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-8.25</v>
-      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AG5" t="n">
-        <v>-1.25</v>
+        <v>-1</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.1666666666666665</v>
+        <v>2.75</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.1666666666666665</v>
+        <v>-4.25</v>
       </c>
       <c r="AJ5" t="n">
         <v>67.7590909090909</v>
@@ -1392,61 +1392,61 @@
         <v>66.84595959595958</v>
       </c>
       <c r="AL5" t="n">
+        <v>-3.844034424878735</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.298787878787877</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-0.0935099111414901</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.7657575757575614</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-0.4399999999999977</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-2.270556856471174</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0.004141414141415112</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-484968.2158682763</v>
+      </c>
+      <c r="AT5" t="n">
         <v>15</v>
       </c>
-      <c r="AM5" t="n">
-        <v>-0.4399999999999977</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0.298787878787877</v>
-      </c>
-      <c r="AO5" t="n">
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-0.01818181818181808</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1240000</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>426972.2222222225</v>
+      </c>
+      <c r="BB5" t="n">
         <v>-1.907425065511973</v>
       </c>
-      <c r="AP5" t="n">
-        <v>-0.004141414141415112</v>
-      </c>
-      <c r="AQ5" t="n">
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
         <v>-0.8062073696408696</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>-3.844034424878735</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>426972.2222222225</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-0.0935099111414901</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1240000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-484968.2158682763</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0.7657575757575614</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>-2.270556856471174</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>-0.01818181818181808</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -1521,54 +1521,54 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.0445</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.2875000000000001</v>
+      </c>
+      <c r="X6" t="n">
         <v>4.350000000000001</v>
       </c>
-      <c r="S6" t="n">
+      <c r="Y6" t="n">
         <v>-4.350000000000001</v>
       </c>
-      <c r="T6" t="n">
-        <v>1.0445</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-0.2875000000000001</v>
-      </c>
-      <c r="V6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="X6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-0.3499999999999996</v>
-      </c>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AB6" t="n">
         <v>3.9</v>
       </c>
       <c r="AC6" t="n">
         <v>-0.09999999999999964</v>
       </c>
-      <c r="AD6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>-4.5</v>
-      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.2</v>
+        <v>-1.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.75</v>
+        <v>4.1</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.5</v>
+        <v>-0.3499999999999996</v>
       </c>
       <c r="AJ6" t="n">
         <v>66.60606060606061</v>
@@ -1577,61 +1577,61 @@
         <v>67.58181818181818</v>
       </c>
       <c r="AL6" t="n">
+        <v>-0.7248012897033504</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-2.124214876033058</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-0.0306771911663215</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-0.04542699724518684</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-2.117061524334261</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0.3235549889865723</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-4.911331496786048</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-184865.2815633246</v>
+      </c>
+      <c r="AT6" t="n">
         <v>208</v>
       </c>
-      <c r="AM6" t="n">
-        <v>-2.117061524334261</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>-2.124214876033058</v>
-      </c>
-      <c r="AO6" t="n">
+      <c r="AU6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-0.04222222222222216</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>192</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-1944304.178145088</v>
+      </c>
+      <c r="BB6" t="n">
         <v>1.003418932878077</v>
       </c>
-      <c r="AP6" t="n">
-        <v>-4.911331496786048</v>
-      </c>
-      <c r="AQ6" t="n">
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
         <v>1.003045009351396</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>-0.7248012897033504</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>-1944304.178145088</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>-0.0306771911663215</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>192</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>-184865.2815633246</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>-0.04542699724518684</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>-0.3235549889865723</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>-0.04222222222222216</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -1706,54 +1706,54 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="T7" t="n">
+        <v>6.600000000000001</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-8.600000000000001</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.5115000000000001</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-1.2215</v>
+      </c>
+      <c r="X7" t="n">
         <v>-5.200000000000003</v>
       </c>
-      <c r="S7" t="n">
+      <c r="Y7" t="n">
         <v>5.200000000000003</v>
       </c>
-      <c r="T7" t="n">
-        <v>0.5115000000000001</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-1.2215</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
+      <c r="Z7" t="n">
+        <v>0.1499999999999999</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.5999999999999996</v>
+      </c>
       <c r="AB7" t="n">
         <v>1.4</v>
       </c>
       <c r="AC7" t="n">
         <v>-0.1999999999999993</v>
       </c>
-      <c r="AD7" t="n">
-        <v>6.600000000000001</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-8.600000000000001</v>
-      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.8</v>
+        <v>-1.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.1499999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.5999999999999996</v>
+        <v>-3.4</v>
       </c>
       <c r="AJ7" t="n">
         <v>67.93818181818182</v>
@@ -1762,61 +1762,61 @@
         <v>68.78909090909092</v>
       </c>
       <c r="AL7" t="n">
+        <v>-1.104131745410186</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-1.863636363636363</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-0.2947686030934114</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>2.030000000000001</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.124545454545455</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>2.815060032472886</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-1.952727272727273</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>84859.6771782008</v>
+      </c>
+      <c r="AT7" t="n">
         <v>74</v>
       </c>
-      <c r="AM7" t="n">
-        <v>1.124545454545455</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>-1.863636363636363</v>
-      </c>
-      <c r="AO7" t="n">
+      <c r="AU7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-0.1054545454545455</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>17950000</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>68</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-1039872.727272728</v>
+      </c>
+      <c r="BB7" t="n">
         <v>-0.8621562542914489</v>
       </c>
-      <c r="AP7" t="n">
-        <v>-1.952727272727273</v>
-      </c>
-      <c r="AQ7" t="n">
+      <c r="BC7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BD7" t="n">
         <v>-3.502215123272801</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>-1.104131745410186</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>-1039872.727272728</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>-0.2947686030934114</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>17950000</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>68</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>84859.6771782008</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>2.030000000000001</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>2.815060032472886</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>-0.1054545454545455</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0.5</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -1891,54 +1891,54 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-6.199999999999999</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.2593333333333332</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.7086666666666667</v>
+      </c>
+      <c r="X8" t="n">
         <v>5.950000000000003</v>
       </c>
-      <c r="S8" t="n">
+      <c r="Y8" t="n">
         <v>-5.950000000000003</v>
       </c>
-      <c r="T8" t="n">
-        <v>0.2593333333333332</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-0.7086666666666667</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-0.6499999999999999</v>
-      </c>
-      <c r="W8" t="n">
+      <c r="Z8" t="n">
         <v>0.25</v>
       </c>
-      <c r="X8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-4.05</v>
-      </c>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
+      <c r="AA8" t="n">
+        <v>-0.25</v>
+      </c>
       <c r="AB8" t="n">
         <v>-0.5999999999999996</v>
       </c>
       <c r="AC8" t="n">
         <v>-2.199999999999999</v>
       </c>
-      <c r="AD8" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>-6.199999999999999</v>
-      </c>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="n">
-        <v>0.3</v>
+        <v>-0.6499999999999999</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="AH8" t="n">
         <v>0.25</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.25</v>
+        <v>-4.05</v>
       </c>
       <c r="AJ8" t="n">
         <v>65.88727272727272</v>
@@ -1947,61 +1947,61 @@
         <v>68.55227272727272</v>
       </c>
       <c r="AL8" t="n">
+        <v>2.71180243292519</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>5.129040404040403</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.05126811594202896</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>2.505050505050519</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-1.412991021324345</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-4.935305472327045</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>3.15970819304151</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>-262377.6618656204</v>
+      </c>
+      <c r="AT8" t="n">
         <v>346</v>
       </c>
-      <c r="AM8" t="n">
-        <v>-1.412991021324345</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>5.129040404040403</v>
-      </c>
-      <c r="AO8" t="n">
+      <c r="AU8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.1636363636363638</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-5.666666666666657</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>5675000</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>334</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1470414.562289563</v>
+      </c>
+      <c r="BB8" t="n">
         <v>2.131452263226976</v>
       </c>
-      <c r="AP8" t="n">
-        <v>3.15970819304151</v>
-      </c>
-      <c r="AQ8" t="n">
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
         <v>6.045468885853413</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>2.71180243292519</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1470414.562289563</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0.05126811594202896</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>5675000</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>334</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>-5.666666666666657</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>-262377.6618656204</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>2.505050505050519</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>-4.935305472327045</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0.1636363636363638</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -2068,54 +2068,54 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5.766666666666667</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-3.966666666666667</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.0525000000000001</v>
+      </c>
+      <c r="X9" t="n">
         <v>1.200000000000003</v>
       </c>
-      <c r="S9" t="n">
+      <c r="Y9" t="n">
         <v>-1.200000000000003</v>
       </c>
-      <c r="T9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-0.0525000000000001</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-1.033333333333333</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.933333333333333</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>-0.9666666666666668</v>
-      </c>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
+      <c r="Z9" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.7999999999999998</v>
+      </c>
       <c r="AB9" t="n">
         <v>3.333333333333334</v>
       </c>
       <c r="AC9" t="n">
         <v>0.9000000000000004</v>
       </c>
-      <c r="AD9" t="n">
-        <v>5.766666666666667</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>-3.966666666666667</v>
-      </c>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
-        <v>-0.2</v>
+        <v>-1.033333333333333</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.1</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AH9" t="n">
-        <v>-2.2</v>
+        <v>1.933333333333333</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.7999999999999998</v>
+        <v>-0.9666666666666668</v>
       </c>
       <c r="AJ9" t="n">
         <v>68.88545454545455</v>
@@ -2124,56 +2124,56 @@
         <v>69.91818181818181</v>
       </c>
       <c r="AL9" t="n">
+        <v>-0.8646347583700305</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-0.4830176767676804</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.04063644688644685</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>2.90681818181821</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-0.5128787878787762</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0.4962656232363685</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.7770833333333371</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-749698.4368223345</v>
+      </c>
+      <c r="AT9" t="n">
         <v>-380</v>
       </c>
-      <c r="AM9" t="n">
-        <v>-0.5128787878787762</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>-0.4830176767676804</v>
-      </c>
-      <c r="AO9" t="n">
+      <c r="AU9" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.0368686868686865</v>
+      </c>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="n">
+        <v>-56100000</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>-359</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>-1412476.957070707</v>
+      </c>
+      <c r="BB9" t="n">
         <v>2.629907805276702</v>
       </c>
-      <c r="AP9" t="n">
-        <v>0.7770833333333371</v>
-      </c>
-      <c r="AQ9" t="n">
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="n">
         <v>-1.665747722029273</v>
       </c>
-      <c r="AR9" t="n">
-        <v>-0.8646347583700305</v>
-      </c>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>-1412476.957070707</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>-0.04063644688644685</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>-56100000</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>-359</v>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="n">
-        <v>-749698.4368223345</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>2.90681818181821</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>-0.4962656232363685</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>0.0368686868686865</v>
-      </c>
-      <c r="BD9" t="inlineStr"/>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
@@ -2247,54 +2247,54 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
+        <v>-0.7857142857142858</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-1.285714285714286</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.3571428571428577</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.3809999999999999</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.8159999999999997</v>
+      </c>
+      <c r="X10" t="n">
         <v>5.642857142857146</v>
       </c>
-      <c r="S10" t="n">
+      <c r="Y10" t="n">
         <v>-5.642857142857146</v>
       </c>
-      <c r="T10" t="n">
-        <v>0.3809999999999999</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-0.8159999999999997</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.07142857142857145</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-0.5714285714285716</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.142857142857143</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>-1.214285714285714</v>
-      </c>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
+      <c r="Z10" t="n">
+        <v>-3.333333333333333</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-1.8</v>
+      </c>
       <c r="AB10" t="n">
         <v>-3.5</v>
       </c>
       <c r="AC10" t="n">
         <v>5.285714285714286</v>
       </c>
-      <c r="AD10" t="n">
-        <v>-0.3571428571428577</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>-2.5</v>
-      </c>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="n">
-        <v>-0.7857142857142858</v>
+        <v>0.07142857142857145</v>
       </c>
       <c r="AG10" t="n">
-        <v>-1.285714285714286</v>
+        <v>-0.5714285714285716</v>
       </c>
       <c r="AH10" t="n">
-        <v>-3.333333333333333</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.8</v>
+        <v>-1.214285714285714</v>
       </c>
       <c r="AJ10" t="n">
         <v>68.14090909090909</v>
@@ -2303,61 +2303,61 @@
         <v>66.93333333333334</v>
       </c>
       <c r="AL10" t="n">
+        <v>1.507395550007423</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-1.733044733044732</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-0.06822406257188884</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.567171717171675</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>3.170598845598846</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>2.882642728589019</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.856421356421365</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>760376.2857075199</v>
+      </c>
+      <c r="AT10" t="n">
         <v>-74</v>
       </c>
-      <c r="AM10" t="n">
-        <v>3.170598845598846</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>-1.733044733044732</v>
-      </c>
-      <c r="AO10" t="n">
+      <c r="AU10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-0.05454545454545445</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-1950000</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-66</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1667378.246753247</v>
+      </c>
+      <c r="BB10" t="n">
         <v>1.031940604744307</v>
       </c>
-      <c r="AP10" t="n">
-        <v>1.856421356421365</v>
-      </c>
-      <c r="AQ10" t="n">
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
         <v>-0.7562135820511777</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.507395550007423</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1667378.246753247</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>-0.06822406257188884</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>-1950000</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>-66</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>760376.2857075199</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0.567171717171675</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>2.882642728589019</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>-0.05454545454545445</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -2432,54 +2432,54 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
+        <v>0.1666666666666665</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.1666666666666665</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.166666666666666</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.7020000000000002</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.07399999999999984</v>
+      </c>
+      <c r="X11" t="n">
         <v>2.5</v>
       </c>
-      <c r="S11" t="n">
+      <c r="Y11" t="n">
         <v>-2.5</v>
       </c>
-      <c r="T11" t="n">
-        <v>0.7020000000000002</v>
-      </c>
-      <c r="U11" t="n">
-        <v>-0.07399999999999984</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.1666666666666666</v>
-      </c>
-      <c r="W11" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>-0.833333333333333</v>
-      </c>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
+      <c r="Z11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0.2000000000000002</v>
+      </c>
       <c r="AB11" t="n">
         <v>-1.5</v>
       </c>
       <c r="AC11" t="n">
         <v>-3.833333333333332</v>
       </c>
-      <c r="AD11" t="n">
-        <v>3.166666666666666</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>-3.5</v>
-      </c>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="n">
-        <v>0.1666666666666665</v>
+        <v>0.1666666666666666</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.1666666666666665</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="AH11" t="n">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.2000000000000002</v>
+        <v>-0.833333333333333</v>
       </c>
       <c r="AJ11" t="n">
         <v>67.4590909090909</v>
@@ -2488,61 +2488,61 @@
         <v>68.87239057239057</v>
       </c>
       <c r="AL11" t="n">
+        <v>-2.440674125125952</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.135206611570247</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-0.07760590540910872</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>3.854876033057849</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-0.588512396694199</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>2.443193316865049</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-0.8647107438016377</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-383308.3381888666</v>
+      </c>
+      <c r="AT11" t="n">
         <v>205</v>
       </c>
-      <c r="AM11" t="n">
-        <v>-0.588512396694199</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0.135206611570247</v>
-      </c>
-      <c r="AO11" t="n">
+      <c r="AU11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-0.05404958677685956</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>2125000</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>194</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>-472622.7272727271</v>
+      </c>
+      <c r="BB11" t="n">
         <v>2.314807860470381</v>
       </c>
-      <c r="AP11" t="n">
-        <v>-0.8647107438016377</v>
-      </c>
-      <c r="AQ11" t="n">
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
         <v>-2.505192864482446</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>-2.440674125125952</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>-472622.7272727271</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>-0.07760590540910872</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>2125000</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>194</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>-383308.3381888666</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>3.854876033057849</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>2.443193316865049</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>-0.05404958677685956</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>0</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -2617,54 +2617,54 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
+        <v>-0.2142857142857142</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T12" t="n">
+        <v>11.53571428571428</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-5.392857142857142</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.2225</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.02083333333333348</v>
+      </c>
+      <c r="X12" t="n">
         <v>11.03571428571428</v>
       </c>
-      <c r="S12" t="n">
+      <c r="Y12" t="n">
         <v>-11.03571428571428</v>
       </c>
-      <c r="T12" t="n">
-        <v>1.2225</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0.02083333333333348</v>
-      </c>
-      <c r="V12" t="n">
-        <v>-1.214285714285714</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0.9285714285714284</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.392857142857143</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>-1.464285714285714</v>
-      </c>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v>-0.666666666666667</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-1.5</v>
+      </c>
       <c r="AB12" t="n">
         <v>-2.071428571428571</v>
       </c>
       <c r="AC12" t="n">
         <v>-2.357142857142858</v>
       </c>
-      <c r="AD12" t="n">
-        <v>11.53571428571428</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>-5.392857142857142</v>
-      </c>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="n">
-        <v>-0.2142857142857142</v>
+        <v>-1.214285714285714</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.25</v>
+        <v>0.9285714285714284</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.666666666666667</v>
+        <v>2.392857142857143</v>
       </c>
       <c r="AI12" t="n">
-        <v>-1.5</v>
+        <v>-1.464285714285714</v>
       </c>
       <c r="AJ12" t="n">
         <v>67.826443001443</v>
@@ -2673,61 +2673,61 @@
         <v>68.34886363636363</v>
       </c>
       <c r="AL12" t="n">
+        <v>0.009777622723447621</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-0.2416528925619872</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-0.02425421197160338</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.7838016528925777</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>2.278016528925619</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.8869191051398531</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>3.291074380165284</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-56348.01347093843</v>
+      </c>
+      <c r="AT12" t="n">
         <v>286</v>
       </c>
-      <c r="AM12" t="n">
-        <v>2.278016528925619</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>-0.2416528925619872</v>
-      </c>
-      <c r="AO12" t="n">
+      <c r="AU12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.05785123966942152</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-4.800000000000001</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>2.400000000000006</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>12325000</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>279</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1366474.380165289</v>
+      </c>
+      <c r="BB12" t="n">
         <v>0.2800701513087915</v>
       </c>
-      <c r="AP12" t="n">
-        <v>3.291074380165284</v>
-      </c>
-      <c r="AQ12" t="n">
+      <c r="BC12" t="n">
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="BD12" t="n">
         <v>-1.647175696439238</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0.009777622723447621</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>-4.800000000000001</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1366474.380165289</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>-0.02425421197160338</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>12325000</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>279</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>2.400000000000006</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>-56348.01347093843</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0.7838016528925777</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0.8869191051398531</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0.05785123966942152</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>-0.6000000000000001</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -2802,54 +2802,54 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.2666666666666668</v>
+      </c>
+      <c r="T13" t="n">
+        <v>7.266666666666667</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.7549999999999999</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-1.794166666666666</v>
+      </c>
+      <c r="X13" t="n">
         <v>2.200000000000003</v>
       </c>
-      <c r="S13" t="n">
+      <c r="Y13" t="n">
         <v>-2.200000000000003</v>
       </c>
-      <c r="T13" t="n">
-        <v>0.7549999999999999</v>
-      </c>
-      <c r="U13" t="n">
-        <v>-1.794166666666666</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.3999999999999999</v>
-      </c>
-      <c r="W13" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.533333333333333</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>-1.866666666666667</v>
-      </c>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
+      <c r="Z13" t="n">
+        <v>1.416666666666667</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1</v>
+      </c>
       <c r="AB13" t="n">
         <v>-2.666666666666666</v>
       </c>
       <c r="AC13" t="n">
         <v>1.933333333333333</v>
       </c>
-      <c r="AD13" t="n">
-        <v>7.266666666666667</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>-9.4</v>
-      </c>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.2666666666666668</v>
+        <v>-0.4</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.416666666666667</v>
+        <v>2.533333333333333</v>
       </c>
       <c r="AI13" t="n">
-        <v>1</v>
+        <v>-1.866666666666667</v>
       </c>
       <c r="AJ13" t="n">
         <v>67.79050505050505</v>
@@ -2858,61 +2858,61 @@
         <v>69.42424242424242</v>
       </c>
       <c r="AL13" t="n">
+        <v>-4.450771461269383</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-1.377525252525249</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-0.08890100912159737</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-1.547727272727229</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.628282828282835</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-4.7376721554471</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0.2032828282828376</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-30191.94156434387</v>
+      </c>
+      <c r="AT13" t="n">
         <v>-144</v>
       </c>
-      <c r="AM13" t="n">
-        <v>1.628282828282835</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>-1.377525252525249</v>
-      </c>
-      <c r="AO13" t="n">
+      <c r="AU13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-0.09545454545454568</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-7650000</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-139</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>728231.060606061</v>
+      </c>
+      <c r="BB13" t="n">
         <v>0.01656441074203485</v>
       </c>
-      <c r="AP13" t="n">
-        <v>0.2032828282828376</v>
-      </c>
-      <c r="AQ13" t="n">
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
         <v>-0.9438040970289983</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>-4.450771461269383</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>728231.060606061</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>-0.08890100912159737</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>-7650000</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>-139</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>-30191.94156434387</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>-1.547727272727229</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>-4.7376721554471</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>-0.09545454545454568</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -2987,54 +2987,54 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.06666666666666665</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.1999999999999993</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-8.466666666666669</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.08166666666666678</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.5183333333333333</v>
+      </c>
+      <c r="X14" t="n">
         <v>-0.3999999999999986</v>
       </c>
-      <c r="S14" t="n">
+      <c r="Y14" t="n">
         <v>0.3999999999999986</v>
       </c>
-      <c r="T14" t="n">
-        <v>0.08166666666666678</v>
-      </c>
-      <c r="U14" t="n">
-        <v>-0.5183333333333333</v>
-      </c>
-      <c r="V14" t="n">
-        <v>-1.133333333333333</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.266666666666667</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
+      <c r="Z14" t="n">
+        <v>-0.4166666666666665</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
       <c r="AB14" t="n">
         <v>-2.066666666666666</v>
       </c>
       <c r="AC14" t="n">
         <v>1.133333333333335</v>
       </c>
-      <c r="AD14" t="n">
-        <v>0.1999999999999993</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>-8.466666666666669</v>
-      </c>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="n">
-        <v>-1.6</v>
+        <v>-1.133333333333333</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.06666666666666665</v>
+        <v>1.266666666666667</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.4166666666666665</v>
+        <v>-2</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0.3333333333333335</v>
+        <v>-1.8</v>
       </c>
       <c r="AJ14" t="n">
         <v>69.91797979797981</v>
@@ -3043,61 +3043,61 @@
         <v>66.59090909090908</v>
       </c>
       <c r="AL14" t="n">
+        <v>-1.641670340211519</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.180707070707072</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-0.01730930587337931</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-2.27555555555557</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.087070707070708</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0.02280751835671424</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.982020202020195</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1165322.2044186</v>
+      </c>
+      <c r="AT14" t="n">
         <v>-61</v>
       </c>
-      <c r="AM14" t="n">
-        <v>1.087070707070708</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.180707070707072</v>
-      </c>
-      <c r="AO14" t="n">
+      <c r="AU14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.1622222222222225</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>2.833333333333343</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-2660000</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-95</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>532786.8686868688</v>
+      </c>
+      <c r="BB14" t="n">
         <v>-0.751210450918677</v>
       </c>
-      <c r="AP14" t="n">
-        <v>1.982020202020195</v>
-      </c>
-      <c r="AQ14" t="n">
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
         <v>-1.282047355983284</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>-1.641670340211519</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>532786.8686868688</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>-0.01730930587337931</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>-2660000</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>-95</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>2.833333333333343</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1165322.2044186</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>-2.27555555555557</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>-0.02280751835671424</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>0.1622222222222225</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>0</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
@@ -3172,54 +3172,54 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4.949999999999999</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-2.699999999999999</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.3524999999999998</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.4099999999999999</v>
+      </c>
+      <c r="X15" t="n">
         <v>-0.6499999999999986</v>
       </c>
-      <c r="S15" t="n">
+      <c r="Y15" t="n">
         <v>0.6499999999999986</v>
       </c>
-      <c r="T15" t="n">
-        <v>0.3524999999999998</v>
-      </c>
-      <c r="U15" t="n">
-        <v>-0.4099999999999999</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.9500000000000002</v>
-      </c>
-      <c r="W15" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
+      <c r="Z15" t="n">
+        <v>-0.916666666666667</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.75</v>
+      </c>
       <c r="AB15" t="n">
         <v>1.1</v>
       </c>
       <c r="AC15" t="n">
         <v>1.1</v>
       </c>
-      <c r="AD15" t="n">
-        <v>4.949999999999999</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>-2.699999999999999</v>
-      </c>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="n">
-        <v>0.8</v>
+        <v>0.9500000000000002</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.45</v>
+        <v>-0.85</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0.916666666666667</v>
+        <v>3.15</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.75</v>
+        <v>0.25</v>
       </c>
       <c r="AJ15" t="n">
         <v>68.31272727272727</v>
@@ -3228,61 +3228,61 @@
         <v>68.5409090909091</v>
       </c>
       <c r="AL15" t="n">
+        <v>0.8899904743145726</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-2.955454545454547</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-0.06943696430101065</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-2.30545454545458</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>6.488181818181829</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>2.787371215927536</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>3.599999999999994</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>190353.8610155566</v>
+      </c>
+      <c r="AT15" t="n">
         <v>-137</v>
       </c>
-      <c r="AM15" t="n">
-        <v>6.488181818181829</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>-2.955454545454547</v>
-      </c>
-      <c r="AO15" t="n">
+      <c r="AU15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-0.07363636363636372</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-9.866666666666667</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-1.199999999999989</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-4175000</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>-172</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>852163.6363636365</v>
+      </c>
+      <c r="BB15" t="n">
         <v>2.321211952896533</v>
       </c>
-      <c r="AP15" t="n">
-        <v>3.599999999999994</v>
-      </c>
-      <c r="AQ15" t="n">
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
         <v>0.002499866273925733</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0.8899904743145726</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>-9.866666666666667</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>852163.6363636365</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>-0.06943696430101065</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>-4175000</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>-172</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>-1.199999999999989</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>190353.8610155566</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>-2.30545454545458</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>2.787371215927536</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>-0.07363636363636372</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>0</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>

--- a/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
@@ -515,84 +515,84 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal</t>
@@ -620,92 +620,92 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -786,25 +786,25 @@
         <v>0.5</v>
       </c>
       <c r="S2" t="n">
+        <v>2.666666666666666</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U2" t="n">
         <v>-0.8333333333333334</v>
       </c>
-      <c r="T2" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-7.333333333333334</v>
-      </c>
       <c r="V2" t="n">
-        <v>0.4173333333333333</v>
+        <v>3.333333333333336</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.6193333333333333</v>
+        <v>-3.333333333333336</v>
       </c>
       <c r="X2" t="n">
-        <v>3.333333333333336</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="Y2" t="n">
-        <v>-3.333333333333336</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="Z2" t="n">
         <v>0.3333333333333339</v>
@@ -813,22 +813,22 @@
         <v>-1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.666666666666666</v>
+        <v>-0.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.5</v>
+        <v>8.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.5</v>
+        <v>-7.333333333333334</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.166666666666667</v>
+        <v>0.4173333333333333</v>
       </c>
       <c r="AG2" t="n">
-        <v>-1.333333333333333</v>
+        <v>-0.6193333333333333</v>
       </c>
       <c r="AH2" t="n">
         <v>0.6666666666666665</v>
@@ -846,52 +846,52 @@
         <v>-0.0842319001685965</v>
       </c>
       <c r="AM2" t="n">
+        <v>0.1370435120435118</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.7264763014762963</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-1.135349536645123</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-15450000</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>0.3731085978061515</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>-109254.0965385477</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>-757832.5563325565</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="n">
+        <v>-229</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>-0.8809675693206387</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0.9790209790209587</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-2.060411810411836</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>-206</v>
+      </c>
+      <c r="BB2" t="n">
         <v>0.7532828282828241</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0.05693617135769502</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-2.060411810411836</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0.9790209790209587</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0.3731085978061515</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0.7264763014762963</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>-109254.0965385477</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>-229</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.1370435120435118</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="n">
-        <v>-15450000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-206</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>-757832.5563325565</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>-1.135349536645123</v>
       </c>
       <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="n">
-        <v>-0.8809675693206387</v>
+        <v>0.05693617135769502</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -966,28 +966,28 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
+        <v>3.666666666666666</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-2.833333333333334</v>
+      </c>
+      <c r="T3" t="n">
         <v>1.25</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>0.08333333333333326</v>
       </c>
-      <c r="T3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-7.083333333333334</v>
-      </c>
       <c r="V3" t="n">
-        <v>0.5779999999999998</v>
+        <v>7.25</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.9330000000000001</v>
+        <v>-7.25</v>
       </c>
       <c r="X3" t="n">
-        <v>7.25</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="Y3" t="n">
-        <v>-7.25</v>
+        <v>-0.8333333333333333</v>
       </c>
       <c r="Z3" t="n">
         <v>0.3999999999999999</v>
@@ -995,19 +995,19 @@
       <c r="AA3" t="n">
         <v>0.8499999999999996</v>
       </c>
-      <c r="AB3" t="n">
-        <v>3.666666666666666</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-2.833333333333334</v>
-      </c>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-7.083333333333334</v>
+      </c>
       <c r="AF3" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.5779999999999998</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.8333333333333333</v>
+        <v>-0.9330000000000001</v>
       </c>
       <c r="AH3" t="n">
         <v>1.083333333333333</v>
@@ -1025,58 +1025,58 @@
         <v>2.192552960420159</v>
       </c>
       <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.6612121212121167</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.979606226529341</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-525000</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-0.2282825099466947</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>550487.0562760041</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>96916.16161616147</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>2.01695216398743</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0.3835353535353505</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.439393939393966</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="BB3" t="n">
         <v>1.117676767676773</v>
       </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1.439393939393966</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0.3835353535353505</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-0.2282825099466947</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0.6612121212121167</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>550487.0562760041</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AX3" t="n">
+      <c r="BC3" t="n">
         <v>3</v>
       </c>
-      <c r="AY3" t="n">
-        <v>-525000</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>96916.16161616147</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.979606226529341</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
       <c r="BD3" t="n">
-        <v>2.01695216398743</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
@@ -1151,28 +1151,28 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-2.199999999999999</v>
+      </c>
+      <c r="T4" t="n">
         <v>0.3999999999999999</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="T4" t="n">
-        <v>4.600000000000001</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-6.800000000000001</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.03</v>
+        <v>10.8</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.58</v>
+        <v>-10.8</v>
       </c>
       <c r="X4" t="n">
-        <v>10.8</v>
+        <v>2.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>-10.8</v>
+        <v>-2</v>
       </c>
       <c r="Z4" t="n">
         <v>0.25</v>
@@ -1181,22 +1181,22 @@
         <v>1.25</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.6</v>
+        <v>-8</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.199999999999999</v>
+        <v>-16</v>
       </c>
       <c r="AD4" t="n">
-        <v>-8</v>
+        <v>4.600000000000001</v>
       </c>
       <c r="AE4" t="n">
-        <v>-16</v>
+        <v>-6.800000000000001</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.2</v>
+        <v>1.03</v>
       </c>
       <c r="AG4" t="n">
-        <v>-2</v>
+        <v>-1.58</v>
       </c>
       <c r="AH4" t="n">
         <v>4.199999999999999</v>
@@ -1214,58 +1214,58 @@
         <v>1.732702993162775</v>
       </c>
       <c r="AM4" t="n">
+        <v>0.3266299357208451</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>2.602387511478426</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-0.8689361731038048</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.287032299445116</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>365763.7921170387</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1706640.955004592</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>93</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.6431171330671468</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>2.296786042240583</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-0.4331496786042237</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>64</v>
+      </c>
+      <c r="BB4" t="n">
         <v>0.5262626262626142</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="BC4" t="n">
+        <v>-2.166666666666657</v>
+      </c>
+      <c r="BD4" t="n">
         <v>0.01154401154401152</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>-0.4331496786042237</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>2.296786042240583</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>2.287032299445116</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>2.602387511478426</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>365763.7921170387</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>157</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.3266299357208451</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>-4.666666666666657</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>128</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1706640.955004592</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>-0.8689361731038048</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0.6431171330671468</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -1336,28 +1336,28 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T5" t="n">
         <v>1</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>-1.25</v>
       </c>
-      <c r="T5" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-8.25</v>
-      </c>
       <c r="V5" t="n">
-        <v>1.016666666666666</v>
+        <v>13.25</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.228333333333333</v>
+        <v>-13.25</v>
       </c>
       <c r="X5" t="n">
-        <v>13.25</v>
+        <v>1.25</v>
       </c>
       <c r="Y5" t="n">
-        <v>-13.25</v>
+        <v>-1</v>
       </c>
       <c r="Z5" t="n">
         <v>-0.1666666666666665</v>
@@ -1365,19 +1365,19 @@
       <c r="AA5" t="n">
         <v>-0.1666666666666665</v>
       </c>
-      <c r="AB5" t="n">
-        <v>-4.25</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-8.25</v>
+      </c>
       <c r="AF5" t="n">
-        <v>1.25</v>
+        <v>1.016666666666666</v>
       </c>
       <c r="AG5" t="n">
-        <v>-1</v>
+        <v>-1.228333333333333</v>
       </c>
       <c r="AH5" t="n">
         <v>2.75</v>
@@ -1395,58 +1395,58 @@
         <v>-3.844034424878735</v>
       </c>
       <c r="AM5" t="n">
+        <v>-0.01818181818181808</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0.004141414141415112</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-1.907425065511973</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1240000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-2.270556856471174</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-484968.2158682763</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>426972.2222222225</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-0.8062073696408696</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-0.4399999999999977</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.7657575757575614</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BB5" t="n">
         <v>0.298787878787877</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="BC5" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="BD5" t="n">
         <v>-0.0935099111414901</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0.7657575757575614</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-0.4399999999999977</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-2.270556856471174</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>-0.004141414141415112</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>-484968.2158682763</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-0.01818181818181808</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1240000</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>426972.2222222225</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>-1.907425065511973</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>-0.8062073696408696</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -1521,28 +1521,28 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.09999999999999964</v>
+      </c>
+      <c r="T6" t="n">
         <v>2.65</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>-0.2</v>
       </c>
-      <c r="T6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-4.5</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.0445</v>
+        <v>4.350000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.2875000000000001</v>
+        <v>-4.350000000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>4.350000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>-4.350000000000001</v>
+        <v>-1.8</v>
       </c>
       <c r="Z6" t="n">
         <v>0.75</v>
@@ -1550,19 +1550,19 @@
       <c r="AA6" t="n">
         <v>0.5</v>
       </c>
-      <c r="AB6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-0.09999999999999964</v>
-      </c>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-4.5</v>
+      </c>
       <c r="AF6" t="n">
-        <v>2.4</v>
+        <v>1.0445</v>
       </c>
       <c r="AG6" t="n">
-        <v>-1.8</v>
+        <v>-0.2875000000000001</v>
       </c>
       <c r="AH6" t="n">
         <v>4.1</v>
@@ -1580,58 +1580,58 @@
         <v>-0.7248012897033504</v>
       </c>
       <c r="AM6" t="n">
+        <v>-0.04222222222222216</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-4.911331496786048</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.003418932878077</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-0.3235549889865723</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-184865.2815633246</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-1944304.178145088</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>208</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.003045009351396</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-2.117061524334261</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-0.04542699724518684</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>192</v>
+      </c>
+      <c r="BB6" t="n">
         <v>-2.124214876033058</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="BC6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD6" t="n">
         <v>-0.0306771911663215</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>-0.04542699724518684</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>-2.117061524334261</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>-0.3235549889865723</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>-4.911331496786048</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>-184865.2815633246</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>208</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>-0.04222222222222216</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>192</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>-1944304.178145088</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.003418932878077</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>1.003045009351396</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -1709,25 +1709,25 @@
         <v>1.4</v>
       </c>
       <c r="S7" t="n">
+        <v>-0.1999999999999993</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U7" t="n">
         <v>-0.8</v>
       </c>
-      <c r="T7" t="n">
-        <v>6.600000000000001</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-8.600000000000001</v>
-      </c>
       <c r="V7" t="n">
-        <v>0.5115000000000001</v>
+        <v>-5.200000000000003</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.2215</v>
+        <v>5.200000000000003</v>
       </c>
       <c r="X7" t="n">
-        <v>-5.200000000000003</v>
+        <v>1.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.200000000000003</v>
+        <v>-1.8</v>
       </c>
       <c r="Z7" t="n">
         <v>0.1499999999999999</v>
@@ -1735,19 +1735,19 @@
       <c r="AA7" t="n">
         <v>0.5999999999999996</v>
       </c>
-      <c r="AB7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-0.1999999999999993</v>
-      </c>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="n">
+        <v>6.600000000000001</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-8.600000000000001</v>
+      </c>
       <c r="AF7" t="n">
-        <v>1.8</v>
+        <v>0.5115000000000001</v>
       </c>
       <c r="AG7" t="n">
-        <v>-1.8</v>
+        <v>-1.2215</v>
       </c>
       <c r="AH7" t="n">
         <v>3.6</v>
@@ -1765,58 +1765,58 @@
         <v>-1.104131745410186</v>
       </c>
       <c r="AM7" t="n">
+        <v>-0.1054545454545455</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-1.952727272727273</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-0.8621562542914489</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>17950000</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.815060032472886</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>84859.6771782008</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-1039872.727272728</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>74</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-3.502215123272801</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.124545454545455</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>2.030000000000001</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>68</v>
+      </c>
+      <c r="BB7" t="n">
         <v>-1.863636363636363</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="BC7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD7" t="n">
         <v>-0.2947686030934114</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>2.030000000000001</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.124545454545455</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>2.815060032472886</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>-1.952727272727273</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>84859.6771782008</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>74</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>-0.1054545454545455</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>17950000</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>68</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>-1039872.727272728</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>-0.8621562542914489</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>-3.502215123272801</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -1891,28 +1891,28 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
+        <v>-0.5999999999999996</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-2.199999999999999</v>
+      </c>
+      <c r="T8" t="n">
         <v>0.3</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>-0.25</v>
       </c>
-      <c r="T8" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-6.199999999999999</v>
-      </c>
       <c r="V8" t="n">
-        <v>0.2593333333333332</v>
+        <v>5.950000000000003</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.7086666666666667</v>
+        <v>-5.950000000000003</v>
       </c>
       <c r="X8" t="n">
-        <v>5.950000000000003</v>
+        <v>-0.6499999999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>-5.950000000000003</v>
+        <v>0.25</v>
       </c>
       <c r="Z8" t="n">
         <v>0.25</v>
@@ -1920,19 +1920,19 @@
       <c r="AA8" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AB8" t="n">
-        <v>-0.5999999999999996</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-2.199999999999999</v>
-      </c>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-6.199999999999999</v>
+      </c>
       <c r="AF8" t="n">
-        <v>-0.6499999999999999</v>
+        <v>0.2593333333333332</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.25</v>
+        <v>-0.7086666666666667</v>
       </c>
       <c r="AH8" t="n">
         <v>0.25</v>
@@ -1950,58 +1950,58 @@
         <v>2.71180243292519</v>
       </c>
       <c r="AM8" t="n">
+        <v>0.1636363636363638</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>3.15970819304151</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2.131452263226976</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>5675000</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>-4.935305472327045</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>-262377.6618656204</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1470414.562289563</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>346</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>6.045468885853413</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-1.412991021324345</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>2.505050505050519</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>334</v>
+      </c>
+      <c r="BB8" t="n">
         <v>5.129040404040403</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="BC8" t="n">
+        <v>-5.666666666666657</v>
+      </c>
+      <c r="BD8" t="n">
         <v>0.05126811594202896</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>2.505050505050519</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>-1.412991021324345</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>-4.935305472327045</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>3.15970819304151</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>-262377.6618656204</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>346</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0.1636363636363638</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>-5.666666666666657</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>5675000</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>334</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1470414.562289563</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>2.131452263226976</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>6.045468885853413</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -2068,28 +2068,28 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
+        <v>3.333333333333334</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.9000000000000004</v>
+      </c>
+      <c r="T9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>1.1</v>
       </c>
-      <c r="T9" t="n">
-        <v>5.766666666666667</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-3.966666666666667</v>
-      </c>
       <c r="V9" t="n">
-        <v>0.165</v>
+        <v>1.200000000000003</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.0525000000000001</v>
+        <v>-1.200000000000003</v>
       </c>
       <c r="X9" t="n">
-        <v>1.200000000000003</v>
+        <v>-1.033333333333333</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.200000000000003</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="Z9" t="n">
         <v>-2.2</v>
@@ -2097,19 +2097,19 @@
       <c r="AA9" t="n">
         <v>0.7999999999999998</v>
       </c>
-      <c r="AB9" t="n">
-        <v>3.333333333333334</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0.9000000000000004</v>
-      </c>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="n">
+        <v>5.766666666666667</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-3.966666666666667</v>
+      </c>
       <c r="AF9" t="n">
-        <v>-1.033333333333333</v>
+        <v>0.165</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.166666666666667</v>
+        <v>-0.0525000000000001</v>
       </c>
       <c r="AH9" t="n">
         <v>1.933333333333333</v>
@@ -2127,52 +2127,52 @@
         <v>-0.8646347583700305</v>
       </c>
       <c r="AM9" t="n">
+        <v>0.0368686868686865</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.7770833333333371</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2.629907805276702</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-8600000</v>
+      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="n">
+        <v>-0.4962656232363685</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>-749698.4368223345</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>-1412476.957070707</v>
+      </c>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="n">
+        <v>-292</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-1.665747722029273</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-0.5128787878787762</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>2.90681818181821</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>-279</v>
+      </c>
+      <c r="BB9" t="n">
         <v>-0.4830176767676804</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>-0.04063644688644685</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>2.90681818181821</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>-0.5128787878787762</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>-0.4962656232363685</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0.7770833333333371</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>-749698.4368223345</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>-380</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0.0368686868686865</v>
-      </c>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="n">
-        <v>-56100000</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>-359</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>-1412476.957070707</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>2.629907805276702</v>
       </c>
       <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="n">
-        <v>-1.665747722029273</v>
+        <v>-0.04063644688644685</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
@@ -2247,28 +2247,28 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5.285714285714286</v>
+      </c>
+      <c r="T10" t="n">
         <v>-0.7857142857142858</v>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>-1.285714285714286</v>
       </c>
-      <c r="T10" t="n">
-        <v>-0.3571428571428577</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-2.5</v>
-      </c>
       <c r="V10" t="n">
-        <v>0.3809999999999999</v>
+        <v>5.642857142857146</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.8159999999999997</v>
+        <v>-5.642857142857146</v>
       </c>
       <c r="X10" t="n">
-        <v>5.642857142857146</v>
+        <v>0.07142857142857145</v>
       </c>
       <c r="Y10" t="n">
-        <v>-5.642857142857146</v>
+        <v>-0.5714285714285716</v>
       </c>
       <c r="Z10" t="n">
         <v>-3.333333333333333</v>
@@ -2276,19 +2276,19 @@
       <c r="AA10" t="n">
         <v>-1.8</v>
       </c>
-      <c r="AB10" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>5.285714285714286</v>
-      </c>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="n">
+        <v>-0.3571428571428577</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-2.5</v>
+      </c>
       <c r="AF10" t="n">
-        <v>0.07142857142857145</v>
+        <v>0.3809999999999999</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.5714285714285716</v>
+        <v>-0.8159999999999997</v>
       </c>
       <c r="AH10" t="n">
         <v>1.142857142857143</v>
@@ -2306,58 +2306,58 @@
         <v>1.507395550007423</v>
       </c>
       <c r="AM10" t="n">
+        <v>-0.05454545454545445</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1.856421356421365</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.031940604744307</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-1950000</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.882642728589019</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>760376.2857075199</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1667378.246753247</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-74</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-0.7562135820511777</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3.170598845598846</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.567171717171675</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>-66</v>
+      </c>
+      <c r="BB10" t="n">
         <v>-1.733044733044732</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="BC10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD10" t="n">
         <v>-0.06822406257188884</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0.567171717171675</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>3.170598845598846</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>2.882642728589019</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.856421356421365</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>760376.2857075199</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>-74</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>-0.05454545454545445</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>-1950000</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>-66</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1667378.246753247</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.031940604744307</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>-0.7562135820511777</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -2432,28 +2432,28 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-3.833333333333332</v>
+      </c>
+      <c r="T11" t="n">
         <v>0.1666666666666665</v>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>0.1666666666666665</v>
       </c>
-      <c r="T11" t="n">
-        <v>3.166666666666666</v>
-      </c>
-      <c r="U11" t="n">
-        <v>-3.5</v>
-      </c>
       <c r="V11" t="n">
-        <v>0.7020000000000002</v>
+        <v>2.5</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.07399999999999984</v>
+        <v>-2.5</v>
       </c>
       <c r="X11" t="n">
-        <v>2.5</v>
+        <v>0.1666666666666666</v>
       </c>
       <c r="Y11" t="n">
-        <v>-2.5</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="Z11" t="n">
         <v>-1</v>
@@ -2461,19 +2461,19 @@
       <c r="AA11" t="n">
         <v>-0.2000000000000002</v>
       </c>
-      <c r="AB11" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>-3.833333333333332</v>
-      </c>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="n">
+        <v>3.166666666666666</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-3.5</v>
+      </c>
       <c r="AF11" t="n">
-        <v>0.1666666666666666</v>
+        <v>0.7020000000000002</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.07399999999999984</v>
       </c>
       <c r="AH11" t="n">
         <v>0.5</v>
@@ -2491,58 +2491,58 @@
         <v>-2.440674125125952</v>
       </c>
       <c r="AM11" t="n">
+        <v>-0.05404958677685956</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-0.8647107438016377</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2.314807860470381</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>2125000</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.443193316865049</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>-383308.3381888666</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-472622.7272727271</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>205</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-2.505192864482446</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>-0.588512396694199</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>3.854876033057849</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>194</v>
+      </c>
+      <c r="BB11" t="n">
         <v>0.135206611570247</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="BC11" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="BD11" t="n">
         <v>-0.07760590540910872</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>3.854876033057849</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>-0.588512396694199</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>2.443193316865049</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>-0.8647107438016377</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>-383308.3381888666</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>205</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>-0.05404958677685956</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>2125000</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>194</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>-472622.7272727271</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>2.314807860470381</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>-2.505192864482446</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -2617,28 +2617,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
+        <v>-2.071428571428571</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-2.357142857142858</v>
+      </c>
+      <c r="T12" t="n">
         <v>-0.2142857142857142</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.25</v>
       </c>
-      <c r="T12" t="n">
-        <v>11.53571428571428</v>
-      </c>
-      <c r="U12" t="n">
-        <v>-5.392857142857142</v>
-      </c>
       <c r="V12" t="n">
-        <v>1.2225</v>
+        <v>11.03571428571428</v>
       </c>
       <c r="W12" t="n">
-        <v>0.02083333333333348</v>
+        <v>-11.03571428571428</v>
       </c>
       <c r="X12" t="n">
-        <v>11.03571428571428</v>
+        <v>-1.214285714285714</v>
       </c>
       <c r="Y12" t="n">
-        <v>-11.03571428571428</v>
+        <v>0.9285714285714284</v>
       </c>
       <c r="Z12" t="n">
         <v>-0.666666666666667</v>
@@ -2646,19 +2646,19 @@
       <c r="AA12" t="n">
         <v>-1.5</v>
       </c>
-      <c r="AB12" t="n">
-        <v>-2.071428571428571</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>-2.357142857142858</v>
-      </c>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>11.53571428571428</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-5.392857142857142</v>
+      </c>
       <c r="AF12" t="n">
-        <v>-1.214285714285714</v>
+        <v>1.2225</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.9285714285714284</v>
+        <v>0.02083333333333348</v>
       </c>
       <c r="AH12" t="n">
         <v>2.392857142857143</v>
@@ -2676,58 +2676,58 @@
         <v>0.009777622723447621</v>
       </c>
       <c r="AM12" t="n">
+        <v>0.05785123966942152</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>3.291074380165284</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.2800701513087915</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>15025000</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0.8869191051398531</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-56348.01347093843</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1366474.380165289</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-5.199999999999999</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>292</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-1.647175696439238</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>2.278016528925619</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.7838016528925777</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>285</v>
+      </c>
+      <c r="BB12" t="n">
         <v>-0.2416528925619872</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
         <v>-0.02425421197160338</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0.7838016528925777</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>2.278016528925619</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0.8869191051398531</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>3.291074380165284</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>-56348.01347093843</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>286</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0.05785123966942152</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>-4.800000000000001</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>2.400000000000006</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>12325000</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>279</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>1366474.380165289</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0.2800701513087915</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>-0.6000000000000001</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>-1.647175696439238</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -2802,28 +2802,28 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.933333333333333</v>
+      </c>
+      <c r="T13" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>-0.2666666666666668</v>
       </c>
-      <c r="T13" t="n">
-        <v>7.266666666666667</v>
-      </c>
-      <c r="U13" t="n">
-        <v>-9.4</v>
-      </c>
       <c r="V13" t="n">
-        <v>0.7549999999999999</v>
+        <v>2.200000000000003</v>
       </c>
       <c r="W13" t="n">
-        <v>-1.794166666666666</v>
+        <v>-2.200000000000003</v>
       </c>
       <c r="X13" t="n">
-        <v>2.200000000000003</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="Y13" t="n">
-        <v>-2.200000000000003</v>
+        <v>-0.4</v>
       </c>
       <c r="Z13" t="n">
         <v>1.416666666666667</v>
@@ -2831,19 +2831,19 @@
       <c r="AA13" t="n">
         <v>1</v>
       </c>
-      <c r="AB13" t="n">
-        <v>-2.666666666666666</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.933333333333333</v>
-      </c>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="n">
+        <v>7.266666666666667</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-9.4</v>
+      </c>
       <c r="AF13" t="n">
-        <v>0.3999999999999999</v>
+        <v>0.7549999999999999</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.4</v>
+        <v>-1.794166666666666</v>
       </c>
       <c r="AH13" t="n">
         <v>2.533333333333333</v>
@@ -2861,58 +2861,58 @@
         <v>-4.450771461269383</v>
       </c>
       <c r="AM13" t="n">
+        <v>-0.09545454545454568</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.2032828282828376</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.01656441074203485</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-7650000</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-4.7376721554471</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-30191.94156434387</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>728231.060606061</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-144</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-0.9438040970289983</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.628282828282835</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-1.547727272727229</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-139</v>
+      </c>
+      <c r="BB13" t="n">
         <v>-1.377525252525249</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="BC13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD13" t="n">
         <v>-0.08890100912159737</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>-1.547727272727229</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.628282828282835</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>-4.7376721554471</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0.2032828282828376</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>-30191.94156434387</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>-144</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>-0.09545454545454568</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>-7650000</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>-139</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>728231.060606061</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0.01656441074203485</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>-0.9438040970289983</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -2987,28 +2987,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
+        <v>-2.066666666666666</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.133333333333335</v>
+      </c>
+      <c r="T14" t="n">
         <v>-1.6</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>-0.06666666666666665</v>
       </c>
-      <c r="T14" t="n">
-        <v>0.1999999999999993</v>
-      </c>
-      <c r="U14" t="n">
-        <v>-8.466666666666669</v>
-      </c>
       <c r="V14" t="n">
-        <v>0.08166666666666678</v>
+        <v>-0.3999999999999986</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.5183333333333333</v>
+        <v>0.3999999999999986</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.3999999999999986</v>
+        <v>-1.133333333333333</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.3999999999999986</v>
+        <v>1.266666666666667</v>
       </c>
       <c r="Z14" t="n">
         <v>-0.4166666666666665</v>
@@ -3016,19 +3016,19 @@
       <c r="AA14" t="n">
         <v>-0.3333333333333335</v>
       </c>
-      <c r="AB14" t="n">
-        <v>-2.066666666666666</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.133333333333335</v>
-      </c>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="n">
+        <v>0.1999999999999993</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-8.466666666666669</v>
+      </c>
       <c r="AF14" t="n">
-        <v>-1.133333333333333</v>
+        <v>0.08166666666666678</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.266666666666667</v>
+        <v>-0.5183333333333333</v>
       </c>
       <c r="AH14" t="n">
         <v>-2</v>
@@ -3046,58 +3046,58 @@
         <v>-1.641670340211519</v>
       </c>
       <c r="AM14" t="n">
+        <v>0.1622222222222225</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.982020202020195</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-0.751210450918677</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-2660000</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-0.02280751835671424</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1165322.2044186</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>532786.8686868688</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>-61</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-1.282047355983284</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.087070707070708</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-2.27555555555557</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-95</v>
+      </c>
+      <c r="BB14" t="n">
         <v>1.180707070707072</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="BC14" t="n">
+        <v>2.833333333333343</v>
+      </c>
+      <c r="BD14" t="n">
         <v>-0.01730930587337931</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>-2.27555555555557</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.087070707070708</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>-0.02280751835671424</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.982020202020195</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1165322.2044186</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>-61</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0.1622222222222225</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>2.833333333333343</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>-2660000</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>-95</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>532786.8686868688</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>-0.751210450918677</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>-1.282047355983284</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
@@ -3172,28 +3172,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="T15" t="n">
         <v>0.8</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>-0.45</v>
       </c>
-      <c r="T15" t="n">
-        <v>4.949999999999999</v>
-      </c>
-      <c r="U15" t="n">
-        <v>-2.699999999999999</v>
-      </c>
       <c r="V15" t="n">
-        <v>0.3524999999999998</v>
+        <v>-0.6499999999999986</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.4099999999999999</v>
+        <v>0.6499999999999986</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6499999999999986</v>
+        <v>0.9500000000000002</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.6499999999999986</v>
+        <v>-0.85</v>
       </c>
       <c r="Z15" t="n">
         <v>-0.916666666666667</v>
@@ -3201,19 +3201,19 @@
       <c r="AA15" t="n">
         <v>-0.75</v>
       </c>
-      <c r="AB15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="n">
+        <v>4.949999999999999</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-2.699999999999999</v>
+      </c>
       <c r="AF15" t="n">
-        <v>0.9500000000000002</v>
+        <v>0.3524999999999998</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.85</v>
+        <v>-0.4099999999999999</v>
       </c>
       <c r="AH15" t="n">
         <v>3.15</v>
@@ -3231,58 +3231,58 @@
         <v>0.8899904743145726</v>
       </c>
       <c r="AM15" t="n">
+        <v>-0.07363636363636372</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>3.599999999999994</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>2.321211952896533</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-4175000</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.787371215927536</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>190353.8610155566</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>852163.6363636365</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-9.866666666666667</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-137</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.002499866273925733</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>6.488181818181829</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>-2.30545454545458</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-172</v>
+      </c>
+      <c r="BB15" t="n">
         <v>-2.955454545454547</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="BC15" t="n">
+        <v>-1.199999999999989</v>
+      </c>
+      <c r="BD15" t="n">
         <v>-0.06943696430101065</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>-2.30545454545458</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>6.488181818181829</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>2.787371215927536</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>3.599999999999994</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>190353.8610155566</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>-137</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>-0.07363636363636372</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>-9.866666666666667</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>-1.199999999999989</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>-4175000</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>-172</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>852163.6363636365</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>2.321211952896533</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>0.002499866273925733</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>

--- a/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
@@ -515,94 +515,94 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -615,97 +615,97 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -783,58 +783,58 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-4.833333333333332</v>
+      </c>
+      <c r="T2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-7.333333333333334</v>
+      </c>
+      <c r="V2" t="n">
         <v>0.5</v>
       </c>
-      <c r="S2" t="n">
+      <c r="W2" t="n">
         <v>2.666666666666666</v>
       </c>
-      <c r="T2" t="n">
+      <c r="X2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.3333333333333339</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.4173333333333333</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-0.6193333333333333</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>3.333333333333336</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-3.333333333333336</v>
+      </c>
+      <c r="AH2" t="n">
         <v>0.5</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AI2" t="n">
         <v>-0.8333333333333334</v>
-      </c>
-      <c r="V2" t="n">
-        <v>3.333333333333336</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-3.333333333333336</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.3333333333333339</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-7.333333333333334</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.4173333333333333</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-0.6193333333333333</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0.6666666666666665</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-4.833333333333332</v>
       </c>
       <c r="AJ2" t="n">
         <v>67.39545454545454</v>
@@ -843,55 +843,55 @@
         <v>68.14565656565655</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.0842319001685965</v>
-      </c>
-      <c r="AM2" t="n">
+        <v>-109254.0965385477</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="n">
+        <v>-1.135349536645123</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.7532828282828241</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.7264763014762963</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-206</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-15450000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.05693617135769502</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>-229</v>
+      </c>
+      <c r="AU2" t="n">
         <v>0.1370435120435118</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0.7264763014762963</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-1.135349536645123</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-15450000</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="n">
-        <v>0.3731085978061515</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>-109254.0965385477</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>-757832.5563325565</v>
       </c>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="n">
-        <v>-229</v>
+        <v>-757832.5563325565</v>
       </c>
       <c r="AX2" t="n">
+        <v>0.3731085978061515</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-0.0842319001685965</v>
+      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="n">
+        <v>0.9790209790209587</v>
+      </c>
+      <c r="BC2" t="n">
         <v>-0.8809675693206387</v>
       </c>
-      <c r="AY2" t="n">
-        <v>0.9790209790209587</v>
-      </c>
-      <c r="AZ2" t="n">
+      <c r="BD2" t="n">
         <v>-2.060411810411836</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>-206</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0.7532828282828241</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="n">
-        <v>0.05693617135769502</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -966,54 +966,54 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-7.083333333333334</v>
+      </c>
+      <c r="V3" t="n">
         <v>3.666666666666666</v>
       </c>
-      <c r="S3" t="n">
+      <c r="W3" t="n">
         <v>-2.833333333333334</v>
       </c>
-      <c r="T3" t="n">
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-0.8333333333333333</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.8499999999999996</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.5779999999999998</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-0.9330000000000001</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-7.25</v>
+      </c>
+      <c r="AH3" t="n">
         <v>1.25</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AI3" t="n">
         <v>0.08333333333333326</v>
-      </c>
-      <c r="V3" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-7.25</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-0.8333333333333333</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.3999999999999999</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.8499999999999996</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-7.083333333333334</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.5779999999999998</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-0.9330000000000001</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.083333333333333</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-2.333333333333333</v>
       </c>
       <c r="AJ3" t="n">
         <v>70.03282828282829</v>
@@ -1022,61 +1022,61 @@
         <v>68.10151515151516</v>
       </c>
       <c r="AL3" t="n">
+        <v>550487.0562760041</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.979606226529341</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1.117676767676773</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.6612121212121167</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-525000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>96916.16161616147</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-0.2282825099466947</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>2.192552960420159</v>
       </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0.6612121212121167</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.979606226529341</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-525000</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>-0.2282825099466947</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>550487.0562760041</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>96916.16161616147</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AX3" t="n">
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0.3835353535353505</v>
+      </c>
+      <c r="BC3" t="n">
         <v>2.01695216398743</v>
       </c>
-      <c r="AY3" t="n">
-        <v>0.3835353535353505</v>
-      </c>
-      <c r="AZ3" t="n">
+      <c r="BD3" t="n">
         <v>1.439393939393966</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.117676767676773</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
@@ -1151,58 +1151,58 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
+        <v>4.199999999999999</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4.600000000000001</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-6.800000000000001</v>
+      </c>
+      <c r="V4" t="n">
         <v>2.6</v>
       </c>
-      <c r="S4" t="n">
+      <c r="W4" t="n">
         <v>-2.199999999999999</v>
       </c>
-      <c r="T4" t="n">
+      <c r="X4" t="n">
+        <v>-8</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-16</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-10.8</v>
+      </c>
+      <c r="AH4" t="n">
         <v>0.3999999999999999</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AI4" t="n">
         <v>-2.8</v>
-      </c>
-      <c r="V4" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-10.8</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-16</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>4.600000000000001</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-6.800000000000001</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-1.58</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>4.199999999999999</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-3.2</v>
       </c>
       <c r="AJ4" t="n">
         <v>69.02727272727273</v>
@@ -1211,61 +1211,61 @@
         <v>67.45454545454547</v>
       </c>
       <c r="AL4" t="n">
+        <v>365763.7921170387</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-0.8689361731038048</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.5262626262626142</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>2.602387511478426</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>63</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.01154401154401152</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.3266299357208451</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.3333333333333428</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1706640.955004592</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>2.287032299445116</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>1.732702993162775</v>
       </c>
-      <c r="AM4" t="n">
-        <v>0.3266299357208451</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>2.602387511478426</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>-0.8689361731038048</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>3800000</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.287032299445116</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>365763.7921170387</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1706640.955004592</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>93</v>
-      </c>
-      <c r="AX4" t="n">
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>2.296786042240583</v>
+      </c>
+      <c r="BC4" t="n">
         <v>0.6431171330671468</v>
       </c>
-      <c r="AY4" t="n">
-        <v>2.296786042240583</v>
-      </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
         <v>-0.4331496786042237</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>64</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0.5262626262626142</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>-2.166666666666657</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0.01154401154401152</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -1336,54 +1336,54 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S5" t="n">
         <v>-4.25</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-8.25</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="W5" t="n">
         <v>2.25</v>
       </c>
-      <c r="T5" t="n">
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0.1666666666666665</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0.1666666666666665</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.016666666666666</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-1.228333333333333</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-13.25</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
+      <c r="AI5" t="n">
         <v>-1.25</v>
-      </c>
-      <c r="V5" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-13.25</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-0.1666666666666665</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-0.1666666666666665</v>
-      </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-8.25</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.016666666666666</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-1.228333333333333</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-4.25</v>
       </c>
       <c r="AJ5" t="n">
         <v>67.7590909090909</v>
@@ -1392,61 +1392,61 @@
         <v>66.84595959595958</v>
       </c>
       <c r="AL5" t="n">
+        <v>-484968.2158682763</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-1.907425065511973</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.298787878787877</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-0.004141414141415112</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1240000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-0.0935099111414901</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-0.01818181818181808</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>426972.2222222225</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-2.270556856471174</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>-3.844034424878735</v>
       </c>
-      <c r="AM5" t="n">
-        <v>-0.01818181818181808</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>-0.004141414141415112</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-1.907425065511973</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1240000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>-2.270556856471174</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>-484968.2158682763</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>426972.2222222225</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX5" t="n">
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-0.4399999999999977</v>
+      </c>
+      <c r="BC5" t="n">
         <v>-0.8062073696408696</v>
       </c>
-      <c r="AY5" t="n">
-        <v>-0.4399999999999977</v>
-      </c>
-      <c r="AZ5" t="n">
+      <c r="BD5" t="n">
         <v>0.7657575757575614</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0.298787878787877</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>-0.0935099111414901</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -1521,54 +1521,54 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.3499999999999996</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="V6" t="n">
         <v>3.9</v>
       </c>
-      <c r="S6" t="n">
+      <c r="W6" t="n">
         <v>-0.09999999999999964</v>
       </c>
-      <c r="T6" t="n">
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.0445</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-0.2875000000000001</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>4.350000000000001</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-4.350000000000001</v>
+      </c>
+      <c r="AH6" t="n">
         <v>2.65</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AI6" t="n">
         <v>-0.2</v>
-      </c>
-      <c r="V6" t="n">
-        <v>4.350000000000001</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-4.350000000000001</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.0445</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>-0.2875000000000001</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>-0.3499999999999996</v>
       </c>
       <c r="AJ6" t="n">
         <v>66.60606060606061</v>
@@ -1577,61 +1577,61 @@
         <v>67.58181818181818</v>
       </c>
       <c r="AL6" t="n">
+        <v>-184865.2815633246</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.003418932878077</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-2.124214876033058</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-4.911331496786048</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>192</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-0.0306771911663215</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>208</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-0.04222222222222216</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-1944304.178145088</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0.3235549889865723</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>-0.7248012897033504</v>
       </c>
-      <c r="AM6" t="n">
-        <v>-0.04222222222222216</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>-4.911331496786048</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.003418932878077</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>-0.3235549889865723</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>-184865.2815633246</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>-1944304.178145088</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>208</v>
-      </c>
-      <c r="AX6" t="n">
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-2.117061524334261</v>
+      </c>
+      <c r="BC6" t="n">
         <v>1.003045009351396</v>
       </c>
-      <c r="AY6" t="n">
-        <v>-2.117061524334261</v>
-      </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
         <v>-0.04542699724518684</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>192</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>-2.124214876033058</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>-0.0306771911663215</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -1706,54 +1706,54 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>6.600000000000001</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-8.600000000000001</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.4</v>
       </c>
-      <c r="S7" t="n">
+      <c r="W7" t="n">
         <v>-0.1999999999999993</v>
       </c>
-      <c r="T7" t="n">
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.1499999999999999</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.5999999999999996</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.5115000000000001</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-1.2215</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-5.200000000000003</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>5.200000000000003</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1.4</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AI7" t="n">
         <v>-0.8</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-5.200000000000003</v>
-      </c>
-      <c r="W7" t="n">
-        <v>5.200000000000003</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.1499999999999999</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.5999999999999996</v>
-      </c>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="n">
-        <v>6.600000000000001</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-8.600000000000001</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0.5115000000000001</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>-1.2215</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>-3.4</v>
       </c>
       <c r="AJ7" t="n">
         <v>67.93818181818182</v>
@@ -1762,61 +1762,61 @@
         <v>68.78909090909092</v>
       </c>
       <c r="AL7" t="n">
+        <v>84859.6771782008</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-0.8621562542914489</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-1.863636363636363</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-1.952727272727273</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>68</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>17950000</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>-0.2947686030934114</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>74</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-0.1054545454545455</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-1039872.727272728</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>2.815060032472886</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>-1.104131745410186</v>
       </c>
-      <c r="AM7" t="n">
-        <v>-0.1054545454545455</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>-1.952727272727273</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>-0.8621562542914489</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>17950000</v>
-      </c>
-      <c r="AR7" t="n">
+      <c r="BA7" t="n">
         <v>0.5</v>
       </c>
-      <c r="AS7" t="n">
-        <v>2.815060032472886</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>84859.6771782008</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>-1039872.727272728</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>74</v>
-      </c>
-      <c r="AX7" t="n">
+      <c r="BB7" t="n">
+        <v>1.124545454545455</v>
+      </c>
+      <c r="BC7" t="n">
         <v>-3.502215123272801</v>
       </c>
-      <c r="AY7" t="n">
-        <v>1.124545454545455</v>
-      </c>
-      <c r="AZ7" t="n">
+      <c r="BD7" t="n">
         <v>2.030000000000001</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>68</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>-1.863636363636363</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>-0.2947686030934114</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -1891,54 +1891,54 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-4.05</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-6.199999999999999</v>
+      </c>
+      <c r="V8" t="n">
         <v>-0.5999999999999996</v>
       </c>
-      <c r="S8" t="n">
+      <c r="W8" t="n">
         <v>-2.199999999999999</v>
       </c>
-      <c r="T8" t="n">
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="n">
+        <v>-0.6499999999999999</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.2593333333333332</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-0.7086666666666667</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>5.950000000000003</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-5.950000000000003</v>
+      </c>
+      <c r="AH8" t="n">
         <v>0.3</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AI8" t="n">
         <v>-0.25</v>
-      </c>
-      <c r="V8" t="n">
-        <v>5.950000000000003</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-5.950000000000003</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-0.6499999999999999</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>-6.199999999999999</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0.2593333333333332</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>-0.7086666666666667</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>-4.05</v>
       </c>
       <c r="AJ8" t="n">
         <v>65.88727272727272</v>
@@ -1947,61 +1947,61 @@
         <v>68.55227272727272</v>
       </c>
       <c r="AL8" t="n">
+        <v>-262377.6618656204</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>2.131452263226976</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>5.129040404040403</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>3.15970819304151</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>334</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>5675000</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.05126811594202896</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>346</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.1636363636363638</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-5.666666666666657</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1470414.562289563</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-4.935305472327045</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>2.71180243292519</v>
       </c>
-      <c r="AM8" t="n">
-        <v>0.1636363636363638</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>3.15970819304151</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>2.131452263226976</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>5675000</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>-4.935305472327045</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>-262377.6618656204</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1470414.562289563</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>346</v>
-      </c>
-      <c r="AX8" t="n">
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-1.412991021324345</v>
+      </c>
+      <c r="BC8" t="n">
         <v>6.045468885853413</v>
       </c>
-      <c r="AY8" t="n">
-        <v>-1.412991021324345</v>
-      </c>
-      <c r="AZ8" t="n">
+      <c r="BD8" t="n">
         <v>2.505050505050519</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>334</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>5.129040404040403</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>-5.666666666666657</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0.05126811594202896</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -2068,54 +2068,54 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
+        <v>1.933333333333333</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.9666666666666668</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5.766666666666667</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-3.966666666666667</v>
+      </c>
+      <c r="V9" t="n">
         <v>3.333333333333334</v>
       </c>
-      <c r="S9" t="n">
+      <c r="W9" t="n">
         <v>0.9000000000000004</v>
       </c>
-      <c r="T9" t="n">
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="n">
+        <v>-1.033333333333333</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.7999999999999998</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.0525000000000001</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.200000000000003</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-1.200000000000003</v>
+      </c>
+      <c r="AH9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AI9" t="n">
         <v>1.1</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.200000000000003</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-1.200000000000003</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-1.033333333333333</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.7999999999999998</v>
-      </c>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="n">
-        <v>5.766666666666667</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>-3.966666666666667</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>-0.0525000000000001</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.933333333333333</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>-0.9666666666666668</v>
       </c>
       <c r="AJ9" t="n">
         <v>68.88545454545455</v>
@@ -2124,55 +2124,55 @@
         <v>69.91818181818181</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.8646347583700305</v>
-      </c>
-      <c r="AM9" t="n">
+        <v>-749698.4368223345</v>
+      </c>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="n">
+        <v>2.629907805276702</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>-0.4830176767676804</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.7770833333333371</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-359</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-56100000</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-0.04063644688644685</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>-380</v>
+      </c>
+      <c r="AU9" t="n">
         <v>0.0368686868686865</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0.7770833333333371</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>2.629907805276702</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>-8600000</v>
-      </c>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="n">
-        <v>-0.4962656232363685</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>-749698.4368223345</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>-1412476.957070707</v>
       </c>
       <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="n">
-        <v>-292</v>
+        <v>-1412476.957070707</v>
       </c>
       <c r="AX9" t="n">
+        <v>-0.4962656232363685</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>-0.8646347583700305</v>
+      </c>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="n">
+        <v>-0.5128787878787762</v>
+      </c>
+      <c r="BC9" t="n">
         <v>-1.665747722029273</v>
       </c>
-      <c r="AY9" t="n">
-        <v>-0.5128787878787762</v>
-      </c>
-      <c r="AZ9" t="n">
+      <c r="BD9" t="n">
         <v>2.90681818181821</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>-279</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>-0.4830176767676804</v>
-      </c>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="n">
-        <v>-0.04063644688644685</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
@@ -2247,54 +2247,54 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-1.214285714285714</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.3571428571428577</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="V10" t="n">
         <v>-3.5</v>
       </c>
-      <c r="S10" t="n">
+      <c r="W10" t="n">
         <v>5.285714285714286</v>
       </c>
-      <c r="T10" t="n">
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="n">
+        <v>0.07142857142857145</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-0.5714285714285716</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-3.333333333333333</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.3809999999999999</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-0.8159999999999997</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>5.642857142857146</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-5.642857142857146</v>
+      </c>
+      <c r="AH10" t="n">
         <v>-0.7857142857142858</v>
       </c>
-      <c r="U10" t="n">
+      <c r="AI10" t="n">
         <v>-1.285714285714286</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5.642857142857146</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-5.642857142857146</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.07142857142857145</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>-0.5714285714285716</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>-3.333333333333333</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="n">
-        <v>-0.3571428571428577</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0.3809999999999999</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>-0.8159999999999997</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.142857142857143</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>-1.214285714285714</v>
       </c>
       <c r="AJ10" t="n">
         <v>68.14090909090909</v>
@@ -2303,61 +2303,61 @@
         <v>66.93333333333334</v>
       </c>
       <c r="AL10" t="n">
+        <v>760376.2857075199</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.031940604744307</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-1.733044733044732</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.856421356421365</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-66</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-1950000</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-0.06822406257188884</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>-74</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-0.05454545454545445</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1667378.246753247</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>2.882642728589019</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>1.507395550007423</v>
       </c>
-      <c r="AM10" t="n">
-        <v>-0.05454545454545445</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1.856421356421365</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.031940604744307</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>-1950000</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.882642728589019</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>760376.2857075199</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1667378.246753247</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>-74</v>
-      </c>
-      <c r="AX10" t="n">
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>3.170598845598846</v>
+      </c>
+      <c r="BC10" t="n">
         <v>-0.7562135820511777</v>
       </c>
-      <c r="AY10" t="n">
-        <v>3.170598845598846</v>
-      </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
         <v>0.567171717171675</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>-66</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>-1.733044733044732</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>-0.06822406257188884</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -2432,54 +2432,54 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.833333333333333</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.166666666666666</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="V11" t="n">
         <v>-1.5</v>
       </c>
-      <c r="S11" t="n">
+      <c r="W11" t="n">
         <v>-3.833333333333332</v>
       </c>
-      <c r="T11" t="n">
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="n">
+        <v>0.1666666666666666</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.2000000000000002</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.7020000000000002</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0.07399999999999984</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AH11" t="n">
         <v>0.1666666666666665</v>
       </c>
-      <c r="U11" t="n">
+      <c r="AI11" t="n">
         <v>0.1666666666666665</v>
-      </c>
-      <c r="V11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.1666666666666666</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>-0.2000000000000002</v>
-      </c>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="n">
-        <v>3.166666666666666</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0.7020000000000002</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>-0.07399999999999984</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>-0.833333333333333</v>
       </c>
       <c r="AJ11" t="n">
         <v>67.4590909090909</v>
@@ -2488,61 +2488,61 @@
         <v>68.87239057239057</v>
       </c>
       <c r="AL11" t="n">
+        <v>-383308.3381888666</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>2.314807860470381</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.135206611570247</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-0.8647107438016377</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>194</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2125000</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-0.07760590540910872</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>205</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-0.05404958677685956</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>-472622.7272727271</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>2.443193316865049</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>-2.440674125125952</v>
       </c>
-      <c r="AM11" t="n">
-        <v>-0.05404958677685956</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>-0.8647107438016377</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>2.314807860470381</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>2125000</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.443193316865049</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>-383308.3381888666</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>-472622.7272727271</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>205</v>
-      </c>
-      <c r="AX11" t="n">
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-0.588512396694199</v>
+      </c>
+      <c r="BC11" t="n">
         <v>-2.505192864482446</v>
       </c>
-      <c r="AY11" t="n">
-        <v>-0.588512396694199</v>
-      </c>
-      <c r="AZ11" t="n">
+      <c r="BD11" t="n">
         <v>3.854876033057849</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>194</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>0.135206611570247</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>-0.07760590540910872</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -2617,54 +2617,54 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
+        <v>2.392857142857143</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-1.464285714285714</v>
+      </c>
+      <c r="T12" t="n">
+        <v>11.53571428571428</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-5.392857142857142</v>
+      </c>
+      <c r="V12" t="n">
         <v>-2.071428571428571</v>
       </c>
-      <c r="S12" t="n">
+      <c r="W12" t="n">
         <v>-2.357142857142858</v>
       </c>
-      <c r="T12" t="n">
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v>-1.214285714285714</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.9285714285714284</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0.666666666666667</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.2225</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.02083333333333348</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>11.03571428571428</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-11.03571428571428</v>
+      </c>
+      <c r="AH12" t="n">
         <v>-0.2142857142857142</v>
       </c>
-      <c r="U12" t="n">
+      <c r="AI12" t="n">
         <v>0.25</v>
-      </c>
-      <c r="V12" t="n">
-        <v>11.03571428571428</v>
-      </c>
-      <c r="W12" t="n">
-        <v>-11.03571428571428</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-1.214285714285714</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.9285714285714284</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>-0.666666666666667</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="n">
-        <v>11.53571428571428</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>-5.392857142857142</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.2225</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0.02083333333333348</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2.392857142857143</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>-1.464285714285714</v>
       </c>
       <c r="AJ12" t="n">
         <v>67.826443001443</v>
@@ -2673,61 +2673,61 @@
         <v>68.34886363636363</v>
       </c>
       <c r="AL12" t="n">
+        <v>-56348.01347093843</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-4.800000000000001</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0.2800701513087915</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-0.2416528925619872</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>3.291074380165284</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>279</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>12325000</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-0.02425421197160338</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>286</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.05785123966942152</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.400000000000006</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1366474.380165289</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.8869191051398531</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>0.009777622723447621</v>
       </c>
-      <c r="AM12" t="n">
-        <v>0.05785123966942152</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>3.291074380165284</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0.2800701513087915</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>15025000</v>
-      </c>
-      <c r="AR12" t="n">
+      <c r="BA12" t="n">
         <v>-0.6000000000000001</v>
       </c>
-      <c r="AS12" t="n">
-        <v>0.8869191051398531</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>-56348.01347093843</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1366474.380165289</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>-5.199999999999999</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>292</v>
-      </c>
-      <c r="AX12" t="n">
+      <c r="BB12" t="n">
+        <v>2.278016528925619</v>
+      </c>
+      <c r="BC12" t="n">
         <v>-1.647175696439238</v>
       </c>
-      <c r="AY12" t="n">
-        <v>2.278016528925619</v>
-      </c>
-      <c r="AZ12" t="n">
+      <c r="BD12" t="n">
         <v>0.7838016528925777</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>285</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>-0.2416528925619872</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>-0.02425421197160338</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -2802,54 +2802,54 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
+        <v>2.533333333333333</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-1.866666666666667</v>
+      </c>
+      <c r="T13" t="n">
+        <v>7.266666666666667</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="V13" t="n">
         <v>-2.666666666666666</v>
       </c>
-      <c r="S13" t="n">
+      <c r="W13" t="n">
         <v>1.933333333333333</v>
       </c>
-      <c r="T13" t="n">
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.416666666666667</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.7549999999999999</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-1.794166666666666</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.200000000000003</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-2.200000000000003</v>
+      </c>
+      <c r="AH13" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="U13" t="n">
+      <c r="AI13" t="n">
         <v>-0.2666666666666668</v>
-      </c>
-      <c r="V13" t="n">
-        <v>2.200000000000003</v>
-      </c>
-      <c r="W13" t="n">
-        <v>-2.200000000000003</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.3999999999999999</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.416666666666667</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="n">
-        <v>7.266666666666667</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>-9.4</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0.7549999999999999</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>-1.794166666666666</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>2.533333333333333</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>-1.866666666666667</v>
       </c>
       <c r="AJ13" t="n">
         <v>67.79050505050505</v>
@@ -2858,61 +2858,61 @@
         <v>69.42424242424242</v>
       </c>
       <c r="AL13" t="n">
+        <v>-30191.94156434387</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.01656441074203485</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-1.377525252525249</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.2032828282828376</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-139</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-7650000</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-0.08890100912159737</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-144</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-0.09545454545454568</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>728231.060606061</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-4.7376721554471</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>-4.450771461269383</v>
       </c>
-      <c r="AM13" t="n">
-        <v>-0.09545454545454568</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0.2032828282828376</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0.01656441074203485</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>-7650000</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>-4.7376721554471</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>-30191.94156434387</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>728231.060606061</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>-144</v>
-      </c>
-      <c r="AX13" t="n">
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.628282828282835</v>
+      </c>
+      <c r="BC13" t="n">
         <v>-0.9438040970289983</v>
       </c>
-      <c r="AY13" t="n">
-        <v>1.628282828282835</v>
-      </c>
-      <c r="AZ13" t="n">
+      <c r="BD13" t="n">
         <v>-1.547727272727229</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>-139</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>-1.377525252525249</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>-0.08890100912159737</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -2987,54 +2987,54 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.1999999999999993</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-8.466666666666669</v>
+      </c>
+      <c r="V14" t="n">
         <v>-2.066666666666666</v>
       </c>
-      <c r="S14" t="n">
+      <c r="W14" t="n">
         <v>1.133333333333335</v>
       </c>
-      <c r="T14" t="n">
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="n">
+        <v>-1.133333333333333</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.266666666666667</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0.4166666666666665</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.08166666666666678</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-0.5183333333333333</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.3999999999999986</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.3999999999999986</v>
+      </c>
+      <c r="AH14" t="n">
         <v>-1.6</v>
       </c>
-      <c r="U14" t="n">
+      <c r="AI14" t="n">
         <v>-0.06666666666666665</v>
-      </c>
-      <c r="V14" t="n">
-        <v>-0.3999999999999986</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0.3999999999999986</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-1.133333333333333</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.266666666666667</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>-0.4166666666666665</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>-0.3333333333333335</v>
-      </c>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="n">
-        <v>0.1999999999999993</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>-8.466666666666669</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0.08166666666666678</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>-0.5183333333333333</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>-1.8</v>
       </c>
       <c r="AJ14" t="n">
         <v>69.91797979797981</v>
@@ -3043,61 +3043,61 @@
         <v>66.59090909090908</v>
       </c>
       <c r="AL14" t="n">
+        <v>1165322.2044186</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-0.751210450918677</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.180707070707072</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.982020202020195</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-99</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-3960000</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-0.01730930587337931</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-60</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.1622222222222225</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>6.333333333333343</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>532786.8686868688</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-0.02280751835671424</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>-1.641670340211519</v>
       </c>
-      <c r="AM14" t="n">
-        <v>0.1622222222222225</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1.982020202020195</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>-0.751210450918677</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>-2660000</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>-0.02280751835671424</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1165322.2044186</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>532786.8686868688</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>-61</v>
-      </c>
-      <c r="AX14" t="n">
+      <c r="BA14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.087070707070708</v>
+      </c>
+      <c r="BC14" t="n">
         <v>-1.282047355983284</v>
       </c>
-      <c r="AY14" t="n">
-        <v>1.087070707070708</v>
-      </c>
-      <c r="AZ14" t="n">
+      <c r="BD14" t="n">
         <v>-2.27555555555557</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>-95</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.180707070707072</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2.833333333333343</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>-0.01730930587337931</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
@@ -3172,54 +3172,54 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4.949999999999999</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-2.699999999999999</v>
+      </c>
+      <c r="V15" t="n">
         <v>1.1</v>
       </c>
-      <c r="S15" t="n">
+      <c r="W15" t="n">
         <v>1.1</v>
       </c>
-      <c r="T15" t="n">
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="n">
+        <v>0.9500000000000002</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.916666666666667</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.3524999999999998</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-0.4099999999999999</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.6499999999999986</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.6499999999999986</v>
+      </c>
+      <c r="AH15" t="n">
         <v>0.8</v>
       </c>
-      <c r="U15" t="n">
+      <c r="AI15" t="n">
         <v>-0.45</v>
-      </c>
-      <c r="V15" t="n">
-        <v>-0.6499999999999986</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0.6499999999999986</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0.9500000000000002</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>-0.916666666666667</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="n">
-        <v>4.949999999999999</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>-2.699999999999999</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0.3524999999999998</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>-0.4099999999999999</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0.25</v>
       </c>
       <c r="AJ15" t="n">
         <v>68.31272727272727</v>
@@ -3228,61 +3228,61 @@
         <v>68.5409090909091</v>
       </c>
       <c r="AL15" t="n">
+        <v>190353.8610155566</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>2.321211952896533</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-2.955454545454547</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>3.599999999999994</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-97</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1825000</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-0.06943696430101065</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>-62</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-0.07363636363636372</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-1.699999999999989</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>852163.6363636365</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>2.787371215927536</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>0.8899904743145726</v>
       </c>
-      <c r="AM15" t="n">
-        <v>-0.07363636363636372</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>3.599999999999994</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>2.321211952896533</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>-4175000</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.787371215927536</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>190353.8610155566</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>852163.6363636365</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>-9.866666666666667</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>-137</v>
-      </c>
-      <c r="AX15" t="n">
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>6.488181818181829</v>
+      </c>
+      <c r="BC15" t="n">
         <v>0.002499866273925733</v>
       </c>
-      <c r="AY15" t="n">
-        <v>6.488181818181829</v>
-      </c>
-      <c r="AZ15" t="n">
+      <c r="BD15" t="n">
         <v>-2.30545454545458</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>-172</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>-2.955454545454547</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>-1.199999999999989</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>-0.06943696430101065</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>

--- a/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE15"/>
+  <dimension ref="A1:BE42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,94 +515,94 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -615,97 +615,97 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_val_player_sub</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -717,32 +717,32 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8K42rT3c</t>
+          <t>YakQgH8Q</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45478.10416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">badawi m 
+          <t xml:space="preserve">unkel t 
   usa </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">lumen field
-  seattle  wa </t>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6P5S63Ah</t>
+          <t>U3ebh62R</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -759,139 +759,127 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>86yPt28</t>
+          <t>2PIEeC7</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>UFWZoX9</t>
+          <t>UL7r7du</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.600000000000001</v>
+      </c>
+      <c r="S2" t="n">
         <v>2</v>
       </c>
-      <c r="P2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.6666666666666665</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-4.833333333333332</v>
-      </c>
       <c r="T2" t="n">
-        <v>8.5</v>
+        <v>1.800000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-7.333333333333334</v>
+        <v>1.600000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>1.181666666666666</v>
       </c>
       <c r="W2" t="n">
-        <v>2.666666666666666</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-0.5</v>
-      </c>
+        <v>0.09333333333333327</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>1.166666666666667</v>
+        <v>1.799999999999997</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1.333333333333333</v>
+        <v>-1.799999999999997</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3333333333333339</v>
+        <v>-1.800000000000001</v>
       </c>
       <c r="AC2" t="n">
         <v>-1</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4173333333333333</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.6193333333333333</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
-        <v>3.333333333333336</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>-3.333333333333336</v>
+        <v>0.6</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>67.39545454545454</v>
+        <v>66.47636363636363</v>
       </c>
       <c r="AK2" t="n">
-        <v>68.14565656565655</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-109254.0965385477</v>
-      </c>
+        <v>67.90000000000001</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
-        <v>-1.135349536645123</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0.7532828282828241</v>
-      </c>
+        <v>-0.2844077134986229</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="n">
-        <v>0.7264763014762963</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-206</v>
-      </c>
+        <v>-2.187449934878742</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>-15450000</v>
+        <v>-1.197272727272718</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.05693617135769502</v>
+        <v>-689263.7741046832</v>
       </c>
       <c r="AT2" t="n">
-        <v>-229</v>
+        <v>-0.5939577594122909</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.1370435120435118</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="n">
-        <v>-757832.5563325565</v>
-      </c>
+        <v>-3.004042901446127</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>-348223.6638921348</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>0.3731085978061515</v>
+        <v>-2.395801063328676</v>
       </c>
       <c r="AY2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-0.0842319001685965</v>
-      </c>
+        <v>0.01913317962230998</v>
+      </c>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
-        <v>0.9790209790209587</v>
+        <v>-1.737612488521577</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0.8809675693206387</v>
+        <v>-1.844325429117646</v>
       </c>
       <c r="BD2" t="n">
-        <v>-2.060411810411836</v>
+        <v>-1.071377410468315</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -900,32 +888,32 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ma0gz0nH</t>
+          <t>jy0LfcgK</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45478.0625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">unkel t 
+          <t xml:space="preserve">allatin m 
   usa </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">providence park
-  portland  or </t>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>bm8usLzB</t>
+          <t>jmBZNRn8</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>K2dlua5N</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -942,141 +930,127 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Onn3tCA</t>
+          <t>z9ZXDy6</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Sd7snoa</t>
+          <t>rXawJi8</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="O3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.083333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.333333333333333</v>
+        <v>-1.9</v>
       </c>
       <c r="T3" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="U3" t="n">
-        <v>-7.083333333333334</v>
+        <v>-2.7</v>
       </c>
       <c r="V3" t="n">
-        <v>3.666666666666666</v>
+        <v>1.57</v>
       </c>
       <c r="W3" t="n">
-        <v>-2.833333333333334</v>
+        <v>-0.6299999999999999</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.6499999999999986</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.8333333333333333</v>
+        <v>-0.6499999999999986</v>
       </c>
       <c r="AB3" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.800000000000001</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-1.366666666666667</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-0.4000000000000004</v>
+      </c>
+      <c r="AF3" t="n">
         <v>0.3999999999999999</v>
       </c>
-      <c r="AC3" t="n">
-        <v>0.8499999999999996</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.5779999999999998</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-0.9330000000000001</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>7.25</v>
-      </c>
       <c r="AG3" t="n">
-        <v>-7.25</v>
+        <v>-1.1</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.25</v>
+        <v>0.9333333333333335</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.08333333333333326</v>
+        <v>-1.166666666666667</v>
       </c>
       <c r="AJ3" t="n">
-        <v>70.03282828282829</v>
+        <v>67.33454545454545</v>
       </c>
       <c r="AK3" t="n">
-        <v>68.10151515151516</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>550487.0562760041</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>-2</v>
-      </c>
+        <v>67.58219336219335</v>
+      </c>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>1.979606226529341</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1.117676767676773</v>
-      </c>
+        <v>-0.05454545454545445</v>
+      </c>
+      <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>0.6612121212121167</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-4</v>
-      </c>
+        <v>-1.265198598763192</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>-525000</v>
+        <v>0.1036363636363262</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>507066.9191919195</v>
       </c>
       <c r="AT3" t="n">
-        <v>-4</v>
+        <v>1.891060606060606</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>-2.530474076103872</v>
       </c>
       <c r="AV3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>96916.16161616147</v>
-      </c>
+        <v>-210987.467692391</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>-0.2282825099466947</v>
+        <v>-2.933321628168173</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>2.192552960420159</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.06822406257188884</v>
+      </c>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>0.3835353535353505</v>
+        <v>-0.4223232323232224</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.01695216398743</v>
+        <v>1.533106537300924</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.439393939393966</v>
+        <v>-3.158787878787873</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
@@ -1085,32 +1059,32 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>xYeHewvE</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45478.02083333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bmo stadium
-  los angeles  ca </t>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>txUJt9AR</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>bm8usLzB</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1127,7 +1101,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>KtuTuMN</t>
+          <t>WWvwigh</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1136,136 +1110,118 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="O4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="P4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>4.199999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.2</v>
+        <v>0.1000000000000014</v>
       </c>
       <c r="T4" t="n">
-        <v>4.600000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>-6.800000000000001</v>
+        <v>1.85</v>
       </c>
       <c r="V4" t="n">
-        <v>2.6</v>
+        <v>0.5083333333333333</v>
       </c>
       <c r="W4" t="n">
-        <v>-2.199999999999999</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-16</v>
-      </c>
+        <v>0.9583333333333337</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>2.2</v>
+        <v>1.049999999999997</v>
       </c>
       <c r="AA4" t="n">
-        <v>-2</v>
+        <v>-1.049999999999997</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.25</v>
+        <v>-1.15</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.25</v>
+        <v>-3.050000000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.03</v>
+        <v>-0.08333333333333304</v>
       </c>
       <c r="AE4" t="n">
-        <v>-1.58</v>
+        <v>-0.5833333333333335</v>
       </c>
       <c r="AF4" t="n">
-        <v>10.8</v>
+        <v>1.35</v>
       </c>
       <c r="AG4" t="n">
-        <v>-10.8</v>
+        <v>0.6499999999999999</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.3999999999999999</v>
+        <v>0.5833333333333335</v>
       </c>
       <c r="AI4" t="n">
-        <v>-2.8</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="AJ4" t="n">
-        <v>69.02727272727273</v>
+        <v>67.71656565656566</v>
       </c>
       <c r="AK4" t="n">
-        <v>67.45454545454547</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>365763.7921170387</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>-3</v>
-      </c>
+        <v>67.43636363636364</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>-0.8689361731038048</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.5262626262626142</v>
-      </c>
+        <v>0.07196969696969702</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>2.602387511478426</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>63</v>
-      </c>
+        <v>0.3836819437572956</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
-        <v>2600000</v>
+        <v>3.828787878787921</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.01154401154401152</v>
+        <v>-82300</v>
       </c>
       <c r="AT4" t="n">
-        <v>80</v>
+        <v>-0.6860606060605932</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.3266299357208451</v>
+        <v>-3.707915034816374</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.3333333333333428</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1706640.955004592</v>
-      </c>
+        <v>-98819.82791469689</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>2.287032299445116</v>
+        <v>-1.998138743743805</v>
       </c>
       <c r="AY4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.732702993162775</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
+        <v>0.03216238058915422</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>2.296786042240583</v>
+        <v>-2.11196969696968</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.6431171330671468</v>
+        <v>0.1875504153363607</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.4331496786042237</v>
+        <v>-1.209848484848486</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -1274,32 +1230,32 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Sx1kytXA</t>
+          <t>OU7ZWg1D</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45466.0625</v>
+        <v>45477.0625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">mendoza r 
-  usa </t>
+          <t xml:space="preserve">fischer d 
+  can </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">dick s sporting goods park
-  commerce city  co </t>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>jmBZNRn8</t>
+          <t>W0ealpQl</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1316,137 +1272,127 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>z9ZXDy6</t>
+          <t>jBBpU7Y</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>rJ9D8rz</t>
+          <t>tOpyQa2</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+        <v>-4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.75</v>
+        <v>7</v>
       </c>
       <c r="S5" t="n">
-        <v>-4.25</v>
+        <v>-2.133333333333335</v>
       </c>
       <c r="T5" t="n">
-        <v>6.25</v>
+        <v>4</v>
       </c>
       <c r="U5" t="n">
-        <v>-8.25</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="V5" t="n">
-        <v>-4.25</v>
+        <v>1.060833333333334</v>
       </c>
       <c r="W5" t="n">
-        <v>2.25</v>
+        <v>0.1283333333333332</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>1.25</v>
+        <v>6</v>
       </c>
       <c r="AA5" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.1666666666666665</v>
+        <v>0.8666666666666654</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.1666666666666665</v>
+        <v>-3.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.016666666666666</v>
+        <v>0.416666666666667</v>
       </c>
       <c r="AE5" t="n">
-        <v>-1.228333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>13.25</v>
+        <v>2.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>-13.25</v>
+        <v>-0.2666666666666668</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AI5" t="n">
         <v>-1.25</v>
       </c>
       <c r="AJ5" t="n">
-        <v>67.7590909090909</v>
+        <v>67.22535353535353</v>
       </c>
       <c r="AK5" t="n">
-        <v>66.84595959595958</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>-484968.2158682763</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-5</v>
-      </c>
+        <v>68.64011784511784</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>-1.907425065511973</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0.298787878787877</v>
-      </c>
+        <v>-0.150413223140496</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>-0.004141414141415112</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-2</v>
-      </c>
+        <v>-1.567753099371373</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
-        <v>1240000</v>
+        <v>-1.341965105601474</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.0935099111414901</v>
+        <v>-244786.5013774105</v>
       </c>
       <c r="AT5" t="n">
-        <v>15</v>
+        <v>1.53452708907254</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.01818181818181808</v>
+        <v>-0.7122733105703674</v>
       </c>
       <c r="AV5" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>426972.2222222225</v>
-      </c>
+        <v>48185.4591978481</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>-2.270556856471174</v>
+        <v>-1.00798929430016</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-3.844034424878735</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.09398017441495687</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>-0.4399999999999977</v>
+        <v>-2.377961432506879</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.8062073696408696</v>
+        <v>1.748269082621249</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.7657575757575614</v>
+        <v>-2.641230486685036</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -1455,32 +1401,32 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2NHGKPBj</t>
+          <t>pv9VXZo7</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45466.0625</v>
+        <v>45477.02083333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">marrufo j 
+          <t xml:space="preserve">de oliveira m 
   usa </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">america first field
-  sandy  ut </t>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>W0ealpQl</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>U3ebh62R</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1497,141 +1443,127 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>jBBpU7Y</t>
+          <t>z9ZXDy6</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>dp6AQn9</t>
+          <t>EqKWmJf</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>4.1</v>
+        <v>6.850000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3499999999999996</v>
+        <v>-7.550000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>5.9</v>
+        <v>1.6</v>
       </c>
       <c r="U6" t="n">
-        <v>-4.5</v>
+        <v>-4.3</v>
       </c>
       <c r="V6" t="n">
-        <v>3.9</v>
+        <v>0.3266666666666667</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.09999999999999964</v>
+        <v>-1.435</v>
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>2.4</v>
+        <v>8.700000000000003</v>
       </c>
       <c r="AA6" t="n">
-        <v>-1.8</v>
+        <v>-8.700000000000003</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.75</v>
+        <v>5.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.5</v>
+        <v>-4.85</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.0445</v>
+        <v>-1.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.2875000000000001</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="AF6" t="n">
-        <v>4.350000000000001</v>
+        <v>-1.45</v>
       </c>
       <c r="AG6" t="n">
-        <v>-4.350000000000001</v>
+        <v>-2.15</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.65</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.2</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="AJ6" t="n">
-        <v>66.60606060606061</v>
+        <v>68.62200126262626</v>
       </c>
       <c r="AK6" t="n">
-        <v>67.58181818181818</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>-184865.2815633246</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>-3</v>
-      </c>
+        <v>68.2355142332415</v>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="n">
-        <v>1.003418932878077</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>-2.124214876033058</v>
-      </c>
+        <v>0.1898989898989898</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="n">
-        <v>-4.911331496786048</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>192</v>
-      </c>
+        <v>1.792176265895648</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="n">
-        <v>2000000</v>
+        <v>1.541597796143265</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.0306771911663215</v>
+        <v>-330620.2938475665</v>
       </c>
       <c r="AT6" t="n">
-        <v>208</v>
+        <v>-1.196969696969688</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.04222222222222216</v>
+        <v>-0.809521819457089</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>-1944304.178145088</v>
-      </c>
+        <v>-50415.08298984356</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="n">
-        <v>-0.3235549889865723</v>
+        <v>-1.479793172162296</v>
       </c>
       <c r="AY6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>-0.7248012897033504</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="n">
-        <v>-2.117061524334261</v>
+        <v>-1.257851239669421</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.003045009351396</v>
+        <v>-0.1703247037542042</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.04542699724518684</v>
+        <v>-1.196326905417823</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -1640,32 +1572,32 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4nxtRRYM</t>
+          <t>IHxZYFW0</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45477.02083333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">fischer d 
-  can </t>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz field
-  saint paul  mn </t>
+          <t xml:space="preserve">soldier field
+  chicago  il </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>IeT6JBE3</t>
+          <t>Szrwix67</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1682,141 +1614,127 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>WWvwigh</t>
+          <t>xA45kov</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>UL7r7du</t>
+          <t>6BusaLE</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.6</v>
+        <v>0.3333333333333339</v>
       </c>
       <c r="S7" t="n">
-        <v>-3.4</v>
+        <v>-3.166666666666666</v>
       </c>
       <c r="T7" t="n">
-        <v>6.600000000000001</v>
+        <v>-3</v>
       </c>
       <c r="U7" t="n">
-        <v>-8.600000000000001</v>
+        <v>-1.083333333333333</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>-0.5800000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.1999999999999993</v>
+        <v>0.1425</v>
       </c>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>1.8</v>
+        <v>1.416666666666664</v>
       </c>
       <c r="AA7" t="n">
-        <v>-1.8</v>
+        <v>-1.416666666666664</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.1499999999999999</v>
+        <v>6.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.5999999999999996</v>
+        <v>-2.666666666666666</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.5115000000000001</v>
+        <v>-0.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>-1.2215</v>
+        <v>0.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>-5.200000000000003</v>
+        <v>-1</v>
       </c>
       <c r="AG7" t="n">
-        <v>5.200000000000003</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.4</v>
+        <v>-0.25</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AJ7" t="n">
-        <v>67.93818181818182</v>
+        <v>67.77499999999999</v>
       </c>
       <c r="AK7" t="n">
-        <v>68.78909090909092</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>84859.6771782008</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>-2</v>
-      </c>
+        <v>66.52272727272728</v>
+      </c>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="n">
-        <v>-0.8621562542914489</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>-1.863636363636363</v>
-      </c>
+        <v>-0.001285583103765031</v>
+      </c>
+      <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="n">
-        <v>-1.952727272727273</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>68</v>
-      </c>
+        <v>-0.4709040812795706</v>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="n">
-        <v>17950000</v>
+        <v>-1.377134986225911</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.2947686030934114</v>
+        <v>-453473.3700642795</v>
       </c>
       <c r="AT7" t="n">
-        <v>74</v>
+        <v>-1.461248852157937</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.1054545454545455</v>
+        <v>0.428019318187296</v>
       </c>
       <c r="AV7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>-1039872.727272728</v>
-      </c>
+        <v>-223713.6612472581</v>
+      </c>
+      <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="n">
-        <v>2.815060032472886</v>
+        <v>1.888718551613813</v>
       </c>
       <c r="AY7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>-1.104131745410186</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0.08885534755099966</v>
+      </c>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="n">
-        <v>1.124545454545455</v>
+        <v>-1.272084481175384</v>
       </c>
       <c r="BC7" t="n">
-        <v>-3.502215123272801</v>
+        <v>-1.753648812393862</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.030000000000001</v>
+        <v>-0.043801652892558</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -1825,32 +1743,32 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>IktpQolT</t>
+          <t>UN8LwZh9</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45477.02083333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">rivas v 
+          <t xml:space="preserve">simon n 
   usa </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">geodis park
-  nashville  tn </t>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>84yIDQMe</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1867,12 +1785,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>xA45kov</t>
+          <t>WWvwigh</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>dp6AQn9</t>
+          <t>Sd7snoa</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -1882,126 +1800,112 @@
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.25</v>
+        <v>5.9</v>
       </c>
       <c r="S8" t="n">
-        <v>-4.05</v>
+        <v>-4.85</v>
       </c>
       <c r="T8" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="U8" t="n">
-        <v>-6.199999999999999</v>
+        <v>-1.2</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5999999999999996</v>
+        <v>0.4875</v>
       </c>
       <c r="W8" t="n">
-        <v>-2.199999999999999</v>
+        <v>-1.0275</v>
       </c>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>-0.6499999999999999</v>
+        <v>1.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.25</v>
+        <v>-1.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.25</v>
+        <v>1.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.25</v>
+        <v>-1.65</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.2593333333333332</v>
+        <v>0.5333333333333337</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.7086666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>5.950000000000003</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="n">
-        <v>-5.950000000000003</v>
+        <v>-0.55</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.3</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.25</v>
+        <v>-1.233333333333333</v>
       </c>
       <c r="AJ8" t="n">
-        <v>65.88727272727272</v>
+        <v>67.76509090909092</v>
       </c>
       <c r="AK8" t="n">
-        <v>68.55227272727272</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-262377.6618656204</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>3</v>
-      </c>
+        <v>68.23848484848484</v>
+      </c>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="n">
-        <v>2.131452263226976</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>5.129040404040403</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="n">
-        <v>3.15970819304151</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>334</v>
-      </c>
+        <v>2.808114971751309</v>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="n">
-        <v>5675000</v>
+        <v>4.543030303030321</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.05126811594202896</v>
+        <v>-1489802.020202021</v>
       </c>
       <c r="AT8" t="n">
-        <v>346</v>
+        <v>-1.975555555555559</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.1636363636363638</v>
+        <v>-0.9122744356585883</v>
       </c>
       <c r="AV8" t="n">
-        <v>-5.666666666666657</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1470414.562289563</v>
-      </c>
+        <v>127777.2589452071</v>
+      </c>
+      <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="n">
-        <v>-4.935305472327045</v>
+        <v>-0.1347091353703931</v>
       </c>
       <c r="AY8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>2.71180243292519</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="n">
-        <v>-1.412991021324345</v>
+        <v>-3.587878787878793</v>
       </c>
       <c r="BC8" t="n">
-        <v>6.045468885853413</v>
+        <v>0.4953167792940008</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.505050505050519</v>
+        <v>0.2049494949494957</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -2010,27 +1914,27 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>OWICL5dp</t>
+          <t>vRwVZeHf</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45476.98958333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">dujic f 
+          <t xml:space="preserve">lauziere p 
   can </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">citypark
-  st  louis  mo </t>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2052,7 +1956,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>z9ZXDy6</t>
+          <t>GzULyFo</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2060,119 +1964,119 @@
           <t>l6eEjGl</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.933333333333333</v>
+        <v>2.300000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9666666666666668</v>
+        <v>0.5500000000000007</v>
       </c>
       <c r="T9" t="n">
-        <v>5.766666666666667</v>
+        <v>2.8</v>
       </c>
       <c r="U9" t="n">
-        <v>-3.966666666666667</v>
+        <v>1.75</v>
       </c>
       <c r="V9" t="n">
-        <v>3.333333333333334</v>
+        <v>-0.6733333333333332</v>
       </c>
       <c r="W9" t="n">
-        <v>0.9000000000000004</v>
+        <v>0.4899999999999999</v>
       </c>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>-1.033333333333333</v>
+        <v>5.049999999999997</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.166666666666667</v>
+        <v>-5.049999999999997</v>
       </c>
       <c r="AB9" t="n">
-        <v>-2.2</v>
+        <v>1.449999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.7999999999999998</v>
+        <v>2.15</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.165</v>
+        <v>-1.533333333333333</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.0525000000000001</v>
+        <v>0.2333333333333334</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.200000000000003</v>
+        <v>-0.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>-1.200000000000003</v>
+        <v>0.9</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.2</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.1</v>
+        <v>0.5666666666666665</v>
       </c>
       <c r="AJ9" t="n">
-        <v>68.88545454545455</v>
+        <v>67.93219336219336</v>
       </c>
       <c r="AK9" t="n">
-        <v>69.91818181818181</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>-749698.4368223345</v>
-      </c>
+        <v>69.89818181818181</v>
+      </c>
+      <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="n">
-        <v>2.629907805276702</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>-0.4830176767676804</v>
-      </c>
+        <v>-0.05757575757575761</v>
+      </c>
+      <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="n">
-        <v>0.7770833333333371</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>-359</v>
-      </c>
+        <v>1.61425383151996</v>
+      </c>
+      <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="n">
-        <v>-56100000</v>
+        <v>1.684848484848459</v>
       </c>
       <c r="AS9" t="n">
-        <v>-0.04063644688644685</v>
+        <v>-466940.3409090913</v>
       </c>
       <c r="AT9" t="n">
-        <v>-380</v>
+        <v>-0.1431818181818159</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.0368686868686865</v>
-      </c>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="n">
-        <v>-1412476.957070707</v>
-      </c>
+        <v>0.2931114089688265</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-846455.6344911519</v>
+      </c>
+      <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="n">
-        <v>-0.4962656232363685</v>
+        <v>-0.2448129179917196</v>
       </c>
       <c r="AY9" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>-0.8646347583700305</v>
-      </c>
+        <v>0.04826456223515052</v>
+      </c>
+      <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="n">
-        <v>-0.5128787878787762</v>
+        <v>1.592992424242425</v>
       </c>
       <c r="BC9" t="n">
-        <v>-1.665747722029273</v>
+        <v>1.287999165981986</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.90681818181821</v>
+        <v>0.4035984848484802</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
@@ -2181,32 +2085,32 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>naJGvFw3</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45476.97916666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">de oliveira m 
+          <t xml:space="preserve">chapman a 
   usa </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">lower com field
-  columbus  oh </t>
+          <t xml:space="preserve">bmo field
+  toronto  on </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>zsdfgnmL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2223,141 +2127,127 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>6gpXy3v</t>
+          <t>xA45kov</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>rXawJi8</t>
+          <t>K4zRMgT</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.142857142857143</v>
+        <v>2.4</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.214285714285714</v>
+        <v>-4.4</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3571428571428577</v>
+        <v>2.8</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.5</v>
+        <v>0.6000000000000005</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.5</v>
+        <v>1.1275</v>
       </c>
       <c r="W10" t="n">
-        <v>5.285714285714286</v>
+        <v>0.3525</v>
       </c>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>0.07142857142857145</v>
+        <v>2</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.5714285714285716</v>
+        <v>-2</v>
       </c>
       <c r="AB10" t="n">
-        <v>-3.333333333333333</v>
+        <v>4.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.8</v>
+        <v>1.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.3809999999999999</v>
+        <v>-0.3666666666666671</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.8159999999999997</v>
+        <v>-0.5333333333333332</v>
       </c>
       <c r="AF10" t="n">
-        <v>5.642857142857146</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="n">
-        <v>-5.642857142857146</v>
+        <v>1.6</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.7857142857142858</v>
+        <v>-0.9</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.285714285714286</v>
+        <v>1.4</v>
       </c>
       <c r="AJ10" t="n">
-        <v>68.14090909090909</v>
+        <v>66.58565656565656</v>
       </c>
       <c r="AK10" t="n">
-        <v>66.93333333333334</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>760376.2857075199</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>12</v>
-      </c>
+        <v>68.50065469509916</v>
+      </c>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="n">
-        <v>1.031940604744307</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>-1.733044733044732</v>
-      </c>
+        <v>-0.04515151515151516</v>
+      </c>
+      <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="n">
-        <v>1.856421356421365</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>-66</v>
-      </c>
+        <v>-1.755091136933231</v>
+      </c>
+      <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="n">
-        <v>-1950000</v>
+        <v>2.587070707070751</v>
       </c>
       <c r="AS10" t="n">
-        <v>-0.06822406257188884</v>
+        <v>-972824.242424242</v>
       </c>
       <c r="AT10" t="n">
-        <v>-74</v>
+        <v>-4.89747474747476</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.05454545454545445</v>
+        <v>-1.27813624971521</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1667378.246753247</v>
-      </c>
+        <v>-977649.0126832228</v>
+      </c>
+      <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="n">
-        <v>2.882642728589019</v>
+        <v>-2.037201336675025</v>
       </c>
       <c r="AY10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.507395550007423</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.003672818409660383</v>
+      </c>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="n">
-        <v>3.170598845598846</v>
+        <v>-5.326464646464643</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0.7562135820511777</v>
+        <v>-0.0126832232095353</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.567171717171675</v>
+        <v>-0.4797979797979792</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -2366,32 +2256,32 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
+          <t>88KCueOd</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45476.97916666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ford t 
+          <t xml:space="preserve">szpala l 
   usa </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi field
-  washington  dc </t>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2408,141 +2298,127 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>nJ01AhX</t>
+          <t>2PIEeC7</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>tOpyQa2</t>
+          <t>rJ9D8rz</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>-11</v>
+        <v>10</v>
       </c>
       <c r="N11" t="n">
-        <v>-11</v>
+        <v>10</v>
       </c>
       <c r="O11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-8.25</v>
+      </c>
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S11" t="n">
-        <v>-0.833333333333333</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.166666666666666</v>
-      </c>
       <c r="U11" t="n">
-        <v>-3.5</v>
+        <v>-4</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.5</v>
+        <v>-0.07333333333333325</v>
       </c>
       <c r="W11" t="n">
-        <v>-3.833333333333332</v>
+        <v>-2.231666666666666</v>
       </c>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>0.1666666666666666</v>
+        <v>12.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-12.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>-1</v>
+        <v>3.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.2000000000000002</v>
+        <v>0.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.7020000000000002</v>
+        <v>-1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.07399999999999984</v>
+        <v>-1.2</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="AG11" t="n">
-        <v>-2.5</v>
+        <v>-1.75</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.1666666666666665</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.1666666666666665</v>
+        <v>-0.2666666666666668</v>
       </c>
       <c r="AJ11" t="n">
-        <v>67.4590909090909</v>
+        <v>68.14529292929292</v>
       </c>
       <c r="AK11" t="n">
-        <v>68.87239057239057</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>-383308.3381888666</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>6.25</v>
-      </c>
+        <v>66.63498316498317</v>
+      </c>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="n">
-        <v>2.314807860470381</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0.135206611570247</v>
-      </c>
+        <v>-0.01818181818181808</v>
+      </c>
+      <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="n">
-        <v>-0.8647107438016377</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>194</v>
-      </c>
+        <v>0.1812912537442344</v>
+      </c>
+      <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="n">
-        <v>2125000</v>
+        <v>1.931313131313118</v>
       </c>
       <c r="AS11" t="n">
-        <v>-0.07760590540910872</v>
+        <v>528449.0740740737</v>
       </c>
       <c r="AT11" t="n">
-        <v>205</v>
+        <v>1.231172839506172</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0.05404958677685956</v>
+        <v>-2.046000334565868</v>
       </c>
       <c r="AV11" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>-472622.7272727271</v>
-      </c>
+        <v>112986.7941997242</v>
+      </c>
+      <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="n">
-        <v>2.443193316865049</v>
+        <v>-1.552295320288543</v>
       </c>
       <c r="AY11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>-2.440674125125952</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.0935099111414901</v>
+      </c>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="n">
-        <v>-0.588512396694199</v>
+        <v>0.5130190796857477</v>
       </c>
       <c r="BC11" t="n">
-        <v>-2.505192864482446</v>
+        <v>0.07440959284421922</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.854876033057849</v>
+        <v>-1.101767676767679</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -2551,32 +2427,32 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>APxxS7JG</t>
+          <t>p4vRzx2l</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45476.97916666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">da silva a 
+          <t xml:space="preserve">marrufo j 
   usa </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">subaru park
-  chester  pa </t>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Szrwix67</t>
+          <t>O6hjfSXE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2593,19 +2469,19 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>roEEsq7</t>
+          <t>nJ01AhX</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>K4zRMgT</t>
+          <t>6BusaLE</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2617,117 +2493,103 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.392857142857143</v>
+        <v>3.083333333333334</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.464285714285714</v>
+        <v>-4.083333333333334</v>
       </c>
       <c r="T12" t="n">
-        <v>11.53571428571428</v>
+        <v>-0.916666666666667</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.392857142857142</v>
+        <v>-1.416666666666667</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.071428571428571</v>
+        <v>0.7733333333333334</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.357142857142858</v>
+        <v>0.5166666666666668</v>
       </c>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
-        <v>-1.214285714285714</v>
+        <v>2.916666666666664</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.9285714285714284</v>
+        <v>-2.916666666666664</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.666666666666667</v>
+        <v>-5</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.5</v>
+        <v>1.833333333333334</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.2225</v>
+        <v>1.35</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.02083333333333348</v>
+        <v>1.05</v>
       </c>
       <c r="AF12" t="n">
-        <v>11.03571428571428</v>
+        <v>-2.333333333333333</v>
       </c>
       <c r="AG12" t="n">
-        <v>-11.03571428571428</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.2142857142857142</v>
+        <v>-1.9</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.25</v>
+        <v>1.55</v>
       </c>
       <c r="AJ12" t="n">
-        <v>67.826443001443</v>
+        <v>66.97239669421488</v>
       </c>
       <c r="AK12" t="n">
-        <v>68.34886363636363</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>-56348.01347093843</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>-4.800000000000001</v>
-      </c>
+        <v>67.86180555555556</v>
+      </c>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="n">
-        <v>0.2800701513087915</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>-0.2416528925619872</v>
-      </c>
+        <v>0.09636363636363643</v>
+      </c>
+      <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="n">
-        <v>3.291074380165284</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>279</v>
-      </c>
+        <v>1.036507081856342</v>
+      </c>
+      <c r="AQ12" t="inlineStr"/>
       <c r="AR12" t="n">
-        <v>12325000</v>
+        <v>4.74909090909091</v>
       </c>
       <c r="AS12" t="n">
-        <v>-0.02425421197160338</v>
+        <v>-2497910.606060606</v>
       </c>
       <c r="AT12" t="n">
-        <v>286</v>
+        <v>-3.338282828282814</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.05785123966942152</v>
+        <v>0.3780051008453285</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.400000000000006</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1366474.380165289</v>
-      </c>
+        <v>-421454.7285021306</v>
+      </c>
+      <c r="AW12" t="inlineStr"/>
       <c r="AX12" t="n">
-        <v>0.8869191051398531</v>
+        <v>-1.244180025938679</v>
       </c>
       <c r="AY12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0.009777622723447621</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>-0.6000000000000001</v>
-      </c>
+        <v>0.01637426900584815</v>
+      </c>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="n">
-        <v>2.278016528925619</v>
+        <v>-2.294646464646462</v>
       </c>
       <c r="BC12" t="n">
-        <v>-1.647175696439238</v>
+        <v>3.937808185567647</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.7838016528925777</v>
+        <v>1.794343434343435</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -2736,32 +2598,32 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
+          <t>QJcftbvR</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45476.97916666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">simon n 
-  usa </t>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">tql stadium
-  cincinnati  oh </t>
+          <t xml:space="preserve">bank of america stadium
+  charlotte  nc </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>QJF7WTFB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
+          <t>0AheRyBg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2778,141 +2640,127 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>roEEsq7</t>
+          <t>022mBmS</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Sd7snoa</t>
+          <t>zoZ995a</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.533333333333333</v>
+        <v>3.65</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.866666666666667</v>
+        <v>-4.4</v>
       </c>
       <c r="T13" t="n">
-        <v>7.266666666666667</v>
+        <v>-1.1</v>
       </c>
       <c r="U13" t="n">
-        <v>-9.4</v>
+        <v>0.8499999999999996</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.666666666666666</v>
+        <v>-0.1933333333333334</v>
       </c>
       <c r="W13" t="n">
-        <v>1.933333333333333</v>
+        <v>-0.34</v>
       </c>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.9000000000000004</v>
+      </c>
+      <c r="AD13" t="n">
         <v>0.3999999999999999</v>
       </c>
-      <c r="AA13" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.416666666666667</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.7549999999999999</v>
-      </c>
       <c r="AE13" t="n">
-        <v>-1.794166666666666</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.200000000000003</v>
+        <v>-0.95</v>
       </c>
       <c r="AG13" t="n">
-        <v>-2.200000000000003</v>
+        <v>-0.6</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.4000000000000001</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.2666666666666668</v>
+        <v>0.2</v>
       </c>
       <c r="AJ13" t="n">
-        <v>67.79050505050505</v>
+        <v>68.02626262626262</v>
       </c>
       <c r="AK13" t="n">
-        <v>69.42424242424242</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>-30191.94156434387</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1</v>
-      </c>
+        <v>68.38363636363637</v>
+      </c>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="n">
-        <v>0.01656441074203485</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>-1.377525252525249</v>
-      </c>
+        <v>-0.7272727272727273</v>
+      </c>
+      <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="n">
-        <v>0.2032828282828376</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>-139</v>
-      </c>
+        <v>-3.428047740835439</v>
+      </c>
+      <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="n">
-        <v>-7650000</v>
+        <v>0.4418181818182063</v>
       </c>
       <c r="AS13" t="n">
-        <v>-0.08890100912159737</v>
+        <v>-5087218.181818182</v>
       </c>
       <c r="AT13" t="n">
-        <v>-144</v>
+        <v>-6.61272727272727</v>
       </c>
       <c r="AU13" t="n">
-        <v>-0.09545454545454568</v>
+        <v>-2.095827142451171</v>
       </c>
       <c r="AV13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>728231.060606061</v>
-      </c>
+        <v>-830146.4184224415</v>
+      </c>
+      <c r="AW13" t="inlineStr"/>
       <c r="AX13" t="n">
-        <v>-4.7376721554471</v>
+        <v>2.29774712783664</v>
       </c>
       <c r="AY13" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>-4.450771461269383</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.02042909917590219</v>
+      </c>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="n">
-        <v>1.628282828282835</v>
+        <v>-7.910909090909087</v>
       </c>
       <c r="BC13" t="n">
-        <v>-0.9438040970289983</v>
+        <v>-3.8734013315471</v>
       </c>
       <c r="BD13" t="n">
-        <v>-1.547727272727229</v>
+        <v>-1.49636363636364</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -2921,32 +2769,32 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>WYwYSm4A</t>
+          <t>W0zNyInr</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45476.9375</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">simon n 
+          <t xml:space="preserve">penso c 
   usa </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">inter co stadium
-  orlando  fl </t>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>rsHkUNCo</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>84yIDQMe</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2963,141 +2811,127 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>022mBmS</t>
+          <t>6gpXy3v</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Uw6sTk0</t>
+          <t>EgT3xN3</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-2</v>
+        <v>4.6</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8</v>
+        <v>-7.199999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1999999999999993</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>-8.466666666666669</v>
+        <v>1.6</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.066666666666666</v>
+        <v>0.1566666666666667</v>
       </c>
       <c r="W14" t="n">
-        <v>1.133333333333335</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
-        <v>-1.133333333333333</v>
+        <v>6.200000000000003</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.266666666666667</v>
+        <v>-6.200000000000003</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.4166666666666665</v>
+        <v>-2.800000000000001</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.3333333333333335</v>
+        <v>3</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.08166666666666678</v>
+        <v>-2</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.5183333333333333</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.3999999999999986</v>
+        <v>0.2</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.3999999999999986</v>
+        <v>1.6</v>
       </c>
       <c r="AH14" t="n">
-        <v>-1.6</v>
+        <v>-1.1</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0.06666666666666665</v>
+        <v>1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>69.91797979797981</v>
+        <v>68.07727272727271</v>
       </c>
       <c r="AK14" t="n">
-        <v>66.59090909090908</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1165322.2044186</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>-8</v>
-      </c>
+        <v>66.75818181818182</v>
+      </c>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
       <c r="AN14" t="n">
-        <v>-0.751210450918677</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1.180707070707072</v>
-      </c>
+        <v>-0.1636363636363638</v>
+      </c>
+      <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="n">
-        <v>1.982020202020195</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>-99</v>
-      </c>
+        <v>-1.923029378975684</v>
+      </c>
+      <c r="AQ14" t="inlineStr"/>
       <c r="AR14" t="n">
-        <v>-3960000</v>
+        <v>-3.207070707070727</v>
       </c>
       <c r="AS14" t="n">
-        <v>-0.01730930587337931</v>
+        <v>-411580.086580086</v>
       </c>
       <c r="AT14" t="n">
-        <v>-60</v>
+        <v>1.021356421356415</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.1622222222222225</v>
+        <v>-0.4719668971267623</v>
       </c>
       <c r="AV14" t="n">
-        <v>6.333333333333343</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>532786.8686868688</v>
-      </c>
+        <v>635786.4051975308</v>
+      </c>
+      <c r="AW14" t="inlineStr"/>
       <c r="AX14" t="n">
-        <v>-0.02280751835671424</v>
+        <v>-3.122272889088745</v>
       </c>
       <c r="AY14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>-1.641670340211519</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>-0.5</v>
-      </c>
+        <v>-0.05126811594202896</v>
+      </c>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
       <c r="BB14" t="n">
-        <v>1.087070707070708</v>
+        <v>-1.398124098124086</v>
       </c>
       <c r="BC14" t="n">
-        <v>-1.282047355983284</v>
+        <v>3.939875214299747</v>
       </c>
       <c r="BD14" t="n">
-        <v>-2.27555555555557</v>
+        <v>-2.302741702741706</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
@@ -3106,32 +2940,32 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>ln2oxMH4</t>
+          <t>YyTMIXGq</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45473.10416666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">dickerson j 
+          <t xml:space="preserve">gonzales g 
   usa </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">red bull arena
-  harrison  nj </t>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3148,143 +2982,4922 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>K4FYmLD</t>
+          <t>GzULyFo</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>EgT3xN3</t>
+          <t>lAVQ9RG</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.15</v>
+        <v>1.416666666666668</v>
       </c>
       <c r="S15" t="n">
-        <v>0.25</v>
+        <v>-7.75</v>
       </c>
       <c r="T15" t="n">
-        <v>4.949999999999999</v>
+        <v>-1.5</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.699999999999999</v>
+        <v>-4.666666666666666</v>
       </c>
       <c r="V15" t="n">
-        <v>1.1</v>
+        <v>0.74</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>-1.26</v>
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="n">
+        <v>11.66666666666666</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-11.66666666666666</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-8.416666666666668</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>68.01515151515152</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>70.08636363636364</v>
+      </c>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="n">
+        <v>-0.1898989898989898</v>
+      </c>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="n">
+        <v>-4.689963029953844</v>
+      </c>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="n">
+        <v>-5.136363636363683</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>511590.9090909096</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0.2979797979797922</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.09949275998991425</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-368085.9509626839</v>
+      </c>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="n">
+        <v>0.7914387490659536</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="n">
+        <v>0.9878787878787847</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-0.5697757654402835</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0.2393939393939384</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lauziere p 
+  can </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>167</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>86yPt28</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Uw6sTk0</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>8</v>
+      </c>
+      <c r="N16" t="n">
+        <v>8</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-5.833333333333334</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.666666666666667</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.02833333333333343</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0.9283333333333332</v>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-1.333333333333332</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.833333333333334</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.392857142857143</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-0.8333333333333334</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.6071428571428572</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-0.6785714285714286</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>67.44015151515151</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>67.41116161616162</v>
+      </c>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="n">
+        <v>0.1433566433566433</v>
+      </c>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="n">
+        <v>-2.116583102003403</v>
+      </c>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="n">
+        <v>-1.671017871017852</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>-503797.2027972024</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0.7098290598290475</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>-2.554570151098957</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>32828.21693893173</v>
+      </c>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="n">
+        <v>-2.613244765385026</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>-0.07695876030611526</v>
+      </c>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="n">
+        <v>0.4555167055167004</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0.5385153589723473</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0.9843434343434332</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vazquez r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>167</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Onn3tCA</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>dp6AQn9</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-3.666666666666666</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.4558333333333333</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.1966666666666665</v>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.08333333333333393</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.03333333333333366</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-0.6333333333333333</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.5833333333333333</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.3666666666666667</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.2666666666666668</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>70.00727272727273</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>67.0768044077135</v>
+      </c>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="n">
+        <v>-0.04222222222222216</v>
+      </c>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="n">
+        <v>3.056386107982547</v>
+      </c>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="n">
+        <v>1.630422405876942</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>-1017377.180899909</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>-1.702828282828293</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.271339908283352</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>-17540.12822490395</v>
+      </c>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="n">
+        <v>1.752683930261529</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>-0.0306771911663215</v>
+      </c>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="n">
+        <v>-0.8647750229568487</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>-0.4427068703274699</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0.5451147842057011</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">demianchuk s 
+  usa </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">providence park
+  portland  or </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>167</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Onn3tCA</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>UFWZoX9</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>-6</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-6</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-7.449999999999999</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.7866666666666666</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-1.265</v>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="n">
+        <v>9.350000000000001</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-9.350000000000001</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-0.09999999999999964</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.4000000000000004</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.4000000000000004</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.6499999999999999</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-0.8500000000000001</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>69.84020202020203</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>68.99454545454546</v>
+      </c>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="n">
+        <v>-0.828508745221967</v>
+      </c>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="n">
+        <v>-3.103636363636355</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1586718.181818182</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.359090909090909</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.104827396078747</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>422709.797330797</v>
+      </c>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="n">
+        <v>2.151661299357823</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="n">
+        <v>4.24909090909091</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>-0.7235992892406955</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0.9127272727272775</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzales g 
+  usa </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>167</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>KtuTuMN</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>lAVQ9RG</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-4</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.9950000000000001</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-1.615833333333333</v>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-13.15</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.1999999999999993</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>68.76219008264462</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>67.68681818181818</v>
+      </c>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="n">
+        <v>0.3266299357208451</v>
+      </c>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="n">
+        <v>0.904624203136791</v>
+      </c>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="n">
+        <v>0.1928282828282875</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2527763.774104683</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>4.109513314967856</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6.48558641015395</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1048331.034847764</v>
+      </c>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="n">
+        <v>3.79984436905676</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0.01154401154401152</v>
+      </c>
+      <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="n">
+        <v>6.3098347107438</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>3.154465231415358</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>3.225821854912759</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>167</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>jBBpU7Y</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>UL7r7du</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>11</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-7.800000000000001</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-0.3658333333333336</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-0.5808333333333333</v>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="n">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-8.399999999999999</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.600000000000001</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.366666666666667</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>-0.06666666666666732</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>67.64090909090909</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>68.2378787878788</v>
+      </c>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="n">
+        <v>-0.05090909090909101</v>
+      </c>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="n">
+        <v>-1.280846239461965</v>
+      </c>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="n">
+        <v>0.3521212121212614</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>-1059231.060606061</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0.2953030303030317</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>-1.704237591171726</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>-95996.32285281271</v>
+      </c>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="n">
+        <v>-2.902557172627507</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>-0.2265445405215225</v>
+      </c>
+      <c r="AZ20" t="inlineStr"/>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="n">
+        <v>-1.379999999999995</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0.6593042531022064</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>-0.6524242424242459</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">geodis park
+  nashville  tn </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>167</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>xA45kov</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>zoZ995a</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-7</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-0.6124999999999999</v>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.2999999999999998</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>-0.1000000000000001</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>-0.8999999999999999</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>65.29714927048261</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>68.15227272727273</v>
+      </c>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="n">
+        <v>-0.5727272727272725</v>
+      </c>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="n">
+        <v>-1.619008436150352</v>
+      </c>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="n">
+        <v>1.609090909090952</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>-3365000</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>-6.418181818181807</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>-2.146024212360516</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>-1348281.868600283</v>
+      </c>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="n">
+        <v>3.619207489015672</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>-0.07061715990744144</v>
+      </c>
+      <c r="AZ21" t="inlineStr"/>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="n">
+        <v>-4.472727272727283</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>-7.251663668811986</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0.5272727272727238</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>167</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>86yPt28</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>K4zRMgT</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-4.066666666666666</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.533333333333334</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.1333333333333329</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.7466666666666669</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-0.05666666666666664</v>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-14.2</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.933333333333334</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.266666666666666</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>-0.06666666666666665</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>66.69318181818183</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>68.95185950413224</v>
+      </c>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="n">
+        <v>0.141322314049587</v>
+      </c>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="n">
+        <v>-1.122782977290598</v>
+      </c>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="n">
+        <v>-2.211239669421474</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>289309.0909090911</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>-0.1996694214875987</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>-1.091018063572562</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>-386656.1681857656</v>
+      </c>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="n">
+        <v>-0.5628429646470678</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>-0.007476002258611336</v>
+      </c>
+      <c r="AZ22" t="inlineStr"/>
+      <c r="BA22" t="inlineStr"/>
+      <c r="BB22" t="n">
+        <v>1.800165289256185</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>-1.549607583563343</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0.9666115702479381</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>167</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>WWvwigh</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>6BusaLE</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.850000000000001</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.4500000000000002</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.5999999999999996</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.4750000000000001</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.635</v>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="n">
+        <v>-5.450000000000003</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>5.450000000000003</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>-1.300000000000001</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-0.1499999999999999</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>-0.1000000000000001</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>-0.3999999999999999</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>67.37045454545455</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>68.2570707070707</v>
+      </c>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="n">
+        <v>0.07196969696969702</v>
+      </c>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="n">
+        <v>-1.327585296652501</v>
+      </c>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="n">
+        <v>2.901515151515184</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>-1147560.606060606</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>-2.002525252525245</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.877155979524225</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>210530.4166317845</v>
+      </c>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="n">
+        <v>0.3331214623010226</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0.03216238058915422</v>
+      </c>
+      <c r="AZ23" t="inlineStr"/>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="n">
+        <v>-1.482070707070704</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>2.342899506178128</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0.6381313131313142</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>167</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>K4FYmLD</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>6BusaLE</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-1.083333333333334</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.083333333333334</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-2.583333333333333</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.2866666666666666</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.4308333333333334</v>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="n">
+        <v>1.833333333333336</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-1.833333333333336</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.416666666666666</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>-0.6666666666666661</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>-0.4166666666666665</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>68.97609427609429</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>66.63863636363635</v>
+      </c>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="n">
+        <v>-0.04876033057851248</v>
+      </c>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="n">
+        <v>-0.7837743635949153</v>
+      </c>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="n">
+        <v>-4.052892561983469</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>-1643119.834710744</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>-1.901652892561984</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>-0.7257767909921142</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>-312396.569041007</v>
+      </c>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="n">
+        <v>-1.524537507946601</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0.01630794643952527</v>
+      </c>
+      <c r="AZ24" t="inlineStr"/>
+      <c r="BA24" t="inlineStr"/>
+      <c r="BB24" t="n">
+        <v>-3.525619834710739</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0.5957144370780867</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>-1.761983471074373</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">penso c 
+  usa </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>167</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>nJ01AhX</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>EgT3xN3</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6.333333333333334</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.5891666666666665</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-0.1016666666666666</v>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-13.33333333333334</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.833333333333332</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>-0.416666666666667</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>-0.08333333333333337</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>68.1509090909091</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>68.12727272727273</v>
+      </c>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="n">
+        <v>-0.02969696969696956</v>
+      </c>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="n">
+        <v>1.221835076884133</v>
+      </c>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="n">
+        <v>-2.960757575757611</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1580342.613636364</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>4.058636363636367</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>2.7299724117727</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>620526.2811658133</v>
+      </c>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="n">
+        <v>2.442467049313617</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>-0.1044387410834779</v>
+      </c>
+      <c r="AZ25" t="inlineStr"/>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="n">
+        <v>2.759280303030295</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.307670986019431</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>-0.1340530303030292</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lauziere p 
+  can </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>167</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>K4FYmLD</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>l6eEjGl</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O26" t="n">
+        <v>4</v>
+      </c>
+      <c r="P26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.08666666666666667</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-0.6566666666666671</v>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0.4000000000000004</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>67.58181818181819</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>69.40909090909091</v>
+      </c>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="n">
+        <v>0.0127272727272727</v>
+      </c>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="n">
+        <v>-1.567948448105938</v>
+      </c>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="n">
+        <v>-4.230909090909108</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1508440.909090909</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>4.282727272727257</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1.939673013997101</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>867929.8844073697</v>
+      </c>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="n">
+        <v>-0.007170142080294539</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0.059263954663066</v>
+      </c>
+      <c r="AZ26" t="inlineStr"/>
+      <c r="BA26" t="inlineStr"/>
+      <c r="BB26" t="n">
+        <v>1.339090909090899</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0.9915650338055713</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>-3.641818181818184</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>167</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>GzULyFo</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>zoZ995a</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>-8</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-8</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.949999999999999</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.2000000000000002</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-0.8466666666666666</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.05999999999999983</v>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="n">
+        <v>-4.950000000000003</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>4.950000000000003</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="AD27" t="n">
         <v>0.9500000000000002</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AE27" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>-0.8999999999999999</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>67.9375</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>68.12808080808081</v>
+      </c>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="n">
+        <v>0.09545454545454568</v>
+      </c>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="n">
+        <v>0.2529434648720041</v>
+      </c>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="n">
+        <v>0.482070707070676</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>275727.8138528131</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>-0.2940836940836959</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1.063238138761648</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>-435968.7913278469</v>
+      </c>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="n">
+        <v>0.9207608217478764</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0.08890100912159737</v>
+      </c>
+      <c r="AZ27" t="inlineStr"/>
+      <c r="BA27" t="inlineStr"/>
+      <c r="BB27" t="n">
+        <v>0.9867604617604542</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>1.131836826146298</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0.9641053391053411</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>jqf7smJ3</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45471.97916666666</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>167</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2PIEeC7</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>K4zRMgT</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.5999999999999996</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.8041666666666668</v>
+      </c>
+      <c r="W28" t="n">
+        <v>-0.6941666666666666</v>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>-0.3000000000000007</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>-0.7000000000000002</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>-0.6500000000000004</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0.8500000000000001</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>-0.1000000000000001</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>67.71363636363637</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>68.97090909090909</v>
+      </c>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="n">
+        <v>-0.227878787878788</v>
+      </c>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="n">
+        <v>0.6196314223475667</v>
+      </c>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="n">
+        <v>1.53111111111113</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>-1193984.259259259</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>-0.2963019079685836</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>-1.558126103533759</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>-1141018.318012625</v>
+      </c>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="n">
+        <v>-3.683504023865673</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>-0.1487480063795852</v>
+      </c>
+      <c r="AZ28" t="inlineStr"/>
+      <c r="BA28" t="inlineStr"/>
+      <c r="BB28" t="n">
+        <v>-3.722536475869802</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>2.446580360672883</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>-4.000656565656566</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>UT5bq9li</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45466.10416666666</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>167</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>KtuTuMN</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>EqKWmJf</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>4.600000000000001</v>
+      </c>
+      <c r="S29" t="n">
+        <v>-6.800000000000001</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4.199999999999999</v>
+      </c>
+      <c r="U29" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W29" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="X29" t="n">
+        <v>-8</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>-16</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-10.8</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>-2.199999999999999</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>69.02727272727273</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>67.45454545454547</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>91</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0.3266299357208451</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>-2.166666666666657</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>-0.8689361731038048</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>-0.4331496786042237</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1706640.955004592</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>2.296786042240583</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1.732702993162775</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>365763.7921170387</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>3775000</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0.6431171330671468</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0.01154401154401152</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>69</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>2.602387511478426</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>2.287032299445116</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0.5262626262626142</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>8K42rT3c</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45466.10416666666</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badawi m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>167</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>86yPt28</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>UFWZoX9</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>9</v>
+      </c>
+      <c r="N30" t="n">
+        <v>9</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="S30" t="n">
+        <v>-7.333333333333334</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="U30" t="n">
+        <v>-4.833333333333332</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.4173333333333333</v>
+      </c>
+      <c r="W30" t="n">
+        <v>-0.6193333333333333</v>
+      </c>
+      <c r="X30" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.333333333333336</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-3.333333333333336</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.666666666666666</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.3333333333333339</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>-0.8333333333333334</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>67.39545454545454</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>68.14565656565655</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>-229</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0.1370435120435118</v>
+      </c>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="n">
+        <v>-1.135349536645123</v>
+      </c>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="n">
+        <v>-2.060411810411836</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>-757832.5563325565</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0.9790209790209587</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>-0.0842319001685965</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>-109254.0965385477</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>-15450000</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>-0.8809675693206387</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0.05693617135769502</v>
+      </c>
+      <c r="AZ30" t="inlineStr"/>
+      <c r="BA30" t="n">
+        <v>-206</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0.7264763014762963</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0.3731085978061515</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0.7532828282828241</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Ma0gz0nH</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45466.10416666666</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">providence park
+  portland  or </t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>167</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Onn3tCA</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Sd7snoa</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>5</v>
+      </c>
+      <c r="N31" t="n">
+        <v>5</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S31" t="n">
+        <v>-7.083333333333334</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="U31" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.5779999999999998</v>
+      </c>
+      <c r="W31" t="n">
+        <v>-0.9330000000000001</v>
+      </c>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-7.25</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>3.666666666666666</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>-2.833333333333334</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.8499999999999996</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.08333333333333326</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>-0.8333333333333333</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>70.03282828282829</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>68.10151515151516</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.979606226529341</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.439393939393966</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>96916.16161616147</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0.3835353535353505</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>2.192552960420159</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>550487.0562760041</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>-525000</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>2.01695216398743</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>-4</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0.6612121212121167</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>-0.2282825099466947</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>1.117676767676773</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>2NHGKPBj</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45466.0625</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>167</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>jBBpU7Y</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>dp6AQn9</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="S32" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>-0.3499999999999996</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.0445</v>
+      </c>
+      <c r="W32" t="n">
+        <v>-0.2875000000000001</v>
+      </c>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="n">
+        <v>4.350000000000001</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-4.350000000000001</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>-0.09999999999999964</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>66.60606060606061</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>67.58181818181818</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>208</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>-0.04222222222222216</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.003418932878077</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>-0.04542699724518684</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>-1944304.178145088</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>-2.117061524334261</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>-0.7248012897033504</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>-184865.2815633246</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.003045009351396</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>-0.0306771911663215</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>-3</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>192</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>-4.911331496786048</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>-0.3235549889865723</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>-2.124214876033058</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Sx1kytXA</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45466.0625</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mendoza r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>167</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>z9ZXDy6</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>rJ9D8rz</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>3</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="S33" t="n">
+        <v>-8.25</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U33" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.016666666666666</v>
+      </c>
+      <c r="W33" t="n">
+        <v>-1.228333333333333</v>
+      </c>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-13.25</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>-0.1666666666666665</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>-0.1666666666666665</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>67.7590909090909</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>66.84595959595958</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>-0.01818181818181808</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>-1.907425065511973</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0.7657575757575614</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>426972.2222222225</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>-0.4399999999999977</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>-3.844034424878735</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>-484968.2158682763</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1240000</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>-0.8062073696408696</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>-0.0935099111414901</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>-5</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>-0.004141414141415112</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>-2.270556856471174</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0.298787878787877</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>OWICL5dp</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45466.02083333334</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dujic f 
+  can </t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>167</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>z9ZXDy6</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>l6eEjGl</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>5.766666666666667</v>
+      </c>
+      <c r="S34" t="n">
+        <v>-3.966666666666667</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.933333333333333</v>
+      </c>
+      <c r="U34" t="n">
+        <v>-0.9666666666666668</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="W34" t="n">
+        <v>-0.0525000000000001</v>
+      </c>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="n">
+        <v>1.200000000000003</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-1.200000000000003</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>3.333333333333334</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.9000000000000004</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0.7999999999999998</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>-1.033333333333333</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>68.88545454545455</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>69.91818181818181</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>-292</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0.0368686868686865</v>
+      </c>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="n">
+        <v>2.629907805276702</v>
+      </c>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="n">
+        <v>2.90681818181821</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>-1412476.957070707</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>-0.5128787878787762</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>-0.8646347583700305</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>-749698.4368223345</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>-8600000</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>-1.665747722029273</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>-0.04063644688644685</v>
+      </c>
+      <c r="AZ34" t="inlineStr"/>
+      <c r="BA34" t="n">
+        <v>-279</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0.7770833333333371</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>-0.4962656232363685</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>-0.4830176767676804</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>4nxtRRYM</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45466.02083333334</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fischer d 
+  can </t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>167</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>WWvwigh</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>UL7r7du</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6.600000000000001</v>
+      </c>
+      <c r="S35" t="n">
+        <v>-8.600000000000001</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U35" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.5115000000000001</v>
+      </c>
+      <c r="W35" t="n">
+        <v>-1.2215</v>
+      </c>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="n">
+        <v>-5.200000000000003</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>5.200000000000003</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>-0.1999999999999993</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.1499999999999999</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.5999999999999996</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>67.93818181818182</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>68.78909090909092</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>74</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>-0.1054545454545455</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>-0.8621562542914489</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>2.030000000000001</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>-1039872.727272728</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>1.124545454545455</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>-1.104131745410186</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>84859.6771782008</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>17950000</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>-3.502215123272801</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>-0.2947686030934114</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>68</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>-1.952727272727273</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>2.815060032472886</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>-1.863636363636363</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>IktpQolT</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45466.02083333334</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rivas v 
+  usa </t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">geodis park
+  nashville  tn </t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>167</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>xA45kov</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>dp6AQn9</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S36" t="n">
+        <v>-6.199999999999999</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U36" t="n">
+        <v>-4.05</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.2593333333333332</v>
+      </c>
+      <c r="W36" t="n">
+        <v>-0.7086666666666667</v>
+      </c>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="n">
+        <v>5.950000000000003</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-5.950000000000003</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>-0.5999999999999996</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>-2.199999999999999</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>-0.6499999999999999</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>65.88727272727272</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>68.55227272727272</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>346</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0.1636363636363638</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>-5.666666666666657</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>2.131452263226976</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>2.505050505050519</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>1470414.562289563</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>-1.412991021324345</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>2.71180243292519</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>-262377.6618656204</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>5675000</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>6.045468885853413</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0.05126811594202896</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>334</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>3.15970819304151</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>-4.935305472327045</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>5.129040404040403</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>EcqTTTl4</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ford t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>167</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>nJ01AhX</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>tOpyQa2</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>-11</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-11</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>3.166666666666666</v>
+      </c>
+      <c r="S37" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U37" t="n">
+        <v>-0.833333333333333</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.7020000000000002</v>
+      </c>
+      <c r="W37" t="n">
+        <v>-0.07399999999999984</v>
+      </c>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>-3.833333333333332</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>-0.2000000000000002</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.1666666666666665</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.1666666666666665</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.1666666666666666</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>67.4590909090909</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>68.87239057239057</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>205</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>-0.05404958677685956</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>2.314807860470381</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>3.854876033057849</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>-472622.7272727271</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>-0.588512396694199</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>-2.440674125125952</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>-383308.3381888666</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>2125000</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>-2.505192864482446</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>-0.07760590540910872</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>194</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>-0.8647107438016377</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>2.443193316865049</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0.135206611570247</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>z7pPU9Zc</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>167</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>6gpXy3v</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>rXawJi8</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>-0.3571428571428577</v>
+      </c>
+      <c r="S38" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="U38" t="n">
+        <v>-1.214285714285714</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.3809999999999999</v>
+      </c>
+      <c r="W38" t="n">
+        <v>-0.8159999999999997</v>
+      </c>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="n">
+        <v>5.642857142857146</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-5.642857142857146</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>5.285714285714286</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>-3.333333333333333</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>-0.7857142857142858</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>-1.285714285714286</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0.07142857142857145</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>-0.5714285714285716</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>68.14090909090909</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>66.93333333333334</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>-74</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>-0.05454545454545445</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.031940604744307</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0.567171717171675</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>1667378.246753247</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>3.170598845598846</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>1.507395550007423</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>760376.2857075199</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>-1950000</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>-0.7562135820511777</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>-0.06822406257188884</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>-66</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>1.856421356421365</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>2.882642728589019</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>-1.733044733044732</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>tpoLVkKi</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">simon n 
+  usa </t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tql stadium
+  cincinnati  oh </t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>167</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>roEEsq7</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Sd7snoa</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P39" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7.266666666666667</v>
+      </c>
+      <c r="S39" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.533333333333333</v>
+      </c>
+      <c r="U39" t="n">
+        <v>-1.866666666666667</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.7549999999999999</v>
+      </c>
+      <c r="W39" t="n">
+        <v>-1.794166666666666</v>
+      </c>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="n">
+        <v>2.200000000000003</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-2.200000000000003</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.933333333333333</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.416666666666667</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>-0.2666666666666668</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>67.79050505050505</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>69.42424242424242</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>-144</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>-0.09545454545454568</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0.01656441074203485</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>-1.547727272727229</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>728231.060606061</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1.628282828282835</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>-4.450771461269383</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>-30191.94156434387</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>-7650000</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>-0.9438040970289983</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>-0.08890100912159737</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>-139</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>0.2032828282828376</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>-4.7376721554471</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>-1.377525252525249</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>WYwYSm4A</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">simon n 
+  usa </t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>167</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>022mBmS</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Uw6sTk0</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>3</v>
+      </c>
+      <c r="P40" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.1999999999999993</v>
+      </c>
+      <c r="S40" t="n">
+        <v>-8.466666666666669</v>
+      </c>
+      <c r="T40" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.08166666666666678</v>
+      </c>
+      <c r="W40" t="n">
+        <v>-0.5183333333333333</v>
+      </c>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="n">
+        <v>-0.3999999999999986</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.3999999999999986</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>-2.066666666666666</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.133333333333335</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>-0.4166666666666665</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>-0.06666666666666665</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>-1.133333333333333</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1.266666666666667</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>69.91797979797981</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>66.59090909090908</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>-60</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0.1622222222222225</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>6.333333333333343</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>-0.751210450918677</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>-2.27555555555557</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>532786.8686868688</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>1.087070707070708</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>-1.641670340211519</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>1165322.2044186</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>-3960000</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>-1.282047355983284</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>-0.01730930587337931</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>-8</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>-99</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>1.982020202020195</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>-0.02280751835671424</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>1.180707070707072</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>ln2oxMH4</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>167</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>K4FYmLD</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>EgT3xN3</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>12</v>
+      </c>
+      <c r="N41" t="n">
+        <v>12</v>
+      </c>
+      <c r="O41" t="n">
+        <v>3</v>
+      </c>
+      <c r="P41" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>4.949999999999999</v>
+      </c>
+      <c r="S41" t="n">
+        <v>-2.699999999999999</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.3524999999999998</v>
+      </c>
+      <c r="W41" t="n">
+        <v>-0.4099999999999999</v>
+      </c>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="n">
+        <v>-0.6499999999999986</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.6499999999999986</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>-0.916666666666667</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0.9500000000000002</v>
+      </c>
+      <c r="AI41" t="n">
         <v>-0.85</v>
       </c>
-      <c r="AB15" t="n">
-        <v>-0.916666666666667</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0.3524999999999998</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>-0.4099999999999999</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>-0.6499999999999986</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0.6499999999999986</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="AJ15" t="n">
+      <c r="AJ41" t="n">
         <v>68.31272727272727</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AK41" t="n">
         <v>68.5409090909091</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AL41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>-62</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>-0.07363636363636372</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>-1.699999999999989</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>2.321211952896533</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>-2.30545454545458</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>852163.6363636365</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>6.488181818181829</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0.8899904743145726</v>
+      </c>
+      <c r="AV41" t="n">
         <v>190353.8610155566</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AW41" t="n">
+        <v>1825000</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0.002499866273925733</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>-0.06943696430101065</v>
+      </c>
+      <c r="AZ41" t="n">
         <v>-8.199999999999999</v>
       </c>
-      <c r="AN15" t="n">
-        <v>2.321211952896533</v>
-      </c>
-      <c r="AO15" t="n">
+      <c r="BA41" t="n">
+        <v>-97</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>3.599999999999994</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>2.787371215927536</v>
+      </c>
+      <c r="BD41" t="n">
         <v>-2.955454545454547</v>
       </c>
-      <c r="AP15" t="n">
-        <v>3.599999999999994</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>-97</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1825000</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>-0.06943696430101065</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>-62</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>-0.07363636363636372</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>-1.699999999999989</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>852163.6363636365</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>2.787371215927536</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0.8899904743145726</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>6.488181818181829</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>0.002499866273925733</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>-2.30545454545458</v>
-      </c>
-      <c r="BE15" t="n">
+      <c r="BE41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>APxxS7JG</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">da silva a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subaru park
+  chester  pa </t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>167</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>roEEsq7</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>K4zRMgT</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>11.53571428571428</v>
+      </c>
+      <c r="S42" t="n">
+        <v>-5.392857142857142</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.392857142857143</v>
+      </c>
+      <c r="U42" t="n">
+        <v>-1.464285714285714</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.2225</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.02083333333333348</v>
+      </c>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="n">
+        <v>11.03571428571428</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-11.03571428571428</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>-2.071428571428571</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>-2.357142857142858</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>-0.666666666666667</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>-0.2142857142857142</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>-1.214285714285714</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0.9285714285714284</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>67.826443001443</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>68.34886363636363</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>286</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>0.05785123966942152</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>2.400000000000006</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0.2800701513087915</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0.7838016528925777</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>1366474.380165289</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>2.278016528925619</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0.009777622723447621</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>-56348.01347093843</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>12325000</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>-1.647175696439238</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>-0.02425421197160338</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>-4.800000000000001</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>279</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>3.291074380165284</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>0.8869191051398531</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>-0.2416528925619872</v>
+      </c>
+      <c r="BE42" t="n">
         <v>0</v>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
@@ -515,94 +515,94 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -615,97 +615,97 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_start</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_pot_player_miss</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -783,108 +783,108 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4173333333333333</v>
+        <v>-0.1999999999999993</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6193333333333333</v>
+        <v>2.300000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3333333333333339</v>
+        <v>1.1</v>
       </c>
       <c r="U2" t="n">
-        <v>-1</v>
+        <v>-1.3</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.6171428571428572</v>
       </c>
       <c r="W2" t="n">
-        <v>-4.833333333333332</v>
+        <v>-0.5436507936507937</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5</v>
+        <v>4.099999999999994</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.666666666666666</v>
+        <v>-4.099999999999994</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.5</v>
+        <v>-0.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>-7.333333333333334</v>
+        <v>-0.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5</v>
+        <v>0.5999999999999996</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.8999999999999995</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.5</v>
+        <v>-0.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>3.333333333333336</v>
+        <v>1.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>-3.333333333333336</v>
+        <v>-3.7</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.166666666666667</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1.333333333333333</v>
+        <v>-8.6</v>
       </c>
       <c r="AJ2" t="n">
-        <v>67.39545454545454</v>
+        <v>67.49318181818182</v>
       </c>
       <c r="AK2" t="n">
-        <v>68.14565656565655</v>
+        <v>67.81705948372615</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.8809675693206387</v>
+        <v>-1.856329966329952</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1.135349536645123</v>
+        <v>0.4124964541125706</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9790209790209587</v>
+        <v>0.3834223344123586</v>
       </c>
       <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="n">
-        <v>-2.060411810411836</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0.1370435120435118</v>
-      </c>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>126822.8720131733</v>
+      </c>
       <c r="AT2" t="n">
-        <v>0.7264763014762963</v>
+        <v>-0.6424344120465975</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.05693617135769502</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.7532828282828241</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="n">
-        <v>-757832.5563325565</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+        <v>-485418.7469937471</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="n">
+        <v>0.05010740792594737</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="n">
+        <v>0.577905242905242</v>
+      </c>
       <c r="AZ2" t="n">
-        <v>-0.0842319001685965</v>
+        <v>0.1678090428090424</v>
       </c>
       <c r="BA2" t="n">
-        <v>-109254.0965385477</v>
-      </c>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="n">
-        <v>0.3731085978061515</v>
-      </c>
-      <c r="BD2" t="inlineStr"/>
+        <v>-0.8417998119167009</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.347914862914848</v>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="n">
+        <v>1.399759499759497</v>
+      </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -958,104 +958,104 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5779999999999998</v>
+        <v>2.263888888888889</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9330000000000001</v>
+        <v>1.916666666666666</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3999999999999999</v>
+        <v>-0.05555555555555558</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8499999999999996</v>
+        <v>-0.09722222222222232</v>
       </c>
       <c r="V3" t="n">
-        <v>1.083333333333333</v>
+        <v>0.3049999999999997</v>
       </c>
       <c r="W3" t="n">
-        <v>-2.333333333333333</v>
+        <v>-0.125</v>
       </c>
       <c r="X3" t="n">
-        <v>3.666666666666666</v>
+        <v>4.888888888888886</v>
       </c>
       <c r="Y3" t="n">
-        <v>-2.833333333333334</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-7.083333333333334</v>
-      </c>
+        <v>-4.888888888888886</v>
+      </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>1.25</v>
+        <v>-0.1746031746031749</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.08333333333333326</v>
-      </c>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+        <v>-0.04761904761904745</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.8055555555555556</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.6527777777777777</v>
+      </c>
       <c r="AF3" t="n">
-        <v>7.25</v>
+        <v>0.6527777777777777</v>
       </c>
       <c r="AG3" t="n">
-        <v>-7.25</v>
+        <v>-0.375</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.9166666666666666</v>
+        <v>2.777777777777779</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.8333333333333333</v>
+        <v>-2.722222222222221</v>
       </c>
       <c r="AJ3" t="n">
-        <v>70.03282828282829</v>
+        <v>69.25063131313132</v>
       </c>
       <c r="AK3" t="n">
-        <v>68.10151515151516</v>
+        <v>68.65656565656565</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.01695216398743</v>
+        <v>1.688967070081617</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.979606226529341</v>
+        <v>-0.3651008675909395</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.3835353535353505</v>
+        <v>1.360629448130339</v>
       </c>
       <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="n">
-        <v>1.439393939393966</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
+      <c r="AS3" t="n">
+        <v>265869.6239433771</v>
+      </c>
       <c r="AT3" t="n">
-        <v>0.6612121212121167</v>
+        <v>1.55785332598435</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.117676767676773</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="n">
-        <v>96916.16161616147</v>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+        <v>-77789.61441035755</v>
+      </c>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="n">
+        <v>1.026766113143822</v>
+      </c>
       <c r="AZ3" t="n">
-        <v>2.192552960420159</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>550487.0562760041</v>
-      </c>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="n">
-        <v>-0.2282825099466947</v>
-      </c>
-      <c r="BD3" t="inlineStr"/>
+        <v>2.078844773304326</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>-0.03498452012384234</v>
+      </c>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="n">
+        <v>0.2696875879538396</v>
+      </c>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1129,108 +1129,108 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.03</v>
+        <v>2.699999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.58</v>
+        <v>-2.9</v>
       </c>
       <c r="T4" t="n">
-        <v>0.25</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.25</v>
+        <v>-2.3</v>
       </c>
       <c r="V4" t="n">
-        <v>4.199999999999999</v>
+        <v>0.838888888888889</v>
       </c>
       <c r="W4" t="n">
-        <v>-3.2</v>
+        <v>-1.052222222222222</v>
       </c>
       <c r="X4" t="n">
-        <v>2.6</v>
+        <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>-2.199999999999999</v>
+        <v>-8</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.600000000000001</v>
+        <v>-8</v>
       </c>
       <c r="AA4" t="n">
-        <v>-6.800000000000001</v>
+        <v>-16</v>
       </c>
       <c r="AB4" t="n">
+        <v>-0.2222222222222223</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.4444444444444438</v>
+      </c>
+      <c r="AD4" t="n">
         <v>0.3999999999999999</v>
       </c>
-      <c r="AC4" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-8</v>
-      </c>
       <c r="AE4" t="n">
-        <v>-16</v>
+        <v>-2.4</v>
       </c>
       <c r="AF4" t="n">
-        <v>10.8</v>
+        <v>3.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>-10.8</v>
+        <v>-2.399999999999999</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.2</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="AI4" t="n">
-        <v>-2</v>
+        <v>-3.6</v>
       </c>
       <c r="AJ4" t="n">
-        <v>69.02727272727273</v>
+        <v>69.02850729517395</v>
       </c>
       <c r="AK4" t="n">
-        <v>67.45454545454547</v>
+        <v>67.85331088664424</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.6431171330671468</v>
+        <v>0.169949494949492</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.8689361731038048</v>
+        <v>2.655983023637575</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.296786042240583</v>
+        <v>0.694417022110926</v>
       </c>
       <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="n">
-        <v>-0.4331496786042237</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0.3266299357208451</v>
-      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>253253.8212535749</v>
+      </c>
       <c r="AT4" t="n">
-        <v>2.602387511478426</v>
+        <v>-0.6112600270461321</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.01154401154401152</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.5262626262626142</v>
-      </c>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="n">
-        <v>1706640.955004592</v>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+        <v>1996529.797979798</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="n">
+        <v>0.006349206349206327</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="n">
+        <v>0.6844444444444413</v>
+      </c>
       <c r="AZ4" t="n">
-        <v>1.732702993162775</v>
+        <v>0.3541919191919194</v>
       </c>
       <c r="BA4" t="n">
-        <v>365763.7921170387</v>
-      </c>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="n">
-        <v>2.287032299445116</v>
-      </c>
-      <c r="BD4" t="inlineStr"/>
+        <v>-1.841286573838119</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>3.039595959595957</v>
+      </c>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="n">
+        <v>3.181313131313146</v>
+      </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45466.0625</v>
+        <v>45465.9375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1300,104 +1300,104 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.016666666666666</v>
+        <v>-1.574999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.228333333333333</v>
+        <v>-0.7750000000000004</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1666666666666665</v>
+        <v>0.85</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1666666666666665</v>
+        <v>-0.8</v>
       </c>
       <c r="V5" t="n">
-        <v>2.75</v>
+        <v>0.2182857142857142</v>
       </c>
       <c r="W5" t="n">
-        <v>-4.25</v>
+        <v>-1.162714285714285</v>
       </c>
       <c r="X5" t="n">
-        <v>-4.25</v>
+        <v>10.025</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-8.25</v>
-      </c>
+        <v>-10.025</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>1.277777777777778</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
+        <v>0.6944444444444446</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-1.025</v>
+      </c>
       <c r="AF5" t="n">
-        <v>13.25</v>
+        <v>1.2</v>
       </c>
       <c r="AG5" t="n">
-        <v>-13.25</v>
+        <v>-3.6</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>4.625</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1</v>
+        <v>-8.125</v>
       </c>
       <c r="AJ5" t="n">
-        <v>67.7590909090909</v>
+        <v>67.8340909090909</v>
       </c>
       <c r="AK5" t="n">
-        <v>66.84595959595958</v>
+        <v>68.02292929292929</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.8062073696408696</v>
+        <v>1.382668793195052</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1.907425065511973</v>
+        <v>-1.718562139863792</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.4399999999999977</v>
+        <v>-4.40528768299496</v>
       </c>
       <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="n">
-        <v>0.7657575757575614</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-0.01818181818181808</v>
-      </c>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>-537860.388673124</v>
+      </c>
       <c r="AT5" t="n">
-        <v>-0.004141414141415112</v>
+        <v>-1.56172887495239</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.0935099111414901</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.298787878787877</v>
-      </c>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="n">
-        <v>426972.2222222225</v>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+        <v>364170.1222753853</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="n">
+        <v>-0.1326377813219919</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="n">
+        <v>-0.08229665071770498</v>
+      </c>
       <c r="AZ5" t="n">
-        <v>-3.844034424878735</v>
+        <v>-0.02020202020202011</v>
       </c>
       <c r="BA5" t="n">
-        <v>-484968.2158682763</v>
-      </c>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="n">
-        <v>-2.270556856471174</v>
-      </c>
-      <c r="BD5" t="inlineStr"/>
+        <v>-1.024630916662147</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-0.3855927698032815</v>
+      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="n">
+        <v>-0.503987240829332</v>
+      </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45466.0625</v>
+        <v>45465.9375</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1471,104 +1471,104 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0445</v>
+        <v>5.675000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2875000000000001</v>
+        <v>-0.5999999999999996</v>
       </c>
       <c r="T6" t="n">
-        <v>0.75</v>
+        <v>1.075</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5</v>
+        <v>-0.8</v>
       </c>
       <c r="V6" t="n">
-        <v>4.1</v>
+        <v>0.4597222222222226</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3499999999999996</v>
+        <v>-0.661388888888889</v>
       </c>
       <c r="X6" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.09999999999999964</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>-4.5</v>
-      </c>
+        <v>-2.5</v>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="n">
-        <v>2.65</v>
+        <v>-0.1500000000000004</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
+        <v>0.4000000000000004</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-0.5249999999999999</v>
+      </c>
       <c r="AF6" t="n">
-        <v>4.350000000000001</v>
+        <v>1.95</v>
       </c>
       <c r="AG6" t="n">
-        <v>-4.350000000000001</v>
+        <v>-0.9000000000000004</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.4</v>
+        <v>2.025</v>
       </c>
       <c r="AI6" t="n">
-        <v>-1.8</v>
+        <v>-4.949999999999999</v>
       </c>
       <c r="AJ6" t="n">
-        <v>66.60606060606061</v>
+        <v>66.84141414141413</v>
       </c>
       <c r="AK6" t="n">
-        <v>67.58181818181818</v>
+        <v>68.17636363636363</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.003045009351396</v>
+        <v>0.2505316321105511</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.003418932878077</v>
+        <v>0.1766835188235945</v>
       </c>
       <c r="AN6" t="n">
-        <v>-2.117061524334261</v>
+        <v>-1.028231173520354</v>
       </c>
       <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="n">
-        <v>-0.04542699724518684</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>-0.04222222222222216</v>
-      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>-370466.8899641812</v>
+      </c>
       <c r="AT6" t="n">
-        <v>-4.911331496786048</v>
+        <v>0.7207818287325374</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.0306771911663215</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>-2.124214876033058</v>
-      </c>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="n">
-        <v>-1944304.178145088</v>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+        <v>-2355041.135034557</v>
+      </c>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="n">
+        <v>-0.024729849987287</v>
+      </c>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="n">
+        <v>-2.525491759702287</v>
+      </c>
       <c r="AZ6" t="n">
-        <v>-0.7248012897033504</v>
+        <v>-0.06374269005847943</v>
       </c>
       <c r="BA6" t="n">
-        <v>-184865.2815633246</v>
-      </c>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="n">
-        <v>-0.3235549889865723</v>
-      </c>
-      <c r="BD6" t="inlineStr"/>
+        <v>0.9195897095417251</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-2.069909622541203</v>
+      </c>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="n">
+        <v>-5.483426368952678</v>
+      </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1642,104 +1642,104 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5115000000000001</v>
+        <v>1.222222222222221</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2215</v>
+        <v>-2.111111111111112</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1499999999999999</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5999999999999996</v>
+        <v>-1.222222222222222</v>
       </c>
       <c r="V7" t="n">
-        <v>3.6</v>
+        <v>0.803472222222222</v>
       </c>
       <c r="W7" t="n">
-        <v>-3.4</v>
+        <v>-0.7922222222222224</v>
       </c>
       <c r="X7" t="n">
-        <v>1.4</v>
+        <v>-1.666666666666664</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.1999999999999993</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>6.600000000000001</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>-8.600000000000001</v>
-      </c>
+        <v>1.666666666666664</v>
+      </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="n">
-        <v>1.4</v>
+        <v>-1.111111111111111</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
+        <v>-0.333333333333333</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.222222222222222</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
       <c r="AF7" t="n">
-        <v>-5.200000000000003</v>
+        <v>3.777777777777778</v>
       </c>
       <c r="AG7" t="n">
-        <v>5.200000000000003</v>
+        <v>-2.555555555555555</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.8</v>
+        <v>9.555555555555554</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1.8</v>
+        <v>-8.444444444444445</v>
       </c>
       <c r="AJ7" t="n">
-        <v>67.93818181818182</v>
+        <v>68.50998877665545</v>
       </c>
       <c r="AK7" t="n">
-        <v>68.78909090909092</v>
+        <v>67.97979797979798</v>
       </c>
       <c r="AL7" t="n">
-        <v>-3.502215123272801</v>
+        <v>1.247740563530044</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.8621562542914489</v>
+        <v>2.413225044270206</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.124545454545455</v>
+        <v>-1.57084357910793</v>
       </c>
       <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="n">
-        <v>2.030000000000001</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>-0.1054545454545455</v>
-      </c>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
+      <c r="AS7" t="n">
+        <v>29262.45470763673</v>
+      </c>
       <c r="AT7" t="n">
-        <v>-1.952727272727273</v>
+        <v>-3.592612603412302</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.2947686030934114</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>-1.863636363636363</v>
-      </c>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="n">
-        <v>-1039872.727272728</v>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+        <v>-755191.3875598088</v>
+      </c>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="n">
+        <v>-0.3060454943951165</v>
+      </c>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="n">
+        <v>-2.084848484848489</v>
+      </c>
       <c r="AZ7" t="n">
-        <v>-1.104131745410186</v>
+        <v>-0.1009569377990431</v>
       </c>
       <c r="BA7" t="n">
-        <v>84859.6771782008</v>
-      </c>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="n">
-        <v>2.815060032472886</v>
-      </c>
-      <c r="BD7" t="inlineStr"/>
+        <v>-0.7879756813832444</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.472514619883057</v>
+      </c>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="n">
+        <v>-1.59813928761298</v>
+      </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1813,104 +1813,104 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2593333333333332</v>
+        <v>-1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7086666666666667</v>
+        <v>-3.425000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.25</v>
+        <v>0.1499999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.25</v>
+        <v>-0.5249999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>0.25</v>
+        <v>0.3184285714285711</v>
       </c>
       <c r="W8" t="n">
-        <v>-4.05</v>
+        <v>-0.3965714285714284</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5999999999999996</v>
+        <v>0.375</v>
       </c>
       <c r="Y8" t="n">
-        <v>-2.199999999999999</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>-6.199999999999999</v>
-      </c>
+        <v>-0.375</v>
+      </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="n">
-        <v>0.3</v>
+        <v>-0.1746031746031749</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
+        <v>-0.06349206349206327</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.7250000000000001</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-0.05000000000000004</v>
+      </c>
       <c r="AF8" t="n">
-        <v>5.950000000000003</v>
+        <v>0.6500000000000004</v>
       </c>
       <c r="AG8" t="n">
-        <v>-5.950000000000003</v>
+        <v>-2.15</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0.6499999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.25</v>
+        <v>-2.449999999999999</v>
       </c>
       <c r="AJ8" t="n">
-        <v>65.88727272727272</v>
+        <v>67.17808080808081</v>
       </c>
       <c r="AK8" t="n">
-        <v>68.55227272727272</v>
+        <v>68.88939393939395</v>
       </c>
       <c r="AL8" t="n">
-        <v>6.045468885853413</v>
+        <v>2.094360269360237</v>
       </c>
       <c r="AM8" t="n">
-        <v>2.131452263226976</v>
+        <v>-4.693622716934243</v>
       </c>
       <c r="AN8" t="n">
-        <v>-1.412991021324345</v>
+        <v>3.443674117364196</v>
       </c>
       <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="n">
-        <v>2.505050505050519</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0.1636363636363638</v>
-      </c>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
+      <c r="AS8" t="n">
+        <v>-41029.75435512234</v>
+      </c>
       <c r="AT8" t="n">
-        <v>3.15970819304151</v>
+        <v>6.388933506051387</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.05126811594202896</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>5.129040404040403</v>
-      </c>
-      <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="n">
-        <v>1470414.562289563</v>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+        <v>971222.9938271602</v>
+      </c>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="n">
+        <v>0.05095860258903739</v>
+      </c>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="n">
+        <v>4.812640291806961</v>
+      </c>
       <c r="AZ8" t="n">
-        <v>2.71180243292519</v>
+        <v>0.1212121212121215</v>
       </c>
       <c r="BA8" t="n">
-        <v>-262377.6618656204</v>
-      </c>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="n">
-        <v>-4.935305472327045</v>
-      </c>
-      <c r="BD8" t="inlineStr"/>
+        <v>2.178013191945126</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-2.67790404040403</v>
+      </c>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="n">
+        <v>1.803675645342324</v>
+      </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1976,104 +1976,104 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.165</v>
+        <v>4.366666666666665</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0525000000000001</v>
+        <v>2.077777777777779</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.2</v>
+        <v>-0.03333333333333321</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7999999999999998</v>
+        <v>-0.03333333333333321</v>
       </c>
       <c r="V9" t="n">
-        <v>1.933333333333333</v>
+        <v>0.2084126984126986</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.9666666666666668</v>
+        <v>-0.3568253968253969</v>
       </c>
       <c r="X9" t="n">
-        <v>3.333333333333334</v>
+        <v>0.3555555555555543</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.9000000000000004</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.766666666666667</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>-3.966666666666667</v>
-      </c>
+        <v>-0.3555555555555543</v>
+      </c>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="n">
-        <v>-0.2</v>
+        <v>-2.305555555555555</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
+        <v>-0.6805555555555554</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.3222222222222223</v>
+      </c>
       <c r="AF9" t="n">
-        <v>1.200000000000003</v>
+        <v>1.822222222222222</v>
       </c>
       <c r="AG9" t="n">
-        <v>-1.200000000000003</v>
+        <v>-1.644444444444445</v>
       </c>
       <c r="AH9" t="n">
-        <v>-1.033333333333333</v>
+        <v>5.077777777777779</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.166666666666667</v>
+        <v>-6.611111111111111</v>
       </c>
       <c r="AJ9" t="n">
-        <v>68.88545454545455</v>
+        <v>67.88098484848486</v>
       </c>
       <c r="AK9" t="n">
-        <v>69.91818181818181</v>
+        <v>68.7746212121212</v>
       </c>
       <c r="AL9" t="n">
-        <v>-1.665747722029273</v>
+        <v>3.228282828282772</v>
       </c>
       <c r="AM9" t="n">
-        <v>2.629907805276702</v>
+        <v>-0.3943355022011161</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.5128787878787762</v>
+        <v>-0.3520799704598119</v>
       </c>
       <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="n">
-        <v>2.90681818181821</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0.0368686868686865</v>
-      </c>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
+      <c r="AS9" t="n">
+        <v>-482365.734690642</v>
+      </c>
       <c r="AT9" t="n">
-        <v>0.7770833333333371</v>
+        <v>-1.343103367977431</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.04063644688644685</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>-0.4830176767676804</v>
-      </c>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="n">
-        <v>-1412476.957070707</v>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+        <v>-2655420.517676768</v>
+      </c>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="n">
+        <v>-0.02438186813186816</v>
+      </c>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="n">
+        <v>-0.5989520202020202</v>
+      </c>
       <c r="AZ9" t="n">
-        <v>-0.8646347583700305</v>
+        <v>-0.02414141414141424</v>
       </c>
       <c r="BA9" t="n">
-        <v>-749698.4368223345</v>
-      </c>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="n">
-        <v>-0.4962656232363685</v>
-      </c>
-      <c r="BD9" t="inlineStr"/>
+        <v>3.035402039938589</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-1.054444444444428</v>
+      </c>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="n">
+        <v>-0.1464772727272674</v>
+      </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2147,104 +2147,104 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3809999999999999</v>
+        <v>-2.371428571428572</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8159999999999997</v>
+        <v>2.457142857142857</v>
       </c>
       <c r="T10" t="n">
-        <v>-3.333333333333333</v>
+        <v>0.9142857142857141</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.8</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="V10" t="n">
-        <v>1.142857142857143</v>
+        <v>0.6103571428571429</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.214285714285714</v>
+        <v>-0.5589285714285714</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.5</v>
+        <v>7.857142857142854</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.285714285714286</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>-0.3571428571428577</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-2.5</v>
-      </c>
+        <v>-7.857142857142854</v>
+      </c>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="n">
-        <v>-0.7857142857142858</v>
+        <v>-2.444444444444444</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.285714285714286</v>
-      </c>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.1285714285714286</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-0.9428571428571429</v>
+      </c>
       <c r="AF10" t="n">
-        <v>5.642857142857146</v>
+        <v>1.914285714285715</v>
       </c>
       <c r="AG10" t="n">
-        <v>-5.642857142857146</v>
+        <v>-1.971428571428572</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.07142857142857145</v>
+        <v>1.742857142857142</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.5714285714285716</v>
+        <v>-3.171428571428571</v>
       </c>
       <c r="AJ10" t="n">
-        <v>68.14090909090909</v>
+        <v>68.80360750360749</v>
       </c>
       <c r="AK10" t="n">
-        <v>66.93333333333334</v>
+        <v>67.15802469135802</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.7562135820511777</v>
+        <v>0.2275432900432861</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.031940604744307</v>
+        <v>2.696758949627281</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.170598845598846</v>
+        <v>1.525271918385272</v>
       </c>
       <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="n">
-        <v>0.567171717171675</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>-0.05454545454545445</v>
-      </c>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
+      <c r="AS10" t="n">
+        <v>485187.5659744573</v>
+      </c>
       <c r="AT10" t="n">
-        <v>1.856421356421365</v>
+        <v>-0.3111848824949419</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.06822406257188884</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>-1.733044733044732</v>
-      </c>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="n">
-        <v>1667378.246753247</v>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+        <v>1850828.778860029</v>
+      </c>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="n">
+        <v>-0.05540619146209225</v>
+      </c>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="n">
+        <v>-2.225234487734486</v>
+      </c>
       <c r="AZ10" t="n">
-        <v>1.507395550007423</v>
+        <v>-0.06450216450216439</v>
       </c>
       <c r="BA10" t="n">
-        <v>760376.2857075199</v>
-      </c>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="n">
-        <v>2.882642728589019</v>
-      </c>
-      <c r="BD10" t="inlineStr"/>
+        <v>2.062547346041015</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>2.44452561327563</v>
+      </c>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="n">
+        <v>0.636679292929287</v>
+      </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2318,104 +2318,104 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7020000000000002</v>
+        <v>1.277777777777779</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.07399999999999984</v>
+        <v>-2.444444444444445</v>
       </c>
       <c r="T11" t="n">
-        <v>-1</v>
+        <v>-0.02222222222222237</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2000000000000002</v>
+        <v>-0.05555555555555558</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>1.136666666666667</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.833333333333333</v>
+        <v>0.1251388888888889</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.5</v>
+        <v>1.299999999999997</v>
       </c>
       <c r="Y11" t="n">
-        <v>-3.833333333333332</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.166666666666666</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>-3.5</v>
-      </c>
+        <v>-1.299999999999997</v>
+      </c>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="n">
-        <v>0.1666666666666665</v>
+        <v>-0.3333333333333339</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.1666666666666665</v>
-      </c>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
+        <v>-0.4444444444444446</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.2777777777777777</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.3555555555555556</v>
+      </c>
       <c r="AF11" t="n">
-        <v>2.5</v>
+        <v>1.366666666666667</v>
       </c>
       <c r="AG11" t="n">
-        <v>-2.5</v>
+        <v>-0.7111111111111104</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.1666666666666666</v>
+        <v>6.699999999999999</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-3.033333333333333</v>
       </c>
       <c r="AJ11" t="n">
-        <v>67.4590909090909</v>
+        <v>68.40909090909091</v>
       </c>
       <c r="AK11" t="n">
-        <v>68.87239057239057</v>
+        <v>68.42962962962964</v>
       </c>
       <c r="AL11" t="n">
-        <v>-2.505192864482446</v>
+        <v>3.328654970760255</v>
       </c>
       <c r="AM11" t="n">
-        <v>2.314807860470381</v>
+        <v>2.795515720335771</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0.588512396694199</v>
+        <v>-2.430261547165962</v>
       </c>
       <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="n">
-        <v>3.854876033057849</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>-0.05404958677685956</v>
-      </c>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr"/>
+      <c r="AS11" t="n">
+        <v>-311708.3553284412</v>
+      </c>
       <c r="AT11" t="n">
-        <v>-0.8647107438016377</v>
+        <v>-2.832262146717234</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0.07760590540910872</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0.135206611570247</v>
-      </c>
-      <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="n">
-        <v>-472622.7272727271</v>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+        <v>-190078.6815523659</v>
+      </c>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="n">
+        <v>-0.06419539111160155</v>
+      </c>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="n">
+        <v>0.4582137161084496</v>
+      </c>
       <c r="AZ11" t="n">
-        <v>-2.440674125125952</v>
+        <v>0.001754385964912508</v>
       </c>
       <c r="BA11" t="n">
-        <v>-383308.3381888666</v>
-      </c>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="n">
-        <v>2.443193316865049</v>
-      </c>
-      <c r="BD11" t="inlineStr"/>
+        <v>2.260264525956501</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-0.3542264752791198</v>
+      </c>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="n">
+        <v>-0.007974481658706623</v>
+      </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2489,104 +2489,104 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2225</v>
+        <v>-1.805555555555555</v>
       </c>
       <c r="S12" t="n">
-        <v>0.02083333333333348</v>
+        <v>-0.1944444444444446</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.666666666666667</v>
+        <v>-0.2083333333333334</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>2.392857142857143</v>
+        <v>1.215</v>
       </c>
       <c r="W12" t="n">
-        <v>-1.464285714285714</v>
+        <v>0.1650000000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.071428571428571</v>
+        <v>8.930555555555557</v>
       </c>
       <c r="Y12" t="n">
-        <v>-2.357142857142858</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>11.53571428571428</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>-5.392857142857142</v>
-      </c>
+        <v>-8.930555555555557</v>
+      </c>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="n">
-        <v>-0.2142857142857142</v>
+        <v>1.625</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
+        <v>1.285714285714286</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.2777777777777777</v>
+      </c>
       <c r="AF12" t="n">
-        <v>11.03571428571428</v>
+        <v>2.027777777777778</v>
       </c>
       <c r="AG12" t="n">
-        <v>-11.03571428571428</v>
+        <v>-0.4027777777777777</v>
       </c>
       <c r="AH12" t="n">
-        <v>-1.214285714285714</v>
+        <v>10.29166666666667</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.9285714285714284</v>
+        <v>-2.791666666666666</v>
       </c>
       <c r="AJ12" t="n">
-        <v>67.826443001443</v>
+        <v>67.72157687991022</v>
       </c>
       <c r="AK12" t="n">
-        <v>68.34886363636363</v>
+        <v>68.51306818181818</v>
       </c>
       <c r="AL12" t="n">
-        <v>-1.647175696439238</v>
+        <v>1.168527379053643</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.2800701513087915</v>
+        <v>0.5834712189529512</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.278016528925619</v>
+        <v>0.09612246777915345</v>
       </c>
       <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="n">
-        <v>0.7838016528925777</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0.05785123966942152</v>
-      </c>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
       <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="inlineStr"/>
+      <c r="AS12" t="n">
+        <v>45052.53749039094</v>
+      </c>
       <c r="AT12" t="n">
-        <v>3.291074380165284</v>
+        <v>-1.110747861012868</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0.02425421197160338</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>-0.2416528925619872</v>
-      </c>
-      <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="n">
-        <v>1366474.380165289</v>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+        <v>1330648.856990963</v>
+      </c>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="n">
+        <v>0.01707728935064368</v>
+      </c>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="n">
+        <v>-0.6745348219032472</v>
+      </c>
       <c r="AZ12" t="n">
-        <v>0.009777622723447621</v>
+        <v>0.04752791068580575</v>
       </c>
       <c r="BA12" t="n">
-        <v>-56348.01347093843</v>
-      </c>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="n">
-        <v>0.8869191051398531</v>
-      </c>
-      <c r="BD12" t="inlineStr"/>
+        <v>0.3617345724115069</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>2.054226475279108</v>
+      </c>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="n">
+        <v>2.65106326422115</v>
+      </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
@@ -2598,7 +2598,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2660,104 +2660,104 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7549999999999999</v>
+        <v>-0.5396825396825395</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.794166666666666</v>
+        <v>0.1111111111111107</v>
       </c>
       <c r="T13" t="n">
-        <v>1.416666666666667</v>
+        <v>1.031746031746032</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>-1.253968253968254</v>
       </c>
       <c r="V13" t="n">
-        <v>2.533333333333333</v>
+        <v>0.5489285714285715</v>
       </c>
       <c r="W13" t="n">
-        <v>-1.866666666666667</v>
+        <v>-2.000714285714286</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.666666666666666</v>
+        <v>1.873015873015873</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.933333333333333</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>7.266666666666667</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>-9.4</v>
-      </c>
+        <v>-1.873015873015873</v>
+      </c>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.291666666666667</v>
+      </c>
+      <c r="AD13" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="AC13" t="n">
-        <v>-0.2666666666666668</v>
-      </c>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
+      <c r="AE13" t="n">
+        <v>-1.142857142857143</v>
+      </c>
       <c r="AF13" t="n">
-        <v>2.200000000000003</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AG13" t="n">
-        <v>-2.200000000000003</v>
+        <v>-2.920634920634921</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.3999999999999999</v>
+        <v>3.873015873015873</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.4</v>
+        <v>-10.47619047619048</v>
       </c>
       <c r="AJ13" t="n">
-        <v>67.79050505050505</v>
+        <v>67.91952861952862</v>
       </c>
       <c r="AK13" t="n">
-        <v>69.42424242424242</v>
+        <v>68.21266233766234</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0.9438040970289983</v>
+        <v>-1.899999999999977</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.01656441074203485</v>
+        <v>-3.803331390131007</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.628282828282835</v>
+        <v>-3.81916678922321</v>
       </c>
       <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="n">
-        <v>-1.547727272727229</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>-0.09545454545454568</v>
-      </c>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
+      <c r="AS13" t="n">
+        <v>301379.355881332</v>
+      </c>
       <c r="AT13" t="n">
-        <v>0.2032828282828376</v>
+        <v>-1.150921132250105</v>
       </c>
       <c r="AU13" t="n">
-        <v>-0.08890100912159737</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>-1.377525252525249</v>
-      </c>
-      <c r="AW13" t="inlineStr"/>
-      <c r="AX13" t="n">
-        <v>728231.060606061</v>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+        <v>511994.94949495</v>
+      </c>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="n">
+        <v>-0.06716164114093681</v>
+      </c>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="n">
+        <v>-0.7921717171717226</v>
+      </c>
       <c r="AZ13" t="n">
-        <v>-4.450771461269383</v>
+        <v>-0.1092171717171717</v>
       </c>
       <c r="BA13" t="n">
-        <v>-30191.94156434387</v>
-      </c>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="n">
-        <v>-4.7376721554471</v>
-      </c>
-      <c r="BD13" t="inlineStr"/>
+        <v>1.749501716961106</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.5793560606060595</v>
+      </c>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="n">
+        <v>0.0388257575757649</v>
+      </c>
       <c r="BE13" t="n">
         <v>0</v>
       </c>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2831,104 +2831,104 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.08166666666666678</v>
+        <v>0.2916666666666661</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5183333333333333</v>
+        <v>0.1666666666666661</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4166666666666665</v>
+        <v>-0.2083333333333334</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3333333333333335</v>
+        <v>0.375</v>
       </c>
       <c r="V14" t="n">
-        <v>-2</v>
+        <v>0.3985714285714288</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.8</v>
+        <v>-0.6614285714285715</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.066666666666666</v>
+        <v>4.708333333333336</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.133333333333335</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0.1999999999999993</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>-8.466666666666669</v>
-      </c>
+        <v>-4.708333333333336</v>
+      </c>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="n">
-        <v>-1.6</v>
+        <v>-0.03571428571428559</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.06666666666666665</v>
-      </c>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
+        <v>0.625</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.4722222222222222</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-0.2916666666666667</v>
+      </c>
       <c r="AF14" t="n">
-        <v>-0.3999999999999986</v>
+        <v>0.5972222222222223</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.3999999999999986</v>
+        <v>-2.472222222222222</v>
       </c>
       <c r="AH14" t="n">
-        <v>-1.133333333333333</v>
+        <v>4.263888888888889</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.266666666666667</v>
+        <v>-8.652777777777779</v>
       </c>
       <c r="AJ14" t="n">
-        <v>69.91797979797981</v>
+        <v>68.85342312008979</v>
       </c>
       <c r="AK14" t="n">
-        <v>66.59090909090908</v>
+        <v>68.0625</v>
       </c>
       <c r="AL14" t="n">
-        <v>-1.282047355983284</v>
+        <v>-2.363636363636374</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0.751210450918677</v>
+        <v>0.2296468669909615</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.087070707070708</v>
+        <v>-1.044533830663909</v>
       </c>
       <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="n">
-        <v>-2.27555555555557</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0.1622222222222225</v>
-      </c>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
       <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="inlineStr"/>
+      <c r="AS14" t="n">
+        <v>1035099.281434715</v>
+      </c>
       <c r="AT14" t="n">
-        <v>1.982020202020195</v>
+        <v>-0.7731005320788604</v>
       </c>
       <c r="AU14" t="n">
-        <v>-0.01730930587337931</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>1.180707070707072</v>
-      </c>
-      <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="n">
-        <v>532786.8686868688</v>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+        <v>393638.888888889</v>
+      </c>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="n">
+        <v>0.03718893826551883</v>
+      </c>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="n">
+        <v>0.6873737373737399</v>
+      </c>
       <c r="AZ14" t="n">
-        <v>-1.641670340211519</v>
+        <v>0.08484848484848473</v>
       </c>
       <c r="BA14" t="n">
-        <v>1165322.2044186</v>
-      </c>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="n">
-        <v>-0.02280751835671424</v>
-      </c>
-      <c r="BD14" t="inlineStr"/>
+        <v>-1.215278296153059</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.057070707070707</v>
+      </c>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="n">
+        <v>1.350505050505049</v>
+      </c>
       <c r="BE14" t="n">
         <v>0</v>
       </c>
@@ -2940,7 +2940,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -3002,104 +3002,104 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3524999999999998</v>
+        <v>-2.236111111111111</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4099999999999999</v>
+        <v>-1.027777777777779</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.916666666666667</v>
+        <v>1.25</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.75</v>
+        <v>-1.291666666666667</v>
       </c>
       <c r="V15" t="n">
-        <v>3.15</v>
+        <v>0.4422222222222221</v>
       </c>
       <c r="W15" t="n">
-        <v>0.25</v>
+        <v>-0.6511111111111109</v>
       </c>
       <c r="X15" t="n">
-        <v>1.1</v>
+        <v>-2.625</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.949999999999999</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>-2.699999999999999</v>
-      </c>
+        <v>2.625</v>
+      </c>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="n">
-        <v>0.8</v>
+        <v>0.375</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
+        <v>0.75</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9861111111111112</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-0.9305555555555556</v>
+      </c>
       <c r="AF15" t="n">
-        <v>-0.6499999999999986</v>
+        <v>3.375</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.6499999999999986</v>
+        <v>-2.069444444444445</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.9500000000000002</v>
+        <v>6.125</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.85</v>
+        <v>-5.111111111111111</v>
       </c>
       <c r="AJ15" t="n">
-        <v>68.31272727272727</v>
+        <v>68.76931818181819</v>
       </c>
       <c r="AK15" t="n">
-        <v>68.5409090909091</v>
+        <v>68.75881032547699</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.002499866273925733</v>
+        <v>-2.160765550239233</v>
       </c>
       <c r="AM15" t="n">
-        <v>2.321211952896533</v>
+        <v>3.091790983079207</v>
       </c>
       <c r="AN15" t="n">
-        <v>6.488181818181829</v>
+        <v>1.079492808770929</v>
       </c>
       <c r="AO15" t="inlineStr"/>
-      <c r="AP15" t="n">
-        <v>-2.30545454545458</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>-0.07363636363636372</v>
-      </c>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
       <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="inlineStr"/>
+      <c r="AS15" t="n">
+        <v>454684.7282312156</v>
+      </c>
       <c r="AT15" t="n">
-        <v>3.599999999999994</v>
+        <v>-0.3417111085176749</v>
       </c>
       <c r="AU15" t="n">
-        <v>-0.06943696430101065</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>-2.955454545454547</v>
-      </c>
-      <c r="AW15" t="inlineStr"/>
-      <c r="AX15" t="n">
-        <v>852163.6363636365</v>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+        <v>736282.296650718</v>
+      </c>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="n">
+        <v>-0.04908617967824047</v>
+      </c>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="n">
+        <v>-3.048325358851674</v>
+      </c>
       <c r="AZ15" t="n">
-        <v>0.8899904743145726</v>
+        <v>-0.08660287081339679</v>
       </c>
       <c r="BA15" t="n">
-        <v>190353.8610155566</v>
-      </c>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="n">
-        <v>2.787371215927536</v>
-      </c>
-      <c r="BD15" t="inlineStr"/>
+        <v>1.336127697941123</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>5.993779904306223</v>
+      </c>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="n">
+        <v>3.272727272727266</v>
+      </c>
       <c r="BE15" t="n">
         <v>0</v>
       </c>

--- a/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
@@ -460,34 +460,34 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>h2h_27_segun_loc</t>
@@ -515,94 +515,94 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions_against</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -615,97 +615,97 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_val_player_start</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_pot_player_miss</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -745,27 +745,27 @@
           <t>x05z14ue</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Onn3tCA5</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>167</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>1671</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>2024</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>KtuTuMN</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>EqKWmJf</t>
-        </is>
       </c>
       <c r="M2" t="n">
         <v>2</v>
@@ -783,10 +783,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>5.699999999999999</v>
+        <v>-0.2222222222222223</v>
       </c>
       <c r="S2" t="n">
-        <v>-3.6</v>
+        <v>0.4444444444444438</v>
       </c>
       <c r="T2" t="n">
         <v>-8</v>
@@ -795,46 +795,46 @@
         <v>-16</v>
       </c>
       <c r="V2" t="n">
+        <v>0.838888888888889</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-1.052222222222222</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.699999999999999</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-2.399999999999999</v>
+      </c>
+      <c r="AF2" t="n">
         <v>2.2</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AG2" t="n">
         <v>-2.3</v>
       </c>
-      <c r="X2" t="n">
-        <v>-0.2222222222222223</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.4444444444444438</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.838888888888889</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-1.052222222222222</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-2.399999999999999</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2.699999999999999</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.3999999999999999</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-2.4</v>
-      </c>
       <c r="AH2" t="n">
-        <v>8</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="AI2" t="n">
-        <v>-8</v>
+        <v>-3.6</v>
       </c>
       <c r="AJ2" t="n">
         <v>69.02850729517395</v>
@@ -843,47 +843,47 @@
         <v>67.85331088664424</v>
       </c>
       <c r="AL2" t="n">
-        <v>1996529.797979798</v>
-      </c>
-      <c r="AM2" t="n">
+        <v>0.694417022110926</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="n">
+        <v>3.181313131313146</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>3.039595959595957</v>
+      </c>
+      <c r="AP2" t="n">
         <v>-0.6112600270461321</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="n">
-        <v>3.181313131313146</v>
       </c>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
-        <v>0.006349206349206327</v>
+        <v>-1.841286573838119</v>
       </c>
       <c r="AT2" t="n">
-        <v>-1.841286573838119</v>
+        <v>253253.8212535749</v>
       </c>
       <c r="AU2" t="n">
-        <v>253253.8212535749</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.6844444444444413</v>
-      </c>
+        <v>2.655983023637575</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>2.655983023637575</v>
+        <v>1996529.797979798</v>
       </c>
       <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
+      <c r="AZ2" t="n">
+        <v>0.6844444444444413</v>
+      </c>
       <c r="BA2" t="n">
-        <v>3.039595959595957</v>
+        <v>0.3541919191919194</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.3541919191919194</v>
-      </c>
-      <c r="BC2" t="n">
+        <v>0.006349206349206327</v>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="n">
         <v>0.169949494949492</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0.694417022110926</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -920,27 +920,27 @@
           <t>4GtbI4Q1</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>167</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>1671</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>2024</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>86yPt28</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>UFWZoX9</t>
-        </is>
       </c>
       <c r="M3" t="n">
         <v>9</v>
@@ -958,10 +958,10 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>7.100000000000001</v>
+        <v>0.5999999999999996</v>
       </c>
       <c r="S3" t="n">
-        <v>-8.6</v>
+        <v>-0.8999999999999995</v>
       </c>
       <c r="T3" t="n">
         <v>-0.5</v>
@@ -970,46 +970,46 @@
         <v>-0.5</v>
       </c>
       <c r="V3" t="n">
+        <v>0.6171428571428572</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-0.5436507936507937</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.1999999999999993</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.300000000000001</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4.099999999999994</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-4.099999999999994</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="AF3" t="n">
         <v>1.1</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AG3" t="n">
         <v>-1.3</v>
       </c>
-      <c r="X3" t="n">
-        <v>0.5999999999999996</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-0.8999999999999995</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.6171428571428572</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-0.5436507936507937</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-0.1999999999999993</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2.300000000000001</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-0.8</v>
-      </c>
       <c r="AH3" t="n">
-        <v>4.099999999999994</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="AI3" t="n">
-        <v>-4.099999999999994</v>
+        <v>-8.6</v>
       </c>
       <c r="AJ3" t="n">
         <v>67.49318181818182</v>
@@ -1018,47 +1018,47 @@
         <v>67.81705948372615</v>
       </c>
       <c r="AL3" t="n">
-        <v>-485418.7469937471</v>
-      </c>
-      <c r="AM3" t="n">
+        <v>0.3834223344123586</v>
+      </c>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="n">
+        <v>1.399759499759497</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1.347914862914848</v>
+      </c>
+      <c r="AP3" t="n">
         <v>-0.6424344120465975</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="n">
-        <v>1.399759499759497</v>
       </c>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>0.05010740792594737</v>
+        <v>-0.8417998119167009</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.8417998119167009</v>
+        <v>126822.8720131733</v>
       </c>
       <c r="AU3" t="n">
-        <v>126822.8720131733</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0.577905242905242</v>
-      </c>
+        <v>0.4124964541125706</v>
+      </c>
+      <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>0.4124964541125706</v>
+        <v>-485418.7469937471</v>
       </c>
       <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
+      <c r="AZ3" t="n">
+        <v>0.577905242905242</v>
+      </c>
       <c r="BA3" t="n">
-        <v>1.347914862914848</v>
+        <v>0.1678090428090424</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.1678090428090424</v>
-      </c>
-      <c r="BC3" t="n">
+        <v>0.05010740792594737</v>
+      </c>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="n">
         <v>-1.856329966329952</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0.3834223344123586</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
@@ -1095,27 +1095,27 @@
           <t>K2dlua5N</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>167</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>1671</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>2024</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Onn3tCA</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Sd7snoa</t>
-        </is>
       </c>
       <c r="M4" t="n">
         <v>5</v>
@@ -1133,54 +1133,54 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.777777777777779</v>
+        <v>-0.1746031746031749</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.722222222222221</v>
+        <v>-0.04761904761904745</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
+        <v>0.3049999999999997</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-0.125</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.263888888888889</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.916666666666666</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4.888888888888886</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-4.888888888888886</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8055555555555556</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.6527777777777777</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.6527777777777777</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-0.375</v>
+      </c>
+      <c r="AF4" t="n">
         <v>-0.05555555555555558</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AG4" t="n">
         <v>-0.09722222222222232</v>
       </c>
-      <c r="X4" t="n">
-        <v>-0.1746031746031749</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-0.04761904761904745</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.3049999999999997</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-0.125</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.6527777777777777</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-0.375</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.263888888888889</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.916666666666666</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.8055555555555556</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.6527777777777777</v>
-      </c>
       <c r="AH4" t="n">
-        <v>4.888888888888886</v>
+        <v>2.777777777777779</v>
       </c>
       <c r="AI4" t="n">
-        <v>-4.888888888888886</v>
+        <v>-2.722222222222221</v>
       </c>
       <c r="AJ4" t="n">
         <v>69.25063131313132</v>
@@ -1189,47 +1189,47 @@
         <v>68.65656565656565</v>
       </c>
       <c r="AL4" t="n">
-        <v>-77789.61441035755</v>
-      </c>
-      <c r="AM4" t="n">
+        <v>1.360629448130339</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="n">
+        <v>0.2696875879538396</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.03498452012384234</v>
+      </c>
+      <c r="AP4" t="n">
         <v>1.55785332598435</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="n">
-        <v>0.2696875879538396</v>
       </c>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.078844773304326</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.078844773304326</v>
+        <v>265869.6239433771</v>
       </c>
       <c r="AU4" t="n">
-        <v>265869.6239433771</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1.026766113143822</v>
-      </c>
+        <v>-0.3651008675909395</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>-0.3651008675909395</v>
+        <v>-77789.61441035755</v>
       </c>
       <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
+      <c r="AZ4" t="n">
+        <v>1.026766113143822</v>
+      </c>
       <c r="BA4" t="n">
-        <v>-0.03498452012384234</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
         <v>0</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="n">
         <v>1.688967070081617</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>1.360629448130339</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>

--- a/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
@@ -515,94 +515,94 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions_against</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -615,97 +615,97 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -783,58 +783,58 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
+        <v>5.699999999999999</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.838888888888889</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-1.052222222222222</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-8</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="X2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-8</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.699999999999999</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="AD2" t="n">
         <v>-0.2222222222222223</v>
       </c>
-      <c r="S2" t="n">
+      <c r="AE2" t="n">
         <v>0.4444444444444438</v>
       </c>
-      <c r="T2" t="n">
-        <v>-8</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.838888888888889</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-1.052222222222222</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.699999999999999</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-8</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.3999999999999999</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="AD2" t="n">
+      <c r="AF2" t="n">
         <v>3.1</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AG2" t="n">
         <v>-2.399999999999999</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AH2" t="n">
         <v>2.2</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AI2" t="n">
         <v>-2.3</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>5.699999999999999</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-3.6</v>
       </c>
       <c r="AJ2" t="n">
         <v>69.02850729517395</v>
@@ -842,49 +842,49 @@
       <c r="AK2" t="n">
         <v>67.85331088664424</v>
       </c>
-      <c r="AL2" t="n">
-        <v>0.694417022110926</v>
-      </c>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
-        <v>3.181313131313146</v>
+        <v>1996529.797979798</v>
       </c>
       <c r="AO2" t="n">
+        <v>0.6844444444444413</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>253253.8212535749</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.006349206349206327</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-1.841286573838119</v>
+      </c>
+      <c r="AS2" t="n">
         <v>3.039595959595957</v>
       </c>
-      <c r="AP2" t="n">
-        <v>-0.6112600270461321</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="n">
-        <v>-1.841286573838119</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>253253.8212535749</v>
-      </c>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
         <v>2.655983023637575</v>
       </c>
-      <c r="AV2" t="inlineStr"/>
+      <c r="AV2" t="n">
+        <v>3.181313131313146</v>
+      </c>
       <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="n">
-        <v>1996529.797979798</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="n">
+        <v>0.169949494949492</v>
+      </c>
       <c r="AZ2" t="n">
-        <v>0.6844444444444413</v>
-      </c>
-      <c r="BA2" t="n">
+        <v>0.694417022110926</v>
+      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="n">
         <v>0.3541919191919194</v>
       </c>
-      <c r="BB2" t="n">
-        <v>0.006349206349206327</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="n">
-        <v>0.169949494949492</v>
-      </c>
+      <c r="BC2" t="n">
+        <v>-0.6112600270461321</v>
+      </c>
+      <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
@@ -958,58 +958,58 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
+        <v>7.100000000000001</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.6171428571428572</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-0.5436507936507937</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>4.099999999999994</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-4.099999999999994</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-0.1999999999999993</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.300000000000001</v>
+      </c>
+      <c r="AD3" t="n">
         <v>0.5999999999999996</v>
       </c>
-      <c r="S3" t="n">
+      <c r="AE3" t="n">
         <v>-0.8999999999999995</v>
       </c>
-      <c r="T3" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.6171428571428572</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-0.5436507936507937</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.1999999999999993</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.300000000000001</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.099999999999994</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-4.099999999999994</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="AD3" t="n">
+      <c r="AF3" t="n">
         <v>1.2</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AG3" t="n">
         <v>-3.7</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AH3" t="n">
         <v>1.1</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AI3" t="n">
         <v>-1.3</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>7.100000000000001</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-8.6</v>
       </c>
       <c r="AJ3" t="n">
         <v>67.49318181818182</v>
@@ -1017,49 +1017,49 @@
       <c r="AK3" t="n">
         <v>67.81705948372615</v>
       </c>
-      <c r="AL3" t="n">
-        <v>0.3834223344123586</v>
-      </c>
+      <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>1.399759499759497</v>
+        <v>-485418.7469937471</v>
       </c>
       <c r="AO3" t="n">
+        <v>0.577905242905242</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>126822.8720131733</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.05010740792594737</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-0.8417998119167009</v>
+      </c>
+      <c r="AS3" t="n">
         <v>1.347914862914848</v>
       </c>
-      <c r="AP3" t="n">
-        <v>-0.6424344120465975</v>
-      </c>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="n">
-        <v>-0.8417998119167009</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>126822.8720131733</v>
-      </c>
+      <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="n">
         <v>0.4124964541125706</v>
       </c>
-      <c r="AV3" t="inlineStr"/>
+      <c r="AV3" t="n">
+        <v>1.399759499759497</v>
+      </c>
       <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="n">
-        <v>-485418.7469937471</v>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="n">
+        <v>-1.856329966329952</v>
+      </c>
       <c r="AZ3" t="n">
-        <v>0.577905242905242</v>
-      </c>
-      <c r="BA3" t="n">
+        <v>0.3834223344123586</v>
+      </c>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="n">
         <v>0.1678090428090424</v>
       </c>
-      <c r="BB3" t="n">
-        <v>0.05010740792594737</v>
-      </c>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="n">
-        <v>-1.856329966329952</v>
-      </c>
+      <c r="BC3" t="n">
+        <v>-0.6424344120465975</v>
+      </c>
+      <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
@@ -1133,54 +1133,54 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
+        <v>2.777777777777779</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-2.722222222222221</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.3049999999999997</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0.125</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>4.888888888888886</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-4.888888888888886</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.8055555555555556</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.6527777777777777</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.263888888888889</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.916666666666666</v>
+      </c>
+      <c r="AD4" t="n">
         <v>-0.1746031746031749</v>
       </c>
-      <c r="S4" t="n">
+      <c r="AE4" t="n">
         <v>-0.04761904761904745</v>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="n">
-        <v>0.3049999999999997</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-0.125</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.263888888888889</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.916666666666666</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4.888888888888886</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-4.888888888888886</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.8055555555555556</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="AF4" t="n">
         <v>0.6527777777777777</v>
       </c>
-      <c r="AD4" t="n">
-        <v>0.6527777777777777</v>
-      </c>
-      <c r="AE4" t="n">
+      <c r="AG4" t="n">
         <v>-0.375</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AH4" t="n">
         <v>-0.05555555555555558</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AI4" t="n">
         <v>-0.09722222222222232</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>2.777777777777779</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-2.722222222222221</v>
       </c>
       <c r="AJ4" t="n">
         <v>69.25063131313132</v>
@@ -1188,49 +1188,49 @@
       <c r="AK4" t="n">
         <v>68.65656565656565</v>
       </c>
-      <c r="AL4" t="n">
-        <v>1.360629448130339</v>
-      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>0.2696875879538396</v>
+        <v>-77789.61441035755</v>
       </c>
       <c r="AO4" t="n">
+        <v>1.026766113143822</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>265869.6239433771</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2.078844773304326</v>
+      </c>
+      <c r="AS4" t="n">
         <v>-0.03498452012384234</v>
       </c>
-      <c r="AP4" t="n">
-        <v>1.55785332598435</v>
-      </c>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="n">
-        <v>2.078844773304326</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>265869.6239433771</v>
-      </c>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
         <v>-0.3651008675909395</v>
       </c>
-      <c r="AV4" t="inlineStr"/>
+      <c r="AV4" t="n">
+        <v>0.2696875879538396</v>
+      </c>
       <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="n">
-        <v>-77789.61441035755</v>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="n">
+        <v>1.688967070081617</v>
+      </c>
       <c r="AZ4" t="n">
-        <v>1.026766113143822</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
+        <v>1.360629448130339</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
         <v>0</v>
       </c>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="n">
-        <v>1.688967070081617</v>
-      </c>
+      <c r="BC4" t="n">
+        <v>1.55785332598435</v>
+      </c>
+      <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="n">
         <v>0</v>
       </c>

--- a/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE15"/>
+  <dimension ref="A1:BG15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,235 +480,245 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>competition</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>h2h_27_segun_loc</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>h2h_27</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>h2h_3_segun_loc</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>h2h_3</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>result</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_away_against</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_start</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_sub</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>is_rival_match</t>
         </is>
@@ -717,32 +727,32 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8K42rT3c</t>
+          <t>xbHaKGH7</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">badawi m 
+          <t xml:space="preserve">mendoza r 
   usa </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">lumen field
-  seattle  wa </t>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6P5S63Ah</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
+          <t>jmBZNRn8</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -759,19 +769,23 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>86yPt28</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>UFWZoX9</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>9</v>
-      </c>
-      <c r="N2" t="n">
-        <v>9</v>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
       </c>
       <c r="O2" t="n">
         <v>2</v>
@@ -780,144 +794,146 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.1999999999999993</v>
+        <v>-1</v>
       </c>
       <c r="S2" t="n">
-        <v>2.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1</v>
+        <v>0.7000000000000002</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.3</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6171428571428572</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.5436507936507937</v>
+        <v>-1.2</v>
       </c>
       <c r="X2" t="n">
-        <v>4.099999999999994</v>
+        <v>0.9905555555555556</v>
       </c>
       <c r="Y2" t="n">
-        <v>-4.099999999999994</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-0.5</v>
-      </c>
+        <v>-0.8773611111111113</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>0.5999999999999996</v>
+        <v>8.899999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.8999999999999995</v>
+        <v>-8.899999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.6</v>
+        <v>6.000000000000002</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.8</v>
+        <v>-3.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.2</v>
+        <v>0.8000000000000003</v>
       </c>
       <c r="AG2" t="n">
-        <v>-3.7</v>
+        <v>-0.9000000000000001</v>
       </c>
       <c r="AH2" t="n">
-        <v>7.100000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="AI2" t="n">
-        <v>-8.6</v>
+        <v>-2</v>
       </c>
       <c r="AJ2" t="n">
-        <v>67.49318181818182</v>
+        <v>3.1</v>
       </c>
       <c r="AK2" t="n">
-        <v>67.81705948372615</v>
+        <v>-3.199999999999999</v>
       </c>
       <c r="AL2" t="n">
-        <v>-1.856329966329952</v>
+        <v>69.30628507295175</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.4124964541125706</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0.3834223344123586</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
+        <v>67.47583333333334</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="n">
+        <v>2514428.487253487</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>5.66823727869582</v>
+      </c>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="n">
-        <v>126822.8720131733</v>
-      </c>
+      <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
-        <v>-0.6424344120465975</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>-485418.7469937471</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
+        <v>0.1612616517502943</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="n">
+        <v>0.5843097643098076</v>
+      </c>
       <c r="AW2" t="n">
-        <v>0.05010740792594737</v>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+        <v>3.636296296296294</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>2.977982606947716</v>
+      </c>
       <c r="AY2" t="n">
-        <v>0.577905242905242</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.1678090428090424</v>
-      </c>
+        <v>6.529850889850891</v>
+      </c>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
-        <v>-0.8417998119167009</v>
+        <v>4.183626743626718</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.347914862914848</v>
+        <v>0.006046863189720364</v>
       </c>
       <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="n">
-        <v>1.399759499759497</v>
+        <v>0.3546416546416549</v>
       </c>
       <c r="BE2" t="n">
+        <v>2.876827007246263</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>826287.0203028677</v>
+      </c>
+      <c r="BG2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ma0gz0nH</t>
+          <t>nTbjsvPK</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">unkel t 
+          <t xml:space="preserve">simon n 
   usa </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">providence park
-  portland  or </t>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>bm8usLzB</t>
+          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>K2dlua5N</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -934,161 +950,171 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Onn3tCA</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Sd7snoa</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>5</v>
-      </c>
-      <c r="N3" t="n">
-        <v>5</v>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Uw6sTk0t</t>
+        </is>
       </c>
       <c r="O3" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q3" t="n">
         <v>-1</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>-1</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.263888888888889</v>
-      </c>
       <c r="S3" t="n">
-        <v>1.916666666666666</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.05555555555555558</v>
+        <v>2.775</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.09722222222222232</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3049999999999997</v>
+        <v>1.068181818181818</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.125</v>
+        <v>-1.147727272727273</v>
       </c>
       <c r="X3" t="n">
-        <v>4.888888888888886</v>
+        <v>0.4288095238095239</v>
       </c>
       <c r="Y3" t="n">
-        <v>-4.888888888888886</v>
+        <v>-0.7014285714285715</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>-0.1746031746031749</v>
+        <v>5.488636363636367</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.04761904761904745</v>
+        <v>-5.488636363636367</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.8055555555555556</v>
+        <v>5.625</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.6527777777777777</v>
+        <v>-5.943181818181818</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.6527777777777777</v>
+        <v>0.3863636363636365</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.375</v>
+        <v>-0.9659090909090909</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.777777777777779</v>
+        <v>0.5568181818181817</v>
       </c>
       <c r="AI3" t="n">
-        <v>-2.722222222222221</v>
+        <v>-2.613636363636364</v>
       </c>
       <c r="AJ3" t="n">
-        <v>69.25063131313132</v>
+        <v>1.443181818181818</v>
       </c>
       <c r="AK3" t="n">
-        <v>68.65656565656565</v>
+        <v>2.477272727272727</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.688967070081617</v>
+        <v>67.5090909090909</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.3651008675909395</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.360629448130339</v>
-      </c>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
+        <v>68.00113636363636</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>-492168.5636266973</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-2.47096780148717</v>
+      </c>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="n">
-        <v>265869.6239433771</v>
-      </c>
+      <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>1.55785332598435</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>-77789.61441035755</v>
-      </c>
-      <c r="AV3" t="inlineStr"/>
+        <v>-2.001097225431039</v>
+      </c>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="n">
+        <v>-1.424819970035259</v>
+      </c>
       <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+        <v>0.288290802764493</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-2.040349198995298</v>
+      </c>
       <c r="AY3" t="n">
-        <v>1.026766113143822</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
+        <v>0.2767278043593819</v>
+      </c>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
-        <v>2.078844773304326</v>
+        <v>1.008369580977231</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.03498452012384234</v>
+        <v>-0.04773409260416539</v>
       </c>
       <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="n">
-        <v>0.2696875879538396</v>
+        <v>0.1011502585665267</v>
       </c>
       <c r="BE3" t="n">
+        <v>-0.01280881749406149</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>-29161.03879759973</v>
+      </c>
+      <c r="BG3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>YyTMIXGq</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
+          <t xml:space="preserve">dujic f 
+  can </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bmo stadium
-  los angeles  ca </t>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>txUJt9AR</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1105,165 +1131,171 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>KtuTuMN</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>EqKWmJf</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2</v>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
       </c>
       <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.8035714285714288</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.03571428571428559</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-0.375</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.4057142857142859</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-0.8542857142857142</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="n">
+        <v>5.875</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-5.875</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-2.125</v>
+      </c>
+      <c r="AE4" t="n">
         <v>-2</v>
       </c>
-      <c r="P4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.699999999999999</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.838888888888889</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-1.052222222222222</v>
-      </c>
-      <c r="X4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y4" t="n">
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-2.375</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>-8</v>
       </c>
-      <c r="Z4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-16</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-0.2222222222222223</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.4444444444444438</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0.3999999999999999</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-2.399999999999999</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>5.699999999999999</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>69.02850729517395</v>
-      </c>
       <c r="AK4" t="n">
-        <v>67.85331088664424</v>
+        <v>-0.625</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.169949494949492</v>
+        <v>68.08080808080808</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.655983023637575</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0.694417022110926</v>
-      </c>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
+        <v>69.45694444444445</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="n">
+        <v>649856.4593301439</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.2170156160859733</v>
+      </c>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="n">
-        <v>253253.8212535749</v>
-      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>-0.6112600270461321</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1996529.797979798</v>
-      </c>
-      <c r="AV4" t="inlineStr"/>
+        <v>-4.001063388247303</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="n">
+        <v>-5.013716108452968</v>
+      </c>
       <c r="AW4" t="n">
-        <v>0.006349206349206327</v>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+        <v>0.494391281233387</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.199859915608478</v>
+      </c>
       <c r="AY4" t="n">
-        <v>0.6844444444444413</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.3541919191919194</v>
-      </c>
+        <v>1.653349282296645</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>-1.841286573838119</v>
+        <v>0.7078415736310433</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.039595959595957</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>3.181313131313146</v>
+        <v>-0.187772461456672</v>
       </c>
       <c r="BE4" t="n">
+        <v>-0.839753553953571</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-271808.8584670851</v>
+      </c>
+      <c r="BG4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Sx1kytXA</t>
+          <t>v3erq0f8</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45465.9375</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">mendoza r 
-  usa </t>
+          <t xml:space="preserve">fischer d 
+  can </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">dick s sporting goods park
-  commerce city  co </t>
+          <t xml:space="preserve">providence park
+  portland  or </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>jmBZNRn8</t>
+          <t>bm8usLzB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1280,136 +1312,150 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>z9ZXDy6</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>rJ9D8rz</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>3</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>-6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-6</v>
+      </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.574999999999999</v>
+        <v>-2</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7750000000000004</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.85</v>
+        <v>1.214285714285714</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8</v>
+        <v>0.3928571428571423</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2182857142857142</v>
+        <v>0.25</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.162714285714285</v>
+        <v>-0.5</v>
       </c>
       <c r="X5" t="n">
-        <v>10.025</v>
+        <v>0.5457142857142856</v>
       </c>
       <c r="Y5" t="n">
-        <v>-10.025</v>
+        <v>-0.8785714285714286</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>1.277777777777778</v>
+        <v>8.125</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.6944444444444446</v>
+        <v>-8.125</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.55</v>
+        <v>3.75</v>
       </c>
       <c r="AE5" t="n">
-        <v>-1.025</v>
+        <v>-4.625</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.2</v>
+        <v>0.25</v>
       </c>
       <c r="AG5" t="n">
-        <v>-3.6</v>
+        <v>-0.375</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.625</v>
+        <v>1.125</v>
       </c>
       <c r="AI5" t="n">
-        <v>-8.125</v>
+        <v>-1.125</v>
       </c>
       <c r="AJ5" t="n">
-        <v>67.8340909090909</v>
+        <v>-0.125</v>
       </c>
       <c r="AK5" t="n">
-        <v>68.02292929292929</v>
+        <v>4.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.382668793195052</v>
+        <v>69.46527777777777</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1.718562139863792</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-4.40528768299496</v>
-      </c>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
+        <v>69.25227272727273</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="n">
+        <v>1431853.947368421</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>2.599791682031785</v>
+      </c>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="n">
-        <v>-537860.388673124</v>
-      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>-1.56172887495239</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>364170.1222753853</v>
-      </c>
-      <c r="AV5" t="inlineStr"/>
+        <v>-0.3475502881717603</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="n">
+        <v>-2.027583732057423</v>
+      </c>
       <c r="AW5" t="n">
-        <v>-0.1326377813219919</v>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+        <v>0.7515789473684187</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.978456147060083</v>
+      </c>
       <c r="AY5" t="n">
-        <v>-0.08229665071770498</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-0.02020202020202011</v>
-      </c>
+        <v>3.701985645933007</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>-1.024630916662147</v>
+        <v>1.946363636363614</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.3855927698032815</v>
+        <v>-0.006578947368421018</v>
       </c>
       <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
-        <v>-0.503987240829332</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
+        <v>-0.887478109195257</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>140905.7732465644</v>
+      </c>
+      <c r="BG5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2NHGKPBj</t>
+          <t>IgfnrK9E</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45465.9375</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1419,13 +1465,13 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">america first field
-  sandy  ut </t>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>W0ealpQl</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1447,161 +1493,171 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>jBBpU7Y</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>dp6AQn9</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2PIEeC7j</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
         <v>-3</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>-3</v>
       </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1</v>
-      </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="R6" t="n">
-        <v>5.675000000000001</v>
+        <v>-3</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5999999999999996</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.075</v>
+        <v>0.7666666666666666</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8</v>
+        <v>-0.02222222222222214</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4597222222222226</v>
+        <v>-0.4545454545454546</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.661388888888889</v>
+        <v>0.718181818181818</v>
       </c>
       <c r="X6" t="n">
-        <v>2.5</v>
+        <v>-0.1463492063492062</v>
       </c>
       <c r="Y6" t="n">
-        <v>-2.5</v>
+        <v>-0.3803174603174602</v>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="n">
-        <v>-0.1500000000000004</v>
+        <v>-3.263636363636365</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.4000000000000004</v>
+        <v>3.263636363636365</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>3.263636363636364</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.5249999999999999</v>
+        <v>-4.009090909090908</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.95</v>
+        <v>-0.2545454545454546</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.9000000000000004</v>
+        <v>0.6272727272727272</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.025</v>
+        <v>-0.09090909090909083</v>
       </c>
       <c r="AI6" t="n">
-        <v>-4.949999999999999</v>
+        <v>-0.2727272727272725</v>
       </c>
       <c r="AJ6" t="n">
-        <v>66.84141414141413</v>
+        <v>2.581818181818182</v>
       </c>
       <c r="AK6" t="n">
-        <v>68.17636363636363</v>
+        <v>-1.890909090909092</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.2505316321105511</v>
+        <v>69.46329966329967</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.1766835188235945</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>-1.028231173520354</v>
-      </c>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
+        <v>68.14012855831038</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>-1459956.529581529</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.081022677747569</v>
+      </c>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="n">
-        <v>-370466.8899641812</v>
-      </c>
+      <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
-        <v>0.7207818287325374</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>-2355041.135034557</v>
-      </c>
-      <c r="AV6" t="inlineStr"/>
+        <v>3.414585697296985</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>1.805974025973995</v>
+      </c>
       <c r="AW6" t="n">
-        <v>-0.024729849987287</v>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+        <v>-0.00422077922078401</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.664858851435312</v>
+      </c>
       <c r="AY6" t="n">
-        <v>-2.525491759702287</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>-0.06374269005847943</v>
-      </c>
+        <v>-1.740353535353535</v>
+      </c>
+      <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
-        <v>0.9195897095417251</v>
+        <v>-1.898455988455993</v>
       </c>
       <c r="BB6" t="n">
-        <v>-2.069909622541203</v>
+        <v>-0.02599335748792275</v>
       </c>
       <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="n">
-        <v>-5.483426368952678</v>
+        <v>-0.06555555555555559</v>
       </c>
       <c r="BE6" t="n">
+        <v>-0.5029787847633145</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-234223.9796822791</v>
+      </c>
+      <c r="BG6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4nxtRRYM</t>
+          <t>zZKrObIr</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">fischer d 
-  can </t>
+          <t xml:space="preserve">freemon j 
+  usa </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz field
-  saint paul  mn </t>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>IeT6JBE3</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1618,161 +1674,167 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>WWvwigh</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>UL7r7du</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.222222222222221</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>-2.111111111111112</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.111111111111111</v>
+        <v>1.375</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.222222222222222</v>
+        <v>1.125</v>
       </c>
       <c r="V7" t="n">
-        <v>0.803472222222222</v>
+        <v>-0.5555555555555558</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.7922222222222224</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.666666666666664</v>
+        <v>0.1483333333333332</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.666666666666664</v>
+        <v>0.2171428571428575</v>
       </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="n">
-        <v>-1.111111111111111</v>
+        <v>-1.111111111111114</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.333333333333333</v>
+        <v>1.111111111111114</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.222222222222222</v>
+        <v>-0.2222222222222232</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-1.888888888888889</v>
       </c>
       <c r="AF7" t="n">
-        <v>3.777777777777778</v>
+        <v>-0.2222222222222223</v>
       </c>
       <c r="AG7" t="n">
-        <v>-2.555555555555555</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>9.555555555555554</v>
+        <v>0.2222222222222223</v>
       </c>
       <c r="AI7" t="n">
-        <v>-8.444444444444445</v>
+        <v>0.2222222222222223</v>
       </c>
       <c r="AJ7" t="n">
-        <v>68.50998877665545</v>
+        <v>-0.7777777777777768</v>
       </c>
       <c r="AK7" t="n">
-        <v>67.97979797979798</v>
+        <v>-1.777777777777777</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.247740563530044</v>
+        <v>68.02840909090909</v>
       </c>
       <c r="AM7" t="n">
-        <v>2.413225044270206</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>-1.57084357910793</v>
-      </c>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
+        <v>68.04051627384962</v>
+      </c>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="n">
+        <v>-1372584.529505583</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.8644595945901017</v>
+      </c>
       <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="n">
-        <v>29262.45470763673</v>
-      </c>
+      <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
-        <v>-3.592612603412302</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>-755191.3875598088</v>
-      </c>
-      <c r="AV7" t="inlineStr"/>
+        <v>-1.209323031531824</v>
+      </c>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="n">
+        <v>3.09539758487125</v>
+      </c>
       <c r="AW7" t="n">
-        <v>-0.3060454943951165</v>
-      </c>
-      <c r="AX7" t="inlineStr"/>
+        <v>0.3064935064935028</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.308092536832504</v>
+      </c>
       <c r="AY7" t="n">
-        <v>-2.084848484848489</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>-0.1009569377990431</v>
-      </c>
+        <v>-2.123239917976747</v>
+      </c>
+      <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
-        <v>-0.7879756813832444</v>
+        <v>-1.83984962406015</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.472514619883057</v>
+        <v>0.03204309946709416</v>
       </c>
       <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="n">
-        <v>-1.59813928761298</v>
+        <v>0.05411255411255422</v>
       </c>
       <c r="BE7" t="n">
+        <v>1.686561601634111</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>-232178.8455168807</v>
+      </c>
+      <c r="BG7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>IktpQolT</t>
+          <t>hAFmNIXl</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">rivas v 
+          <t xml:space="preserve">da silva a 
   usa </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">geodis park
-  nashville  tn </t>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>84yIDQMe</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>QJF7WTFB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1789,161 +1851,171 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>xA45kov</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>dp6AQn9</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.4</v>
+        <v>-1</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.425000000000001</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1499999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5249999999999999</v>
+        <v>0.375</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3184285714285711</v>
+        <v>0.2222222222222221</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3965714285714284</v>
+        <v>-0.4444444444444444</v>
       </c>
       <c r="X8" t="n">
-        <v>0.375</v>
+        <v>0.453214285714286</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.375</v>
+        <v>-0.04874999999999985</v>
       </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="n">
-        <v>-0.1746031746031749</v>
+        <v>15.55555555555556</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.06349206349206327</v>
+        <v>-15.55555555555556</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.7250000000000001</v>
+        <v>7.666666666666666</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.05000000000000004</v>
+        <v>-2.666666666666666</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.6500000000000004</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AG8" t="n">
-        <v>-2.15</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.4</v>
+        <v>2.444444444444445</v>
       </c>
       <c r="AI8" t="n">
-        <v>-2.449999999999999</v>
+        <v>-0.4444444444444446</v>
       </c>
       <c r="AJ8" t="n">
-        <v>67.17808080808081</v>
+        <v>3.222222222222221</v>
       </c>
       <c r="AK8" t="n">
-        <v>68.88939393939395</v>
+        <v>0.7777777777777786</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.094360269360237</v>
+        <v>67.45113636363638</v>
       </c>
       <c r="AM8" t="n">
-        <v>-4.693622716934243</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>3.443674117364196</v>
-      </c>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
+        <v>68.45606060606059</v>
+      </c>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="n">
+        <v>-66920.45454545435</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-1.872908410977388</v>
+      </c>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="n">
-        <v>-41029.75435512234</v>
-      </c>
+      <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
-        <v>6.388933506051387</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>971222.9938271602</v>
-      </c>
-      <c r="AV8" t="inlineStr"/>
+        <v>-1.999617762660904</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="n">
+        <v>-1.78000000000003</v>
+      </c>
       <c r="AW8" t="n">
-        <v>0.05095860258903739</v>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+        <v>0.3818181818181756</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-0.7310272870329761</v>
+      </c>
       <c r="AY8" t="n">
-        <v>4.812640291806961</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0.1212121212121215</v>
-      </c>
+        <v>0.5550000000000068</v>
+      </c>
+      <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
-        <v>2.178013191945126</v>
+        <v>-0.6804545454545377</v>
       </c>
       <c r="BB8" t="n">
-        <v>-2.67790404040403</v>
+        <v>-0.02067239576990221</v>
       </c>
       <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="n">
-        <v>1.803675645342324</v>
+        <v>0.07363636363636372</v>
       </c>
       <c r="BE8" t="n">
+        <v>-1.835476596146194</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>-449295.7251512283</v>
+      </c>
+      <c r="BG8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>OWICL5dp</t>
+          <t>QNDeLd21</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">dujic f 
-  can </t>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">citypark
-  st  louis  mo </t>
+          <t xml:space="preserve">geodis park
+  nashville  tn </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
+          <t>84yIDQMe</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
+          <t>0AheRyBg</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1960,153 +2032,171 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>z9ZXDy6</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>l6eEjGl</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>zoZ995a</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R9" t="n">
-        <v>4.366666666666665</v>
+        <v>-1</v>
       </c>
       <c r="S9" t="n">
-        <v>2.077777777777779</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.03333333333333321</v>
+        <v>-0.5250000000000004</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.03333333333333321</v>
+        <v>-0.2750000000000004</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2084126984126986</v>
+        <v>-0.7749999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3568253968253969</v>
+        <v>0.5</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3555555555555543</v>
+        <v>0.289365079365079</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.3555555555555543</v>
+        <v>0.02079365079365081</v>
       </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="n">
-        <v>-2.305555555555555</v>
+        <v>-4.325000000000003</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.6805555555555554</v>
+        <v>4.325000000000003</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.2222222222222222</v>
+        <v>2.6</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.3222222222222223</v>
+        <v>-2.4</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.822222222222222</v>
+        <v>-0.425</v>
       </c>
       <c r="AG9" t="n">
-        <v>-1.644444444444445</v>
+        <v>-0.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>5.077777777777779</v>
+        <v>-0.5999999999999996</v>
       </c>
       <c r="AI9" t="n">
-        <v>-6.611111111111111</v>
+        <v>-0.2999999999999998</v>
       </c>
       <c r="AJ9" t="n">
-        <v>67.88098484848486</v>
+        <v>0.4749999999999996</v>
       </c>
       <c r="AK9" t="n">
-        <v>68.7746212121212</v>
+        <v>-0.5500000000000007</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.228282828282772</v>
+        <v>67.09685746352415</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.3943355022011161</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>-0.3520799704598119</v>
-      </c>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
+        <v>68.33863636363637</v>
+      </c>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="n">
+        <v>-3547428.229665072</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-2.196653511648364</v>
+      </c>
       <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="n">
-        <v>-482365.734690642</v>
-      </c>
+      <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
-        <v>-1.343103367977431</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>-2655420.517676768</v>
-      </c>
-      <c r="AV9" t="inlineStr"/>
+        <v>-1.836322547681107</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="n">
+        <v>1.074641148325384</v>
+      </c>
       <c r="AW9" t="n">
-        <v>-0.02438186813186816</v>
-      </c>
-      <c r="AX9" t="inlineStr"/>
+        <v>0.4349282296650792</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>3.191401503317291</v>
+      </c>
       <c r="AY9" t="n">
-        <v>-0.5989520202020202</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>-0.02414141414141424</v>
-      </c>
+        <v>-4.966985645933008</v>
+      </c>
+      <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="n">
-        <v>3.035402039938589</v>
+        <v>-7.166985645933025</v>
       </c>
       <c r="BB9" t="n">
-        <v>-1.054444444444428</v>
+        <v>-0.2149367025584696</v>
       </c>
       <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="n">
-        <v>-0.1464772727272674</v>
+        <v>-0.6110047846889952</v>
       </c>
       <c r="BE9" t="n">
+        <v>-6.982767895371879</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-1741247.396748824</v>
+      </c>
+      <c r="BG9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>W0EiMxme</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">de oliveira m 
-  usa </t>
+          <t xml:space="preserve">fischer d 
+  can </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">lower com field
-  columbus  oh </t>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>IeT6JBE3</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2123,161 +2213,171 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>6gpXy3v</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>rXawJi8</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-2</v>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="R10" t="n">
-        <v>-2.371428571428572</v>
+        <v>-4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.457142857142857</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9142857142857141</v>
+        <v>-0.2777777777777777</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.142857142857143</v>
+        <v>-0.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6103571428571429</v>
+        <v>0.1909090909090908</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.5589285714285714</v>
+        <v>-0.1636363636363636</v>
       </c>
       <c r="X10" t="n">
-        <v>7.857142857142854</v>
+        <v>0.4101388888888889</v>
       </c>
       <c r="Y10" t="n">
-        <v>-7.857142857142854</v>
+        <v>-0.3400000000000001</v>
       </c>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="n">
-        <v>-2.444444444444444</v>
+        <v>5.581818181818178</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1</v>
+        <v>-5.581818181818178</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.1285714285714286</v>
+        <v>9.1</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.9428571428571429</v>
+        <v>-6.390909090909092</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.914285714285715</v>
+        <v>1.681818181818182</v>
       </c>
       <c r="AG10" t="n">
-        <v>-1.971428571428572</v>
+        <v>0.7909090909090908</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.742857142857142</v>
+        <v>4.163636363636363</v>
       </c>
       <c r="AI10" t="n">
-        <v>-3.171428571428571</v>
+        <v>-0.5272727272727273</v>
       </c>
       <c r="AJ10" t="n">
-        <v>68.80360750360749</v>
+        <v>1.163636363636364</v>
       </c>
       <c r="AK10" t="n">
-        <v>67.15802469135802</v>
+        <v>1.463636363636363</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.2275432900432861</v>
+        <v>68.91252525252524</v>
       </c>
       <c r="AM10" t="n">
-        <v>2.696758949627281</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1.525271918385272</v>
-      </c>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
+        <v>67.83636363636364</v>
+      </c>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="n">
+        <v>-649653.9256198348</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-2.601394477751576</v>
+      </c>
       <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="n">
-        <v>485187.5659744573</v>
-      </c>
+      <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
-        <v>-0.3111848824949419</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1850828.778860029</v>
-      </c>
-      <c r="AV10" t="inlineStr"/>
+        <v>-1.197193682809086</v>
+      </c>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="n">
+        <v>-0.004710743801638273</v>
+      </c>
       <c r="AW10" t="n">
-        <v>-0.05540619146209225</v>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+        <v>-0.6488429752066125</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-3.303916290061547</v>
+      </c>
       <c r="AY10" t="n">
-        <v>-2.225234487734486</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>-0.06450216450216439</v>
-      </c>
+        <v>-0.3543388429751957</v>
+      </c>
+      <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="n">
-        <v>2.062547346041015</v>
+        <v>1.015785123966936</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.44452561327563</v>
+        <v>-0.2444527136837675</v>
       </c>
       <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="n">
-        <v>0.636679292929287</v>
+        <v>-0.04433884297520674</v>
       </c>
       <c r="BE10" t="n">
+        <v>0.274158475001542</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>-292637.3184193238</v>
+      </c>
+      <c r="BG10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
+          <t>fiHVGBod</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ford t 
+          <t xml:space="preserve">da silva a 
   usa </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi field
-  washington  dc </t>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>Szrwix67</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2294,19 +2394,23 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>nJ01AhX</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>tOpyQa2</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>-11</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-11</v>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -2315,140 +2419,146 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.277777777777779</v>
+        <v>-1</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.444444444444445</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.02222222222222237</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.05555555555555558</v>
+        <v>2.375</v>
       </c>
       <c r="V11" t="n">
-        <v>1.136666666666667</v>
+        <v>-0.3055555555555556</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1251388888888889</v>
+        <v>0.3611111111111112</v>
       </c>
       <c r="X11" t="n">
-        <v>1.299999999999997</v>
+        <v>-0.02041666666666675</v>
       </c>
       <c r="Y11" t="n">
-        <v>-1.299999999999997</v>
+        <v>-0.01083333333333325</v>
       </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="n">
-        <v>-0.3333333333333339</v>
+        <v>5.736111111111114</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.4444444444444446</v>
+        <v>-5.736111111111114</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.2777777777777777</v>
+        <v>-0.5555555555555554</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.3555555555555556</v>
+        <v>-0.4722222222222214</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.366666666666667</v>
+        <v>-0.375</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.7111111111111104</v>
+        <v>0.1805555555555556</v>
       </c>
       <c r="AH11" t="n">
-        <v>6.699999999999999</v>
+        <v>-1.805555555555555</v>
       </c>
       <c r="AI11" t="n">
-        <v>-3.033333333333333</v>
+        <v>0.3611111111111107</v>
       </c>
       <c r="AJ11" t="n">
-        <v>68.40909090909091</v>
+        <v>0.75</v>
       </c>
       <c r="AK11" t="n">
-        <v>68.42962962962964</v>
+        <v>-0.8611111111111107</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.328654970760255</v>
+        <v>69.40012626262626</v>
       </c>
       <c r="AM11" t="n">
-        <v>2.795515720335771</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>-2.430261547165962</v>
-      </c>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
+        <v>67.48080808080807</v>
+      </c>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="n">
+        <v>-1559153.110047847</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.02137251904034088</v>
+      </c>
       <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="n">
-        <v>-311708.3553284412</v>
-      </c>
+      <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
-        <v>-2.832262146717234</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>-190078.6815523659</v>
-      </c>
-      <c r="AV11" t="inlineStr"/>
+        <v>-1.99800866126435</v>
+      </c>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="n">
+        <v>-4.617224880382764</v>
+      </c>
       <c r="AW11" t="n">
-        <v>-0.06419539111160155</v>
-      </c>
-      <c r="AX11" t="inlineStr"/>
+        <v>-1.33923444976076</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-1.390993361100904</v>
+      </c>
       <c r="AY11" t="n">
-        <v>0.4582137161084496</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.001754385964912508</v>
-      </c>
+        <v>-2.91531100478467</v>
+      </c>
+      <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="n">
-        <v>2.260264525956501</v>
+        <v>-1.94736842105263</v>
       </c>
       <c r="BB11" t="n">
-        <v>-0.3542264752791198</v>
+        <v>0.0227410502972667</v>
       </c>
       <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="n">
-        <v>-0.007974481658706623</v>
+        <v>-0.04401913875598118</v>
       </c>
       <c r="BE11" t="n">
+        <v>0.9569849973772762</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-239882.585765356</v>
+      </c>
+      <c r="BG11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>APxxS7JG</t>
+          <t>4nbBt7Y9</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">da silva a 
+          <t xml:space="preserve">de oliveira m 
   usa </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">subaru park
-  chester  pa </t>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Szrwix67</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2465,161 +2575,171 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>roEEsq7</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>K4zRMgT</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R12" t="n">
-        <v>-1.805555555555555</v>
+        <v>-1</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1944444444444446</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2083333333333334</v>
+        <v>-0.5</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.215</v>
+        <v>-0.5555555555555556</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1650000000000001</v>
+        <v>0.7777777777777777</v>
       </c>
       <c r="X12" t="n">
-        <v>8.930555555555557</v>
+        <v>-0.2583928571428573</v>
       </c>
       <c r="Y12" t="n">
-        <v>-8.930555555555557</v>
+        <v>-0.01553571428571443</v>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="n">
-        <v>1.625</v>
+        <v>-2.444444444444443</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.285714285714286</v>
+        <v>2.444444444444443</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.4444444444444444</v>
+        <v>2.555555555555555</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.2777777777777777</v>
+        <v>0.5555555555555554</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.027777777777778</v>
+        <v>-0.7777777777777779</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.4027777777777777</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AH12" t="n">
-        <v>10.29166666666667</v>
+        <v>-0.1111111111111107</v>
       </c>
       <c r="AI12" t="n">
-        <v>-2.791666666666666</v>
+        <v>-0.2222222222222223</v>
       </c>
       <c r="AJ12" t="n">
-        <v>67.72157687991022</v>
+        <v>4.444444444444445</v>
       </c>
       <c r="AK12" t="n">
-        <v>68.51306818181818</v>
+        <v>-5.111111111111111</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.168527379053643</v>
+        <v>67.94898989898989</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.5834712189529512</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0.09612246777915345</v>
-      </c>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
+        <v>67.5246913580247</v>
+      </c>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="n">
+        <v>136423.1469102786</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.805217729279093</v>
+      </c>
       <c r="AQ12" t="inlineStr"/>
       <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="n">
-        <v>45052.53749039094</v>
-      </c>
+      <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
-        <v>-1.110747861012868</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1330648.856990963</v>
-      </c>
-      <c r="AV12" t="inlineStr"/>
+        <v>-2.180919295100381</v>
+      </c>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="n">
+        <v>1.065663992869901</v>
+      </c>
       <c r="AW12" t="n">
-        <v>0.01707728935064368</v>
-      </c>
-      <c r="AX12" t="inlineStr"/>
+        <v>0.7770424836601322</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.33416095028301</v>
+      </c>
       <c r="AY12" t="n">
-        <v>-0.6745348219032472</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0.04752791068580575</v>
-      </c>
+        <v>1.276994206773608</v>
+      </c>
+      <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="n">
-        <v>0.3617345724115069</v>
+        <v>0.2100304515745677</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.054226475279108</v>
+        <v>0.07889723087774447</v>
       </c>
       <c r="BC12" t="inlineStr"/>
       <c r="BD12" t="n">
-        <v>2.65106326422115</v>
+        <v>0.1093285799168153</v>
       </c>
       <c r="BE12" t="n">
+        <v>0.8243736101266705</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>-194216.7726975693</v>
+      </c>
+      <c r="BG12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
+          <t>b9cFuRmG</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">simon n 
+          <t xml:space="preserve">ford t 
   usa </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">tql stadium
-  cincinnati  oh </t>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>zV5YmQAr</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
+          <t>O6hjfSXE</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2636,19 +2756,23 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>roEEsq7</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Sd7snoa</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
-        <v>-3</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-3</v>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
       </c>
       <c r="O13" t="n">
         <v>-2</v>
@@ -2657,140 +2781,146 @@
         <v>-2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.5396825396825395</v>
+        <v>4</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1111111111111107</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.031746031746032</v>
+        <v>0.5</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.253968253968254</v>
+        <v>0.375</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5489285714285715</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="W13" t="n">
-        <v>-2.000714285714286</v>
+        <v>-1.444444444444444</v>
       </c>
       <c r="X13" t="n">
-        <v>1.873015873015873</v>
+        <v>0.05874999999999986</v>
       </c>
       <c r="Y13" t="n">
-        <v>-1.873015873015873</v>
+        <v>-0.8424999999999999</v>
       </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="n">
-        <v>0.833333333333333</v>
+        <v>-0.8888888888888928</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.291666666666667</v>
+        <v>0.8888888888888928</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.3333333333333333</v>
+        <v>3.888888888888889</v>
       </c>
       <c r="AE13" t="n">
-        <v>-1.142857142857143</v>
+        <v>-4.555555555555555</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.666666666666667</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="AG13" t="n">
-        <v>-2.920634920634921</v>
+        <v>-1.111111111111111</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.873015873015873</v>
+        <v>2.444444444444445</v>
       </c>
       <c r="AI13" t="n">
-        <v>-10.47619047619048</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="AJ13" t="n">
-        <v>67.91952861952862</v>
+        <v>-4.333333333333334</v>
       </c>
       <c r="AK13" t="n">
-        <v>68.21266233766234</v>
+        <v>-1.444444444444445</v>
       </c>
       <c r="AL13" t="n">
-        <v>-1.899999999999977</v>
+        <v>68.35050505050505</v>
       </c>
       <c r="AM13" t="n">
-        <v>-3.803331390131007</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>-3.81916678922321</v>
-      </c>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
+        <v>68.67954545454546</v>
+      </c>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="n">
+        <v>1521779.292929293</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2.772781397075789</v>
+      </c>
       <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="n">
-        <v>301379.355881332</v>
-      </c>
+      <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
-        <v>-1.150921132250105</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>511994.94949495</v>
-      </c>
-      <c r="AV13" t="inlineStr"/>
+        <v>-1.651231052014737</v>
+      </c>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="n">
+        <v>-3.719494949494987</v>
+      </c>
       <c r="AW13" t="n">
-        <v>-0.06716164114093681</v>
-      </c>
-      <c r="AX13" t="inlineStr"/>
+        <v>-3.488484848484845</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.04388560991997892</v>
+      </c>
       <c r="AY13" t="n">
-        <v>-0.7921717171717226</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>-0.1092171717171717</v>
-      </c>
+        <v>1.219393939393939</v>
+      </c>
+      <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="n">
-        <v>1.749501716961106</v>
+        <v>3.981060606060609</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.5793560606060595</v>
+        <v>0.04871978636819119</v>
       </c>
       <c r="BC13" t="inlineStr"/>
       <c r="BD13" t="n">
-        <v>0.0388257575757649</v>
+        <v>0.02878787878787903</v>
       </c>
       <c r="BE13" t="n">
+        <v>1.094297923065255</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>964710.8332939812</v>
+      </c>
+      <c r="BG13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>WYwYSm4A</t>
+          <t>G0IRHiWk</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">simon n 
+          <t xml:space="preserve">dickerson j 
   usa </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">inter co stadium
-  orlando  fl </t>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>rsHkUNCo</t>
+          <t>EPngUvhk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>zsdfgnmL</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2807,161 +2937,171 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>022mBmS</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Uw6sTk0</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>z9ZXDy6o</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2916666666666661</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1666666666666661</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2083333333333334</v>
+        <v>0.125</v>
       </c>
       <c r="U14" t="n">
-        <v>0.375</v>
+        <v>-1.034090909090909</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3985714285714288</v>
+        <v>0.3838383838383839</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6614285714285715</v>
+        <v>-0.3434343434343434</v>
       </c>
       <c r="X14" t="n">
-        <v>4.708333333333336</v>
+        <v>0.6530555555555555</v>
       </c>
       <c r="Y14" t="n">
-        <v>-4.708333333333336</v>
+        <v>-0.2943055555555556</v>
       </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="n">
-        <v>-0.03571428571428559</v>
+        <v>8.070707070707066</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.625</v>
+        <v>-7.979797979797979</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.4722222222222222</v>
+        <v>7.606060606060607</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.2916666666666667</v>
+        <v>-0.8888888888888893</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.5972222222222223</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AG14" t="n">
-        <v>-2.472222222222222</v>
+        <v>-0.4343434343434343</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.263888888888889</v>
+        <v>2.545454545454546</v>
       </c>
       <c r="AI14" t="n">
-        <v>-8.652777777777779</v>
+        <v>-0.8989898989898988</v>
       </c>
       <c r="AJ14" t="n">
-        <v>68.85342312008979</v>
+        <v>-1.373737373737374</v>
       </c>
       <c r="AK14" t="n">
-        <v>68.0625</v>
+        <v>-0.6767676767676765</v>
       </c>
       <c r="AL14" t="n">
-        <v>-2.363636363636374</v>
+        <v>69.10363636363635</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.2296468669909615</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>-1.044533830663909</v>
-      </c>
-      <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr"/>
+        <v>68.44567901234569</v>
+      </c>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="n">
+        <v>2163582.386363636</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>2.797210860128551</v>
+      </c>
       <c r="AQ14" t="inlineStr"/>
       <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="n">
-        <v>1035099.281434715</v>
-      </c>
+      <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
-        <v>-0.7731005320788604</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>393638.888888889</v>
-      </c>
-      <c r="AV14" t="inlineStr"/>
+        <v>-0.1666238177419643</v>
+      </c>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="n">
+        <v>-3.180000000000007</v>
+      </c>
       <c r="AW14" t="n">
-        <v>0.03718893826551883</v>
-      </c>
-      <c r="AX14" t="inlineStr"/>
+        <v>-0.5285227272727298</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>2.349485298254567</v>
+      </c>
       <c r="AY14" t="n">
-        <v>0.6873737373737399</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0.08484848484848473</v>
-      </c>
+        <v>2.418750000000003</v>
+      </c>
+      <c r="AZ14" t="inlineStr"/>
       <c r="BA14" t="n">
-        <v>-1.215278296153059</v>
+        <v>3.988181818181801</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.057070707070707</v>
+        <v>-0.08721505896849147</v>
       </c>
       <c r="BC14" t="inlineStr"/>
       <c r="BD14" t="n">
-        <v>1.350505050505049</v>
+        <v>-0.0190909090909086</v>
       </c>
       <c r="BE14" t="n">
+        <v>1.551623087515452</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>515855.8736060229</v>
+      </c>
+      <c r="BG14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>ln2oxMH4</t>
+          <t>jqf7smJ3</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45471.85416666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">dickerson j 
+          <t xml:space="preserve">simon n 
   usa </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">red bull arena
-  harrison  nj </t>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2978,129 +3118,139 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>K4FYmLD</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>EgT3xN3</t>
-        </is>
-      </c>
-      <c r="M15" t="n">
-        <v>12</v>
-      </c>
-      <c r="N15" t="n">
-        <v>12</v>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Uw6sTk0t</t>
+        </is>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>-2.236111111111111</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.027777777777779</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.25</v>
+        <v>-0.5750000000000002</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.291666666666667</v>
+        <v>-1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>0.4422222222222221</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.6511111111111109</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.625</v>
+        <v>0.6459722222222222</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.625</v>
+        <v>-0.6845833333333332</v>
       </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="n">
-        <v>0.375</v>
+        <v>2.833333333333336</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.75</v>
+        <v>-2.833333333333336</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.9861111111111112</v>
+        <v>5.577777777777779</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.9305555555555556</v>
+        <v>-3.011111111111111</v>
       </c>
       <c r="AF15" t="n">
-        <v>3.375</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="AG15" t="n">
-        <v>-2.069444444444445</v>
+        <v>-0.6888888888888889</v>
       </c>
       <c r="AH15" t="n">
-        <v>6.125</v>
+        <v>2.022222222222222</v>
       </c>
       <c r="AI15" t="n">
-        <v>-5.111111111111111</v>
+        <v>-0.6222222222222227</v>
       </c>
       <c r="AJ15" t="n">
-        <v>68.76931818181819</v>
+        <v>6.444444444444445</v>
       </c>
       <c r="AK15" t="n">
-        <v>68.75881032547699</v>
+        <v>-0.4333333333333336</v>
       </c>
       <c r="AL15" t="n">
-        <v>-2.160765550239233</v>
+        <v>67.63181818181819</v>
       </c>
       <c r="AM15" t="n">
-        <v>3.091790983079207</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.079492808770929</v>
-      </c>
-      <c r="AO15" t="inlineStr"/>
-      <c r="AP15" t="inlineStr"/>
+        <v>69.41414141414141</v>
+      </c>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="n">
+        <v>-1068421.824236517</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-2.369161208091057</v>
+      </c>
       <c r="AQ15" t="inlineStr"/>
       <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="n">
-        <v>454684.7282312156</v>
-      </c>
+      <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
-        <v>-0.3417111085176749</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>736282.296650718</v>
-      </c>
-      <c r="AV15" t="inlineStr"/>
+        <v>1.070816450259372</v>
+      </c>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="n">
+        <v>1.666033138401588</v>
+      </c>
       <c r="AW15" t="n">
-        <v>-0.04908617967824047</v>
-      </c>
-      <c r="AX15" t="inlineStr"/>
+        <v>-4.184304300313073</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-4.064201927125762</v>
+      </c>
       <c r="AY15" t="n">
-        <v>-3.048325358851674</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>-0.08660287081339679</v>
-      </c>
+        <v>-3.218082875539025</v>
+      </c>
+      <c r="AZ15" t="inlineStr"/>
       <c r="BA15" t="n">
-        <v>1.336127697941123</v>
+        <v>0.2873670919723423</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.993779904306223</v>
+        <v>-0.1802207575682435</v>
       </c>
       <c r="BC15" t="inlineStr"/>
       <c r="BD15" t="n">
-        <v>3.272727272727266</v>
+        <v>-0.2129186602870814</v>
       </c>
       <c r="BE15" t="n">
+        <v>2.132758791146699</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>-1180159.584184752</v>
+      </c>
+      <c r="BG15" t="n">
         <v>0</v>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG15"/>
+  <dimension ref="A1:BG46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,94 +525,94 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions_against</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -625,97 +625,97 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
           <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
@@ -727,15 +727,15 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>xbHaKGH7</t>
+          <t>0YXnLoFb</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mendoza r 
+          <t xml:space="preserve">corbyn m 
   usa </t>
         </is>
       </c>
@@ -752,17 +752,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>jmBZNRn8</t>
+          <t>dI5p0xzH</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>167</v>
       </c>
       <c r="H2" t="n">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>2024</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>mls</t>
+          <t>us open cup</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -784,123 +784,89 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>K4FYmLD9</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-1</v>
-      </c>
+          <t>6V8Ndys8</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7000000000000002</v>
+        <v>0.2727272727272729</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3999999999999995</v>
+        <v>-0.6363636363636364</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W2" t="n">
-        <v>-1.2</v>
+        <v>0.2083333333333335</v>
       </c>
       <c r="X2" t="n">
-        <v>0.9905555555555556</v>
+        <v>-4.458333333333334</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.8773611111111113</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
+        <v>-2.958333333333334</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-8.583333333333336</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>8.583333333333336</v>
+      </c>
       <c r="AB2" t="n">
-        <v>8.899999999999999</v>
+        <v>1.041666666666667</v>
       </c>
       <c r="AC2" t="n">
-        <v>-8.899999999999999</v>
+        <v>-0.1666666666666666</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.000000000000002</v>
+        <v>2.916666666666666</v>
       </c>
       <c r="AE2" t="n">
-        <v>-3.5</v>
+        <v>1.083333333333334</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.8000000000000003</v>
+        <v>2.318181818181818</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.9000000000000001</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-2</v>
-      </c>
+        <v>2.106060606060606</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>3.1</v>
+        <v>-0.166666666666667</v>
       </c>
       <c r="AK2" t="n">
-        <v>-3.199999999999999</v>
+        <v>-0.3333333333333339</v>
       </c>
       <c r="AL2" t="n">
-        <v>69.30628507295175</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>67.47583333333334</v>
-      </c>
+        <v>67.9912904040404</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="n">
-        <v>2514428.487253487</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>5.66823727869582</v>
-      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="n">
-        <v>0.1612616517502943</v>
-      </c>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>0.5843097643098076</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>3.636296296296294</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>2.977982606947716</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>6.529850889850891</v>
-      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="n">
-        <v>4.183626743626718</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0.006046863189720364</v>
-      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="n">
-        <v>0.3546416546416549</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>2.876827007246263</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>826287.0203028677</v>
-      </c>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="n">
         <v>0</v>
       </c>
@@ -908,42 +874,42 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nTbjsvPK</t>
+          <t>d0ReJPqB</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45483.91666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">simon n 
+          <t xml:space="preserve">badawi m 
   usa </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">lumen field
-  seattle  wa </t>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6P5S63Ah</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>167</v>
       </c>
       <c r="H3" t="n">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>2024</v>
@@ -955,132 +921,136 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>mls</t>
+          <t>us open cup</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>tOpyQa24</t>
+          <t>zoZ995af</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Uw6sTk0t</t>
+          <t>WWvwigh8</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.775</v>
+        <v>-0.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8</v>
+        <v>0.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.068181818181818</v>
+        <v>-0.5555555555555554</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.147727272727273</v>
+        <v>-2.777777777777778</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4288095238095239</v>
+        <v>1.222222222222221</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.7014285714285715</v>
-      </c>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+        <v>1.777777777777779</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>7.444444444444443</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-7.444444444444443</v>
+      </c>
       <c r="AB3" t="n">
-        <v>5.488636363636367</v>
+        <v>-0.1111111111111112</v>
       </c>
       <c r="AC3" t="n">
-        <v>-5.488636363636367</v>
+        <v>0.7777777777777777</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.625</v>
+        <v>7.111111111111111</v>
       </c>
       <c r="AE3" t="n">
-        <v>-5.943181818181818</v>
+        <v>-10</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3863636363636365</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.9659090909090909</v>
+        <v>-0.416666666666667</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.5568181818181817</v>
+        <v>-0.07600000000000007</v>
       </c>
       <c r="AI3" t="n">
-        <v>-2.613636363636364</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.443181818181818</v>
+        <v>-4.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.477272727272727</v>
+        <v>-4.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>67.5090909090909</v>
+        <v>67.6392265310447</v>
       </c>
       <c r="AM3" t="n">
-        <v>68.00113636363636</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>68.500727555273</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-1536566.433566433</v>
+      </c>
       <c r="AO3" t="n">
-        <v>-492168.5636266973</v>
+        <v>-1.622413397687993</v>
       </c>
       <c r="AP3" t="n">
-        <v>-2.47096780148717</v>
-      </c>
-      <c r="AQ3" t="inlineStr"/>
+        <v>-0.00221150067827125</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-2.561538461538461</v>
+      </c>
       <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
+      <c r="AS3" t="n">
+        <v>0.5188406990924186</v>
+      </c>
       <c r="AT3" t="n">
-        <v>-2.001097225431039</v>
+        <v>-2.273426573426576</v>
       </c>
       <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="n">
-        <v>-1.424819970035259</v>
-      </c>
+      <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="n">
-        <v>0.288290802764493</v>
+        <v>-0.01608391608391613</v>
       </c>
       <c r="AX3" t="n">
-        <v>-2.040349198995298</v>
+        <v>0.0332877064456012</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.2767278043593819</v>
+        <v>-486384.4483859645</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="n">
-        <v>1.008369580977231</v>
-      </c>
+      <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>-0.04773409260416539</v>
+        <v>0.06169891257992788</v>
       </c>
       <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="n">
-        <v>0.1011502585665267</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>-0.01280881749406149</v>
-      </c>
+        <v>-1.831468531468516</v>
+      </c>
+      <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="n">
-        <v>-29161.03879759973</v>
+        <v>1.303496503496508</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1089,42 +1059,42 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>YyTMIXGq</t>
+          <t>APpAklQ6</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45483</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">dujic f 
-  can </t>
+          <t xml:space="preserve">badawi m 
+  usa </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bc place
-  vancouver  bc </t>
+          <t xml:space="preserve">heart health park
+  sacramento  ca </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>K2dlua5N</t>
+          <t>z3BFwb83</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
+          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>167</v>
       </c>
       <c r="H4" t="n">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>2024</v>
@@ -1136,133 +1106,103 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>mls</t>
+          <t>us open cup</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>EqKWmJfM</t>
+          <t>vucevHGn</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>l6eEjGlO</t>
+          <t>WWvwigh8</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8035714285714288</v>
+        <v>-0.3809523809523809</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03571428571428559</v>
+        <v>0.3690476190476192</v>
       </c>
       <c r="V4" t="n">
-        <v>0.75</v>
+        <v>0.08571428571428541</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.375</v>
+        <v>1.185714285714286</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4057142857142859</v>
+        <v>1.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.8542857142857142</v>
-      </c>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
+        <v>4.085714285714285</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.614285714285714</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-3.614285714285714</v>
+      </c>
       <c r="AB4" t="n">
-        <v>5.875</v>
+        <v>-0.1714285714285715</v>
       </c>
       <c r="AC4" t="n">
-        <v>-5.875</v>
+        <v>-0.01428571428571423</v>
       </c>
       <c r="AD4" t="n">
-        <v>-2.125</v>
+        <v>-2.157142857142858</v>
       </c>
       <c r="AE4" t="n">
-        <v>-2</v>
+        <v>0.7857142857142865</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>-3.25</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-2.375</v>
-      </c>
+        <v>-0.5952380952380958</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>-8</v>
+        <v>-4.857142857142858</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.625</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>68.08080808080808</v>
-      </c>
+        <v>0.2857142857142856</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>69.45694444444445</v>
+        <v>67.74787266605448</v>
       </c>
       <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="n">
-        <v>649856.4593301439</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0.2170156160859733</v>
-      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="n">
-        <v>-4.001063388247303</v>
-      </c>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="n">
-        <v>-5.013716108452968</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.494391281233387</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.199859915608478</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.653349282296645</v>
-      </c>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="n">
-        <v>0.7078415736310433</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="n">
-        <v>-0.187772461456672</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>-0.839753553953571</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>-271808.8584670851</v>
-      </c>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="n">
         <v>0</v>
       </c>
@@ -1270,42 +1210,42 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>v3erq0f8</t>
+          <t>SKZvN7pn</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45482.83333333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">fischer d 
-  can </t>
+          <t xml:space="preserve">surgan j 
+  usa </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">providence park
-  portland  or </t>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>bm8usLzB</t>
+          <t>EPngUvhk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>dtMNCXyk</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>167</v>
       </c>
       <c r="H5" t="n">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>2024</v>
@@ -1317,133 +1257,111 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>mls</t>
+          <t>us open cup</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>EqKWmJfM</t>
+          <t>z9ZXDy6o</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>KtuTuMN0</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>-6</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-6</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-2</v>
-      </c>
+          <t>MRdhQQTs</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.214285714285714</v>
+        <v>-1.471153846153846</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3928571428571423</v>
+        <v>1.009615384615385</v>
       </c>
       <c r="V5" t="n">
-        <v>0.25</v>
+        <v>-1.5</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.5</v>
+        <v>1.55</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5457142857142856</v>
+        <v>-1.324999999999999</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.8785714285714286</v>
-      </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
+        <v>-0.875</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7.424999999999997</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-7.424999999999997</v>
+      </c>
       <c r="AB5" t="n">
-        <v>8.125</v>
+        <v>-0.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>-8.125</v>
+        <v>0.675</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.75</v>
+        <v>0.625</v>
       </c>
       <c r="AE5" t="n">
-        <v>-4.625</v>
+        <v>1.949999999999999</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.25</v>
+        <v>2.269230769230769</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.375</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-1.125</v>
-      </c>
+        <v>1.653846153846154</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>-0.125</v>
+        <v>11.125</v>
       </c>
       <c r="AK5" t="n">
-        <v>4.5</v>
+        <v>10.25</v>
       </c>
       <c r="AL5" t="n">
-        <v>69.46527777777777</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>69.25227272727273</v>
-      </c>
+        <v>68.65129004693399</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>1431853.947368421</v>
+        <v>5.48947342993273</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.599791682031785</v>
+        <v>-10.16174159473275</v>
       </c>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="n">
-        <v>-0.3475502881717603</v>
-      </c>
+      <c r="AS5" t="n">
+        <v>5.251870490093232</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="n">
-        <v>-2.027583732057423</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.7515789473684187</v>
-      </c>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>1.978456147060083</v>
+        <v>0.03751056635672034</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.701985645933007</v>
+        <v>1855655.305903589</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="n">
-        <v>1.946363636363614</v>
-      </c>
+      <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>-0.006578947368421018</v>
+        <v>11.72562230722339</v>
       </c>
       <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>-0.887478109195257</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>140905.7732465644</v>
-      </c>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
         <v>0</v>
       </c>
@@ -1451,32 +1369,32 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IgfnrK9E</t>
+          <t>dx5Z1E0m</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45480.97916666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">marrufo j 
-  usa </t>
+          <t xml:space="preserve">fischer d 
+  can </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">paypal park
-  san jose  ca </t>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>U3ebh62R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>U3ebh62R</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1503,127 +1421,127 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>UL7r7duf</t>
+          <t>rXawJi8t</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2PIEeC7j</t>
+          <t>KtuTuMN0</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="R6" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7666666666666666</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.02222222222222214</v>
+        <v>-0.8181818181818181</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4545454545454546</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="W6" t="n">
-        <v>0.718181818181818</v>
+        <v>-0.7777777777777777</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1463492063492062</v>
+        <v>-4.555555555555555</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.3803174603174602</v>
-      </c>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
+        <v>1.888888888888889</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>7.111111111111107</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-7.111111111111107</v>
+      </c>
       <c r="AB6" t="n">
-        <v>-3.263636363636365</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.263636363636365</v>
+        <v>-0.8888888888888888</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.263636363636364</v>
+        <v>0.3333333333333339</v>
       </c>
       <c r="AE6" t="n">
-        <v>-4.009090909090908</v>
+        <v>2.777777777777779</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.2545454545454546</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.6272727272727272</v>
+        <v>-0.7272727272727275</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.09090909090909083</v>
+        <v>0.2983333333333333</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.2727272727272725</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>2.581818181818182</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>-1.890909090909092</v>
-      </c>
+        <v>-0.115</v>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>69.46329966329967</v>
+        <v>67.50988674625039</v>
       </c>
       <c r="AM6" t="n">
-        <v>68.14012855831038</v>
-      </c>
-      <c r="AN6" t="inlineStr"/>
+        <v>68.46830119375574</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>2252948.519283747</v>
+      </c>
       <c r="AO6" t="n">
-        <v>-1459956.529581529</v>
+        <v>0.339291414471603</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.081022677747569</v>
-      </c>
-      <c r="AQ6" t="inlineStr"/>
+        <v>-1.354836013734257</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4.372513774104675</v>
+      </c>
       <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>-0.551034184702246</v>
+      </c>
       <c r="AT6" t="n">
-        <v>3.414585697296985</v>
+        <v>-2.243930211202922</v>
       </c>
       <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="n">
-        <v>1.805974025973995</v>
-      </c>
+      <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="n">
-        <v>-0.00422077922078401</v>
+        <v>0.04361111111111104</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.664858851435312</v>
+        <v>0.03425008599931223</v>
       </c>
       <c r="AY6" t="n">
-        <v>-1.740353535353535</v>
+        <v>387447.5737984327</v>
       </c>
       <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="n">
-        <v>-1.898455988455993</v>
-      </c>
+      <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="n">
-        <v>-0.02599335748792275</v>
+        <v>0.8634858327909285</v>
       </c>
       <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="n">
-        <v>-0.06555555555555559</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>-0.5029787847633145</v>
-      </c>
+        <v>4.866209825528003</v>
+      </c>
+      <c r="BE6" t="inlineStr"/>
       <c r="BF6" t="n">
-        <v>-234223.9796822791</v>
+        <v>0.346453168044075</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1632,32 +1550,32 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>zZKrObIr</t>
+          <t>v1fv1YFg</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45472.89583333334</v>
+        <v>45480.97916666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">freemon j 
+          <t xml:space="preserve">rivas v 
   usa </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">toyota stadium
-  frisco  tx </t>
+          <t xml:space="preserve">providence park
+  portland  or </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
+          <t>bm8usLzB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>84yIDQMe</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1684,12 +1602,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>tOpyQa24</t>
+          <t>EqKWmJfM</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>GzULyFoh</t>
+          <t>dp6AQn9c</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -1698,109 +1616,113 @@
       <c r="P7" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.375</v>
+        <v>0.1818181818181819</v>
       </c>
       <c r="U7" t="n">
-        <v>1.125</v>
+        <v>-0.09090909090909094</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5555555555555558</v>
+        <v>1.555555555555555</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.1111111111111112</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1483333333333332</v>
+        <v>2.888888888888888</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.2171428571428575</v>
-      </c>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
+        <v>-2.111111111111111</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
       <c r="AB7" t="n">
-        <v>-1.111111111111114</v>
+        <v>0.7777777777777777</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.111111111111114</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.2222222222222232</v>
+        <v>1.888888888888889</v>
       </c>
       <c r="AE7" t="n">
-        <v>-1.888888888888889</v>
+        <v>-1.666666666666666</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.2222222222222223</v>
+        <v>-0.09090909090909083</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>0.9090909090909092</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.2222222222222223</v>
+        <v>0.2430952380952383</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.2222222222222223</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>-0.7777777777777768</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>-1.777777777777777</v>
-      </c>
+        <v>0.5545238095238095</v>
+      </c>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>68.02840909090909</v>
+        <v>68.33831994451829</v>
       </c>
       <c r="AM7" t="n">
-        <v>68.04051627384962</v>
-      </c>
-      <c r="AN7" t="inlineStr"/>
+        <v>67.06968181818181</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-434256.1983471075</v>
+      </c>
       <c r="AO7" t="n">
-        <v>-1372584.529505583</v>
+        <v>3.135695523314681</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.8644595945901017</v>
-      </c>
-      <c r="AQ7" t="inlineStr"/>
+        <v>-3.381583671824302</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.280991735537185</v>
+      </c>
       <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
+      <c r="AS7" t="n">
+        <v>-1.158590929208227</v>
+      </c>
       <c r="AT7" t="n">
-        <v>-1.209323031531824</v>
+        <v>-5.322314049586794</v>
       </c>
       <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="n">
-        <v>3.09539758487125</v>
-      </c>
+      <c r="AV7" t="inlineStr"/>
       <c r="AW7" t="n">
-        <v>0.3064935064935028</v>
+        <v>-0.1652892561983472</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.308092536832504</v>
+        <v>-0.05091927176907385</v>
       </c>
       <c r="AY7" t="n">
-        <v>-2.123239917976747</v>
+        <v>534919.6599855747</v>
       </c>
       <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="n">
-        <v>-1.83984962406015</v>
-      </c>
+      <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="n">
-        <v>0.03204309946709416</v>
+        <v>1.965784933245999</v>
       </c>
       <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="n">
-        <v>0.05411255411255422</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.686561601634111</v>
-      </c>
+        <v>0.4380165289256155</v>
+      </c>
+      <c r="BE7" t="inlineStr"/>
       <c r="BF7" t="n">
-        <v>-232178.8455168807</v>
+        <v>-1.198347107438018</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1809,32 +1731,32 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hAFmNIXl</t>
+          <t>rZ0V2fos</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45472.89583333334</v>
+        <v>45480.9375</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">da silva a 
-  usa </t>
+          <t xml:space="preserve">dujic f 
+  can </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">shell energy stadium
-  houston  tx </t>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>jmBZNRn8</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1861,127 +1783,127 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>nJ01AhXP</t>
+          <t>lAVQ9RGh</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>022mBmSn</t>
+          <t>l6eEjGlO</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.25</v>
+        <v>0.6363636363636362</v>
       </c>
       <c r="U8" t="n">
-        <v>0.375</v>
+        <v>-0.4545454545454546</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2222222222222221</v>
+        <v>1.444444444444444</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.4444444444444444</v>
+        <v>-0.8888888888888893</v>
       </c>
       <c r="X8" t="n">
-        <v>0.453214285714286</v>
+        <v>-5.222222222222223</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.04874999999999985</v>
-      </c>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
+        <v>2.222222222222221</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.3333333333333357</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0.3333333333333357</v>
+      </c>
       <c r="AB8" t="n">
-        <v>15.55555555555556</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="AC8" t="n">
-        <v>-15.55555555555556</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>7.666666666666666</v>
+        <v>-1.999999999999998</v>
       </c>
       <c r="AE8" t="n">
-        <v>-2.666666666666666</v>
+        <v>0.1111111111111107</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.09090909090909083</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>-0.454545454545455</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.444444444444445</v>
+        <v>0.5816666666666668</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.4444444444444446</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>3.222222222222221</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0.7777777777777786</v>
-      </c>
+        <v>0.1833333333333336</v>
+      </c>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
-        <v>67.45113636363638</v>
+        <v>67.71736361281816</v>
       </c>
       <c r="AM8" t="n">
-        <v>68.45606060606059</v>
-      </c>
-      <c r="AN8" t="inlineStr"/>
+        <v>68.97771349862259</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-549320.7070707069</v>
+      </c>
       <c r="AO8" t="n">
-        <v>-66920.45454545435</v>
+        <v>-0.6994137231204718</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1.872908410977388</v>
-      </c>
-      <c r="AQ8" t="inlineStr"/>
+        <v>-2.001684463328388</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-0.8736363636363649</v>
+      </c>
       <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
+      <c r="AS8" t="n">
+        <v>-1.936795721235587</v>
+      </c>
       <c r="AT8" t="n">
-        <v>-1.999617762660904</v>
+        <v>-2.306969696969702</v>
       </c>
       <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="n">
-        <v>-1.78000000000003</v>
-      </c>
+      <c r="AV8" t="inlineStr"/>
       <c r="AW8" t="n">
-        <v>0.3818181818181756</v>
+        <v>-0.193131313131313</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.7310272870329761</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.5550000000000068</v>
+        <v>-623264.3100354349</v>
       </c>
       <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="n">
-        <v>-0.6804545454545377</v>
-      </c>
+      <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="n">
-        <v>-0.02067239576990221</v>
+        <v>-4.386555549825509</v>
       </c>
       <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="n">
-        <v>0.07363636363636372</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>-1.835476596146194</v>
-      </c>
+        <v>-2.528181818181821</v>
+      </c>
+      <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="n">
-        <v>-449295.7251512283</v>
+        <v>-1.414040404040403</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -1990,32 +1912,32 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>QNDeLd21</t>
+          <t>QgE37zwQ</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45472.89583333334</v>
+        <v>45480.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
+          <t xml:space="preserve">simon n 
+  usa </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">geodis park
-  nashville  tn </t>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>84yIDQMe</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0AheRyBg</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2042,127 +1964,127 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>EgT3xN3S</t>
+          <t>UL7r7duf</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>zoZ995a</t>
+          <t>Uw6sTk0t</t>
         </is>
       </c>
       <c r="O9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>-1</v>
-      </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5250000000000004</v>
+        <v>-0.4545454545454546</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2750000000000004</v>
+        <v>0.5818181818181816</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7749999999999999</v>
+        <v>-0.708333333333333</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5</v>
+        <v>1.611111111111111</v>
       </c>
       <c r="X9" t="n">
-        <v>0.289365079365079</v>
+        <v>-6.930555555555555</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.02079365079365081</v>
-      </c>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
+        <v>2.847222222222221</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-2.805555555555557</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.805555555555557</v>
+      </c>
       <c r="AB9" t="n">
-        <v>-4.325000000000003</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.325000000000003</v>
+        <v>1.347222222222222</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>-2.4</v>
+        <v>4.527777777777779</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.425</v>
+        <v>1.409090909090909</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.3</v>
+        <v>-0.07272727272727231</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.5999999999999996</v>
+        <v>0.3116666666666664</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.2999999999999998</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0.4749999999999996</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>-0.5500000000000007</v>
-      </c>
+        <v>0.5913333333333335</v>
+      </c>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>67.09685746352415</v>
+        <v>68.84850252525253</v>
       </c>
       <c r="AM9" t="n">
-        <v>68.33863636363637</v>
-      </c>
-      <c r="AN9" t="inlineStr"/>
+        <v>67.88551887926887</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>37363.63636363624</v>
+      </c>
       <c r="AO9" t="n">
-        <v>-3547428.229665072</v>
+        <v>0.8896568730235543</v>
       </c>
       <c r="AP9" t="n">
-        <v>-2.196653511648364</v>
-      </c>
-      <c r="AQ9" t="inlineStr"/>
+        <v>-0.4233019940056124</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.3978956228956179</v>
+      </c>
       <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
+      <c r="AS9" t="n">
+        <v>-0.6983513983685548</v>
+      </c>
       <c r="AT9" t="n">
-        <v>-1.836322547681107</v>
+        <v>-1.197811447811461</v>
       </c>
       <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="n">
-        <v>1.074641148325384</v>
-      </c>
+      <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="n">
-        <v>0.4349282296650792</v>
+        <v>-0.06363636363636371</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.191401503317291</v>
+        <v>-0.1435562721031829</v>
       </c>
       <c r="AY9" t="n">
-        <v>-4.966985645933008</v>
+        <v>98939.42903756956</v>
       </c>
       <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="n">
-        <v>-7.166985645933025</v>
-      </c>
+      <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="n">
-        <v>-0.2149367025584696</v>
+        <v>0.09864734161929789</v>
       </c>
       <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="n">
-        <v>-0.6110047846889952</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>-6.982767895371879</v>
-      </c>
+        <v>1.215656565656573</v>
+      </c>
+      <c r="BE9" t="inlineStr"/>
       <c r="BF9" t="n">
-        <v>-1741247.396748824</v>
+        <v>1.405134680134676</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2171,32 +2093,32 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>W0EiMxme</t>
+          <t>AoWGqXpJ</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45472.89583333334</v>
+        <v>45480.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">fischer d 
-  can </t>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">children s mercy park
-  kansas city  ks </t>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>IeT6JBE3</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2223,127 +2145,127 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>zoZ995af</t>
+          <t>nJ01AhXP</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>KtuTuMN0</t>
+          <t>Onn3tCA5</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="P10" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2777777777777777</v>
+        <v>-1.136363636363636</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5</v>
+        <v>0.8409090909090908</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1909090909090908</v>
+        <v>-0.3666666666666671</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1636363636363636</v>
+        <v>2.022222222222222</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4101388888888889</v>
+        <v>3.68888888888889</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.3400000000000001</v>
-      </c>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
+        <v>3.1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.200000000000003</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-2.200000000000003</v>
+      </c>
       <c r="AB10" t="n">
-        <v>5.581818181818178</v>
+        <v>-0.6111111111111112</v>
       </c>
       <c r="AC10" t="n">
-        <v>-5.581818181818178</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="AD10" t="n">
-        <v>9.1</v>
+        <v>-1.155555555555555</v>
       </c>
       <c r="AE10" t="n">
-        <v>-6.390909090909092</v>
+        <v>-0.1333333333333346</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.681818181818182</v>
+        <v>0.4924242424242422</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.7909090909090908</v>
+        <v>0.6287878787878789</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.163636363636363</v>
+        <v>-0.5353333333333332</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.5272727272727273</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.163636363636364</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.463636363636363</v>
-      </c>
+        <v>0.5243333333333332</v>
+      </c>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>68.91252525252524</v>
+        <v>67.60686131285304</v>
       </c>
       <c r="AM10" t="n">
-        <v>67.83636363636364</v>
-      </c>
-      <c r="AN10" t="inlineStr"/>
+        <v>68.15992676767677</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-2359507.996632996</v>
+      </c>
       <c r="AO10" t="n">
-        <v>-649653.9256198348</v>
+        <v>-3.783869257923214</v>
       </c>
       <c r="AP10" t="n">
-        <v>-2.601394477751576</v>
-      </c>
-      <c r="AQ10" t="inlineStr"/>
+        <v>0.3191754570330261</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-4.106902356902367</v>
+      </c>
       <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
+      <c r="AS10" t="n">
+        <v>-0.2966417802819024</v>
+      </c>
       <c r="AT10" t="n">
-        <v>-1.197193682809086</v>
+        <v>-0.01809764309763295</v>
       </c>
       <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="n">
-        <v>-0.004710743801638273</v>
-      </c>
+      <c r="AV10" t="inlineStr"/>
       <c r="AW10" t="n">
-        <v>-0.6488429752066125</v>
+        <v>-0.1827441077441079</v>
       </c>
       <c r="AX10" t="n">
-        <v>-3.303916290061547</v>
+        <v>0.08251092707614438</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.3543388429751957</v>
+        <v>-508649.5945214585</v>
       </c>
       <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="n">
-        <v>1.015785123966936</v>
-      </c>
+      <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="n">
-        <v>-0.2444527136837675</v>
+        <v>-2.822180211768739</v>
       </c>
       <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="n">
-        <v>-0.04433884297520674</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0.274158475001542</v>
-      </c>
+        <v>-4.279461279461287</v>
+      </c>
+      <c r="BE10" t="inlineStr"/>
       <c r="BF10" t="n">
-        <v>-292637.3184193238</v>
+        <v>-0.7604377104377136</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2352,32 +2274,32 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>fiHVGBod</t>
+          <t>n3Fa8GNJ</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45472.85416666666</v>
+        <v>45480.89583333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">da silva a 
+          <t xml:space="preserve">badawi m 
   usa </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">saputo stadium
-  montreal  qc </t>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Szrwix67</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2404,127 +2326,131 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lAVQ9RGh</t>
+          <t>zoZ995af</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>022mBmSn</t>
+          <t>WWvwigh8</t>
         </is>
       </c>
       <c r="O11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1</v>
       </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
         <v>1</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>-1</v>
-      </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>-0.7500000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>2.375</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3055555555555556</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="W11" t="n">
-        <v>0.3611111111111112</v>
+        <v>-2.3</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.02041666666666675</v>
+        <v>1.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.01083333333333325</v>
-      </c>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
+        <v>2.1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-7.5</v>
+      </c>
       <c r="AB11" t="n">
-        <v>5.736111111111114</v>
+        <v>-0.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>-5.736111111111114</v>
+        <v>0.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.5555555555555554</v>
+        <v>6.900000000000002</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.4722222222222214</v>
+        <v>-9.499999999999998</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.375</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.1805555555555556</v>
+        <v>-0.333333333333333</v>
       </c>
       <c r="AH11" t="n">
-        <v>-1.805555555555555</v>
+        <v>-0.1950000000000003</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.3611111111111107</v>
+        <v>-0.1816666666666669</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.75</v>
+        <v>-4.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.8611111111111107</v>
+        <v>-4.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>69.40012626262626</v>
+        <v>67.69853994490357</v>
       </c>
       <c r="AM11" t="n">
-        <v>67.48080808080807</v>
-      </c>
-      <c r="AN11" t="inlineStr"/>
+        <v>68.6852157943067</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-1536566.433566433</v>
+      </c>
       <c r="AO11" t="n">
-        <v>-1559153.110047847</v>
+        <v>-1.622413397687993</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.02137251904034088</v>
-      </c>
-      <c r="AQ11" t="inlineStr"/>
+        <v>-0.00221150067827125</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-2.561538461538461</v>
+      </c>
       <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr"/>
+      <c r="AS11" t="n">
+        <v>0.5188406990924186</v>
+      </c>
       <c r="AT11" t="n">
-        <v>-1.99800866126435</v>
+        <v>-2.273426573426576</v>
       </c>
       <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="n">
-        <v>-4.617224880382764</v>
-      </c>
+      <c r="AV11" t="inlineStr"/>
       <c r="AW11" t="n">
-        <v>-1.33923444976076</v>
+        <v>-0.01608391608391613</v>
       </c>
       <c r="AX11" t="n">
-        <v>-1.390993361100904</v>
+        <v>0.0332877064456012</v>
       </c>
       <c r="AY11" t="n">
-        <v>-2.91531100478467</v>
+        <v>-486384.4483859645</v>
       </c>
       <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="n">
-        <v>-1.94736842105263</v>
-      </c>
+      <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="n">
-        <v>0.0227410502972667</v>
+        <v>0.06169891257992788</v>
       </c>
       <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="n">
-        <v>-0.04401913875598118</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>0.9569849973772762</v>
-      </c>
+        <v>-1.831468531468516</v>
+      </c>
+      <c r="BE11" t="inlineStr"/>
       <c r="BF11" t="n">
-        <v>-239882.585765356</v>
+        <v>1.303496503496508</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2533,32 +2459,32 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>4nbBt7Y9</t>
+          <t>WfXCpDVC</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45472.85416666666</v>
+        <v>45479.97916666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">de oliveira m 
+          <t xml:space="preserve">freemon j 
   usa </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">gillette stadium
-  foxborough  ma </t>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>tr3oe8I8</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2585,127 +2511,123 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>roEEsq76</t>
+          <t>tOpyQa24</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>jBBpU7Y0</t>
+          <t>GzULyFoh</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="P12" t="n">
-        <v>-8</v>
-      </c>
-      <c r="Q12" t="n">
         <v>-1</v>
       </c>
-      <c r="R12" t="n">
-        <v>-1</v>
-      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5</v>
+        <v>0.2777777777777777</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0.388888888888889</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5555555555555556</v>
+        <v>-1.48051948051948</v>
       </c>
       <c r="W12" t="n">
-        <v>0.7777777777777777</v>
+        <v>-1.727272727272728</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2583928571428573</v>
+        <v>-1.220779220779221</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.01553571428571443</v>
-      </c>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
+        <v>0.3116883116883127</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-2.155844155844157</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.155844155844157</v>
+      </c>
       <c r="AB12" t="n">
-        <v>-2.444444444444443</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.444444444444443</v>
+        <v>-0.3506493506493507</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.555555555555555</v>
+        <v>1.025974025974026</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.5555555555555554</v>
+        <v>-3.571428571428573</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.7777777777777779</v>
+        <v>2.416666666666667</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.2020202020202015</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.1111111111111107</v>
+        <v>-0.01033333333333342</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.2222222222222223</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>4.444444444444445</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>-5.111111111111111</v>
-      </c>
+        <v>-0.921</v>
+      </c>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
-        <v>67.94898989898989</v>
+        <v>67.63545454545455</v>
       </c>
       <c r="AM12" t="n">
-        <v>67.5246913580247</v>
-      </c>
-      <c r="AN12" t="inlineStr"/>
+        <v>68.39667832167832</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-1091323.70330287</v>
+      </c>
       <c r="AO12" t="n">
-        <v>136423.1469102786</v>
+        <v>-2.14876069257852</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.805217729279093</v>
-      </c>
-      <c r="AQ12" t="inlineStr"/>
+        <v>-3.127233136338987</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.7550104216770848</v>
+      </c>
       <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="inlineStr"/>
+      <c r="AS12" t="n">
+        <v>-1.687577720103402</v>
+      </c>
       <c r="AT12" t="n">
-        <v>-2.180919295100381</v>
+        <v>-2.112271524771472</v>
       </c>
       <c r="AU12" t="inlineStr"/>
-      <c r="AV12" t="n">
-        <v>1.065663992869901</v>
-      </c>
+      <c r="AV12" t="inlineStr"/>
       <c r="AW12" t="n">
-        <v>0.7770424836601322</v>
+        <v>0.1313772647105975</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.33416095028301</v>
+        <v>-0.01541314942400773</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.276994206773608</v>
+        <v>-67714.16612046305</v>
       </c>
       <c r="AZ12" t="inlineStr"/>
-      <c r="BA12" t="n">
-        <v>0.2100304515745677</v>
-      </c>
+      <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="n">
-        <v>0.07889723087774447</v>
+        <v>-3.062332932384102</v>
       </c>
       <c r="BC12" t="inlineStr"/>
       <c r="BD12" t="n">
-        <v>0.1093285799168153</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>0.8243736101266705</v>
-      </c>
+        <v>-0.1500300625300639</v>
+      </c>
+      <c r="BE12" t="inlineStr"/>
       <c r="BF12" t="n">
-        <v>-194216.7726975693</v>
+        <v>0.316466249799582</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2714,32 +2636,32 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>b9cFuRmG</t>
+          <t>xYX8ogG6</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45472.85416666666</v>
+        <v>45479.9375</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ford t 
-  usa </t>
+          <t xml:space="preserve">dujic f 
+  can </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">red bull arena
-  harrison  nj </t>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>W0ealpQl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>EPngUvhk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2766,12 +2688,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>rJ9D8rzj</t>
+          <t>rXawJi8t</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>86yPt28f</t>
+          <t>l6eEjGlO</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -2781,112 +2703,116 @@
         <v>-2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="R13" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
+        <v>0.3787878787878787</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.4166666666666667</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.7999999999999998</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.2000000000000011</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-3.700000000000003</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC13" t="n">
         <v>0.5</v>
       </c>
-      <c r="U13" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.555555555555556</v>
-      </c>
-      <c r="W13" t="n">
-        <v>-1.444444444444444</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.05874999999999986</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>-0.8424999999999999</v>
-      </c>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="n">
-        <v>-0.8888888888888928</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0.8888888888888928</v>
-      </c>
       <c r="AD13" t="n">
-        <v>3.888888888888889</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="n">
-        <v>-4.555555555555555</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.8888888888888888</v>
+        <v>-1.416666666666667</v>
       </c>
       <c r="AG13" t="n">
-        <v>-1.111111111111111</v>
+        <v>0.1590909090909092</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.444444444444445</v>
+        <v>0.7366666666666668</v>
       </c>
       <c r="AI13" t="n">
-        <v>-1.666666666666667</v>
+        <v>0.2149999999999999</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-4.333333333333334</v>
+        <v>-11</v>
       </c>
       <c r="AK13" t="n">
-        <v>-1.444444444444445</v>
+        <v>-12</v>
       </c>
       <c r="AL13" t="n">
-        <v>68.35050505050505</v>
+        <v>67.81664141414142</v>
       </c>
       <c r="AM13" t="n">
-        <v>68.67954545454546</v>
-      </c>
-      <c r="AN13" t="inlineStr"/>
+        <v>68.88799287642263</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-2093418.609168609</v>
+      </c>
       <c r="AO13" t="n">
-        <v>1521779.292929293</v>
+        <v>-0.2279199760392885</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.772781397075789</v>
-      </c>
-      <c r="AQ13" t="inlineStr"/>
+        <v>-1.086574051936083</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0.4768842268842093</v>
+      </c>
       <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
+      <c r="AS13" t="n">
+        <v>-1.008724228992417</v>
+      </c>
       <c r="AT13" t="n">
-        <v>-1.651231052014737</v>
+        <v>-0.490332815332863</v>
       </c>
       <c r="AU13" t="inlineStr"/>
-      <c r="AV13" t="n">
-        <v>-3.719494949494987</v>
-      </c>
+      <c r="AV13" t="inlineStr"/>
       <c r="AW13" t="n">
-        <v>-3.488484848484845</v>
+        <v>-0.1755244755244758</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.04388560991997892</v>
+        <v>-0.03751056635672034</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.219393939393939</v>
+        <v>-608923.2072607961</v>
       </c>
       <c r="AZ13" t="inlineStr"/>
-      <c r="BA13" t="n">
-        <v>3.981060606060609</v>
-      </c>
+      <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="n">
-        <v>0.04871978636819119</v>
+        <v>-1.929757058509928</v>
       </c>
       <c r="BC13" t="inlineStr"/>
       <c r="BD13" t="n">
-        <v>0.02878787878787903</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.094297923065255</v>
-      </c>
+        <v>-1.186182336182327</v>
+      </c>
+      <c r="BE13" t="inlineStr"/>
       <c r="BF13" t="n">
-        <v>964710.8332939812</v>
+        <v>-1.500116550116552</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -2895,32 +2821,32 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>G0IRHiWk</t>
+          <t>QcU4nZ00</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45472.85416666666</v>
+        <v>45479.89583333334</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">dickerson j 
+          <t xml:space="preserve">rivas v 
   usa </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">mercedes benz stadium
-  atlanta  ga </t>
+          <t xml:space="preserve">q2 stadium
+  austin  tx </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
+          <t>IeT6JBE3</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2947,127 +2873,119 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>z9ZXDy6o</t>
+          <t>UFWZoX9L</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>xA45kovo</t>
-        </is>
-      </c>
-      <c r="O14" t="n">
-        <v>-2</v>
-      </c>
-      <c r="P14" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.125</v>
+        <v>-0.5</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.034090909090909</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3838383838383839</v>
+        <v>-1.166666666666667</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3434343434343434</v>
+        <v>-1.5</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6530555555555555</v>
+        <v>1.180555555555555</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.2943055555555556</v>
-      </c>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
+        <v>0.7361111111111107</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.194444444444443</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-1.194444444444443</v>
+      </c>
       <c r="AB14" t="n">
-        <v>8.070707070707066</v>
+        <v>-0.875</v>
       </c>
       <c r="AC14" t="n">
-        <v>-7.979797979797979</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="AD14" t="n">
-        <v>7.606060606060607</v>
+        <v>-3.291666666666666</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.8888888888888893</v>
+        <v>1.319444444444445</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.111111111111111</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.4343434343434343</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.545454545454546</v>
+        <v>-0.07866666666666688</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0.8989898989898988</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>-1.373737373737374</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>-0.6767676767676765</v>
-      </c>
+        <v>0.6826666666666665</v>
+      </c>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="n">
-        <v>69.10363636363635</v>
+        <v>67.96524475524475</v>
       </c>
       <c r="AM14" t="n">
-        <v>68.44567901234569</v>
-      </c>
-      <c r="AN14" t="inlineStr"/>
+        <v>68.45333333333333</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>551759.6801346801</v>
+      </c>
       <c r="AO14" t="n">
-        <v>2163582.386363636</v>
+        <v>-4.675784019939016</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.797210860128551</v>
-      </c>
-      <c r="AQ14" t="inlineStr"/>
+        <v>0.4778867800847308</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-3.238540965207619</v>
+      </c>
       <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="inlineStr"/>
+      <c r="AS14" t="n">
+        <v>6.443748292153693</v>
+      </c>
       <c r="AT14" t="n">
-        <v>-0.1666238177419643</v>
+        <v>-2.903367003366952</v>
       </c>
       <c r="AU14" t="inlineStr"/>
-      <c r="AV14" t="n">
-        <v>-3.180000000000007</v>
-      </c>
+      <c r="AV14" t="inlineStr"/>
       <c r="AW14" t="n">
-        <v>-0.5285227272727298</v>
+        <v>0.1163636363636364</v>
       </c>
       <c r="AX14" t="n">
-        <v>2.349485298254567</v>
+        <v>0.2614352697600781</v>
       </c>
       <c r="AY14" t="n">
-        <v>2.418750000000003</v>
+        <v>-276944.8221992149</v>
       </c>
       <c r="AZ14" t="inlineStr"/>
-      <c r="BA14" t="n">
-        <v>3.988181818181801</v>
-      </c>
+      <c r="BA14" t="inlineStr"/>
       <c r="BB14" t="n">
-        <v>-0.08721505896849147</v>
+        <v>2.170030776439269</v>
       </c>
       <c r="BC14" t="inlineStr"/>
       <c r="BD14" t="n">
-        <v>-0.0190909090909086</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.551623087515452</v>
-      </c>
+        <v>1.403776655443295</v>
+      </c>
+      <c r="BE14" t="inlineStr"/>
       <c r="BF14" t="n">
-        <v>515855.8736060229</v>
+        <v>4.834977553310885</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3076,181 +2994,5810 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>jqf7smJ3</t>
+          <t>rZv0mFof</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45471.85416666666</v>
+        <v>45479.85416666666</v>
       </c>
       <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subaru park
+  chester  pa </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>167</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>2</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-1.072727272727273</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.9181818181818181</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-1.222222222222221</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>9.111111111111107</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-9.111111111111107</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.444444444444443</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.318181818181818</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.1272727272727279</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.4366666666666665</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-0.0283333333333331</v>
+      </c>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="n">
+        <v>67.45277986476334</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>67.00370064279154</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>153365.9320477499</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-0.943038107043435</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.531882193914754</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-1.328772574227116</v>
+      </c>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="n">
+        <v>1.316740991453045</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>4.325612182430376</v>
+      </c>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="n">
+        <v>-0.04242424242424248</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.002080970852166741</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-121660.5220761718</v>
+      </c>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="n">
+        <v>1.534592221969525</v>
+      </c>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="n">
+        <v>1.564041934496473</v>
+      </c>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="n">
+        <v>2.707307927762471</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>4rtdleWm</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ford t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>167</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.7272727272727273</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.666666666666667</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-4.666666666666668</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-0.7777777777777768</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.1111111111111143</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.1111111111111143</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.2222222222222221</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0.7777777777777779</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-1.555555555555555</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.333333333333332</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-0.3636363636363633</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-0.8149999999999999</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-0.1633333333333333</v>
+      </c>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="n">
+        <v>68.61944629954272</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>68.12141247182569</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1657181.818181818</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-1.576787069764805</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-2.642094317790907</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>2.301652892561989</v>
+      </c>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="n">
+        <v>2.205796840992452</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>-4.852892561983509</v>
+      </c>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="n">
+        <v>0.1396694214876033</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0.139366931345541</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1746889.47463863</v>
+      </c>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="n">
+        <v>2.766895788328384</v>
+      </c>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="n">
+        <v>3.585950413223131</v>
+      </c>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="n">
+        <v>0.341322314049588</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>z9yhkyHs</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tql stadium
+  cincinnati  oh </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>167</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.1000000000000001</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.1000000000000001</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.625</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0.625</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>5.625</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.28888888888889</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.3856666666666666</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-0.6803333333333331</v>
+      </c>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="n">
+        <v>68.0824962915872</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>68.30929292929292</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>-2878086.363636363</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>-6.634738852721597</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-2.885435493037761</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-4.096363636363634</v>
+      </c>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="n">
+        <v>0.4209283370792356</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>-2.49454545454546</v>
+      </c>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="n">
+        <v>-0.7536363636363634</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>-0.13625</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>-1147255.943062337</v>
+      </c>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="n">
+        <v>-5.543661777622773</v>
+      </c>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="n">
+        <v>-4.840000000000003</v>
+      </c>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="n">
+        <v>-2.365454545454547</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>rRCPxg8F</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>167</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>6</v>
+      </c>
+      <c r="P18" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.252525252525253</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-1.111111111111111</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.9206349206349209</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.5396825396825395</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-3.746031746031746</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>4.412698412698413</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>8.428571428571431</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-8.428571428571431</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8730158730158728</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-1.190476190476191</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.2698412698412689</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-2.746031746031747</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-0.2727272727272725</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-0.05916666666666659</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>-0.1758333333333333</v>
+      </c>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="n">
+        <v>67.85302435125668</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>67.31837751321223</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1018565.599173554</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1.655135225420182</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>2.327370572735049</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>4.764772727272714</v>
+      </c>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="n">
+        <v>1.132567252943055</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-2.007438016528909</v>
+      </c>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="n">
+        <v>-0.2024793388429751</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>-0.1462406015037594</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>337955.4402194789</v>
+      </c>
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="n">
+        <v>2.047288761822607</v>
+      </c>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="n">
+        <v>3.779132231404958</v>
+      </c>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="n">
+        <v>-0.9260330578512388</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xlCTyDNL</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>167</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.08181818181818179</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.1636363636363636</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-0.05555555555555536</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.847222222222222</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.138888888888889</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-1.486111111111111</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.458333333333336</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-1.458333333333336</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.5833333333333335</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-1.222222222222221</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.09090909090909083</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.1633333333333333</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="n">
+        <v>68.17680848892969</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>67.98885123966943</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-1402322.314049587</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>2.253964624701069</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>2.859329138662929</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>-0.4736363636363734</v>
+      </c>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="n">
+        <v>-1.75823832398099</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2.090082644628097</v>
+      </c>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="n">
+        <v>0.01652892561983466</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0.09740570434350326</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>283834.8223009913</v>
+      </c>
+      <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="n">
+        <v>-0.08151588622411055</v>
+      </c>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="n">
+        <v>-3.343966942148768</v>
+      </c>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="n">
+        <v>-2.035454545454549</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45477.97916666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>167</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Onn3tCA5</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>2</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.7363636363636363</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.5181818181818181</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-0.7000000000000002</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.133333333333333</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-1.533333333333333</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.8777777777777782</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.08888888888888857</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-0.08888888888888857</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-0.6111111111111112</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-1.71111111111111</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.533333333333333</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.4545454545454541</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>-0.1486666666666665</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.6426666666666666</v>
+      </c>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="n">
+        <v>67.06156565656565</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>67.90606060606061</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>-744729.5875420873</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>-1.943638723033075</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>-0.8577192442633645</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>-0.6721296296296515</v>
+      </c>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="n">
+        <v>-1.940979588007455</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>-1.245016835016827</v>
+      </c>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="n">
+        <v>-0.2921632996632999</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0.02366807541730176</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>-194563.2732724934</v>
+      </c>
+      <c r="AZ20" t="inlineStr"/>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="n">
+        <v>-2.218655409133333</v>
+      </c>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="n">
+        <v>-1.548375420875416</v>
+      </c>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="n">
+        <v>-1.132786195286201</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45477.9375</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>167</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.5666666666666665</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.6833333333333336</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.929292929292929</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-1.121212121212121</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-3.626262626262626</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.6666666666666661</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-5.141414141414145</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>5.141414141414145</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.494949494949495</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-0.4747474747474749</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-1.393939393939393</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.979797979797981</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>-0.01818181818181852</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.02500000000000036</v>
+      </c>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="n">
+        <v>67.91021885521886</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>67.91384848484849</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>509286.7132867135</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1.477395454786773</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>-0.1909197324415288</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.760139860139859</v>
+      </c>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="n">
+        <v>-3.361033314511577</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0.1615384615384414</v>
+      </c>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="n">
+        <v>-0.05034965034965033</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>-0.06297605775866666</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>-230696.3777768123</v>
+      </c>
+      <c r="AZ21" t="inlineStr"/>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="n">
+        <v>-3.248668312363975</v>
+      </c>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="n">
+        <v>-0.2433566433566483</v>
+      </c>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="n">
+        <v>-2.879020979020982</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45477.89583333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>167</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.2166666666666668</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.1833333333333332</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.09090909090909083</v>
+      </c>
+      <c r="W22" t="n">
+        <v>3.919191919191919</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-1.666666666666666</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-0.6464646464646471</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-1.242424242424242</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.242424242424242</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.04040404040404044</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.4343434343434343</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>-2.979797979797981</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>7.626262626262628</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>-0.04999999999999982</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>-0.5547619047619047</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0.7004761904761907</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>68.58101010101009</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>68.41012396694215</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>-133009.5359186274</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>-0.3517252722911763</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0.7281188681306787</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>-0.9242212333121387</v>
+      </c>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="n">
+        <v>-1.594665494695171</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.735028607755908</v>
+      </c>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="n">
+        <v>0.06643356643356646</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0.02968835131306546</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>-237429.9202725799</v>
+      </c>
+      <c r="AZ22" t="inlineStr"/>
+      <c r="BA22" t="inlineStr"/>
+      <c r="BB22" t="n">
+        <v>-3.968851748893421</v>
+      </c>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="n">
+        <v>-2.106993006993022</v>
+      </c>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="n">
+        <v>-0.9186904005085808</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45476.9375</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ford t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>167</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.4545454545454546</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.3636363636363636</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.1363636363636367</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.536363636363637</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-2.990909090909092</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>-1.145454545454545</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.172727272727272</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-1.081818181818178</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.2727272727272729</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>-0.06363636363636349</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.872727272727273</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>-0.2363636363636363</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.6290476190476193</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0.105952380952381</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>67.81800505050505</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>67.76279155188246</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>100880.0505050505</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1.749907422367542</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>-1.098338265799015</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.811616161616158</v>
+      </c>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="n">
+        <v>-0.9275046332628989</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>-1.645286195286246</v>
+      </c>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="n">
+        <v>-0.1530303030303031</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>-0.09309293765815485</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>223824.3369515643</v>
+      </c>
+      <c r="AZ23" t="inlineStr"/>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="n">
+        <v>-0.4829092016856933</v>
+      </c>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="n">
+        <v>-1.66607744107742</v>
+      </c>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="n">
+        <v>-2.392424242424241</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45476.89583333334</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">da silva a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">soldier field
+  chicago  il </t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>167</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>-6</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.09999999999999987</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-1.111111111111112</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-0.1111111111111107</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.444444444444443</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>-0.2222222222222214</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-4.444444444444443</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>4.444444444444443</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.1111111111111109</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>-4.666666666666664</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.1111111111111107</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.03333333333333321</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>-0.9564285714285714</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.127142857142857</v>
+      </c>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="n">
+        <v>67.84192460317459</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>67.43169421487603</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>-563489.8989898986</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>-1.439020322815836</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>-0.1532190678913707</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>-1.008417508417509</v>
+      </c>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="n">
+        <v>1.845930102672664</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>-1.84048821548825</v>
+      </c>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="n">
+        <v>-0.003030303030302939</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0.07271327973382147</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>-162460.2215688201</v>
+      </c>
+      <c r="AZ24" t="inlineStr"/>
+      <c r="BA24" t="inlineStr"/>
+      <c r="BB24" t="n">
+        <v>0.6104682718752912</v>
+      </c>
+      <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="n">
+        <v>-1.681397306397315</v>
+      </c>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="n">
+        <v>-0.6064814814814774</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45476.89583333334</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>167</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>z9ZXDy6o</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Onn3tCA5</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>2</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.2727272727272727</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-0.3000000000000007</v>
+      </c>
+      <c r="X25" t="n">
+        <v>6.300000000000001</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>-1.799999999999999</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.200000000000003</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-2.200000000000003</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>-0.7000000000000001</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.581818181818182</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0.01142857142857157</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>-0.3108571428571429</v>
+      </c>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="n">
+        <v>68.89777777777778</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>68.9345987654321</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>-230770.2020202023</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>-0.4927628301973641</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.433488006001426</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>-0.8969865319865278</v>
+      </c>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="n">
+        <v>-1.713427264313488</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.913872053872069</v>
+      </c>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="n">
+        <v>0.193131313131313</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>-132045.4242117989</v>
+      </c>
+      <c r="AZ25" t="inlineStr"/>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="n">
+        <v>-1.484931970303322</v>
+      </c>
+      <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="n">
+        <v>-0.8056565656565624</v>
+      </c>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="n">
+        <v>-0.9820033670033652</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45476.89583333334</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>167</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.7777777777777781</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.2222222222222214</v>
+      </c>
+      <c r="X26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>-1.333333333333332</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-2.888888888888886</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.888888888888886</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.4444444444444446</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.344444444444445</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>-0.01071428571428568</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>-0.1026190476190476</v>
+      </c>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="n">
+        <v>68.42040404040404</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>68.20372727272726</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>-1478768.595041323</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0.6967642591327063</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>2.301744488031687</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>-2.035619834710758</v>
+      </c>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="n">
+        <v>-0.406806046737394</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>4.404132231404958</v>
+      </c>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>145202.6331474271</v>
+      </c>
+      <c r="AZ26" t="inlineStr"/>
+      <c r="BA26" t="inlineStr"/>
+      <c r="BB26" t="n">
+        <v>-0.9693554621071598</v>
+      </c>
+      <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="n">
+        <v>-3.36876033057851</v>
+      </c>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="n">
+        <v>0.4025619834710703</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45476.86458333334</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dujic f 
+  can </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>167</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.2222222222222221</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.011363636363637</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.1818181818181817</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.7613636363636367</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-1.329545454545453</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.238636363636367</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>-0.07954545454545459</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.3181818181818181</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>-2.022727272727273</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>3.375</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>-0.07954545454545414</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>-0.5449999999999999</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0.7299999999999995</v>
+      </c>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="n">
+        <v>68.46161616161618</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>68.8895867768595</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>-910805.6742640077</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1.389722464949443</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.603845687081929</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>-0.2608823275489982</v>
+      </c>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="n">
+        <v>-0.2084215008109105</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1.593758093758055</v>
+      </c>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="n">
+        <v>-0.07833031166364512</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0.07114218249210702</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>-643007.982729305</v>
+      </c>
+      <c r="AZ27" t="inlineStr"/>
+      <c r="BA27" t="inlineStr"/>
+      <c r="BB27" t="n">
+        <v>0.4984833891862337</v>
+      </c>
+      <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="n">
+        <v>1.638312613312607</v>
+      </c>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="n">
+        <v>0.5794850211516867</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mendoza r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>167</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>10</v>
+      </c>
+      <c r="P28" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4</v>
+      </c>
+      <c r="R28" t="n">
+        <v>4</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.8727272727272728</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-0.5181818181818181</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="W28" t="n">
+        <v>-0.9777777777777779</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-0.09999999999999964</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.477777777777778</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.37777777777778</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-2.37777777777778</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.2666666666666668</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>-1.055555555555556</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.477777777777778</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>-2.122222222222222</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>-0.3666666666666671</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0.1673809523809524</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>-0.8271428571428572</v>
+      </c>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="n">
+        <v>68.33300275482092</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>68.45781297826753</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>275448.9975512703</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>-0.05785659033551838</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0.425032800343331</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0.3894500561167291</v>
+      </c>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="n">
+        <v>-1.666801018154864</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>3.404193449647977</v>
+      </c>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="n">
+        <v>-0.01652892561983466</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>-0.09740570434350326</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>22135.27428143215</v>
+      </c>
+      <c r="AZ28" t="inlineStr"/>
+      <c r="BA28" t="inlineStr"/>
+      <c r="BB28" t="n">
+        <v>-2.373599850591368</v>
+      </c>
+      <c r="BC28" t="inlineStr"/>
+      <c r="BD28" t="n">
+        <v>0.3056448321599987</v>
+      </c>
+      <c r="BE28" t="inlineStr"/>
+      <c r="BF28" t="n">
+        <v>-0.5267957351290669</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freemon j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>167</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>3</v>
+      </c>
+      <c r="P29" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>-1.563636363636364</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V29" t="n">
+        <v>-1.066666666666667</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.08888888888888946</v>
+      </c>
+      <c r="X29" t="n">
+        <v>-0.7555555555555546</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.7666666666666657</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-4.011111111111113</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>4.011111111111113</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>-1.022222222222222</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0.6444444444444446</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>-1.277777777777779</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0.04444444444444429</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>-0.9204545454545459</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.1102857142857141</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.5520000000000004</v>
+      </c>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="n">
+        <v>68.08504883546206</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>68.38960372960373</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>-2517322.727272728</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>3.951781693273773</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.100878411832099</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>-3.085867768595051</v>
+      </c>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="n">
+        <v>-1.410505206249407</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>5.017438016528928</v>
+      </c>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="n">
+        <v>0.09173553719008276</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0.01438064859117483</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>-465306.0327683028</v>
+      </c>
+      <c r="AZ29" t="inlineStr"/>
+      <c r="BA29" t="inlineStr"/>
+      <c r="BB29" t="n">
+        <v>0.02018168956028887</v>
+      </c>
+      <c r="BC29" t="inlineStr"/>
+      <c r="BD29" t="n">
+        <v>-2.871074380165282</v>
+      </c>
+      <c r="BE29" t="inlineStr"/>
+      <c r="BF29" t="n">
+        <v>1.330991735537186</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bank of america stadium
+  charlotte  nc </t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>167</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>1</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>-0.1000000000000001</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.03636363636363638</v>
+      </c>
+      <c r="V30" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.1111111111111107</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.544444444444444</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>-1.166666666666666</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-6.955555555555556</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>6.955555555555556</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>-0.9222222222222223</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>-0.7444444444444445</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.033333333333333</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>-3.800000000000001</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.9000000000000004</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>-0.5771428571428573</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>-0.4485714285714287</v>
+      </c>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="n">
+        <v>68.37378328741966</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>68.71528925619835</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>-5093438.934802571</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>-3.488959023003147</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>-2.951882287350173</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>-6.527594123048672</v>
+      </c>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="n">
+        <v>2.180104154609499</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0.350716253443494</v>
+      </c>
+      <c r="AU30" t="inlineStr"/>
+      <c r="AV30" t="inlineStr"/>
+      <c r="AW30" t="n">
+        <v>-0.7453719008264461</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>-0.04184298099405059</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>-761647.3115416965</v>
+      </c>
+      <c r="AZ30" t="inlineStr"/>
+      <c r="BA30" t="inlineStr"/>
+      <c r="BB30" t="n">
+        <v>-1.652049303192356</v>
+      </c>
+      <c r="BC30" t="inlineStr"/>
+      <c r="BD30" t="n">
+        <v>-7.69996326905418</v>
+      </c>
+      <c r="BE30" t="inlineStr"/>
+      <c r="BF30" t="n">
+        <v>-1.425371900826452</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t xml:space="preserve">simon n 
   usa </t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo field
+  toronto  on </t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>167</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Uw6sTk0t</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>-3</v>
+      </c>
+      <c r="R31" t="n">
+        <v>-3</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>-0.3636363636363636</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.4545454545454546</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W31" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>-0.9000000000000004</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.799999999999997</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-2.799999999999997</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.8000000000000003</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.1999999999999993</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.3999999999999995</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.5211904761904762</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.08238095238095222</v>
+      </c>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="n">
+        <v>67.06247969202515</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>69.1661029486787</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>-845173.5537190083</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>-0.2025157489413232</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>-1.207134145524265</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>-4.742148760330565</v>
+      </c>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="n">
+        <v>-2.207316094481868</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>2.771074380165317</v>
+      </c>
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="inlineStr"/>
+      <c r="AW31" t="n">
+        <v>-0.02892561983471098</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>-0.007506978432956446</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>-1058819.504501815</v>
+      </c>
+      <c r="AZ31" t="inlineStr"/>
+      <c r="BA31" t="inlineStr"/>
+      <c r="BB31" t="n">
+        <v>-1.583142652450299</v>
+      </c>
+      <c r="BC31" t="inlineStr"/>
+      <c r="BD31" t="n">
+        <v>-5.128099173553707</v>
+      </c>
+      <c r="BE31" t="inlineStr"/>
+      <c r="BF31" t="n">
+        <v>-0.4826446280991732</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45476.8125</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rivas v 
+  usa </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>167</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="U32" t="n">
+        <v>-0.03409090909090906</v>
+      </c>
+      <c r="V32" t="n">
+        <v>2.342857142857143</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.171428571428571</v>
+      </c>
+      <c r="X32" t="n">
+        <v>-3.057142857142856</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2.157142857142858</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>10.82857142857143</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-10.82857142857143</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.128571428571428</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0.5428571428571428</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.314285714285713</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>-3.357142857142858</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.1749999999999998</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>-0.04321428571428565</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.7553571428571429</v>
+      </c>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="n">
+        <v>67.67349537037038</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>66.79672727272728</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>-127698.8636363638</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>4.371246834958043</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>-1.924238325612947</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.592871900826438</v>
+      </c>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="n">
+        <v>-3.262026221908375</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>-3.444628099173542</v>
+      </c>
+      <c r="AU32" t="inlineStr"/>
+      <c r="AV32" t="inlineStr"/>
+      <c r="AW32" t="n">
+        <v>-0.1652892561983472</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>-0.05091927176907385</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>720263.3758637994</v>
+      </c>
+      <c r="AZ32" t="inlineStr"/>
+      <c r="BA32" t="inlineStr"/>
+      <c r="BB32" t="n">
+        <v>-0.2793131762157799</v>
+      </c>
+      <c r="BC32" t="inlineStr"/>
+      <c r="BD32" t="n">
+        <v>-0.9233471074380191</v>
+      </c>
+      <c r="BE32" t="inlineStr"/>
+      <c r="BF32" t="n">
+        <v>-2.533471074380163</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mendoza r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>167</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>2</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.9454545454545453</v>
+      </c>
+      <c r="U33" t="n">
+        <v>-0.9363636363636364</v>
+      </c>
+      <c r="V33" t="n">
+        <v>-0.07272727272727231</v>
+      </c>
+      <c r="W33" t="n">
+        <v>-1.018181818181819</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.245454545454544</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>-1.018181818181818</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>3.736363636363635</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-3.736363636363635</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.1636363636363636</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>-0.9727272727272727</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8272727272727263</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>-0.1090909090909076</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>-0.1222222222222227</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0.04380952380952396</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>-0.8678571428571428</v>
+      </c>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="n">
+        <v>68.42121212121212</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>67.41090909090909</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>2524454.966329966</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>3.150581479297898</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>-0.5191873444590556</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>4.191750841750846</v>
+      </c>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="n">
+        <v>3.962687617866646</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0.3779461279461316</v>
+      </c>
+      <c r="AU33" t="inlineStr"/>
+      <c r="AV33" t="inlineStr"/>
+      <c r="AW33" t="n">
+        <v>0.3357744107744109</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0.01058201058201047</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1007716.023632224</v>
+      </c>
+      <c r="AZ33" t="inlineStr"/>
+      <c r="BA33" t="inlineStr"/>
+      <c r="BB33" t="n">
+        <v>6.975074744983637</v>
+      </c>
+      <c r="BC33" t="inlineStr"/>
+      <c r="BD33" t="n">
+        <v>6.447643097643095</v>
+      </c>
+      <c r="BE33" t="inlineStr"/>
+      <c r="BF33" t="n">
+        <v>3.444528619528622</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>167</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2PIEeC7j</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P34" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>-3</v>
+      </c>
+      <c r="R34" t="n">
+        <v>-3</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>-0.9909090909090909</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V34" t="n">
+        <v>-1.245454545454546</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X34" t="n">
+        <v>-0.2727272727272734</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0.872727272727273</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-5.172727272727272</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>5.172727272727272</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.02727272727272734</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.727272727272727</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.481818181818182</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.109090909090908</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>-0.7000000000000002</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>-0.2023809523809523</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0.4923809523809526</v>
+      </c>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="n">
+        <v>69.21851851851852</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>67.29363636363635</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>-999634.4696969697</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>-0.01476620294698705</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.945103046049383</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>-1.748998316498302</v>
+      </c>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="n">
+        <v>1.628514955689884</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1.260168350168328</v>
+      </c>
+      <c r="AU34" t="inlineStr"/>
+      <c r="AV34" t="inlineStr"/>
+      <c r="AW34" t="n">
+        <v>-0.04361111111111104</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>-0.03425008599931223</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>-57843.01611249661</v>
+      </c>
+      <c r="AZ34" t="inlineStr"/>
+      <c r="BA34" t="inlineStr"/>
+      <c r="BB34" t="n">
+        <v>1.115068184278527</v>
+      </c>
+      <c r="BC34" t="inlineStr"/>
+      <c r="BD34" t="n">
+        <v>-1.565429292929295</v>
+      </c>
+      <c r="BE34" t="inlineStr"/>
+      <c r="BF34" t="n">
+        <v>0.08430134680134671</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dujic f 
+  can </t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>167</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.1888888888888889</v>
+      </c>
+      <c r="U35" t="n">
+        <v>-0.01111111111111107</v>
+      </c>
+      <c r="V35" t="n">
+        <v>-1.511111111111112</v>
+      </c>
+      <c r="W35" t="n">
+        <v>-0.7111111111111104</v>
+      </c>
+      <c r="X35" t="n">
+        <v>-5.277777777777779</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0.9222222222222207</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-0.9333333333333371</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.9333333333333371</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>-0.01111111111111118</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>-0.1444444444444444</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>-4.088888888888889</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>-0.2444444444444454</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>-1.111111111111111</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.1142857142857143</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>-0.0128571428571429</v>
+      </c>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="n">
+        <v>68.21818181818182</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>68.89282828282828</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>456224.7474747477</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>-0.5285266404599582</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>-4.325499526348239</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.3090909090909122</v>
+      </c>
+      <c r="AR35" t="inlineStr"/>
+      <c r="AS35" t="n">
+        <v>1.042752540063244</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>-5.334242424242433</v>
+      </c>
+      <c r="AU35" t="inlineStr"/>
+      <c r="AV35" t="inlineStr"/>
+      <c r="AW35" t="n">
+        <v>-0.193131313131313</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>-342761.7666215643</v>
+      </c>
+      <c r="AZ35" t="inlineStr"/>
+      <c r="BA35" t="inlineStr"/>
+      <c r="BB35" t="n">
+        <v>0.4757334153410255</v>
+      </c>
+      <c r="BC35" t="inlineStr"/>
+      <c r="BD35" t="n">
+        <v>0.8736363636363649</v>
+      </c>
+      <c r="BE35" t="inlineStr"/>
+      <c r="BF35" t="n">
+        <v>0.1486868686868732</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">simon n 
+  usa </t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>167</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Uw6sTk0t</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>8</v>
+      </c>
+      <c r="P36" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="U36" t="n">
+        <v>-1.055555555555555</v>
+      </c>
+      <c r="V36" t="n">
+        <v>-0.9444444444444438</v>
+      </c>
+      <c r="W36" t="n">
+        <v>-0.2777777777777777</v>
+      </c>
+      <c r="X36" t="n">
+        <v>-1.888888888888888</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2.527777777777777</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.472222222222221</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-2.472222222222221</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>-0.5277777777777777</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.1388888888888875</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.722222222222223</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>-0.1328571428571427</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>-0.1242857142857141</v>
+      </c>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="n">
+        <v>67.8490909090909</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>67.74413580246913</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>-385611.0209235211</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0.2829817118581559</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>-2.726662001878594</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0.5409812409812389</v>
+      </c>
+      <c r="AR36" t="inlineStr"/>
+      <c r="AS36" t="n">
+        <v>-2.49730817151768</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>-2.904527417027396</v>
+      </c>
+      <c r="AU36" t="inlineStr"/>
+      <c r="AV36" t="inlineStr"/>
+      <c r="AW36" t="n">
+        <v>0.1649350649350645</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>-0.05031667267836326</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>-35278.48073630664</v>
+      </c>
+      <c r="AZ36" t="inlineStr"/>
+      <c r="BA36" t="inlineStr"/>
+      <c r="BB36" t="n">
+        <v>-2.736947331668269</v>
+      </c>
+      <c r="BC36" t="inlineStr"/>
+      <c r="BD36" t="n">
+        <v>1.058387445887448</v>
+      </c>
+      <c r="BE36" t="inlineStr"/>
+      <c r="BF36" t="n">
+        <v>1.696825396825396</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fischer d 
+  can </t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">providence park
+  portland  or </t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>167</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>-6</v>
+      </c>
+      <c r="P37" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R37" t="n">
+        <v>-2</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U37" t="n">
+        <v>-0.3999999999999999</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="W37" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="X37" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.100000000000001</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>5.800000000000004</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-5.800000000000004</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>-1.200000000000001</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>-1.222222222222222</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.02928571428571414</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>-0.1405357142857142</v>
+      </c>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="n">
+        <v>68.38863636363638</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>68.33858585858586</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1633512.396694215</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>-0.3709081266008241</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>-0.5129170600227155</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>2.578512396694222</v>
+      </c>
+      <c r="AR37" t="inlineStr"/>
+      <c r="AS37" t="n">
+        <v>1.864115895552892</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AU37" t="inlineStr"/>
+      <c r="AV37" t="inlineStr"/>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>528805.5698740589</v>
+      </c>
+      <c r="AZ37" t="inlineStr"/>
+      <c r="BA37" t="inlineStr"/>
+      <c r="BB37" t="n">
+        <v>3.262887645618093</v>
+      </c>
+      <c r="BC37" t="inlineStr"/>
+      <c r="BD37" t="n">
+        <v>4.148760330578511</v>
+      </c>
+      <c r="BE37" t="inlineStr"/>
+      <c r="BF37" t="n">
+        <v>0.528925619834709</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45472.89583333334</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fischer d 
+  can </t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>167</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P38" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>-4</v>
+      </c>
+      <c r="R38" t="n">
+        <v>-4</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.733333333333333</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.1333333333333329</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.8666666666666654</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>-0.4666666666666668</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>5.049999999999997</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-5.049999999999997</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.6833333333333332</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>6.466666666666669</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>-5.183333333333335</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>-0.2666666666666666</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>-0.8600000000000001</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>-0.1371428571428572</v>
+      </c>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="n">
+        <v>67.83712121212122</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>68.34636363636363</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>-939718.5314685316</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0.8313934481261782</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>-1.247513923629612</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0.3798601398601278</v>
+      </c>
+      <c r="AR38" t="inlineStr"/>
+      <c r="AS38" t="n">
+        <v>-2.637223896805093</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0.2748251748251676</v>
+      </c>
+      <c r="AU38" t="inlineStr"/>
+      <c r="AV38" t="inlineStr"/>
+      <c r="AW38" t="n">
+        <v>-0.06601398601398611</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>-0.1984592120014115</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>-78831.4400202668</v>
+      </c>
+      <c r="AZ38" t="inlineStr"/>
+      <c r="BA38" t="inlineStr"/>
+      <c r="BB38" t="n">
+        <v>-1.32853569242635</v>
+      </c>
+      <c r="BC38" t="inlineStr"/>
+      <c r="BD38" t="n">
+        <v>-1.523916083916063</v>
+      </c>
+      <c r="BE38" t="inlineStr"/>
+      <c r="BF38" t="n">
+        <v>-0.9564335664335637</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45472.89583333334</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">geodis park
+  nashville  tn </t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>167</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>-0.4222222222222223</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.3444444444444444</v>
+      </c>
+      <c r="V39" t="n">
+        <v>-1.866666666666667</v>
+      </c>
+      <c r="W39" t="n">
+        <v>-1.488888888888889</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.6444444444444439</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>2.033333333333333</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-4.955555555555556</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>4.955555555555556</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>-0.9222222222222223</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>-0.8444444444444444</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.7333333333333343</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0.4027777777777777</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>-2.220446049250313e-16</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>-0.7300000000000001</v>
+      </c>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="n">
+        <v>66.01414141414142</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>68.65151515151514</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>-3437136.363636363</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>-7.178371587691814</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>-1.382176646172837</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>-6.450826446280985</v>
+      </c>
+      <c r="AR39" t="inlineStr"/>
+      <c r="AS39" t="n">
+        <v>3.403497352191842</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1.878264462809909</v>
+      </c>
+      <c r="AU39" t="inlineStr"/>
+      <c r="AV39" t="inlineStr"/>
+      <c r="AW39" t="n">
+        <v>-0.5883471074380162</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>-0.08533072823092613</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>-1306799.941338144</v>
+      </c>
+      <c r="AZ39" t="inlineStr"/>
+      <c r="BA39" t="inlineStr"/>
+      <c r="BB39" t="n">
+        <v>-2.013125014146013</v>
+      </c>
+      <c r="BC39" t="inlineStr"/>
+      <c r="BD39" t="n">
+        <v>-4.550743801652885</v>
+      </c>
+      <c r="BE39" t="inlineStr"/>
+      <c r="BF39" t="n">
+        <v>0.4316528925619778</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45472.89583333334</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">da silva a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>167</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>-0.8272727272727274</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0.6727272727272727</v>
+      </c>
+      <c r="V40" t="n">
+        <v>2.727272727272728</v>
+      </c>
+      <c r="W40" t="n">
+        <v>-0.09090909090909083</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3.263636363636364</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>3.954545454545455</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>9.218181818181819</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-9.218181818181819</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.5181818181818181</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0.8454545454545455</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>4.845454545454547</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>-1.381818181818181</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>-0.1333333333333329</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0.5157142857142857</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0.2271428571428572</v>
+      </c>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="n">
+        <v>67.87606060606061</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>68.43979797979799</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>226704.0863177234</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>-1.683748035191698</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>-1.476902283062117</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>-0.2830119375573901</v>
+      </c>
+      <c r="AR40" t="inlineStr"/>
+      <c r="AS40" t="n">
+        <v>-0.7060100041554698</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>-1.811776859504107</v>
+      </c>
+      <c r="AU40" t="inlineStr"/>
+      <c r="AV40" t="inlineStr"/>
+      <c r="AW40" t="n">
+        <v>0.1447658402203857</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>-0.001314081347794538</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>-465677.2871354646</v>
+      </c>
+      <c r="AZ40" t="inlineStr"/>
+      <c r="BA40" t="inlineStr"/>
+      <c r="BB40" t="n">
+        <v>-1.398217393170228</v>
+      </c>
+      <c r="BC40" t="inlineStr"/>
+      <c r="BD40" t="n">
+        <v>1.573599632690531</v>
+      </c>
+      <c r="BE40" t="inlineStr"/>
+      <c r="BF40" t="n">
+        <v>0.8485537190082653</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45472.89583333334</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freemon j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>167</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>1</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>-0.8333333333333335</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="V41" t="n">
+        <v>-0.8333333333333339</v>
+      </c>
+      <c r="W41" t="n">
+        <v>3.138888888888889</v>
+      </c>
+      <c r="X41" t="n">
+        <v>-2.638888888888889</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>-0.1666666666666679</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-5.277777777777779</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>5.277777777777779</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>-0.4722222222222223</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0.1111111111111112</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>-5.111111111111112</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>7.111111111111112</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>-0.116883116883117</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>-0.6539999999999999</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>1.084857142857143</v>
+      </c>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="n">
+        <v>68.1710101010101</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>68.47508417508418</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>-1126315.734265735</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>2.240337516053287</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>-1.1502059568287</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>-1.997692307692304</v>
+      </c>
+      <c r="AR41" t="inlineStr"/>
+      <c r="AS41" t="n">
+        <v>0.229312591209208</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>2.785524475524483</v>
+      </c>
+      <c r="AU41" t="inlineStr"/>
+      <c r="AV41" t="inlineStr"/>
+      <c r="AW41" t="n">
+        <v>0.06643356643356646</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0.02968835131306546</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>137945.741437187</v>
+      </c>
+      <c r="AZ41" t="inlineStr"/>
+      <c r="BA41" t="inlineStr"/>
+      <c r="BB41" t="n">
+        <v>1.527469947829339</v>
+      </c>
+      <c r="BC41" t="inlineStr"/>
+      <c r="BD41" t="n">
+        <v>-1.379720279720289</v>
+      </c>
+      <c r="BE41" t="inlineStr"/>
+      <c r="BF41" t="n">
+        <v>0.6800699300699264</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45472.85416666666</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>167</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>z9ZXDy6o</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P42" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="U42" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="V42" t="n">
+        <v>-0.8833333333333329</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.2000000000000002</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.316666666666666</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.933333333333337</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-2.850000000000001</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>-0.2833333333333332</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>-0.9500000000000002</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.533333333333333</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>-0.1111111111111107</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>-0.1214285714285717</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>-0.3028571428571427</v>
+      </c>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="n">
+        <v>68.91272727272727</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>67.04535353535354</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>1910964.637635092</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>1.267380318365937</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.193236760245611</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>4.146853146853147</v>
+      </c>
+      <c r="AR42" t="inlineStr"/>
+      <c r="AS42" t="n">
+        <v>2.546409868843135</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>-3.057088366179272</v>
+      </c>
+      <c r="AU42" t="inlineStr"/>
+      <c r="AV42" t="inlineStr"/>
+      <c r="AW42" t="n">
+        <v>-0.02695486331849928</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>-0.1087300351470391</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>529914.9512290233</v>
+      </c>
+      <c r="AZ42" t="inlineStr"/>
+      <c r="BA42" t="inlineStr"/>
+      <c r="BB42" t="n">
+        <v>2.73630811264605</v>
+      </c>
+      <c r="BC42" t="inlineStr"/>
+      <c r="BD42" t="n">
+        <v>2.64696439923712</v>
+      </c>
+      <c r="BE42" t="inlineStr"/>
+      <c r="BF42" t="n">
+        <v>-0.2933407501589294</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>45472.85416666666</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ford t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>167</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P43" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>4</v>
+      </c>
+      <c r="R43" t="n">
+        <v>4</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>-1.800000000000001</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-5.399999999999999</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>5.399999999999999</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>-0.7000000000000002</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>2.300000000000001</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0.1111111111111107</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>-0.2228571428571429</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>-0.02857142857142891</v>
+      </c>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="n">
+        <v>67.83626262626262</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>68.11545454545454</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>1516578.512396694</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0.8281159900318471</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>-1.831380276471407</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>3.996694214876044</v>
+      </c>
+      <c r="AR43" t="inlineStr"/>
+      <c r="AS43" t="n">
+        <v>-0.01647152816862274</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>-5.238016528925613</v>
+      </c>
+      <c r="AU43" t="inlineStr"/>
+      <c r="AV43" t="inlineStr"/>
+      <c r="AW43" t="n">
+        <v>0.01735537190082637</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>0.05438137292601986</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>826661.9968973692</v>
+      </c>
+      <c r="AZ43" t="inlineStr"/>
+      <c r="BA43" t="inlineStr"/>
+      <c r="BB43" t="n">
+        <v>1.948098543149719</v>
+      </c>
+      <c r="BC43" t="inlineStr"/>
+      <c r="BD43" t="n">
+        <v>1.652066115702482</v>
+      </c>
+      <c r="BE43" t="inlineStr"/>
+      <c r="BF43" t="n">
+        <v>-3.336363636363636</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>45472.85416666666</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>167</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>-8</v>
+      </c>
+      <c r="P44" t="n">
+        <v>-8</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>-0.2678571428571428</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0.2678571428571429</v>
+      </c>
+      <c r="V44" t="n">
+        <v>-0.7678571428571432</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.053571428571429</v>
+      </c>
+      <c r="X44" t="n">
+        <v>5.857142857142857</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>-3.732142857142858</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-7.303571428571431</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>7.303571428571431</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>-1.053571428571428</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>-0.4642857142857135</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>7.232142857142858</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0.1428571428571432</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>-0.4908333333333332</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0.5641666666666663</v>
+      </c>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="n">
+        <v>68.47357954545456</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>67.50227272727274</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>-18406.63580246922</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>1.001967557895199</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0.4697118745924911</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>-0.8788019079685654</v>
+      </c>
+      <c r="AR44" t="inlineStr"/>
+      <c r="AS44" t="n">
+        <v>1.20542111508917</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>0.5441077441076914</v>
+      </c>
+      <c r="AU44" t="inlineStr"/>
+      <c r="AV44" t="inlineStr"/>
+      <c r="AW44" t="n">
+        <v>0.09719416386083068</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>0.1086527488488274</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>-451048.4717197607</v>
+      </c>
+      <c r="AZ44" t="inlineStr"/>
+      <c r="BA44" t="inlineStr"/>
+      <c r="BB44" t="n">
+        <v>1.187502740009677</v>
+      </c>
+      <c r="BC44" t="inlineStr"/>
+      <c r="BD44" t="n">
+        <v>0.5061447811447692</v>
+      </c>
+      <c r="BE44" t="inlineStr"/>
+      <c r="BF44" t="n">
+        <v>1.212177328843996</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>45472.85416666666</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">da silva a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>167</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1671</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0.0636363636363636</v>
+      </c>
+      <c r="U45" t="n">
+        <v>-0.1000000000000001</v>
+      </c>
+      <c r="V45" t="n">
+        <v>-2.590909090909091</v>
+      </c>
+      <c r="W45" t="n">
+        <v>2.654545454545454</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.554545454545455</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-4.418181818181822</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>4.418181818181822</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>-0.05454545454545467</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0.6818181818181819</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>-6.154545454545453</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>4.081818181818182</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>-0.2269642857142857</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0.7108928571428572</v>
+      </c>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="n">
+        <v>68.36909090909091</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>67.4854453627181</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>-1702994.031221304</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0.6833117042514658</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>-0.6092034435808671</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>-1.67205387205388</v>
+      </c>
+      <c r="AR45" t="inlineStr"/>
+      <c r="AS45" t="n">
+        <v>-1.281334343927124</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>-4.368587389041977</v>
+      </c>
+      <c r="AU45" t="inlineStr"/>
+      <c r="AV45" t="inlineStr"/>
+      <c r="AW45" t="n">
+        <v>-0.050137741046832</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>0.02656271197414184</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>-254493.1610636225</v>
+      </c>
+      <c r="AZ45" t="inlineStr"/>
+      <c r="BA45" t="inlineStr"/>
+      <c r="BB45" t="n">
+        <v>-0.3815988276918176</v>
+      </c>
+      <c r="BC45" t="inlineStr"/>
+      <c r="BD45" t="n">
+        <v>-3.741727884909707</v>
+      </c>
+      <c r="BE45" t="inlineStr"/>
+      <c r="BF45" t="n">
+        <v>-2.070117845117842</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>jqf7smJ3</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>45471.85416666666</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">simon n 
+  usa </t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t xml:space="preserve">yankee stadium
   new york  ny </t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>vZraQYnO</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>rsHkUNCo</t>
         </is>
       </c>
-      <c r="G15" t="n">
+      <c r="G46" t="n">
         <v>167</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H46" t="n">
         <v>1671</v>
       </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
         <v>2024</v>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>EgT3xN3S</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>Uw6sTk0t</t>
         </is>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
         <v>2</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R46" t="n">
         <v>2</v>
       </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>-0.5750000000000002</v>
-      </c>
-      <c r="U15" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.5666666666666667</v>
-      </c>
-      <c r="W15" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0.6459722222222222</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>-0.6845833333333332</v>
-      </c>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="n">
-        <v>2.833333333333336</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>-2.833333333333336</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>5.577777777777779</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>-3.011111111111111</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0.5666666666666667</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>-0.6888888888888889</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>2.022222222222222</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>-0.6222222222222227</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>6.444444444444445</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>-0.4333333333333336</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>67.63181818181819</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>69.41414141414141</v>
-      </c>
-      <c r="AN15" t="inlineStr"/>
-      <c r="AO15" t="n">
-        <v>-1068421.824236517</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>-2.369161208091057</v>
-      </c>
-      <c r="AQ15" t="inlineStr"/>
-      <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="inlineStr"/>
-      <c r="AT15" t="n">
-        <v>1.070816450259372</v>
-      </c>
-      <c r="AU15" t="inlineStr"/>
-      <c r="AV15" t="n">
-        <v>1.666033138401588</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>-4.184304300313073</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>-4.064201927125762</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>-3.218082875539025</v>
-      </c>
-      <c r="AZ15" t="inlineStr"/>
-      <c r="BA15" t="n">
-        <v>0.2873670919723423</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>-0.1802207575682435</v>
-      </c>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="n">
-        <v>-0.2129186602870814</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>2.132758791146699</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>-1180159.584184752</v>
-      </c>
-      <c r="BG15" t="n">
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0.4666666666666668</v>
+      </c>
+      <c r="U46" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0.4333333333333331</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0.9222222222222225</v>
+      </c>
+      <c r="X46" t="n">
+        <v>2.300000000000001</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0.4777777777777779</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.177777777777777</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>-2.177777777777777</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0.4666666666666668</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0.04444444444444451</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.477777777777778</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0.3777777777777782</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0.6799999999999999</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>-0.3033333333333335</v>
+      </c>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="n">
+        <v>68.17946127946128</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>69.49181818181816</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>-1414782.407407407</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>2.087320066669164</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>1.158425591996718</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>-0.9163350678502127</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>-4390000</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>-3.853662739790018</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>2.976094276094273</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>-259</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>-294</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>-0.2314049586776861</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>-0.1537475799367158</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>-1274245.886599623</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>-0.4000000000000057</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>-4</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>-2.039403701492326</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>-1.199999999999999</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>-3.805925415773885</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>-3.567291602897662</v>
+      </c>
+      <c r="BG46" t="n">
         <v>0</v>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
@@ -525,94 +525,94 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions_against</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -625,97 +625,97 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_val_player_start</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_sub</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
@@ -795,34 +795,34 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2727272727272729</v>
+        <v>1.25</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6363636363636364</v>
+        <v>0.2083333333333335</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25</v>
+        <v>-4.458333333333334</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2083333333333335</v>
+        <v>-2.958333333333334</v>
       </c>
       <c r="X2" t="n">
-        <v>-4.458333333333334</v>
+        <v>-0.166666666666667</v>
       </c>
       <c r="Y2" t="n">
-        <v>-2.958333333333334</v>
+        <v>-0.3333333333333339</v>
       </c>
       <c r="Z2" t="n">
+        <v>2.318181818181818</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.106060606060606</v>
+      </c>
+      <c r="AB2" t="n">
         <v>-8.583333333333336</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AC2" t="n">
         <v>8.583333333333336</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.041666666666667</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-0.1666666666666666</v>
       </c>
       <c r="AD2" t="n">
         <v>2.916666666666666</v>
@@ -830,22 +830,22 @@
       <c r="AE2" t="n">
         <v>1.083333333333334</v>
       </c>
-      <c r="AF2" t="n">
-        <v>2.318181818181818</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.106060606060606</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="n">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
       <c r="AJ2" t="n">
-        <v>-0.166666666666667</v>
+        <v>0.2727272727272729</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.3333333333333339</v>
+        <v>-0.6363636363636364</v>
       </c>
       <c r="AL2" t="n">
-        <v>67.9912904040404</v>
+        <v>68.00505899908174</v>
       </c>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
@@ -950,34 +950,34 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5</v>
+        <v>-0.5555555555555554</v>
       </c>
       <c r="U3" t="n">
-        <v>0.75</v>
+        <v>-2.777777777777778</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5555555555555554</v>
+        <v>1.222222222222221</v>
       </c>
       <c r="W3" t="n">
-        <v>-2.777777777777778</v>
+        <v>1.777777777777779</v>
       </c>
       <c r="X3" t="n">
-        <v>1.222222222222221</v>
+        <v>-4.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.777777777777779</v>
+        <v>-4.5</v>
       </c>
       <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-0.416666666666667</v>
+      </c>
+      <c r="AB3" t="n">
         <v>7.444444444444443</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AC3" t="n">
         <v>-7.444444444444443</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-0.1111111111111112</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.7777777777777777</v>
       </c>
       <c r="AD3" t="n">
         <v>7.111111111111111</v>
@@ -986,71 +986,71 @@
         <v>-10</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>-0.07600000000000007</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.416666666666667</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.07600000000000007</v>
+        <v>-0.1111111111111112</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>0.7777777777777777</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-4.5</v>
+        <v>-0.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>-4.5</v>
+        <v>0.75</v>
       </c>
       <c r="AL3" t="n">
-        <v>67.6392265310447</v>
+        <v>67.64070247933884</v>
       </c>
       <c r="AM3" t="n">
-        <v>68.500727555273</v>
+        <v>68.46278696051422</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1536566.433566433</v>
+        <v>-1.363434619982101</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1.622413397687993</v>
+        <v>-0.01742424242424256</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.00221150067827125</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-2.561538461538461</v>
-      </c>
-      <c r="AR3" t="inlineStr"/>
+        <v>1.212121212121211</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="n">
+        <v>-2.162878787878753</v>
+      </c>
       <c r="AS3" t="n">
-        <v>0.5188406990924186</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>-2.273426573426576</v>
-      </c>
-      <c r="AU3" t="inlineStr"/>
+        <v>-1.992424242424249</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="n">
+        <v>0.4549345668739235</v>
+      </c>
       <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="n">
-        <v>-0.01608391608391613</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0.0332877064456012</v>
-      </c>
+        <v>-2.683333333333337</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="n">
-        <v>-486384.4483859645</v>
+        <v>-0.2907555807612994</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>0.06169891257992788</v>
-      </c>
-      <c r="BC3" t="inlineStr"/>
+        <v>-1576988.636363636</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0.03540030632135882</v>
+      </c>
       <c r="BD3" t="n">
-        <v>-1.831468531468516</v>
+        <v>-376704.8455398212</v>
       </c>
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="n">
-        <v>1.303496503496508</v>
+        <v>0.3426341394219037</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1131,34 +1131,34 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3809523809523809</v>
+        <v>0.08571428571428541</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3690476190476192</v>
+        <v>1.185714285714286</v>
       </c>
       <c r="V4" t="n">
-        <v>0.08571428571428541</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.185714285714286</v>
+        <v>4.085714285714285</v>
       </c>
       <c r="X4" t="n">
-        <v>1.4</v>
+        <v>-4.857142857142858</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.085714285714285</v>
+        <v>0.2857142857142856</v>
       </c>
       <c r="Z4" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0.5952380952380958</v>
+      </c>
+      <c r="AB4" t="n">
         <v>3.614285714285714</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AC4" t="n">
         <v>-3.614285714285714</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-0.1714285714285715</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-0.01428571428571423</v>
       </c>
       <c r="AD4" t="n">
         <v>-2.157142857142858</v>
@@ -1166,23 +1166,23 @@
       <c r="AE4" t="n">
         <v>0.7857142857142865</v>
       </c>
-      <c r="AF4" t="n">
-        <v>-3.25</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-0.5952380952380958</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="n">
+        <v>-0.1714285714285715</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-0.01428571428571423</v>
+      </c>
       <c r="AJ4" t="n">
-        <v>-4.857142857142858</v>
+        <v>-0.3809523809523809</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.2857142857142856</v>
+        <v>0.3690476190476192</v>
       </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>67.74787266605448</v>
+        <v>67.73209366391184</v>
       </c>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
@@ -1278,34 +1278,34 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.471153846153846</v>
+        <v>-1.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.009615384615385</v>
+        <v>1.55</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.5</v>
+        <v>-1.324999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>1.55</v>
+        <v>-0.875</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.324999999999999</v>
+        <v>11.125</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.875</v>
+        <v>10.25</v>
       </c>
       <c r="Z5" t="n">
+        <v>2.269230769230769</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.653846153846154</v>
+      </c>
+      <c r="AB5" t="n">
         <v>7.424999999999997</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AC5" t="n">
         <v>-7.424999999999997</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.675</v>
       </c>
       <c r="AD5" t="n">
         <v>0.625</v>
@@ -1313,55 +1313,55 @@
       <c r="AE5" t="n">
         <v>1.949999999999999</v>
       </c>
-      <c r="AF5" t="n">
-        <v>2.269230769230769</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.653846153846154</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.675</v>
+      </c>
       <c r="AJ5" t="n">
-        <v>11.125</v>
+        <v>-1.471153846153846</v>
       </c>
       <c r="AK5" t="n">
-        <v>10.25</v>
+        <v>1.009615384615385</v>
       </c>
       <c r="AL5" t="n">
-        <v>68.65129004693399</v>
+        <v>68.62944980104071</v>
       </c>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="n">
-        <v>5.48947342993273</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-10.16174159473275</v>
-      </c>
+      <c r="AN5" t="n">
+        <v>5.505753078505549</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="n">
-        <v>5.251870490093232</v>
-      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
+      <c r="AU5" t="n">
+        <v>5.17727146230688</v>
+      </c>
       <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="n">
-        <v>0.03751056635672034</v>
-      </c>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="n">
-        <v>1855655.305903589</v>
+        <v>-10.02325927664674</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="n">
-        <v>11.72562230722339</v>
-      </c>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="n">
+        <v>0.04063644688644685</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1895256.483356339</v>
+      </c>
       <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
+      <c r="BF5" t="n">
+        <v>11.67824769557043</v>
+      </c>
       <c r="BG5" t="n">
         <v>0</v>
       </c>
@@ -1445,34 +1445,30 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8181818181818181</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8181818181818181</v>
+        <v>-0.7777777777777777</v>
       </c>
       <c r="V6" t="n">
-        <v>1.333333333333333</v>
+        <v>-4.555555555555555</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7777777777777777</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-4.555555555555555</v>
-      </c>
-      <c r="Y6" t="n">
         <v>1.888888888888889</v>
       </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0.7272727272727275</v>
+      </c>
+      <c r="AB6" t="n">
         <v>7.111111111111107</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AC6" t="n">
         <v>-7.111111111111107</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-0.8888888888888888</v>
       </c>
       <c r="AD6" t="n">
         <v>0.3333333333333339</v>
@@ -1481,67 +1477,71 @@
         <v>2.777777777777779</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>0.2983333333333333</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.7272727272727275</v>
+        <v>-0.115</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.2983333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.115</v>
-      </c>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
+        <v>-0.8888888888888888</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.8181818181818181</v>
+      </c>
       <c r="AL6" t="n">
-        <v>67.50988674625039</v>
+        <v>67.50732949327991</v>
       </c>
       <c r="AM6" t="n">
-        <v>68.46830119375574</v>
+        <v>68.47006427915518</v>
       </c>
       <c r="AN6" t="n">
-        <v>2252948.519283747</v>
+        <v>0.2570805183247984</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.339291414471603</v>
+        <v>0.04361111111111104</v>
       </c>
       <c r="AP6" t="n">
-        <v>-1.354836013734257</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>4.372513774104675</v>
-      </c>
-      <c r="AR6" t="inlineStr"/>
+        <v>0.4481060606060545</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>-2.267070707070673</v>
+      </c>
       <c r="AS6" t="n">
-        <v>-0.551034184702246</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>-2.243930211202922</v>
-      </c>
-      <c r="AU6" t="inlineStr"/>
+        <v>4.908358585858593</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>-0.5849593880267605</v>
+      </c>
       <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="n">
-        <v>0.04361111111111104</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0.03425008599931223</v>
-      </c>
+        <v>4.301439393939376</v>
+      </c>
+      <c r="AX6" t="inlineStr"/>
       <c r="AY6" t="n">
-        <v>387447.5737984327</v>
+        <v>-1.348108597367258</v>
       </c>
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="n">
-        <v>0.8634858327909285</v>
-      </c>
-      <c r="BC6" t="inlineStr"/>
+        <v>2263816.287878788</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.03425008599931223</v>
+      </c>
       <c r="BD6" t="n">
-        <v>4.866209825528003</v>
+        <v>390219.1133604471</v>
       </c>
       <c r="BE6" t="inlineStr"/>
       <c r="BF6" t="n">
-        <v>0.346453168044075</v>
+        <v>0.8473187764808472</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1626,34 +1626,30 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1818181818181819</v>
+        <v>1.555555555555555</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.09090909090909094</v>
+        <v>0.1111111111111112</v>
       </c>
       <c r="V7" t="n">
-        <v>1.555555555555555</v>
+        <v>2.888888888888888</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1111111111111112</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.888888888888888</v>
-      </c>
-      <c r="Y7" t="n">
         <v>-2.111111111111111</v>
       </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0.09090909090909083</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>0.9090909090909092</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.7777777777777777</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.5555555555555556</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>1.888888888888889</v>
@@ -1662,67 +1658,71 @@
         <v>-1.666666666666666</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.09090909090909083</v>
+        <v>0.2430952380952383</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.9090909090909092</v>
+        <v>0.5545238095238095</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.2430952380952383</v>
+        <v>0.7777777777777777</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.5545238095238095</v>
-      </c>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.1818181818181819</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-0.09090909090909094</v>
+      </c>
       <c r="AL7" t="n">
-        <v>68.33831994451829</v>
+        <v>68.33009641873278</v>
       </c>
       <c r="AM7" t="n">
-        <v>67.06968181818181</v>
+        <v>67.12297258297258</v>
       </c>
       <c r="AN7" t="n">
-        <v>-434256.1983471075</v>
+        <v>3.231873771298325</v>
       </c>
       <c r="AO7" t="n">
-        <v>3.135695523314681</v>
+        <v>-0.1727272727272731</v>
       </c>
       <c r="AP7" t="n">
-        <v>-3.381583671824302</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.280991735537185</v>
-      </c>
-      <c r="AR7" t="inlineStr"/>
+        <v>-1.190909090909088</v>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="n">
+        <v>-5.218181818181819</v>
+      </c>
       <c r="AS7" t="n">
-        <v>-1.158590929208227</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>-5.322314049586794</v>
-      </c>
-      <c r="AU7" t="inlineStr"/>
+        <v>0.3272727272727138</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="n">
+        <v>-1.06575436995513</v>
+      </c>
       <c r="AV7" t="inlineStr"/>
       <c r="AW7" t="n">
-        <v>-0.1652892561983472</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>-0.05091927176907385</v>
-      </c>
+        <v>1.209090909090904</v>
+      </c>
+      <c r="AX7" t="inlineStr"/>
       <c r="AY7" t="n">
-        <v>534919.6599855747</v>
+        <v>-3.476263778137195</v>
       </c>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="n">
-        <v>1.965784933245999</v>
-      </c>
-      <c r="BC7" t="inlineStr"/>
+        <v>-438363.6363636362</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-0.04296772068511179</v>
+      </c>
       <c r="BD7" t="n">
-        <v>0.4380165289256155</v>
+        <v>559476.8433754367</v>
       </c>
       <c r="BE7" t="inlineStr"/>
       <c r="BF7" t="n">
-        <v>-1.198347107438018</v>
+        <v>2.118885165701016</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1807,34 +1807,30 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6363636363636362</v>
+        <v>1.444444444444444</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4545454545454546</v>
+        <v>-0.8888888888888893</v>
       </c>
       <c r="V8" t="n">
-        <v>1.444444444444444</v>
+        <v>-5.222222222222223</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.8888888888888893</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-5.222222222222223</v>
-      </c>
-      <c r="Y8" t="n">
         <v>2.222222222222221</v>
       </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
+        <v>-0.09090909090909083</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0.454545454545455</v>
+      </c>
+      <c r="AB8" t="n">
         <v>0.3333333333333357</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AC8" t="n">
         <v>-0.3333333333333357</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.222222222222222</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>-1.999999999999998</v>
@@ -1843,67 +1839,71 @@
         <v>0.1111111111111107</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.09090909090909083</v>
+        <v>0.5816666666666668</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.454545454545455</v>
+        <v>0.1833333333333336</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.5816666666666668</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.1833333333333336</v>
-      </c>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.6363636363636362</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.4545454545454546</v>
+      </c>
       <c r="AL8" t="n">
-        <v>67.71736361281816</v>
+        <v>67.69001794807581</v>
       </c>
       <c r="AM8" t="n">
-        <v>68.97771349862259</v>
+        <v>68.99102596210035</v>
       </c>
       <c r="AN8" t="n">
-        <v>-549320.7070707069</v>
+        <v>-0.590475897660923</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.6994137231204718</v>
+        <v>-0.193131313131313</v>
       </c>
       <c r="AP8" t="n">
-        <v>-2.001684463328388</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>-0.8736363636363649</v>
-      </c>
-      <c r="AR8" t="inlineStr"/>
+        <v>-1.403131313131315</v>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>-2.455151515151528</v>
+      </c>
       <c r="AS8" t="n">
-        <v>-1.936795721235587</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>-2.306969696969702</v>
-      </c>
-      <c r="AU8" t="inlineStr"/>
+        <v>-2.463636363636368</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="n">
+        <v>-1.808557437779914</v>
+      </c>
       <c r="AV8" t="inlineStr"/>
       <c r="AW8" t="n">
-        <v>-0.193131313131313</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.818181818181813</v>
+      </c>
+      <c r="AX8" t="inlineStr"/>
       <c r="AY8" t="n">
-        <v>-623264.3100354349</v>
+        <v>-1.946681012672769</v>
       </c>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="n">
-        <v>-4.386555549825509</v>
-      </c>
-      <c r="BC8" t="inlineStr"/>
+        <v>-547966.1616161615</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
       <c r="BD8" t="n">
-        <v>-2.528181818181821</v>
+        <v>-598435.7323329443</v>
       </c>
       <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="n">
-        <v>-1.414040404040403</v>
+        <v>-4.096189780329304</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -1912,7 +1912,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>QgE37zwQ</t>
+          <t>n3Fa8GNJ</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1920,24 +1920,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">simon n 
+          <t xml:space="preserve">badawi m 
   usa </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">paypal park
-  san jose  ca </t>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1964,19 +1964,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>UL7r7duf</t>
+          <t>zoZ995af</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Uw6sTk0t</t>
+          <t>WWvwigh8</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -1988,103 +1988,107 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4545454545454546</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5818181818181816</v>
+        <v>-2.3</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.708333333333333</v>
+        <v>1.6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.611111111111111</v>
+        <v>2.1</v>
       </c>
       <c r="X9" t="n">
-        <v>-6.930555555555555</v>
+        <v>-4.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.847222222222221</v>
+        <v>-4.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>-2.805555555555557</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.805555555555557</v>
+        <v>-0.333333333333333</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.1666666666666667</v>
+        <v>7.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.347222222222222</v>
+        <v>-7.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.5</v>
+        <v>6.900000000000002</v>
       </c>
       <c r="AE9" t="n">
-        <v>4.527777777777779</v>
+        <v>-9.499999999999998</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.409090909090909</v>
+        <v>-0.1950000000000003</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.07272727272727231</v>
+        <v>-0.1816666666666669</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.3116666666666664</v>
+        <v>-0.2</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.5913333333333335</v>
-      </c>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-0.7500000000000001</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.9999999999999998</v>
+      </c>
       <c r="AL9" t="n">
-        <v>68.84850252525253</v>
+        <v>67.70440771349863</v>
       </c>
       <c r="AM9" t="n">
-        <v>67.88551887926887</v>
+        <v>68.66629935720844</v>
       </c>
       <c r="AN9" t="n">
-        <v>37363.63636363624</v>
+        <v>-1.363434619982101</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.8896568730235543</v>
+        <v>-0.01742424242424256</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.4233019940056124</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0.3978956228956179</v>
-      </c>
-      <c r="AR9" t="inlineStr"/>
+        <v>1.212121212121211</v>
+      </c>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="n">
+        <v>-2.162878787878753</v>
+      </c>
       <c r="AS9" t="n">
-        <v>-0.6983513983685548</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>-1.197811447811461</v>
-      </c>
-      <c r="AU9" t="inlineStr"/>
+        <v>-1.992424242424249</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="n">
+        <v>0.4549345668739235</v>
+      </c>
       <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="n">
-        <v>-0.06363636363636371</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>-0.1435562721031829</v>
-      </c>
+        <v>-2.683333333333337</v>
+      </c>
+      <c r="AX9" t="inlineStr"/>
       <c r="AY9" t="n">
-        <v>98939.42903756956</v>
+        <v>-0.2907555807612994</v>
       </c>
       <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="n">
-        <v>0.09864734161929789</v>
-      </c>
-      <c r="BC9" t="inlineStr"/>
+        <v>-1576988.636363636</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.03540030632135882</v>
+      </c>
       <c r="BD9" t="n">
-        <v>1.215656565656573</v>
+        <v>-376704.8455398212</v>
       </c>
       <c r="BE9" t="inlineStr"/>
       <c r="BF9" t="n">
-        <v>1.405134680134676</v>
+        <v>0.3426341394219037</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2093,7 +2097,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>AoWGqXpJ</t>
+          <t>QgE37zwQ</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2101,24 +2105,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
+          <t xml:space="preserve">simon n 
+  usa </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">shell energy stadium
-  houston  tx </t>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>txUJt9AR</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2145,12 +2149,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>nJ01AhXP</t>
+          <t>UL7r7duf</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Onn3tCA5</t>
+          <t>Uw6sTk0t</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -2169,103 +2173,103 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.136363636363636</v>
+        <v>-0.708333333333333</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8409090909090908</v>
+        <v>1.611111111111111</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3666666666666671</v>
+        <v>-6.930555555555555</v>
       </c>
       <c r="W10" t="n">
-        <v>2.022222222222222</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3.68888888888889</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>3.1</v>
-      </c>
+        <v>2.847222222222221</v>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>2.200000000000003</v>
+        <v>1.409090909090909</v>
       </c>
       <c r="AA10" t="n">
-        <v>-2.200000000000003</v>
+        <v>-0.07272727272727231</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.6111111111111112</v>
+        <v>-2.805555555555557</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.9444444444444444</v>
+        <v>2.805555555555557</v>
       </c>
       <c r="AD10" t="n">
-        <v>-1.155555555555555</v>
+        <v>1.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.1333333333333346</v>
+        <v>4.527777777777779</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.4924242424242422</v>
+        <v>0.3116666666666664</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.6287878787878789</v>
+        <v>0.5913333333333335</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.5353333333333332</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.5243333333333332</v>
-      </c>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
+        <v>1.347222222222222</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-0.4545454545454546</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.5818181818181816</v>
+      </c>
       <c r="AL10" t="n">
-        <v>67.60686131285304</v>
+        <v>68.84850252525253</v>
       </c>
       <c r="AM10" t="n">
-        <v>68.15992676767677</v>
+        <v>67.8558878999788</v>
       </c>
       <c r="AN10" t="n">
-        <v>-2359507.996632996</v>
+        <v>0.8114687245121956</v>
       </c>
       <c r="AO10" t="n">
-        <v>-3.783869257923214</v>
+        <v>-0.07070707070707072</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.3191754570330261</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>-4.106902356902367</v>
-      </c>
-      <c r="AR10" t="inlineStr"/>
+        <v>1.469329660238749</v>
+      </c>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="n">
+        <v>-1.067768595041315</v>
+      </c>
       <c r="AS10" t="n">
-        <v>-0.2966417802819024</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>-0.01809764309763295</v>
-      </c>
-      <c r="AU10" t="inlineStr"/>
+        <v>1.336639118457299</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="n">
+        <v>-0.7560010038270875</v>
+      </c>
       <c r="AV10" t="inlineStr"/>
       <c r="AW10" t="n">
-        <v>-0.1827441077441079</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0.08251092707614438</v>
-      </c>
+        <v>0.4528007346189042</v>
+      </c>
+      <c r="AX10" t="inlineStr"/>
       <c r="AY10" t="n">
-        <v>-508649.5945214585</v>
+        <v>-0.5964348453478294</v>
       </c>
       <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="n">
-        <v>-2.822180211768739</v>
-      </c>
-      <c r="BC10" t="inlineStr"/>
+        <v>83675.84940312197</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-0.1419631093544138</v>
+      </c>
       <c r="BD10" t="n">
-        <v>-4.279461279461287</v>
+        <v>64995.70236526732</v>
       </c>
       <c r="BE10" t="inlineStr"/>
       <c r="BF10" t="n">
-        <v>-0.7604377104377136</v>
+        <v>0.006976598280942881</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2274,7 +2278,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>n3Fa8GNJ</t>
+          <t>AoWGqXpJ</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2282,24 +2286,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">badawi m 
-  usa </t>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">children s mercy park
-  kansas city  ks </t>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2326,19 +2330,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>zoZ995af</t>
+          <t>nJ01AhXP</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>WWvwigh8</t>
+          <t>Onn3tCA5</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="P11" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -2350,107 +2354,103 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7500000000000001</v>
+        <v>-0.3666666666666671</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9999999999999998</v>
+        <v>2.022222222222222</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2000000000000002</v>
+        <v>3.68888888888889</v>
       </c>
       <c r="W11" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.1</v>
-      </c>
+        <v>3.1</v>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>7.5</v>
+        <v>0.4924242424242422</v>
       </c>
       <c r="AA11" t="n">
-        <v>-7.5</v>
+        <v>0.6287878787878789</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.2</v>
+        <v>2.200000000000003</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.8</v>
+        <v>-2.200000000000003</v>
       </c>
       <c r="AD11" t="n">
-        <v>6.900000000000002</v>
+        <v>-1.155555555555555</v>
       </c>
       <c r="AE11" t="n">
-        <v>-9.499999999999998</v>
+        <v>-0.1333333333333346</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>-0.5353333333333332</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.333333333333333</v>
+        <v>0.5243333333333332</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0.1950000000000003</v>
+        <v>-0.6111111111111112</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.1816666666666669</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-4.5</v>
+        <v>-1.136363636363636</v>
       </c>
       <c r="AK11" t="n">
-        <v>-4.5</v>
+        <v>0.8409090909090908</v>
       </c>
       <c r="AL11" t="n">
-        <v>67.69853994490357</v>
+        <v>67.59447783621339</v>
       </c>
       <c r="AM11" t="n">
-        <v>68.6852157943067</v>
+        <v>68.16638131313132</v>
       </c>
       <c r="AN11" t="n">
-        <v>-1536566.433566433</v>
+        <v>-3.845291453350342</v>
       </c>
       <c r="AO11" t="n">
-        <v>-1.622413397687993</v>
+        <v>-0.1662993572084481</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.00221150067827125</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>-2.561538461538461</v>
-      </c>
-      <c r="AR11" t="inlineStr"/>
+        <v>-0.5981634527089028</v>
+      </c>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="n">
+        <v>0.1372819100091931</v>
+      </c>
       <c r="AS11" t="n">
-        <v>0.5188406990924186</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>-2.273426573426576</v>
-      </c>
-      <c r="AU11" t="inlineStr"/>
+        <v>-4.114784205693297</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="n">
+        <v>-0.3708347166239392</v>
+      </c>
       <c r="AV11" t="inlineStr"/>
       <c r="AW11" t="n">
-        <v>-0.01608391608391613</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0.0332877064456012</v>
-      </c>
+        <v>-4.033976124885214</v>
+      </c>
+      <c r="AX11" t="inlineStr"/>
       <c r="AY11" t="n">
-        <v>-486384.4483859645</v>
+        <v>0.3328431195968449</v>
       </c>
       <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="n">
-        <v>0.06169891257992788</v>
-      </c>
-      <c r="BC11" t="inlineStr"/>
+        <v>-2301735.996326905</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.06403789447267694</v>
+      </c>
       <c r="BD11" t="n">
-        <v>-1.831468531468516</v>
+        <v>-619286.373873862</v>
       </c>
       <c r="BE11" t="inlineStr"/>
       <c r="BF11" t="n">
-        <v>1.303496503496508</v>
+        <v>-3.091729062189287</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2531,34 +2531,30 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2777777777777777</v>
+        <v>-1.48051948051948</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.388888888888889</v>
+        <v>-1.727272727272728</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.48051948051948</v>
+        <v>-1.220779220779221</v>
       </c>
       <c r="W12" t="n">
-        <v>-1.727272727272728</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-1.220779220779221</v>
-      </c>
-      <c r="Y12" t="n">
         <v>0.3116883116883127</v>
       </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
+        <v>2.416666666666667</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.2020202020202015</v>
+      </c>
+      <c r="AB12" t="n">
         <v>-2.155844155844157</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AC12" t="n">
         <v>2.155844155844157</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0.2987012987012987</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>-0.3506493506493507</v>
       </c>
       <c r="AD12" t="n">
         <v>1.025974025974026</v>
@@ -2567,67 +2563,71 @@
         <v>-3.571428571428573</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.416666666666667</v>
+        <v>-0.01033333333333342</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.2020202020202015</v>
+        <v>-0.921</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.01033333333333342</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.921</v>
-      </c>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
+        <v>-0.3506493506493507</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.2777777777777777</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-0.388888888888889</v>
+      </c>
       <c r="AL12" t="n">
-        <v>67.63545454545455</v>
+        <v>67.62969696969697</v>
       </c>
       <c r="AM12" t="n">
-        <v>68.39667832167832</v>
+        <v>68.43870550745551</v>
       </c>
       <c r="AN12" t="n">
-        <v>-1091323.70330287</v>
+        <v>-2.281167188168482</v>
       </c>
       <c r="AO12" t="n">
-        <v>-2.14876069257852</v>
+        <v>0.1339257964257963</v>
       </c>
       <c r="AP12" t="n">
-        <v>-3.127233136338987</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0.7550104216770848</v>
-      </c>
-      <c r="AR12" t="inlineStr"/>
+        <v>0.4100233100233091</v>
+      </c>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="n">
+        <v>-2.204409479409463</v>
+      </c>
       <c r="AS12" t="n">
-        <v>-1.687577720103402</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>-2.112271524771472</v>
-      </c>
-      <c r="AU12" t="inlineStr"/>
+        <v>-0.07080419580418607</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="n">
+        <v>-1.76631100321957</v>
+      </c>
       <c r="AV12" t="inlineStr"/>
       <c r="AW12" t="n">
-        <v>0.1313772647105975</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>-0.01541314942400773</v>
-      </c>
+        <v>0.6412975912975867</v>
+      </c>
+      <c r="AX12" t="inlineStr"/>
       <c r="AY12" t="n">
-        <v>-67714.16612046305</v>
+        <v>-3.361115639120726</v>
       </c>
       <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="n">
-        <v>-3.062332932384102</v>
-      </c>
-      <c r="BC12" t="inlineStr"/>
+        <v>-1053876.748251748</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-0.03801679813508474</v>
+      </c>
       <c r="BD12" t="n">
-        <v>-0.1500300625300639</v>
+        <v>-84938.19139974844</v>
       </c>
       <c r="BE12" t="inlineStr"/>
       <c r="BF12" t="n">
-        <v>0.316466249799582</v>
+        <v>-3.104818836676259</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2712,34 +2712,34 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3787878787878787</v>
+        <v>2.9</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4166666666666667</v>
+        <v>0.7999999999999998</v>
       </c>
       <c r="V13" t="n">
-        <v>2.9</v>
+        <v>-0.2000000000000011</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7999999999999998</v>
+        <v>1.4</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2000000000000011</v>
+        <v>-11</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.4</v>
+        <v>-12</v>
       </c>
       <c r="Z13" t="n">
+        <v>-1.416666666666667</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.1590909090909092</v>
+      </c>
+      <c r="AB13" t="n">
         <v>3.800000000000004</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AC13" t="n">
         <v>-3.700000000000003</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0.5</v>
       </c>
       <c r="AD13" t="n">
         <v>3</v>
@@ -2748,71 +2748,71 @@
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-1.416666666666667</v>
+        <v>0.7366666666666668</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.1590909090909092</v>
+        <v>0.2149999999999999</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.7366666666666668</v>
+        <v>1.1</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.2149999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-11</v>
+        <v>0.3787878787878787</v>
       </c>
       <c r="AK13" t="n">
-        <v>-12</v>
+        <v>-0.4166666666666667</v>
       </c>
       <c r="AL13" t="n">
-        <v>67.81664141414142</v>
+        <v>67.8239554637282</v>
       </c>
       <c r="AM13" t="n">
-        <v>68.88799287642263</v>
+        <v>68.86873278236914</v>
       </c>
       <c r="AN13" t="n">
-        <v>-2093418.609168609</v>
+        <v>-0.1188177598196489</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.2279199760392885</v>
+        <v>-0.1674242424242427</v>
       </c>
       <c r="AP13" t="n">
-        <v>-1.086574051936083</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0.4768842268842093</v>
-      </c>
-      <c r="AR13" t="inlineStr"/>
+        <v>-1.593302341597802</v>
+      </c>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="n">
+        <v>-0.5241276400367667</v>
+      </c>
       <c r="AS13" t="n">
-        <v>-1.008724228992417</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>-0.490332815332863</v>
-      </c>
-      <c r="AU13" t="inlineStr"/>
+        <v>-1.119519054178127</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="n">
+        <v>-1.064427412763742</v>
+      </c>
       <c r="AV13" t="inlineStr"/>
       <c r="AW13" t="n">
-        <v>-0.1755244755244758</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>-0.03751056635672034</v>
-      </c>
+        <v>0.664738292011009</v>
+      </c>
+      <c r="AX13" t="inlineStr"/>
       <c r="AY13" t="n">
-        <v>-608923.2072607961</v>
+        <v>-1.295758861965197</v>
       </c>
       <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="n">
-        <v>-1.929757058509928</v>
-      </c>
-      <c r="BC13" t="inlineStr"/>
+        <v>-1914382.489669421</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-0.04063644688644685</v>
+      </c>
       <c r="BD13" t="n">
-        <v>-1.186182336182327</v>
+        <v>-617471.1992754317</v>
       </c>
       <c r="BE13" t="inlineStr"/>
       <c r="BF13" t="n">
-        <v>-1.500116550116552</v>
+        <v>-1.949068493765367</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -2889,34 +2889,30 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5</v>
+        <v>-1.166666666666667</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3999999999999999</v>
+        <v>-1.5</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.166666666666667</v>
+        <v>1.180555555555555</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.180555555555555</v>
-      </c>
-      <c r="Y14" t="n">
         <v>0.7361111111111107</v>
       </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.3999999999999995</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.194444444444443</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AC14" t="n">
         <v>-1.194444444444443</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>-0.875</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0.2916666666666667</v>
       </c>
       <c r="AD14" t="n">
         <v>-3.291666666666666</v>
@@ -2925,67 +2921,71 @@
         <v>1.319444444444445</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>-0.07866666666666688</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.3999999999999995</v>
+        <v>0.6826666666666665</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.07866666666666688</v>
+        <v>-0.875</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.6826666666666665</v>
-      </c>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.3999999999999999</v>
+      </c>
       <c r="AL14" t="n">
-        <v>67.96524475524475</v>
+        <v>67.94431818181818</v>
       </c>
       <c r="AM14" t="n">
-        <v>68.45333333333333</v>
+        <v>68.44669696969697</v>
       </c>
       <c r="AN14" t="n">
-        <v>551759.6801346801</v>
+        <v>-4.853437958707502</v>
       </c>
       <c r="AO14" t="n">
-        <v>-4.675784019939016</v>
+        <v>0.1163636363636364</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.4778867800847308</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>-3.238540965207619</v>
-      </c>
-      <c r="AR14" t="inlineStr"/>
+        <v>4.805656565656566</v>
+      </c>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="n">
+        <v>-2.723390151515105</v>
+      </c>
       <c r="AS14" t="n">
-        <v>6.443748292153693</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>-2.903367003366952</v>
-      </c>
-      <c r="AU14" t="inlineStr"/>
+        <v>1.493282828282801</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="n">
+        <v>6.574861232024876</v>
+      </c>
       <c r="AV14" t="inlineStr"/>
       <c r="AW14" t="n">
-        <v>0.1163636363636364</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0.2614352697600781</v>
-      </c>
+        <v>-3.082676767676759</v>
+      </c>
+      <c r="AX14" t="inlineStr"/>
       <c r="AY14" t="n">
-        <v>-276944.8221992149</v>
+        <v>0.4139091385461882</v>
       </c>
       <c r="AZ14" t="inlineStr"/>
       <c r="BA14" t="inlineStr"/>
       <c r="BB14" t="n">
-        <v>2.170030776439269</v>
-      </c>
-      <c r="BC14" t="inlineStr"/>
+        <v>565107.481060606</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0.2614352697600781</v>
+      </c>
       <c r="BD14" t="n">
-        <v>1.403776655443295</v>
+        <v>-294793.7177029126</v>
       </c>
       <c r="BE14" t="inlineStr"/>
       <c r="BF14" t="n">
-        <v>4.834977553310885</v>
+        <v>2.226744678143078</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3070,34 +3070,30 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.072727272727273</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9181818181818181</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.222222222222221</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6666666666666665</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-1.222222222222221</v>
-      </c>
-      <c r="Y15" t="n">
         <v>1</v>
       </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="n">
+        <v>1.318181818181818</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.1272727272727279</v>
+      </c>
+      <c r="AB15" t="n">
         <v>9.111111111111107</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AC15" t="n">
         <v>-9.111111111111107</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>-0.6666666666666667</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0.6666666666666667</v>
       </c>
       <c r="AD15" t="n">
         <v>2.444444444444443</v>
@@ -3106,67 +3102,71 @@
         <v>2</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.318181818181818</v>
+        <v>0.4366666666666665</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.1272727272727279</v>
+        <v>-0.0283333333333331</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.4366666666666665</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.0283333333333331</v>
-      </c>
-      <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-1.072727272727273</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.9181818181818181</v>
+      </c>
       <c r="AL15" t="n">
-        <v>67.45277986476334</v>
+        <v>67.44228650137741</v>
       </c>
       <c r="AM15" t="n">
-        <v>67.00370064279154</v>
+        <v>67.00317171717172</v>
       </c>
       <c r="AN15" t="n">
-        <v>153365.9320477499</v>
+        <v>-0.887199189567923</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.943038107043435</v>
+        <v>-0.04545454545454541</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.531882193914754</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>-1.328772574227116</v>
-      </c>
-      <c r="AR15" t="inlineStr"/>
+        <v>2.636161616161612</v>
+      </c>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="n">
+        <v>4.502268135904529</v>
+      </c>
       <c r="AS15" t="n">
-        <v>1.316740991453045</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>4.325612182430376</v>
-      </c>
-      <c r="AU15" t="inlineStr"/>
+        <v>1.386400367309449</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="n">
+        <v>1.380612033375204</v>
+      </c>
       <c r="AV15" t="inlineStr"/>
       <c r="AW15" t="n">
-        <v>-0.04242424242424248</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0.002080970852166741</v>
-      </c>
+        <v>-1.448337924701548</v>
+      </c>
+      <c r="AX15" t="inlineStr"/>
       <c r="AY15" t="n">
-        <v>-121660.5220761718</v>
+        <v>0.1696635767082171</v>
       </c>
       <c r="AZ15" t="inlineStr"/>
       <c r="BA15" t="inlineStr"/>
       <c r="BB15" t="n">
-        <v>1.534592221969525</v>
-      </c>
-      <c r="BC15" t="inlineStr"/>
+        <v>163468.3195592281</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0.0103406929079386</v>
+      </c>
       <c r="BD15" t="n">
-        <v>1.564041934496473</v>
+        <v>-93158.67023843573</v>
       </c>
       <c r="BE15" t="inlineStr"/>
       <c r="BF15" t="n">
-        <v>2.707307927762471</v>
+        <v>1.713197771459839</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3251,34 +3251,30 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6363636363636364</v>
+        <v>-0.666666666666667</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7272727272727273</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.666666666666667</v>
+        <v>-4.666666666666668</v>
       </c>
       <c r="W16" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-4.666666666666668</v>
-      </c>
-      <c r="Y16" t="n">
         <v>-0.7777777777777768</v>
       </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.3636363636363633</v>
+      </c>
+      <c r="AB16" t="n">
         <v>0.1111111111111143</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AC16" t="n">
         <v>-0.1111111111111143</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0.2222222222222221</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>-0.7777777777777779</v>
       </c>
       <c r="AD16" t="n">
         <v>-1.555555555555555</v>
@@ -3287,67 +3283,71 @@
         <v>2.333333333333332</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.3636363636363633</v>
+        <v>-0.1633333333333333</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0.8149999999999999</v>
+        <v>0.2222222222222221</v>
       </c>
       <c r="AI16" t="n">
-        <v>-0.1633333333333333</v>
-      </c>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
+        <v>-0.7777777777777779</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-0.7272727272727273</v>
+      </c>
       <c r="AL16" t="n">
-        <v>68.61944629954272</v>
+        <v>68.60259412304866</v>
       </c>
       <c r="AM16" t="n">
-        <v>68.12141247182569</v>
+        <v>68.10083562901745</v>
       </c>
       <c r="AN16" t="n">
-        <v>1657181.818181818</v>
+        <v>-1.505614236125055</v>
       </c>
       <c r="AO16" t="n">
-        <v>-1.576787069764805</v>
+        <v>0.1627272727272728</v>
       </c>
       <c r="AP16" t="n">
-        <v>-2.642094317790907</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>2.301652892561989</v>
-      </c>
-      <c r="AR16" t="inlineStr"/>
+        <v>0.4154545454545513</v>
+      </c>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="n">
+        <v>-5.018181818181858</v>
+      </c>
       <c r="AS16" t="n">
-        <v>2.205796840992452</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>-4.852892561983509</v>
-      </c>
-      <c r="AU16" t="inlineStr"/>
+        <v>3.582727272727269</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="n">
+        <v>2.004247673551077</v>
+      </c>
       <c r="AV16" t="inlineStr"/>
       <c r="AW16" t="n">
-        <v>0.1396694214876033</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0.139366931345541</v>
-      </c>
+        <v>2.210000000000008</v>
+      </c>
+      <c r="AX16" t="inlineStr"/>
       <c r="AY16" t="n">
-        <v>1746889.47463863</v>
+        <v>-2.511905990466374</v>
       </c>
       <c r="AZ16" t="inlineStr"/>
       <c r="BA16" t="inlineStr"/>
       <c r="BB16" t="n">
-        <v>2.766895788328384</v>
-      </c>
-      <c r="BC16" t="inlineStr"/>
+        <v>1710104.545454545</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0.110446481622952</v>
+      </c>
       <c r="BD16" t="n">
-        <v>3.585950413223131</v>
+        <v>1679511.195211737</v>
       </c>
       <c r="BE16" t="inlineStr"/>
       <c r="BF16" t="n">
-        <v>0.341322314049588</v>
+        <v>2.472997131867118</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3432,34 +3432,30 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1000000000000001</v>
+        <v>-0.625</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="W17" t="n">
         <v>-0.625</v>
       </c>
-      <c r="X17" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>-0.625</v>
-      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.28888888888889</v>
+      </c>
+      <c r="AB17" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AC17" t="n">
         <v>0.25</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0.375</v>
       </c>
       <c r="AD17" t="n">
         <v>5.625</v>
@@ -3468,67 +3464,71 @@
         <v>-5.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>0.3856666666666666</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.28888888888889</v>
+        <v>-0.6803333333333331</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.3856666666666666</v>
+        <v>0.625</v>
       </c>
       <c r="AI17" t="n">
-        <v>-0.6803333333333331</v>
-      </c>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
+        <v>0.375</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.1000000000000001</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.1000000000000001</v>
+      </c>
       <c r="AL17" t="n">
-        <v>68.0824962915872</v>
+        <v>68.07713636363636</v>
       </c>
       <c r="AM17" t="n">
-        <v>68.30929292929292</v>
+        <v>68.30540404040406</v>
       </c>
       <c r="AN17" t="n">
-        <v>-2878086.363636363</v>
+        <v>-6.337209836357331</v>
       </c>
       <c r="AO17" t="n">
-        <v>-6.634738852721597</v>
+        <v>-0.7595959595959596</v>
       </c>
       <c r="AP17" t="n">
-        <v>-2.885435493037761</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>-4.096363636363634</v>
-      </c>
-      <c r="AR17" t="inlineStr"/>
+        <v>-2.617171717171715</v>
+      </c>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="n">
+        <v>-2.393939393939405</v>
+      </c>
       <c r="AS17" t="n">
-        <v>0.4209283370792356</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>-2.49454545454546</v>
-      </c>
-      <c r="AU17" t="inlineStr"/>
+        <v>-5.02222222222224</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="n">
+        <v>0.5880685226806328</v>
+      </c>
       <c r="AV17" t="inlineStr"/>
       <c r="AW17" t="n">
-        <v>-0.7536363636363634</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>-0.13625</v>
-      </c>
+        <v>-3.984848484848484</v>
+      </c>
+      <c r="AX17" t="inlineStr"/>
       <c r="AY17" t="n">
-        <v>-1147255.943062337</v>
+        <v>-2.710669066338312</v>
       </c>
       <c r="AZ17" t="inlineStr"/>
       <c r="BA17" t="inlineStr"/>
       <c r="BB17" t="n">
-        <v>-5.543661777622773</v>
-      </c>
-      <c r="BC17" t="inlineStr"/>
+        <v>-2822318.181818182</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>-0.08888888888888902</v>
+      </c>
       <c r="BD17" t="n">
-        <v>-4.840000000000003</v>
+        <v>-997622.3441433371</v>
       </c>
       <c r="BE17" t="inlineStr"/>
       <c r="BF17" t="n">
-        <v>-2.365454545454547</v>
+        <v>-5.208235308469732</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3613,34 +3613,30 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.252525252525253</v>
+        <v>0.9206349206349209</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.111111111111111</v>
+        <v>-0.5396825396825395</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9206349206349209</v>
+        <v>-3.746031746031746</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.5396825396825395</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-3.746031746031746</v>
-      </c>
-      <c r="Y18" t="n">
         <v>4.412698412698413</v>
       </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0.2727272727272725</v>
+      </c>
+      <c r="AB18" t="n">
         <v>8.428571428571431</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AC18" t="n">
         <v>-8.428571428571431</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0.8730158730158728</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>-1.190476190476191</v>
       </c>
       <c r="AD18" t="n">
         <v>0.2698412698412689</v>
@@ -3649,67 +3645,71 @@
         <v>-2.746031746031747</v>
       </c>
       <c r="AF18" t="n">
-        <v>-1.5</v>
+        <v>-0.05916666666666659</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.2727272727272725</v>
+        <v>-0.1758333333333333</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.05916666666666659</v>
+        <v>0.8730158730158728</v>
       </c>
       <c r="AI18" t="n">
-        <v>-0.1758333333333333</v>
-      </c>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
+        <v>-1.190476190476191</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.252525252525253</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>-1.111111111111111</v>
+      </c>
       <c r="AL18" t="n">
-        <v>67.85302435125668</v>
+        <v>67.84537037037038</v>
       </c>
       <c r="AM18" t="n">
-        <v>67.31837751321223</v>
+        <v>67.30697773186411</v>
       </c>
       <c r="AN18" t="n">
-        <v>1018565.599173554</v>
+        <v>1.297167643563895</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.655135225420182</v>
+        <v>-0.2136363636363636</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.327370572735049</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>4.764772727272714</v>
-      </c>
-      <c r="AR18" t="inlineStr"/>
+        <v>-0.4876623376623392</v>
+      </c>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="n">
+        <v>-2.273636363636371</v>
+      </c>
       <c r="AS18" t="n">
-        <v>1.132567252943055</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>-2.007438016528909</v>
-      </c>
-      <c r="AU18" t="inlineStr"/>
+        <v>4.370129870129887</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="n">
+        <v>0.7984061252265917</v>
+      </c>
       <c r="AV18" t="inlineStr"/>
       <c r="AW18" t="n">
-        <v>-0.2024793388429751</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>-0.1462406015037594</v>
-      </c>
+        <v>4.943636363636372</v>
+      </c>
+      <c r="AX18" t="inlineStr"/>
       <c r="AY18" t="n">
-        <v>337955.4402194789</v>
+        <v>2.697847834786131</v>
       </c>
       <c r="AZ18" t="inlineStr"/>
       <c r="BA18" t="inlineStr"/>
       <c r="BB18" t="n">
-        <v>2.047288761822607</v>
-      </c>
-      <c r="BC18" t="inlineStr"/>
+        <v>1219644.155844156</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>-0.1608646616541354</v>
+      </c>
       <c r="BD18" t="n">
-        <v>3.779132231404958</v>
+        <v>-120838.5541554533</v>
       </c>
       <c r="BE18" t="inlineStr"/>
       <c r="BF18" t="n">
-        <v>-0.9260330578512388</v>
+        <v>1.311764389966527</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -3794,34 +3794,30 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.08181818181818179</v>
+        <v>-0.05555555555555536</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1636363636363636</v>
+        <v>1.847222222222222</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.05555555555555536</v>
+        <v>1.138888888888889</v>
       </c>
       <c r="W19" t="n">
-        <v>1.847222222222222</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.138888888888889</v>
-      </c>
-      <c r="Y19" t="n">
         <v>-1.486111111111111</v>
       </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.09090909090909083</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.458333333333336</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AC19" t="n">
         <v>-1.458333333333336</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0.5833333333333335</v>
       </c>
       <c r="AD19" t="n">
         <v>-1.222222222222221</v>
@@ -3830,67 +3826,71 @@
         <v>2.375</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.5</v>
+        <v>0.1633333333333333</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.09090909090909083</v>
+        <v>0.125</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.1633333333333333</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
+        <v>0.5833333333333335</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>-0.08181818181818179</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>-0.1636363636363636</v>
+      </c>
       <c r="AL19" t="n">
-        <v>68.17680848892969</v>
+        <v>68.14507680106854</v>
       </c>
       <c r="AM19" t="n">
-        <v>67.98885123966943</v>
+        <v>67.98463636363637</v>
       </c>
       <c r="AN19" t="n">
-        <v>-1402322.314049587</v>
+        <v>2.23530963809759</v>
       </c>
       <c r="AO19" t="n">
-        <v>2.253964624701069</v>
+        <v>0.01818181818181808</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.859329138662929</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>-0.4736363636363734</v>
-      </c>
-      <c r="AR19" t="inlineStr"/>
+        <v>-2.276767676767673</v>
+      </c>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="n">
+        <v>2.143434343434336</v>
+      </c>
       <c r="AS19" t="n">
-        <v>-1.75823832398099</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>2.090082644628097</v>
-      </c>
-      <c r="AU19" t="inlineStr"/>
+        <v>-3.484848484848484</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="n">
+        <v>-1.531571267320697</v>
+      </c>
       <c r="AV19" t="inlineStr"/>
       <c r="AW19" t="n">
-        <v>0.01652892561983466</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0.09740570434350326</v>
-      </c>
+        <v>-0.3575757575757592</v>
+      </c>
+      <c r="AX19" t="inlineStr"/>
       <c r="AY19" t="n">
-        <v>283834.8223009913</v>
+        <v>3.07720617511427</v>
       </c>
       <c r="AZ19" t="inlineStr"/>
       <c r="BA19" t="inlineStr"/>
       <c r="BB19" t="n">
-        <v>-0.08151588622411055</v>
-      </c>
-      <c r="BC19" t="inlineStr"/>
+        <v>-1412904.04040404</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0.1029796081111871</v>
+      </c>
       <c r="BD19" t="n">
-        <v>-3.343966942148768</v>
+        <v>293730.5551152804</v>
       </c>
       <c r="BE19" t="inlineStr"/>
       <c r="BF19" t="n">
-        <v>-2.035454545454549</v>
+        <v>0.1212444052966362</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -3975,34 +3975,30 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7363636363636363</v>
+        <v>-0.7000000000000002</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5181818181818181</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.7000000000000002</v>
+        <v>-1.533333333333333</v>
       </c>
       <c r="W20" t="n">
-        <v>1.133333333333333</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-1.533333333333333</v>
-      </c>
-      <c r="Y20" t="n">
         <v>0.8777777777777782</v>
       </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.4545454545454541</v>
+      </c>
+      <c r="AB20" t="n">
         <v>0.08888888888888857</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AC20" t="n">
         <v>-0.08888888888888857</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>-0.6111111111111112</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0.6111111111111112</v>
       </c>
       <c r="AD20" t="n">
         <v>-1.71111111111111</v>
@@ -4011,67 +4007,71 @@
         <v>2.533333333333333</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0.5</v>
+        <v>-0.1486666666666665</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.4545454545454541</v>
+        <v>0.6426666666666666</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.1486666666666665</v>
+        <v>-0.6111111111111112</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.6426666666666666</v>
-      </c>
-      <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="inlineStr"/>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>-0.7363636363636363</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.5181818181818181</v>
+      </c>
       <c r="AL20" t="n">
-        <v>67.06156565656565</v>
+        <v>67.06790633608816</v>
       </c>
       <c r="AM20" t="n">
-        <v>67.90606060606061</v>
+        <v>67.91323232323232</v>
       </c>
       <c r="AN20" t="n">
-        <v>-744729.5875420873</v>
+        <v>-1.99529713777639</v>
       </c>
       <c r="AO20" t="n">
-        <v>-1.943638723033075</v>
+        <v>-0.2896303948576677</v>
       </c>
       <c r="AP20" t="n">
-        <v>-0.8577192442633645</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>-0.6721296296296515</v>
-      </c>
-      <c r="AR20" t="inlineStr"/>
+        <v>-1.083941689623508</v>
+      </c>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="n">
+        <v>-1.241359044995392</v>
+      </c>
       <c r="AS20" t="n">
-        <v>-1.940979588007455</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>-1.245016835016827</v>
-      </c>
-      <c r="AU20" t="inlineStr"/>
+        <v>-1.456838842975202</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="n">
+        <v>-1.764452475785152</v>
+      </c>
       <c r="AV20" t="inlineStr"/>
       <c r="AW20" t="n">
-        <v>-0.2921632996632999</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0.02366807541730176</v>
-      </c>
+        <v>-0.6168342516069885</v>
+      </c>
+      <c r="AX20" t="inlineStr"/>
       <c r="AY20" t="n">
-        <v>-194563.2732724934</v>
+        <v>-0.6745731185035879</v>
       </c>
       <c r="AZ20" t="inlineStr"/>
       <c r="BA20" t="inlineStr"/>
       <c r="BB20" t="n">
-        <v>-2.218655409133333</v>
-      </c>
-      <c r="BC20" t="inlineStr"/>
+        <v>-737118.055555555</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0.02270607445530071</v>
+      </c>
       <c r="BD20" t="n">
-        <v>-1.548375420875416</v>
+        <v>-236254.4378868702</v>
       </c>
       <c r="BE20" t="inlineStr"/>
       <c r="BF20" t="n">
-        <v>-1.132786195286201</v>
+        <v>-2.22783310569406</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4156,34 +4156,30 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5666666666666665</v>
+        <v>1.929292929292929</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6833333333333336</v>
+        <v>-1.121212121212121</v>
       </c>
       <c r="V21" t="n">
-        <v>1.929292929292929</v>
+        <v>-3.626262626262626</v>
       </c>
       <c r="W21" t="n">
-        <v>-1.121212121212121</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-3.626262626262626</v>
-      </c>
-      <c r="Y21" t="n">
         <v>0.6666666666666661</v>
       </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-0.01818181818181852</v>
+      </c>
+      <c r="AB21" t="n">
         <v>-5.141414141414145</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AC21" t="n">
         <v>5.141414141414145</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0.494949494949495</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>-0.4747474747474749</v>
       </c>
       <c r="AD21" t="n">
         <v>-1.393939393939393</v>
@@ -4192,67 +4188,71 @@
         <v>0.979797979797981</v>
       </c>
       <c r="AF21" t="n">
-        <v>-1</v>
+        <v>1.23</v>
       </c>
       <c r="AG21" t="n">
-        <v>-0.01818181818181852</v>
+        <v>0.02500000000000036</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.23</v>
+        <v>0.494949494949495</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.02500000000000036</v>
-      </c>
-      <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr"/>
+        <v>-0.4747474747474749</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.5666666666666665</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>-0.6833333333333336</v>
+      </c>
       <c r="AL21" t="n">
-        <v>67.91021885521886</v>
+        <v>67.90106519742884</v>
       </c>
       <c r="AM21" t="n">
         <v>67.91384848484849</v>
       </c>
       <c r="AN21" t="n">
-        <v>509286.7132867135</v>
+        <v>1.465890269151132</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.477395454786773</v>
+        <v>-0.04621212121212115</v>
       </c>
       <c r="AP21" t="n">
-        <v>-0.1909197324415288</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.760139860139859</v>
-      </c>
-      <c r="AR21" t="inlineStr"/>
+        <v>-2.733787878787883</v>
+      </c>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="n">
+        <v>-0.05803030303033552</v>
+      </c>
       <c r="AS21" t="n">
-        <v>-3.361033314511577</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0.1615384615384414</v>
-      </c>
-      <c r="AU21" t="inlineStr"/>
+        <v>0.03045454545454618</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="n">
+        <v>-3.207709339774556</v>
+      </c>
       <c r="AV21" t="inlineStr"/>
       <c r="AW21" t="n">
-        <v>-0.05034965034965033</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>-0.06297605775866666</v>
-      </c>
+        <v>1.941060606060617</v>
+      </c>
+      <c r="AX21" t="inlineStr"/>
       <c r="AY21" t="n">
-        <v>-230696.3777768123</v>
+        <v>0.02918938348281586</v>
       </c>
       <c r="AZ21" t="inlineStr"/>
       <c r="BA21" t="inlineStr"/>
       <c r="BB21" t="n">
-        <v>-3.248668312363975</v>
-      </c>
-      <c r="BC21" t="inlineStr"/>
+        <v>540494.6969696973</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>-0.06359443294225908</v>
+      </c>
       <c r="BD21" t="n">
-        <v>-0.2433566433566483</v>
+        <v>-225852.4240855763</v>
       </c>
       <c r="BE21" t="inlineStr"/>
       <c r="BF21" t="n">
-        <v>-2.879020979020982</v>
+        <v>-3.086737117552346</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4337,34 +4337,34 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2166666666666668</v>
+        <v>0.09090909090909083</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1833333333333332</v>
+        <v>3.919191919191919</v>
       </c>
       <c r="V22" t="n">
-        <v>0.09090909090909083</v>
+        <v>-1.666666666666666</v>
       </c>
       <c r="W22" t="n">
-        <v>3.919191919191919</v>
+        <v>-0.6464646464646471</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.666666666666666</v>
+        <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.6464646464646471</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-0.04999999999999982</v>
+      </c>
+      <c r="AB22" t="n">
         <v>-1.242424242424242</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AC22" t="n">
         <v>1.242424242424242</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0.04040404040404044</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0.4343434343434343</v>
       </c>
       <c r="AD22" t="n">
         <v>-2.979797979797981</v>
@@ -4373,71 +4373,71 @@
         <v>7.626262626262628</v>
       </c>
       <c r="AF22" t="n">
-        <v>1</v>
+        <v>-0.5547619047619047</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.04999999999999982</v>
+        <v>0.7004761904761907</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.5547619047619047</v>
+        <v>0.04040404040404044</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.7004761904761907</v>
+        <v>0.4343434343434343</v>
       </c>
       <c r="AJ22" t="n">
-        <v>5</v>
+        <v>-0.2166666666666668</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>0.1833333333333332</v>
       </c>
       <c r="AL22" t="n">
-        <v>68.58101010101009</v>
+        <v>68.56656565656564</v>
       </c>
       <c r="AM22" t="n">
-        <v>68.41012396694215</v>
+        <v>68.40590909090909</v>
       </c>
       <c r="AN22" t="n">
-        <v>-133009.5359186274</v>
+        <v>-0.5283417849145025</v>
       </c>
       <c r="AO22" t="n">
-        <v>-0.3517252722911763</v>
+        <v>0.06363636363636371</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.7281188681306787</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>-0.9242212333121387</v>
-      </c>
-      <c r="AR22" t="inlineStr"/>
+        <v>-0.9492424242424242</v>
+      </c>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="n">
+        <v>3.499999999999972</v>
+      </c>
       <c r="AS22" t="n">
-        <v>-1.594665494695171</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>3.735028607755908</v>
-      </c>
-      <c r="AU22" t="inlineStr"/>
+        <v>-2.091666666666654</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="n">
+        <v>-1.565208761751702</v>
+      </c>
       <c r="AV22" t="inlineStr"/>
       <c r="AW22" t="n">
-        <v>0.06643356643356646</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0.02968835131306546</v>
-      </c>
+        <v>-0.875</v>
+      </c>
+      <c r="AX22" t="inlineStr"/>
       <c r="AY22" t="n">
-        <v>-237429.9202725799</v>
+        <v>1.056574334920867</v>
       </c>
       <c r="AZ22" t="inlineStr"/>
       <c r="BA22" t="inlineStr"/>
       <c r="BB22" t="n">
-        <v>-3.968851748893421</v>
-      </c>
-      <c r="BC22" t="inlineStr"/>
+        <v>-146515.1515151523</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0.02819412662090026</v>
+      </c>
       <c r="BD22" t="n">
-        <v>-2.106993006993022</v>
+        <v>-341210.1070090507</v>
       </c>
       <c r="BE22" t="inlineStr"/>
       <c r="BF22" t="n">
-        <v>-0.9186904005085808</v>
+        <v>-4.16691381198482</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4522,34 +4522,34 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4545454545454546</v>
+        <v>0.1363636363636367</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3636363636363636</v>
+        <v>0.536363636363637</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1363636363636367</v>
+        <v>-2.990909090909092</v>
       </c>
       <c r="W23" t="n">
-        <v>0.536363636363637</v>
+        <v>-1.145454545454545</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.990909090909092</v>
+        <v>-7</v>
       </c>
       <c r="Y23" t="n">
-        <v>-1.145454545454545</v>
+        <v>-6</v>
       </c>
       <c r="Z23" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-0.2363636363636363</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.172727272727272</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AC23" t="n">
         <v>-1.081818181818178</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0.2727272727272729</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>-0.06363636363636349</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -4558,71 +4558,71 @@
         <v>2.872727272727273</v>
       </c>
       <c r="AF23" t="n">
-        <v>-0.5</v>
+        <v>0.6290476190476193</v>
       </c>
       <c r="AG23" t="n">
-        <v>-0.2363636363636363</v>
+        <v>0.105952380952381</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.6290476190476193</v>
+        <v>0.2727272727272729</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.105952380952381</v>
+        <v>-0.06363636363636349</v>
       </c>
       <c r="AJ23" t="n">
-        <v>-7</v>
+        <v>0.4545454545454546</v>
       </c>
       <c r="AK23" t="n">
-        <v>-6</v>
+        <v>-0.3636363636363636</v>
       </c>
       <c r="AL23" t="n">
         <v>67.81800505050505</v>
       </c>
       <c r="AM23" t="n">
-        <v>67.76279155188246</v>
+        <v>67.75419191919192</v>
       </c>
       <c r="AN23" t="n">
-        <v>100880.0505050505</v>
+        <v>1.885053067843813</v>
       </c>
       <c r="AO23" t="n">
-        <v>1.749907422367542</v>
+        <v>-0.1669421487603306</v>
       </c>
       <c r="AP23" t="n">
-        <v>-1.098338265799015</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.811616161616158</v>
-      </c>
-      <c r="AR23" t="inlineStr"/>
+        <v>-2.523966942148764</v>
+      </c>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="n">
+        <v>-1.803122130394883</v>
+      </c>
       <c r="AS23" t="n">
-        <v>-0.9275046332628989</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>-1.645286195286246</v>
-      </c>
-      <c r="AU23" t="inlineStr"/>
+        <v>-1.789439853076203</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="n">
+        <v>-0.807086796256236</v>
+      </c>
       <c r="AV23" t="inlineStr"/>
       <c r="AW23" t="n">
-        <v>-0.1530303030303031</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>-0.09309293765815485</v>
-      </c>
+        <v>1.798622589531675</v>
+      </c>
+      <c r="AX23" t="inlineStr"/>
       <c r="AY23" t="n">
-        <v>223824.3369515643</v>
+        <v>-0.9995622945461662</v>
       </c>
       <c r="AZ23" t="inlineStr"/>
       <c r="BA23" t="inlineStr"/>
       <c r="BB23" t="n">
-        <v>-0.4829092016856933</v>
-      </c>
-      <c r="BC23" t="inlineStr"/>
+        <v>30298.8980716255</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>-0.07558190601668846</v>
+      </c>
       <c r="BD23" t="n">
-        <v>-1.66607744107742</v>
+        <v>323823.1371277058</v>
       </c>
       <c r="BE23" t="inlineStr"/>
       <c r="BF23" t="n">
-        <v>-2.392424242424241</v>
+        <v>-0.2892240947342657</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -4707,34 +4707,30 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2000000000000001</v>
+        <v>-1.111111111111112</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.09999999999999987</v>
+        <v>-0.1111111111111107</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.111111111111112</v>
+        <v>3.444444444444443</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.1111111111111107</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.444444444444443</v>
-      </c>
-      <c r="Y24" t="n">
         <v>-0.2222222222222214</v>
       </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.03333333333333321</v>
+      </c>
+      <c r="AB24" t="n">
         <v>-4.444444444444443</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AC24" t="n">
         <v>4.444444444444443</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0.1111111111111109</v>
       </c>
       <c r="AD24" t="n">
         <v>-4.666666666666664</v>
@@ -4743,67 +4739,71 @@
         <v>0.1111111111111107</v>
       </c>
       <c r="AF24" t="n">
-        <v>-1.5</v>
+        <v>-0.9564285714285714</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.03333333333333321</v>
+        <v>0.127142857142857</v>
       </c>
       <c r="AH24" t="n">
-        <v>-0.9564285714285714</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.127142857142857</v>
-      </c>
-      <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr"/>
+        <v>0.1111111111111109</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.2000000000000001</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>-0.09999999999999987</v>
+      </c>
       <c r="AL24" t="n">
-        <v>67.84192460317459</v>
+        <v>67.83824786324786</v>
       </c>
       <c r="AM24" t="n">
-        <v>67.43169421487603</v>
+        <v>67.42590909090909</v>
       </c>
       <c r="AN24" t="n">
-        <v>-563489.8989898986</v>
+        <v>-1.417592487921965</v>
       </c>
       <c r="AO24" t="n">
-        <v>-1.439020322815836</v>
+        <v>0.01616161616161604</v>
       </c>
       <c r="AP24" t="n">
-        <v>-0.1532190678913707</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>-1.008417508417509</v>
-      </c>
-      <c r="AR24" t="inlineStr"/>
+        <v>-0.5848484848484787</v>
+      </c>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="n">
+        <v>-2.031864095500481</v>
+      </c>
       <c r="AS24" t="n">
-        <v>1.845930102672664</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>-1.84048821548825</v>
-      </c>
-      <c r="AU24" t="inlineStr"/>
+        <v>-1.479430670339752</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="n">
+        <v>1.890859590340661</v>
+      </c>
       <c r="AV24" t="inlineStr"/>
       <c r="AW24" t="n">
-        <v>-0.003030303030302939</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>0.07271327973382147</v>
-      </c>
+        <v>-0.74196510560148</v>
+      </c>
+      <c r="AX24" t="inlineStr"/>
       <c r="AY24" t="n">
-        <v>-162460.2215688201</v>
+        <v>0.01750277782383591</v>
       </c>
       <c r="AZ24" t="inlineStr"/>
       <c r="BA24" t="inlineStr"/>
       <c r="BB24" t="n">
-        <v>0.6104682718752912</v>
-      </c>
-      <c r="BC24" t="inlineStr"/>
+        <v>-486185.4912764006</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0.06467984495147405</v>
+      </c>
       <c r="BD24" t="n">
-        <v>-1.681397306397315</v>
+        <v>-125825.2033084496</v>
       </c>
       <c r="BE24" t="inlineStr"/>
       <c r="BF24" t="n">
-        <v>-0.6064814814814774</v>
+        <v>0.7188767982585915</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>pv9VXZo7</t>
+          <t>UN8LwZh9</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
@@ -4820,24 +4820,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
+          <t xml:space="preserve">unkel t 
+  usa </t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">citypark
-  st  louis  mo </t>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4864,127 +4864,127 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>z9ZXDy6o</t>
+          <t>UFWZoX9L</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Onn3tCA5</t>
+          <t>Sd7snoa0</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>0.7777777777777781</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2727272727272727</v>
+        <v>0.2222222222222214</v>
       </c>
       <c r="V25" t="n">
-        <v>0.8000000000000007</v>
+        <v>4</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.3000000000000007</v>
-      </c>
-      <c r="X25" t="n">
-        <v>6.300000000000001</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>-1.799999999999999</v>
-      </c>
+        <v>-1.333333333333332</v>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="n">
-        <v>2.200000000000003</v>
+        <v>0.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>-2.200000000000003</v>
+        <v>1.344444444444445</v>
       </c>
       <c r="AB25" t="n">
-        <v>-0.7000000000000001</v>
+        <v>-2.888888888888886</v>
       </c>
       <c r="AC25" t="n">
-        <v>-1.2</v>
+        <v>2.888888888888886</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>0.4444444444444446</v>
       </c>
       <c r="AE25" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.5</v>
+        <v>-0.01071428571428568</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.581818181818182</v>
+        <v>-0.1026190476190476</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.01142857142857157</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="AI25" t="n">
-        <v>-0.3108571428571429</v>
-      </c>
-      <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr"/>
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>-0.2</v>
+      </c>
       <c r="AL25" t="n">
-        <v>68.89777777777778</v>
+        <v>68.41404040404041</v>
       </c>
       <c r="AM25" t="n">
-        <v>68.9345987654321</v>
+        <v>68.20372727272726</v>
       </c>
       <c r="AN25" t="n">
-        <v>-230770.2020202023</v>
+        <v>0.7491749502580944</v>
       </c>
       <c r="AO25" t="n">
-        <v>-0.4927628301973641</v>
+        <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.433488006001426</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>-0.8969865319865278</v>
-      </c>
-      <c r="AR25" t="inlineStr"/>
+        <v>0.1595959595959648</v>
+      </c>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="n">
+        <v>4.461616161616121</v>
+      </c>
       <c r="AS25" t="n">
-        <v>-1.713427264313488</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>1.913872053872069</v>
-      </c>
-      <c r="AU25" t="inlineStr"/>
+        <v>-3.493939393939399</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="n">
+        <v>-0.2229719528289351</v>
+      </c>
       <c r="AV25" t="inlineStr"/>
       <c r="AW25" t="n">
-        <v>0.193131313131313</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
+        <v>-1.957575757575754</v>
+      </c>
+      <c r="AX25" t="inlineStr"/>
       <c r="AY25" t="n">
-        <v>-132045.4242117989</v>
+        <v>2.441839249896105</v>
       </c>
       <c r="AZ25" t="inlineStr"/>
       <c r="BA25" t="inlineStr"/>
       <c r="BB25" t="n">
-        <v>-1.484931970303322</v>
-      </c>
-      <c r="BC25" t="inlineStr"/>
+        <v>-1503813.131313131</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
       <c r="BD25" t="n">
-        <v>-0.8056565656565624</v>
+        <v>130321.4565701694</v>
       </c>
       <c r="BE25" t="inlineStr"/>
       <c r="BF25" t="n">
-        <v>-0.9820033670033652</v>
+        <v>-0.8619267472223129</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>UN8LwZh9</t>
+          <t>pv9VXZo7</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -5001,24 +5001,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">unkel t 
-  usa </t>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz field
-  saint paul  mn </t>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>K2dlua5N</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5045,127 +5045,127 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>UFWZoX9L</t>
+          <t>z9ZXDy6o</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Sd7snoa0</t>
+          <t>Onn3tCA5</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.8000000000000007</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2</v>
+        <v>-0.3000000000000007</v>
       </c>
       <c r="V26" t="n">
-        <v>0.7777777777777781</v>
+        <v>6.300000000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>0.2222222222222214</v>
-      </c>
-      <c r="X26" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>-1.333333333333332</v>
-      </c>
+        <v>-1.799999999999999</v>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="n">
-        <v>-2.888888888888886</v>
+        <v>-0.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.888888888888886</v>
+        <v>1.581818181818182</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.6666666666666667</v>
+        <v>2.200000000000003</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.4444444444444444</v>
+        <v>-2.200000000000003</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.4444444444444446</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.5</v>
+        <v>0.01142857142857157</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.344444444444445</v>
+        <v>-0.3108571428571429</v>
       </c>
       <c r="AH26" t="n">
-        <v>-0.01071428571428568</v>
+        <v>-0.7000000000000001</v>
       </c>
       <c r="AI26" t="n">
-        <v>-0.1026190476190476</v>
-      </c>
-      <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="inlineStr"/>
+        <v>-1.2</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>-0.2727272727272727</v>
+      </c>
       <c r="AL26" t="n">
-        <v>68.42040404040404</v>
+        <v>68.90532598714417</v>
       </c>
       <c r="AM26" t="n">
-        <v>68.20372727272726</v>
+        <v>68.9345987654321</v>
       </c>
       <c r="AN26" t="n">
-        <v>-1478768.595041323</v>
+        <v>-0.5052274086945516</v>
       </c>
       <c r="AO26" t="n">
-        <v>0.6967642591327063</v>
+        <v>0.193131313131313</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.301744488031687</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>-2.035619834710758</v>
-      </c>
-      <c r="AR26" t="inlineStr"/>
+        <v>-0.9866023875114784</v>
+      </c>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="n">
+        <v>1.916152433425168</v>
+      </c>
       <c r="AS26" t="n">
-        <v>-0.406806046737394</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>4.404132231404958</v>
-      </c>
-      <c r="AU26" t="inlineStr"/>
+        <v>-0.8690633608815403</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="n">
+        <v>-1.718411631797853</v>
+      </c>
       <c r="AV26" t="inlineStr"/>
       <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.9852249770431456</v>
+      </c>
+      <c r="AX26" t="inlineStr"/>
       <c r="AY26" t="n">
-        <v>145202.6331474271</v>
+        <v>1.531830645648427</v>
       </c>
       <c r="AZ26" t="inlineStr"/>
       <c r="BA26" t="inlineStr"/>
       <c r="BB26" t="n">
-        <v>-0.9693554621071598</v>
-      </c>
-      <c r="BC26" t="inlineStr"/>
+        <v>-286728.8797061522</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
       <c r="BD26" t="n">
-        <v>-3.36876033057851</v>
+        <v>-138900.0666506805</v>
       </c>
       <c r="BE26" t="inlineStr"/>
       <c r="BF26" t="n">
-        <v>0.4025619834710703</v>
+        <v>-1.516510828240868</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5250,34 +5250,30 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0.4444444444444444</v>
+        <v>1.011363636363637</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.2222222222222221</v>
+        <v>0.625</v>
       </c>
       <c r="V27" t="n">
-        <v>1.011363636363637</v>
+        <v>0.1818181818181817</v>
       </c>
       <c r="W27" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0.1818181818181817</v>
-      </c>
-      <c r="Y27" t="n">
         <v>0.7613636363636367</v>
       </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-0.07954545454545414</v>
+      </c>
+      <c r="AB27" t="n">
         <v>-1.329545454545453</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AC27" t="n">
         <v>1.238636363636367</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>-0.07954545454545459</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0.3181818181818181</v>
       </c>
       <c r="AD27" t="n">
         <v>-2.022727272727273</v>
@@ -5286,67 +5282,71 @@
         <v>3.375</v>
       </c>
       <c r="AF27" t="n">
-        <v>-2</v>
+        <v>-0.5449999999999999</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.07954545454545414</v>
+        <v>0.7299999999999995</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.5449999999999999</v>
+        <v>-0.07954545454545459</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.7299999999999995</v>
-      </c>
-      <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="inlineStr"/>
+        <v>0.3181818181818181</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>-0.2222222222222221</v>
+      </c>
       <c r="AL27" t="n">
-        <v>68.46161616161618</v>
+        <v>68.5166305916306</v>
       </c>
       <c r="AM27" t="n">
-        <v>68.8895867768595</v>
+        <v>68.88</v>
       </c>
       <c r="AN27" t="n">
-        <v>-910805.6742640077</v>
+        <v>1.545842303236896</v>
       </c>
       <c r="AO27" t="n">
-        <v>1.389722464949443</v>
+        <v>-0.07058080808080835</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.603845687081929</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>-0.2608823275489982</v>
-      </c>
-      <c r="AR27" t="inlineStr"/>
+        <v>0.3644570707070685</v>
+      </c>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="n">
+        <v>1.543181818181779</v>
+      </c>
       <c r="AS27" t="n">
-        <v>-0.2084215008109105</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>1.593758093758055</v>
-      </c>
-      <c r="AU27" t="inlineStr"/>
+        <v>1.639204545454547</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="n">
+        <v>-0.05807884936426788</v>
+      </c>
       <c r="AV27" t="inlineStr"/>
       <c r="AW27" t="n">
-        <v>-0.07833031166364512</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0.07114218249210702</v>
-      </c>
+        <v>0.0489898989899018</v>
+      </c>
+      <c r="AX27" t="inlineStr"/>
       <c r="AY27" t="n">
-        <v>-643007.982729305</v>
+        <v>1.731563880539568</v>
       </c>
       <c r="AZ27" t="inlineStr"/>
       <c r="BA27" t="inlineStr"/>
       <c r="BB27" t="n">
-        <v>0.4984833891862337</v>
-      </c>
-      <c r="BC27" t="inlineStr"/>
+        <v>-748475.694444444</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0.08159789556848396</v>
+      </c>
       <c r="BD27" t="n">
-        <v>1.638312613312607</v>
+        <v>-650481.36978527</v>
       </c>
       <c r="BE27" t="inlineStr"/>
       <c r="BF27" t="n">
-        <v>0.5794850211516867</v>
+        <v>0.6129337128903956</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5355,7 +5355,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>88KCueOd</t>
+          <t>QJcftbvR</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -5363,24 +5363,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">mendoza r 
-  usa </t>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">yankee stadium
-  new york  ny </t>
+          <t xml:space="preserve">bank of america stadium
+  charlotte  nc </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>QJF7WTFB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>0AheRyBg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5407,127 +5407,127 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>EgT3xN3S</t>
+          <t>6BusaLE3</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>K4FYmLD9</t>
+          <t>zoZ995af</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>0.8727272727272728</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.5181818181818181</v>
+        <v>0.1111111111111107</v>
       </c>
       <c r="V28" t="n">
-        <v>0.833333333333333</v>
+        <v>1.544444444444444</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.9777777777777779</v>
-      </c>
-      <c r="X28" t="n">
-        <v>-0.09999999999999964</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.477777777777778</v>
-      </c>
+        <v>-1.166666666666666</v>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="n">
-        <v>2.37777777777778</v>
+        <v>0.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>-2.37777777777778</v>
+        <v>0.9000000000000004</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.2666666666666668</v>
+        <v>-6.955555555555556</v>
       </c>
       <c r="AC28" t="n">
-        <v>-1.055555555555556</v>
+        <v>6.955555555555556</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.477777777777778</v>
+        <v>1.033333333333333</v>
       </c>
       <c r="AE28" t="n">
-        <v>-2.122222222222222</v>
+        <v>-3.800000000000001</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.5</v>
+        <v>-0.5771428571428573</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.3666666666666671</v>
+        <v>-0.4485714285714287</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.1673809523809524</v>
+        <v>-0.9222222222222223</v>
       </c>
       <c r="AI28" t="n">
-        <v>-0.8271428571428572</v>
-      </c>
-      <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="inlineStr"/>
+        <v>-0.7444444444444445</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>-0.1000000000000001</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0.03636363636363638</v>
+      </c>
       <c r="AL28" t="n">
-        <v>68.33300275482092</v>
+        <v>68.38043242340763</v>
       </c>
       <c r="AM28" t="n">
-        <v>68.45781297826753</v>
+        <v>68.72</v>
       </c>
       <c r="AN28" t="n">
-        <v>275448.9975512703</v>
+        <v>-3.342879483443213</v>
       </c>
       <c r="AO28" t="n">
-        <v>-0.05785659033551838</v>
+        <v>-0.7505050505050506</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.425032800343331</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0.3894500561167291</v>
-      </c>
-      <c r="AR28" t="inlineStr"/>
+        <v>-1.490202020202023</v>
+      </c>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="n">
+        <v>0.533838383838372</v>
+      </c>
       <c r="AS28" t="n">
-        <v>-1.666801018154864</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>3.404193449647977</v>
-      </c>
-      <c r="AU28" t="inlineStr"/>
+        <v>-7.823737373737387</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="n">
+        <v>2.448311558630184</v>
+      </c>
       <c r="AV28" t="inlineStr"/>
       <c r="AW28" t="n">
-        <v>-0.01652892561983466</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>-0.09740570434350326</v>
-      </c>
+        <v>-6.589494949494949</v>
+      </c>
+      <c r="AX28" t="inlineStr"/>
       <c r="AY28" t="n">
-        <v>22135.27428143215</v>
+        <v>-3.064850913429325</v>
       </c>
       <c r="AZ28" t="inlineStr"/>
       <c r="BA28" t="inlineStr"/>
       <c r="BB28" t="n">
-        <v>-2.373599850591368</v>
-      </c>
-      <c r="BC28" t="inlineStr"/>
+        <v>-5084245.95959596</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0.01495883201765524</v>
+      </c>
       <c r="BD28" t="n">
-        <v>0.3056448321599987</v>
+        <v>-539594.386382499</v>
       </c>
       <c r="BE28" t="inlineStr"/>
       <c r="BF28" t="n">
-        <v>-0.5267957351290669</v>
+        <v>-1.358013420856551</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -5536,7 +5536,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>p4vRzx2l</t>
+          <t>naJGvFw3</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -5544,24 +5544,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">freemon j 
+          <t xml:space="preserve">simon n 
   usa </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi field
-  washington  dc </t>
+          <t xml:space="preserve">bmo field
+  toronto  on </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>zsdfgnmL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5588,127 +5588,127 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>nJ01AhXP</t>
+          <t>rJ9D8rzj</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>GzULyFoh</t>
+          <t>Uw6sTk0t</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>-1.563636363636364</v>
+        <v>1.4</v>
       </c>
       <c r="U29" t="n">
-        <v>1.3</v>
+        <v>-0.5</v>
       </c>
       <c r="V29" t="n">
-        <v>-1.066666666666667</v>
+        <v>2.4</v>
       </c>
       <c r="W29" t="n">
-        <v>0.08888888888888946</v>
-      </c>
-      <c r="X29" t="n">
-        <v>-0.7555555555555546</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0.7666666666666657</v>
-      </c>
+        <v>-0.9000000000000004</v>
+      </c>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="n">
-        <v>-4.011111111111113</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>4.011111111111113</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="AB29" t="n">
-        <v>-1.022222222222222</v>
+        <v>2.799999999999997</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.6444444444444446</v>
+        <v>-2.799999999999997</v>
       </c>
       <c r="AD29" t="n">
-        <v>-1.277777777777779</v>
+        <v>0.1999999999999993</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.04444444444444429</v>
+        <v>-1.1</v>
       </c>
       <c r="AF29" t="n">
+        <v>0.5211904761904762</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.08238095238095222</v>
+      </c>
+      <c r="AH29" t="n">
         <v>0.5</v>
       </c>
-      <c r="AG29" t="n">
-        <v>-0.9204545454545459</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0.1102857142857141</v>
-      </c>
       <c r="AI29" t="n">
-        <v>0.5520000000000004</v>
-      </c>
-      <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="inlineStr"/>
+        <v>0.8000000000000003</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>-0.3636363636363636</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.4545454545454546</v>
+      </c>
       <c r="AL29" t="n">
-        <v>68.08504883546206</v>
+        <v>67.05185376492194</v>
       </c>
       <c r="AM29" t="n">
-        <v>68.38960372960373</v>
+        <v>69.15796602387512</v>
       </c>
       <c r="AN29" t="n">
-        <v>-2517322.727272728</v>
+        <v>-0.0370530381211438</v>
       </c>
       <c r="AO29" t="n">
-        <v>3.951781693273773</v>
+        <v>-0.04090909090909101</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.100878411832099</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>-3.085867768595051</v>
-      </c>
-      <c r="AR29" t="inlineStr"/>
+        <v>-0.6618181818181839</v>
+      </c>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="n">
+        <v>2.828181818181861</v>
+      </c>
       <c r="AS29" t="n">
-        <v>-1.410505206249407</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>5.017438016528928</v>
-      </c>
-      <c r="AU29" t="inlineStr"/>
+        <v>-5.215454545454548</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="n">
+        <v>-1.870904846787198</v>
+      </c>
       <c r="AV29" t="inlineStr"/>
       <c r="AW29" t="n">
-        <v>0.09173553719008276</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0.01438064859117483</v>
-      </c>
+        <v>-4.74909090909091</v>
+      </c>
+      <c r="AX29" t="inlineStr"/>
       <c r="AY29" t="n">
-        <v>-465306.0327683028</v>
+        <v>-1.199276131505258</v>
       </c>
       <c r="AZ29" t="inlineStr"/>
       <c r="BA29" t="inlineStr"/>
       <c r="BB29" t="n">
-        <v>0.02018168956028887</v>
-      </c>
-      <c r="BC29" t="inlineStr"/>
+        <v>-846031.8181818179</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0.03459946658089086</v>
+      </c>
       <c r="BD29" t="n">
-        <v>-2.871074380165282</v>
+        <v>-931796.6930472353</v>
       </c>
       <c r="BE29" t="inlineStr"/>
       <c r="BF29" t="n">
-        <v>1.330991735537186</v>
+        <v>-1.146218822457229</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -5717,7 +5717,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>QJcftbvR</t>
+          <t>88KCueOd</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -5725,24 +5725,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
+          <t xml:space="preserve">mendoza r 
+  usa </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">bank of america stadium
-  charlotte  nc </t>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0AheRyBg</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5769,127 +5769,127 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>6BusaLE3</t>
+          <t>EgT3xN3S</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>zoZ995af</t>
+          <t>K4FYmLD9</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="P30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.1000000000000001</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="U30" t="n">
-        <v>0.03636363636363638</v>
+        <v>-0.9777777777777779</v>
       </c>
       <c r="V30" t="n">
-        <v>-1.666666666666667</v>
+        <v>-0.09999999999999964</v>
       </c>
       <c r="W30" t="n">
-        <v>0.1111111111111107</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.544444444444444</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>-1.166666666666666</v>
-      </c>
+        <v>1.477777777777778</v>
+      </c>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="n">
-        <v>-6.955555555555556</v>
+        <v>-0.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>6.955555555555556</v>
+        <v>-0.3666666666666671</v>
       </c>
       <c r="AB30" t="n">
-        <v>-0.9222222222222223</v>
+        <v>2.37777777777778</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.7444444444444445</v>
+        <v>-2.37777777777778</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.033333333333333</v>
+        <v>2.477777777777778</v>
       </c>
       <c r="AE30" t="n">
-        <v>-3.800000000000001</v>
+        <v>-2.122222222222222</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.5</v>
+        <v>0.1673809523809524</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.9000000000000004</v>
+        <v>-0.8271428571428572</v>
       </c>
       <c r="AH30" t="n">
-        <v>-0.5771428571428573</v>
+        <v>0.2666666666666668</v>
       </c>
       <c r="AI30" t="n">
-        <v>-0.4485714285714287</v>
-      </c>
-      <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="inlineStr"/>
+        <v>-1.055555555555556</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0.8727272727272728</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>-0.5181818181818181</v>
+      </c>
       <c r="AL30" t="n">
-        <v>68.37378328741966</v>
+        <v>68.33215151515151</v>
       </c>
       <c r="AM30" t="n">
-        <v>68.71528925619835</v>
+        <v>68.43421821520995</v>
       </c>
       <c r="AN30" t="n">
-        <v>-5093438.934802571</v>
+        <v>0.1086521300150309</v>
       </c>
       <c r="AO30" t="n">
-        <v>-3.488959023003147</v>
+        <v>-0.01818181818181808</v>
       </c>
       <c r="AP30" t="n">
-        <v>-2.951882287350173</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>-6.527594123048672</v>
-      </c>
-      <c r="AR30" t="inlineStr"/>
+        <v>-0.3974747474747495</v>
+      </c>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="n">
+        <v>3.205208333333303</v>
+      </c>
       <c r="AS30" t="n">
-        <v>2.180104154609499</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0.350716253443494</v>
-      </c>
-      <c r="AU30" t="inlineStr"/>
+        <v>0.2739898989899103</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="n">
+        <v>-1.874672124102396</v>
+      </c>
       <c r="AV30" t="inlineStr"/>
       <c r="AW30" t="n">
-        <v>-0.7453719008264461</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>-0.04184298099405059</v>
-      </c>
+        <v>0.1244949494949594</v>
+      </c>
+      <c r="AX30" t="inlineStr"/>
       <c r="AY30" t="n">
-        <v>-761647.3115416965</v>
+        <v>0.41795558366195</v>
       </c>
       <c r="AZ30" t="inlineStr"/>
       <c r="BA30" t="inlineStr"/>
       <c r="BB30" t="n">
-        <v>-1.652049303192356</v>
-      </c>
-      <c r="BC30" t="inlineStr"/>
+        <v>258506.1553030305</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>-0.1029796081111871</v>
+      </c>
       <c r="BD30" t="n">
-        <v>-7.69996326905418</v>
+        <v>17978.79995559738</v>
       </c>
       <c r="BE30" t="inlineStr"/>
       <c r="BF30" t="n">
-        <v>-1.425371900826452</v>
+        <v>-2.541812385241158</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -5898,7 +5898,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>naJGvFw3</t>
+          <t>p4vRzx2l</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
@@ -5906,24 +5906,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">simon n 
+          <t xml:space="preserve">freemon j 
   usa </t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">bmo field
-  toronto  on </t>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
+          <t>O6hjfSXE</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>rsHkUNCo</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5950,127 +5950,127 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>rJ9D8rzj</t>
+          <t>nJ01AhXP</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Uw6sTk0t</t>
+          <t>GzULyFoh</t>
         </is>
       </c>
       <c r="O31" t="n">
+        <v>3</v>
+      </c>
+      <c r="P31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q31" t="n">
         <v>1</v>
       </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
         <v>1</v>
       </c>
-      <c r="Q31" t="n">
-        <v>-3</v>
-      </c>
-      <c r="R31" t="n">
-        <v>-3</v>
-      </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>-0.3636363636363636</v>
+        <v>-1.066666666666667</v>
       </c>
       <c r="U31" t="n">
-        <v>0.4545454545454546</v>
+        <v>0.08888888888888946</v>
       </c>
       <c r="V31" t="n">
-        <v>1.4</v>
+        <v>-0.7555555555555546</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>-0.9000000000000004</v>
-      </c>
+        <v>0.7666666666666657</v>
+      </c>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="n">
-        <v>2.799999999999997</v>
+        <v>0.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>-2.799999999999997</v>
+        <v>-0.9204545454545459</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.5</v>
+        <v>-4.011111111111113</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.8000000000000003</v>
+        <v>4.011111111111113</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.1999999999999993</v>
+        <v>-1.277777777777779</v>
       </c>
       <c r="AE31" t="n">
-        <v>-1.1</v>
+        <v>0.04444444444444429</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>0.1102857142857141</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.3999999999999995</v>
+        <v>0.5520000000000004</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.5211904761904762</v>
+        <v>-1.022222222222222</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.08238095238095222</v>
-      </c>
-      <c r="AJ31" t="inlineStr"/>
-      <c r="AK31" t="inlineStr"/>
+        <v>0.6444444444444446</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>-1.563636363636364</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.3</v>
+      </c>
       <c r="AL31" t="n">
-        <v>67.06247969202515</v>
+        <v>68.07760330578513</v>
       </c>
       <c r="AM31" t="n">
-        <v>69.1661029486787</v>
+        <v>68.38477272727273</v>
       </c>
       <c r="AN31" t="n">
-        <v>-845173.5537190083</v>
+        <v>3.828271338399205</v>
       </c>
       <c r="AO31" t="n">
-        <v>-0.2025157489413232</v>
+        <v>0.0918181818181818</v>
       </c>
       <c r="AP31" t="n">
-        <v>-1.207134145524265</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>-4.742148760330565</v>
-      </c>
-      <c r="AR31" t="inlineStr"/>
+        <v>1.575151515151511</v>
+      </c>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="n">
+        <v>4.935353535353556</v>
+      </c>
       <c r="AS31" t="n">
-        <v>-2.207316094481868</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>2.771074380165317</v>
-      </c>
-      <c r="AU31" t="inlineStr"/>
+        <v>-2.731919191919189</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="n">
+        <v>-1.470943905334135</v>
+      </c>
       <c r="AV31" t="inlineStr"/>
       <c r="AW31" t="n">
-        <v>-0.02892561983471098</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>-0.007506978432956446</v>
-      </c>
+        <v>-3.206565656565672</v>
+      </c>
+      <c r="AX31" t="inlineStr"/>
       <c r="AY31" t="n">
-        <v>-1058819.504501815</v>
+        <v>0.7878590729452526</v>
       </c>
       <c r="AZ31" t="inlineStr"/>
       <c r="BA31" t="inlineStr"/>
       <c r="BB31" t="n">
-        <v>-1.583142652450299</v>
-      </c>
-      <c r="BC31" t="inlineStr"/>
+        <v>-2532322.222222222</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0.01581871345029251</v>
+      </c>
       <c r="BD31" t="n">
-        <v>-5.128099173553707</v>
+        <v>-335887.1365424334</v>
       </c>
       <c r="BE31" t="inlineStr"/>
       <c r="BF31" t="n">
-        <v>-0.4826446280991732</v>
+        <v>0.08128387859776609</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6155,34 +6155,30 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0.2727272727272727</v>
+        <v>2.342857142857143</v>
       </c>
       <c r="U32" t="n">
-        <v>-0.03409090909090906</v>
+        <v>1.171428571428571</v>
       </c>
       <c r="V32" t="n">
-        <v>2.342857142857143</v>
+        <v>-3.057142857142856</v>
       </c>
       <c r="W32" t="n">
-        <v>1.171428571428571</v>
-      </c>
-      <c r="X32" t="n">
-        <v>-3.057142857142856</v>
-      </c>
-      <c r="Y32" t="n">
         <v>2.157142857142858</v>
       </c>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.1749999999999998</v>
+      </c>
+      <c r="AB32" t="n">
         <v>10.82857142857143</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AC32" t="n">
         <v>-10.82857142857143</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.128571428571428</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0.5428571428571428</v>
       </c>
       <c r="AD32" t="n">
         <v>1.314285714285713</v>
@@ -6191,67 +6187,71 @@
         <v>-3.357142857142858</v>
       </c>
       <c r="AF32" t="n">
-        <v>-1.5</v>
+        <v>-0.04321428571428565</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.1749999999999998</v>
+        <v>0.7553571428571429</v>
       </c>
       <c r="AH32" t="n">
-        <v>-0.04321428571428565</v>
+        <v>1.128571428571428</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.7553571428571429</v>
-      </c>
-      <c r="AJ32" t="inlineStr"/>
-      <c r="AK32" t="inlineStr"/>
+        <v>0.5428571428571428</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>-0.03409090909090906</v>
+      </c>
       <c r="AL32" t="n">
-        <v>67.67349537037038</v>
+        <v>67.65899621212122</v>
       </c>
       <c r="AM32" t="n">
-        <v>66.79672727272728</v>
+        <v>66.80050505050505</v>
       </c>
       <c r="AN32" t="n">
-        <v>-127698.8636363638</v>
+        <v>4.231681304324709</v>
       </c>
       <c r="AO32" t="n">
-        <v>4.371246834958043</v>
+        <v>-0.1727272727272731</v>
       </c>
       <c r="AP32" t="n">
-        <v>-1.924238325612947</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.592871900826438</v>
-      </c>
-      <c r="AR32" t="inlineStr"/>
+        <v>-2.146753246753246</v>
+      </c>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="n">
+        <v>-3.854545454545473</v>
+      </c>
       <c r="AS32" t="n">
-        <v>-3.262026221908375</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>-3.444628099173542</v>
-      </c>
-      <c r="AU32" t="inlineStr"/>
+        <v>-0.4753246753246714</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AU32" t="n">
+        <v>-3.415977960049933</v>
+      </c>
       <c r="AV32" t="inlineStr"/>
       <c r="AW32" t="n">
-        <v>-0.1652892561983472</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>-0.05091927176907385</v>
-      </c>
+        <v>1.672727272727272</v>
+      </c>
+      <c r="AX32" t="inlineStr"/>
       <c r="AY32" t="n">
-        <v>720263.3758637994</v>
+        <v>-1.426541001015778</v>
       </c>
       <c r="AZ32" t="inlineStr"/>
       <c r="BA32" t="inlineStr"/>
       <c r="BB32" t="n">
-        <v>-0.2793131762157799</v>
-      </c>
-      <c r="BC32" t="inlineStr"/>
+        <v>85389.61038961029</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>-0.04296772068511179</v>
+      </c>
       <c r="BD32" t="n">
-        <v>-0.9233471074380191</v>
+        <v>357955.8686350794</v>
       </c>
       <c r="BE32" t="inlineStr"/>
       <c r="BF32" t="n">
-        <v>-2.533471074380163</v>
+        <v>-0.713129211855005</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">mendoza r 
+          <t xml:space="preserve">penso c 
   usa </t>
         </is>
       </c>
@@ -6336,34 +6336,30 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0.9454545454545453</v>
+        <v>-0.07272727272727231</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.9363636363636364</v>
+        <v>-1.018181818181819</v>
       </c>
       <c r="V33" t="n">
-        <v>-0.07272727272727231</v>
+        <v>1.245454545454544</v>
       </c>
       <c r="W33" t="n">
-        <v>-1.018181818181819</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.245454545454544</v>
-      </c>
-      <c r="Y33" t="n">
         <v>-1.018181818181818</v>
       </c>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-0.1222222222222227</v>
+      </c>
+      <c r="AB33" t="n">
         <v>3.736363636363635</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AC33" t="n">
         <v>-3.736363636363635</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0.1636363636363636</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>-0.9727272727272727</v>
       </c>
       <c r="AD33" t="n">
         <v>0.8272727272727263</v>
@@ -6372,19 +6368,23 @@
         <v>-0.1090909090909076</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.5</v>
+        <v>0.04380952380952396</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.1222222222222227</v>
+        <v>-0.8678571428571428</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.04380952380952396</v>
+        <v>0.1636363636363636</v>
       </c>
       <c r="AI33" t="n">
-        <v>-0.8678571428571428</v>
-      </c>
-      <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="inlineStr"/>
+        <v>-0.9727272727272727</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.9454545454545453</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>-0.9363636363636364</v>
+      </c>
       <c r="AL33" t="n">
         <v>68.42121212121212</v>
       </c>
@@ -6392,47 +6392,61 @@
         <v>67.41090909090909</v>
       </c>
       <c r="AN33" t="n">
-        <v>2524454.966329966</v>
+        <v>3.093302068581664</v>
       </c>
       <c r="AO33" t="n">
-        <v>3.150581479297898</v>
+        <v>0.3332415059687788</v>
       </c>
       <c r="AP33" t="n">
-        <v>-0.5191873444590556</v>
+        <v>3.384775022956841</v>
       </c>
       <c r="AQ33" t="n">
-        <v>4.191750841750846</v>
-      </c>
-      <c r="AR33" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0.5224701561065217</v>
+      </c>
       <c r="AS33" t="n">
-        <v>3.962687617866646</v>
+        <v>6.291561065197428</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.3779461279461316</v>
-      </c>
-      <c r="AU33" t="inlineStr"/>
-      <c r="AV33" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>3.65792222218867</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>-60</v>
+      </c>
       <c r="AW33" t="n">
-        <v>0.3357744107744109</v>
+        <v>4.081000918273631</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.01058201058201047</v>
+        <v>-75</v>
       </c>
       <c r="AY33" t="n">
-        <v>1007716.023632224</v>
-      </c>
-      <c r="AZ33" t="inlineStr"/>
-      <c r="BA33" t="inlineStr"/>
+        <v>-0.7573369208744509</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>-1840000</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>10</v>
+      </c>
       <c r="BB33" t="n">
-        <v>6.975074744983637</v>
-      </c>
-      <c r="BC33" t="inlineStr"/>
+        <v>2515488.888888889</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0.01154401154401152</v>
+      </c>
       <c r="BD33" t="n">
-        <v>6.447643097643095</v>
-      </c>
-      <c r="BE33" t="inlineStr"/>
+        <v>1024578.61054411</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
       <c r="BF33" t="n">
-        <v>3.444528619528622</v>
+        <v>6.693886672048158</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -6441,7 +6455,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>IgfnrK9E</t>
+          <t>YyTMIXGq</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -6449,24 +6463,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">marrufo j 
+          <t xml:space="preserve">allatin m 
   usa </t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">paypal park
-  san jose  ca </t>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>U3ebh62R</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -6493,127 +6507,135 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>UL7r7duf</t>
+          <t>EqKWmJfM</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2PIEeC7j</t>
+          <t>l6eEjGlO</t>
         </is>
       </c>
       <c r="O34" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>-0.9909090909090909</v>
+        <v>-1.511111111111112</v>
       </c>
       <c r="U34" t="n">
-        <v>1.3</v>
+        <v>-0.7111111111111104</v>
       </c>
       <c r="V34" t="n">
-        <v>-1.245454545454546</v>
+        <v>-5.277777777777779</v>
       </c>
       <c r="W34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X34" t="n">
-        <v>-0.2727272727272734</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0.872727272727273</v>
-      </c>
+        <v>0.9222222222222207</v>
+      </c>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="n">
-        <v>-5.172727272727272</v>
+        <v>-0.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>5.172727272727272</v>
+        <v>-1.111111111111111</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.02727272727272734</v>
+        <v>-0.9333333333333371</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.727272727272727</v>
+        <v>0.9333333333333371</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.481818181818182</v>
+        <v>-4.088888888888889</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.109090909090908</v>
+        <v>-0.2444444444444454</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.5</v>
+        <v>0.1142857142857143</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.7000000000000002</v>
+        <v>-0.0128571428571429</v>
       </c>
       <c r="AH34" t="n">
-        <v>-0.2023809523809523</v>
+        <v>-0.01111111111111118</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.4923809523809526</v>
-      </c>
-      <c r="AJ34" t="inlineStr"/>
-      <c r="AK34" t="inlineStr"/>
+        <v>-0.1444444444444444</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0.1888888888888889</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>-0.01111111111111107</v>
+      </c>
       <c r="AL34" t="n">
-        <v>69.21851851851852</v>
+        <v>68.21818181818182</v>
       </c>
       <c r="AM34" t="n">
-        <v>67.29363636363635</v>
+        <v>68.89282828282828</v>
       </c>
       <c r="AN34" t="n">
-        <v>-999634.4696969697</v>
+        <v>-0.4987264354385417</v>
       </c>
       <c r="AO34" t="n">
-        <v>-0.01476620294698705</v>
+        <v>-0.193131313131313</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.945103046049383</v>
+        <v>0.2899999999999991</v>
       </c>
       <c r="AQ34" t="n">
-        <v>-1.748998316498302</v>
-      </c>
-      <c r="AR34" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>-5.368585858585845</v>
+      </c>
       <c r="AS34" t="n">
-        <v>1.628514955689884</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>1.260168350168328</v>
-      </c>
-      <c r="AU34" t="inlineStr"/>
-      <c r="AV34" t="inlineStr"/>
+        <v>0.9566666666666634</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AU34" t="n">
+        <v>0.8928436494792997</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>137</v>
+      </c>
       <c r="AW34" t="n">
-        <v>-0.04361111111111104</v>
+        <v>0.3021212121212073</v>
       </c>
       <c r="AX34" t="n">
-        <v>-0.03425008599931223</v>
+        <v>137</v>
       </c>
       <c r="AY34" t="n">
-        <v>-57843.01611249661</v>
-      </c>
-      <c r="AZ34" t="inlineStr"/>
+        <v>-4.472321704579656</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>2500000</v>
+      </c>
       <c r="BA34" t="inlineStr"/>
       <c r="BB34" t="n">
-        <v>1.115068184278527</v>
-      </c>
-      <c r="BC34" t="inlineStr"/>
+        <v>470401.5151515151</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0</v>
+      </c>
       <c r="BD34" t="n">
-        <v>-1.565429292929295</v>
+        <v>-330652.129606321</v>
       </c>
       <c r="BE34" t="inlineStr"/>
       <c r="BF34" t="n">
-        <v>0.08430134680134671</v>
+        <v>0.3844717567662599</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -6622,7 +6644,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>YyTMIXGq</t>
+          <t>nTbjsvPK</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -6630,24 +6652,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">dujic f 
-  can </t>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">bc place
-  vancouver  bc </t>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>K2dlua5N</t>
+          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6674,127 +6696,135 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>EqKWmJfM</t>
+          <t>tOpyQa24</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>l6eEjGlO</t>
+          <t>Uw6sTk0t</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0.1888888888888889</v>
+        <v>-0.9444444444444438</v>
       </c>
       <c r="U35" t="n">
-        <v>-0.01111111111111107</v>
+        <v>-0.2777777777777777</v>
       </c>
       <c r="V35" t="n">
-        <v>-1.511111111111112</v>
+        <v>-1.888888888888888</v>
       </c>
       <c r="W35" t="n">
-        <v>-0.7111111111111104</v>
-      </c>
-      <c r="X35" t="n">
-        <v>-5.277777777777779</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0.9222222222222207</v>
-      </c>
+        <v>2.527777777777777</v>
+      </c>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="n">
-        <v>-0.9333333333333371</v>
+        <v>2</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.9333333333333371</v>
+        <v>1.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>-0.01111111111111118</v>
+        <v>2.472222222222221</v>
       </c>
       <c r="AC35" t="n">
-        <v>-0.1444444444444444</v>
+        <v>-2.472222222222221</v>
       </c>
       <c r="AD35" t="n">
-        <v>-4.088888888888889</v>
+        <v>0.1388888888888875</v>
       </c>
       <c r="AE35" t="n">
-        <v>-0.2444444444444454</v>
+        <v>1.722222222222223</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.5</v>
+        <v>-0.1328571428571427</v>
       </c>
       <c r="AG35" t="n">
-        <v>-1.111111111111111</v>
+        <v>-0.1242857142857141</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.1142857142857143</v>
+        <v>0.25</v>
       </c>
       <c r="AI35" t="n">
-        <v>-0.0128571428571429</v>
-      </c>
-      <c r="AJ35" t="inlineStr"/>
-      <c r="AK35" t="inlineStr"/>
+        <v>-0.5277777777777777</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>-1.055555555555555</v>
+      </c>
       <c r="AL35" t="n">
-        <v>68.21818181818182</v>
+        <v>67.8490909090909</v>
       </c>
       <c r="AM35" t="n">
-        <v>68.89282828282828</v>
+        <v>67.74413580246913</v>
       </c>
       <c r="AN35" t="n">
-        <v>456224.7474747477</v>
+        <v>0.2323219761199198</v>
       </c>
       <c r="AO35" t="n">
-        <v>-0.5285266404599582</v>
+        <v>0.1600621600621599</v>
       </c>
       <c r="AP35" t="n">
-        <v>-4.325499526348239</v>
+        <v>1.71002331002331</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.3090909090909122</v>
-      </c>
-      <c r="AR35" t="inlineStr"/>
+        <v>-4</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>-2.88723776223776</v>
+      </c>
       <c r="AS35" t="n">
-        <v>1.042752540063244</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>-5.334242424242433</v>
-      </c>
-      <c r="AU35" t="inlineStr"/>
-      <c r="AV35" t="inlineStr"/>
+        <v>1.079195804195805</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AU35" t="n">
+        <v>-2.562931803916456</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>-275</v>
+      </c>
       <c r="AW35" t="n">
-        <v>-0.193131313131313</v>
+        <v>0.5205905205905168</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>-278</v>
       </c>
       <c r="AY35" t="n">
-        <v>-342761.7666215643</v>
-      </c>
-      <c r="AZ35" t="inlineStr"/>
+        <v>-2.769134204811905</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>-6775000</v>
+      </c>
       <c r="BA35" t="inlineStr"/>
       <c r="BB35" t="n">
-        <v>0.4757334153410255</v>
-      </c>
-      <c r="BC35" t="inlineStr"/>
+        <v>-394937.3543123542</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>-0.05774556503456774</v>
+      </c>
       <c r="BD35" t="n">
-        <v>0.8736363636363649</v>
+        <v>-61173.08472999022</v>
       </c>
       <c r="BE35" t="inlineStr"/>
       <c r="BF35" t="n">
-        <v>0.1486868686868732</v>
+        <v>-2.83560712518512</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -6803,7 +6833,7 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>nTbjsvPK</t>
+          <t>IgfnrK9E</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -6811,24 +6841,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">simon n 
+          <t xml:space="preserve">gonzales g 
   usa </t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">lumen field
-  seattle  wa </t>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6P5S63Ah</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>U3ebh62R</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6855,127 +6885,141 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>tOpyQa24</t>
+          <t>UL7r7duf</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Uw6sTk0t</t>
+          <t>2PIEeC7j</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>8</v>
+        <v>-3</v>
       </c>
       <c r="P36" t="n">
-        <v>8</v>
+        <v>-3</v>
       </c>
       <c r="Q36" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="R36" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0.9444444444444444</v>
+        <v>-1.245454545454546</v>
       </c>
       <c r="U36" t="n">
-        <v>-1.055555555555555</v>
+        <v>1.6</v>
       </c>
       <c r="V36" t="n">
-        <v>-0.9444444444444438</v>
+        <v>-0.2727272727272734</v>
       </c>
       <c r="W36" t="n">
-        <v>-0.2777777777777777</v>
-      </c>
-      <c r="X36" t="n">
-        <v>-1.888888888888888</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>2.527777777777777</v>
-      </c>
+        <v>0.872727272727273</v>
+      </c>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="n">
-        <v>2.472222222222221</v>
+        <v>0.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>-2.472222222222221</v>
+        <v>-0.7000000000000002</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.25</v>
+        <v>-5.172727272727272</v>
       </c>
       <c r="AC36" t="n">
-        <v>-0.5277777777777777</v>
+        <v>5.172727272727272</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.1388888888888875</v>
+        <v>1.481818181818182</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.722222222222223</v>
+        <v>1.109090909090908</v>
       </c>
       <c r="AF36" t="n">
-        <v>2</v>
+        <v>-0.2023809523809523</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.1</v>
+        <v>0.4923809523809526</v>
       </c>
       <c r="AH36" t="n">
-        <v>-0.1328571428571427</v>
+        <v>0.02727272727272734</v>
       </c>
       <c r="AI36" t="n">
-        <v>-0.1242857142857141</v>
-      </c>
-      <c r="AJ36" t="inlineStr"/>
-      <c r="AK36" t="inlineStr"/>
+        <v>1.727272727272727</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>-0.9909090909090909</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.3</v>
+      </c>
       <c r="AL36" t="n">
-        <v>67.8490909090909</v>
+        <v>69.21851851851852</v>
       </c>
       <c r="AM36" t="n">
-        <v>67.74413580246913</v>
+        <v>67.29363636363635</v>
       </c>
       <c r="AN36" t="n">
-        <v>-385611.0209235211</v>
+        <v>-0.002301624449799533</v>
       </c>
       <c r="AO36" t="n">
-        <v>0.2829817118581559</v>
+        <v>-0.04361111111111104</v>
       </c>
       <c r="AP36" t="n">
-        <v>-2.726662001878594</v>
+        <v>0.08890036730945994</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.5409812409812389</v>
-      </c>
-      <c r="AR36" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.257887970615229</v>
+      </c>
       <c r="AS36" t="n">
-        <v>-2.49730817151768</v>
+        <v>-1.502022497704317</v>
       </c>
       <c r="AT36" t="n">
-        <v>-2.904527417027396</v>
-      </c>
-      <c r="AU36" t="inlineStr"/>
-      <c r="AV36" t="inlineStr"/>
+        <v>-0.5</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>1.633499323174249</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>47</v>
+      </c>
       <c r="AW36" t="n">
-        <v>0.1649350649350645</v>
+        <v>-1.660759871441684</v>
       </c>
       <c r="AX36" t="n">
-        <v>-0.05031667267836326</v>
+        <v>51</v>
       </c>
       <c r="AY36" t="n">
-        <v>-35278.48073630664</v>
-      </c>
-      <c r="AZ36" t="inlineStr"/>
-      <c r="BA36" t="inlineStr"/>
+        <v>1.846760406402382</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>-15575000</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>12.33333333333334</v>
+      </c>
       <c r="BB36" t="n">
-        <v>-2.736947331668269</v>
-      </c>
-      <c r="BC36" t="inlineStr"/>
+        <v>-943675.7920110198</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>-0.03425008599931223</v>
+      </c>
       <c r="BD36" t="n">
-        <v>1.058387445887448</v>
-      </c>
-      <c r="BE36" t="inlineStr"/>
+        <v>-50988.37367361505</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
       <c r="BF36" t="n">
-        <v>1.696825396825396</v>
+        <v>1.146647042216074</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -6992,8 +7036,8 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">fischer d 
-  can </t>
+          <t xml:space="preserve">ford t 
+  usa </t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7060,34 +7104,30 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0.5</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="U37" t="n">
-        <v>-0.3999999999999999</v>
+        <v>-1.5</v>
       </c>
       <c r="V37" t="n">
-        <v>0.09999999999999964</v>
+        <v>-0.5</v>
       </c>
       <c r="W37" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="X37" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="Y37" t="n">
         <v>1.100000000000001</v>
       </c>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-1.222222222222222</v>
+      </c>
+      <c r="AB37" t="n">
         <v>5.800000000000004</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AC37" t="n">
         <v>-5.800000000000004</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>-0.7</v>
       </c>
       <c r="AD37" t="n">
         <v>-1.200000000000001</v>
@@ -7096,19 +7136,23 @@
         <v>-0.5</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>0.02928571428571414</v>
       </c>
       <c r="AG37" t="n">
-        <v>-1.222222222222222</v>
+        <v>-0.1405357142857142</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.02928571428571414</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>-0.1405357142857142</v>
-      </c>
-      <c r="AJ37" t="inlineStr"/>
-      <c r="AK37" t="inlineStr"/>
+        <v>-0.7</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>-0.3999999999999999</v>
+      </c>
       <c r="AL37" t="n">
         <v>68.38863636363638</v>
       </c>
@@ -7116,47 +7160,61 @@
         <v>68.33858585858586</v>
       </c>
       <c r="AN37" t="n">
-        <v>1633512.396694215</v>
+        <v>-0.4150382767350038</v>
       </c>
       <c r="AO37" t="n">
-        <v>-0.3709081266008241</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>-0.5129170600227155</v>
+        <v>0.6181818181818173</v>
       </c>
       <c r="AQ37" t="n">
-        <v>2.578512396694222</v>
-      </c>
-      <c r="AR37" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>-2.827272727272685</v>
+      </c>
       <c r="AS37" t="n">
-        <v>1.864115895552892</v>
+        <v>4.127272727272725</v>
       </c>
       <c r="AT37" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AU37" t="inlineStr"/>
-      <c r="AV37" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>1.839554400222056</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>10</v>
+      </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>2.454545454545453</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AY37" t="n">
-        <v>528805.5698740589</v>
-      </c>
-      <c r="AZ37" t="inlineStr"/>
-      <c r="BA37" t="inlineStr"/>
+        <v>-0.7112066956316028</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>100000</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>-7.5</v>
+      </c>
       <c r="BB37" t="n">
-        <v>3.262887645618093</v>
-      </c>
-      <c r="BC37" t="inlineStr"/>
+        <v>1668454.545454546</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0</v>
+      </c>
       <c r="BD37" t="n">
-        <v>4.148760330578511</v>
-      </c>
-      <c r="BE37" t="inlineStr"/>
+        <v>545662.3173376555</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0</v>
+      </c>
       <c r="BF37" t="n">
-        <v>0.528925619834709</v>
+        <v>3.292282000242011</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7173,7 +7231,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">fischer d 
+          <t xml:space="preserve">dujic f 
   can </t>
         </is>
       </c>
@@ -7241,34 +7299,30 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>-0.45</v>
+        <v>1.733333333333333</v>
       </c>
       <c r="U38" t="n">
-        <v>0.75</v>
+        <v>0.1333333333333329</v>
       </c>
       <c r="V38" t="n">
-        <v>1.733333333333333</v>
+        <v>0.8666666666666654</v>
       </c>
       <c r="W38" t="n">
-        <v>0.1333333333333329</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0.8666666666666654</v>
-      </c>
-      <c r="Y38" t="n">
         <v>-0.4666666666666668</v>
       </c>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-0.2666666666666666</v>
+      </c>
+      <c r="AB38" t="n">
         <v>5.049999999999997</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AC38" t="n">
         <v>-5.049999999999997</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0.6833333333333332</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0.75</v>
       </c>
       <c r="AD38" t="n">
         <v>6.466666666666669</v>
@@ -7277,19 +7331,23 @@
         <v>-5.183333333333335</v>
       </c>
       <c r="AF38" t="n">
-        <v>1</v>
+        <v>-0.8600000000000001</v>
       </c>
       <c r="AG38" t="n">
-        <v>-0.2666666666666666</v>
+        <v>-0.1371428571428572</v>
       </c>
       <c r="AH38" t="n">
-        <v>-0.8600000000000001</v>
+        <v>0.6833333333333332</v>
       </c>
       <c r="AI38" t="n">
-        <v>-0.1371428571428572</v>
-      </c>
-      <c r="AJ38" t="inlineStr"/>
-      <c r="AK38" t="inlineStr"/>
+        <v>0.75</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0.75</v>
+      </c>
       <c r="AL38" t="n">
         <v>67.83712121212122</v>
       </c>
@@ -7297,47 +7355,55 @@
         <v>68.34636363636363</v>
       </c>
       <c r="AN38" t="n">
-        <v>-939718.5314685316</v>
+        <v>0.9518364592213686</v>
       </c>
       <c r="AO38" t="n">
-        <v>0.8313934481261782</v>
+        <v>-0.0701515151515153</v>
       </c>
       <c r="AP38" t="n">
-        <v>-1.247513923629612</v>
+        <v>-1.090757575757575</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.3798601398601278</v>
-      </c>
-      <c r="AR38" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0.346212121212119</v>
+      </c>
       <c r="AS38" t="n">
-        <v>-2.637223896805093</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0.2748251748251676</v>
-      </c>
-      <c r="AU38" t="inlineStr"/>
-      <c r="AV38" t="inlineStr"/>
+        <v>-1.733181818181805</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AU38" t="n">
+        <v>-2.66230958808644</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>129</v>
+      </c>
       <c r="AW38" t="n">
-        <v>-0.06601398601398611</v>
+        <v>0.2543939393939212</v>
       </c>
       <c r="AX38" t="n">
-        <v>-0.1984592120014115</v>
+        <v>137</v>
       </c>
       <c r="AY38" t="n">
-        <v>-78831.4400202668</v>
-      </c>
-      <c r="AZ38" t="inlineStr"/>
+        <v>-1.412619588898337</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>2000000</v>
+      </c>
       <c r="BA38" t="inlineStr"/>
       <c r="BB38" t="n">
-        <v>-1.32853569242635</v>
-      </c>
-      <c r="BC38" t="inlineStr"/>
+        <v>-969571.96969697</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>-0.1978408368178191</v>
+      </c>
       <c r="BD38" t="n">
-        <v>-1.523916083916063</v>
+        <v>-58846.81600901217</v>
       </c>
       <c r="BE38" t="inlineStr"/>
       <c r="BF38" t="n">
-        <v>-0.9564335664335637</v>
+        <v>-1.200101117741774</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -7354,8 +7420,8 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
+          <t xml:space="preserve">szpala l 
+  usa </t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -7422,34 +7488,30 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>-0.4222222222222223</v>
+        <v>-1.866666666666667</v>
       </c>
       <c r="U39" t="n">
-        <v>0.3444444444444444</v>
+        <v>-1.488888888888889</v>
       </c>
       <c r="V39" t="n">
-        <v>-1.866666666666667</v>
+        <v>0.6444444444444439</v>
       </c>
       <c r="W39" t="n">
-        <v>-1.488888888888889</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0.6444444444444439</v>
-      </c>
-      <c r="Y39" t="n">
         <v>2.033333333333333</v>
       </c>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.4027777777777777</v>
+      </c>
+      <c r="AB39" t="n">
         <v>-4.955555555555556</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AC39" t="n">
         <v>4.955555555555556</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>-0.9222222222222223</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>-0.8444444444444444</v>
       </c>
       <c r="AD39" t="n">
         <v>0.7333333333333343</v>
@@ -7458,19 +7520,23 @@
         <v>-3.5</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.5</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.4027777777777777</v>
+        <v>-0.7300000000000001</v>
       </c>
       <c r="AH39" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>-0.9222222222222223</v>
       </c>
       <c r="AI39" t="n">
-        <v>-0.7300000000000001</v>
-      </c>
-      <c r="AJ39" t="inlineStr"/>
-      <c r="AK39" t="inlineStr"/>
+        <v>-0.8444444444444444</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>-0.4222222222222223</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0.3444444444444444</v>
+      </c>
       <c r="AL39" t="n">
         <v>66.01414141414142</v>
       </c>
@@ -7478,47 +7544,61 @@
         <v>68.65151515151514</v>
       </c>
       <c r="AN39" t="n">
-        <v>-3437136.363636363</v>
+        <v>-6.98611943296514</v>
       </c>
       <c r="AO39" t="n">
-        <v>-7.178371587691814</v>
+        <v>-0.5868686868686865</v>
       </c>
       <c r="AP39" t="n">
-        <v>-1.382176646172837</v>
+        <v>0.3707070707070699</v>
       </c>
       <c r="AQ39" t="n">
-        <v>-6.450826446280985</v>
-      </c>
-      <c r="AR39" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.932323232323256</v>
+      </c>
       <c r="AS39" t="n">
-        <v>3.403497352191842</v>
+        <v>-4.541414141414151</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.878264462809909</v>
-      </c>
-      <c r="AU39" t="inlineStr"/>
-      <c r="AV39" t="inlineStr"/>
+        <v>-2.428571428571427</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>3.464851529386902</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>-143</v>
+      </c>
       <c r="AW39" t="n">
-        <v>-0.5883471074380162</v>
+        <v>-6.459595959595958</v>
       </c>
       <c r="AX39" t="n">
-        <v>-0.08533072823092613</v>
+        <v>-146</v>
       </c>
       <c r="AY39" t="n">
-        <v>-1306799.941338144</v>
-      </c>
-      <c r="AZ39" t="inlineStr"/>
-      <c r="BA39" t="inlineStr"/>
+        <v>-1.509603279562782</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>-78675000</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>1.047619047619065</v>
+      </c>
       <c r="BB39" t="n">
-        <v>-2.013125014146013</v>
-      </c>
-      <c r="BC39" t="inlineStr"/>
+        <v>-3356313.131313131</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>-0.04592116820377723</v>
+      </c>
       <c r="BD39" t="n">
-        <v>-4.550743801652885</v>
-      </c>
-      <c r="BE39" t="inlineStr"/>
+        <v>-1064589.401311801</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>-1.285714285714286</v>
+      </c>
       <c r="BF39" t="n">
-        <v>0.4316528925619778</v>
+        <v>-1.775279518640545</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -7535,8 +7615,8 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">da silva a 
-  usa </t>
+          <t xml:space="preserve">lauziere p 
+  can </t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -7603,34 +7683,30 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>-0.8272727272727274</v>
+        <v>2.727272727272728</v>
       </c>
       <c r="U40" t="n">
-        <v>0.6727272727272727</v>
+        <v>-0.09090909090909083</v>
       </c>
       <c r="V40" t="n">
-        <v>2.727272727272728</v>
+        <v>3.263636363636364</v>
       </c>
       <c r="W40" t="n">
-        <v>-0.09090909090909083</v>
-      </c>
-      <c r="X40" t="n">
-        <v>3.263636363636364</v>
-      </c>
-      <c r="Y40" t="n">
         <v>3.954545454545455</v>
       </c>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-0.1333333333333329</v>
+      </c>
+      <c r="AB40" t="n">
         <v>9.218181818181819</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AC40" t="n">
         <v>-9.218181818181819</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0.5181818181818181</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0.8454545454545455</v>
       </c>
       <c r="AD40" t="n">
         <v>4.845454545454547</v>
@@ -7639,19 +7715,23 @@
         <v>-1.381818181818181</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.5</v>
+        <v>0.5157142857142857</v>
       </c>
       <c r="AG40" t="n">
-        <v>-0.1333333333333329</v>
+        <v>0.2271428571428572</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.5157142857142857</v>
+        <v>0.5181818181818181</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.2271428571428572</v>
-      </c>
-      <c r="AJ40" t="inlineStr"/>
-      <c r="AK40" t="inlineStr"/>
+        <v>0.8454545454545455</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>-0.8272727272727274</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0.6727272727272727</v>
+      </c>
       <c r="AL40" t="n">
         <v>67.87606060606061</v>
       </c>
@@ -7659,47 +7739,55 @@
         <v>68.43979797979799</v>
       </c>
       <c r="AN40" t="n">
-        <v>226704.0863177234</v>
+        <v>-1.589241698737752</v>
       </c>
       <c r="AO40" t="n">
-        <v>-1.683748035191698</v>
+        <v>0.1578512396694216</v>
       </c>
       <c r="AP40" t="n">
-        <v>-1.476902283062117</v>
+        <v>0.9857024793388476</v>
       </c>
       <c r="AQ40" t="n">
-        <v>-0.2830119375573901</v>
-      </c>
-      <c r="AR40" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>-1.880853994490337</v>
+      </c>
       <c r="AS40" t="n">
-        <v>-0.7060100041554698</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>-1.811776859504107</v>
-      </c>
-      <c r="AU40" t="inlineStr"/>
-      <c r="AV40" t="inlineStr"/>
+        <v>1.732736455463723</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AU40" t="n">
+        <v>-1.080110428286016</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>62</v>
+      </c>
       <c r="AW40" t="n">
-        <v>0.1447658402203857</v>
+        <v>-0.2312580348944095</v>
       </c>
       <c r="AX40" t="n">
-        <v>-0.001314081347794538</v>
+        <v>72</v>
       </c>
       <c r="AY40" t="n">
-        <v>-465677.2871354646</v>
-      </c>
-      <c r="AZ40" t="inlineStr"/>
+        <v>-1.550501807905874</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>875000</v>
+      </c>
       <c r="BA40" t="inlineStr"/>
       <c r="BB40" t="n">
-        <v>-1.398217393170228</v>
-      </c>
-      <c r="BC40" t="inlineStr"/>
+        <v>320312.9935720847</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>-0.0282658148898558</v>
+      </c>
       <c r="BD40" t="n">
-        <v>1.573599632690531</v>
+        <v>-503993.3115180654</v>
       </c>
       <c r="BE40" t="inlineStr"/>
       <c r="BF40" t="n">
-        <v>0.8485537190082653</v>
+        <v>-1.607240112339369</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -7716,7 +7804,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">freemon j 
+          <t xml:space="preserve">rivas v 
   usa </t>
         </is>
       </c>
@@ -7780,34 +7868,30 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>-0.8333333333333335</v>
+        <v>-0.8333333333333339</v>
       </c>
       <c r="U41" t="n">
-        <v>0.5833333333333334</v>
+        <v>3.138888888888889</v>
       </c>
       <c r="V41" t="n">
-        <v>-0.8333333333333339</v>
+        <v>-2.638888888888889</v>
       </c>
       <c r="W41" t="n">
-        <v>3.138888888888889</v>
-      </c>
-      <c r="X41" t="n">
-        <v>-2.638888888888889</v>
-      </c>
-      <c r="Y41" t="n">
         <v>-0.1666666666666679</v>
       </c>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-0.116883116883117</v>
+      </c>
+      <c r="AB41" t="n">
         <v>-5.277777777777779</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AC41" t="n">
         <v>5.277777777777779</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>-0.4722222222222223</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>0.1111111111111112</v>
       </c>
       <c r="AD41" t="n">
         <v>-5.111111111111112</v>
@@ -7816,19 +7900,23 @@
         <v>7.111111111111112</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.5</v>
+        <v>-0.6539999999999999</v>
       </c>
       <c r="AG41" t="n">
-        <v>-0.116883116883117</v>
+        <v>1.084857142857143</v>
       </c>
       <c r="AH41" t="n">
-        <v>-0.6539999999999999</v>
+        <v>-0.4722222222222223</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.084857142857143</v>
-      </c>
-      <c r="AJ41" t="inlineStr"/>
-      <c r="AK41" t="inlineStr"/>
+        <v>0.1111111111111112</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>-0.8333333333333335</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0.5833333333333334</v>
+      </c>
       <c r="AL41" t="n">
         <v>68.1710101010101</v>
       </c>
@@ -7836,47 +7924,61 @@
         <v>68.47508417508418</v>
       </c>
       <c r="AN41" t="n">
-        <v>-1126315.734265735</v>
+        <v>2.054622389776014</v>
       </c>
       <c r="AO41" t="n">
-        <v>2.240337516053287</v>
+        <v>0.06363636363636371</v>
       </c>
       <c r="AP41" t="n">
-        <v>-1.1502059568287</v>
+        <v>0.8477272727272727</v>
       </c>
       <c r="AQ41" t="n">
-        <v>-1.997692307692304</v>
-      </c>
-      <c r="AR41" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>2.608080808080814</v>
+      </c>
       <c r="AS41" t="n">
-        <v>0.229312591209208</v>
+        <v>-1.283585858585852</v>
       </c>
       <c r="AT41" t="n">
-        <v>2.785524475524483</v>
-      </c>
-      <c r="AU41" t="inlineStr"/>
-      <c r="AV41" t="inlineStr"/>
+        <v>-4.166666666666668</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0.2458198749994374</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>-78</v>
+      </c>
       <c r="AW41" t="n">
-        <v>0.06643356643356646</v>
+        <v>-2.14065656565657</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.02968835131306546</v>
+        <v>-66</v>
       </c>
       <c r="AY41" t="n">
-        <v>137945.741437187</v>
-      </c>
-      <c r="AZ41" t="inlineStr"/>
-      <c r="BA41" t="inlineStr"/>
+        <v>-1.218623656440798</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>3625000</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>-4.75</v>
+      </c>
       <c r="BB41" t="n">
-        <v>1.527469947829339</v>
-      </c>
-      <c r="BC41" t="inlineStr"/>
+        <v>-1118873.737373738</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>0.02819412662090026</v>
+      </c>
       <c r="BD41" t="n">
-        <v>-1.379720279720289</v>
-      </c>
-      <c r="BE41" t="inlineStr"/>
+        <v>151299.6791979221</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>0</v>
+      </c>
       <c r="BF41" t="n">
-        <v>0.6800699300699264</v>
+        <v>1.384927143545383</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -7893,7 +7995,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">dickerson j 
+          <t xml:space="preserve">de oliveira m 
   usa </t>
         </is>
       </c>
@@ -7961,34 +8063,30 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>0.45</v>
+        <v>-0.8833333333333329</v>
       </c>
       <c r="U42" t="n">
-        <v>-0.5</v>
+        <v>0.2000000000000002</v>
       </c>
       <c r="V42" t="n">
-        <v>-0.8833333333333329</v>
+        <v>1.316666666666666</v>
       </c>
       <c r="W42" t="n">
-        <v>0.2000000000000002</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1.316666666666666</v>
-      </c>
-      <c r="Y42" t="n">
         <v>0.09999999999999964</v>
       </c>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-0.1111111111111107</v>
+      </c>
+      <c r="AB42" t="n">
         <v>2.933333333333337</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="AC42" t="n">
         <v>-2.850000000000001</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>-0.2833333333333332</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>-0.9500000000000002</v>
       </c>
       <c r="AD42" t="n">
         <v>2.25</v>
@@ -7997,19 +8095,23 @@
         <v>1.533333333333333</v>
       </c>
       <c r="AF42" t="n">
-        <v>1</v>
+        <v>-0.1214285714285717</v>
       </c>
       <c r="AG42" t="n">
-        <v>-0.1111111111111107</v>
+        <v>-0.3028571428571427</v>
       </c>
       <c r="AH42" t="n">
-        <v>-0.1214285714285717</v>
+        <v>-0.2833333333333332</v>
       </c>
       <c r="AI42" t="n">
-        <v>-0.3028571428571427</v>
-      </c>
-      <c r="AJ42" t="inlineStr"/>
-      <c r="AK42" t="inlineStr"/>
+        <v>-0.9500000000000002</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="AL42" t="n">
         <v>68.91272727272727</v>
       </c>
@@ -8017,47 +8119,61 @@
         <v>67.04535353535354</v>
       </c>
       <c r="AN42" t="n">
-        <v>1910964.637635092</v>
+        <v>1.123355417686824</v>
       </c>
       <c r="AO42" t="n">
-        <v>1.267380318365937</v>
+        <v>-0.04621212121212093</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.193236760245611</v>
+        <v>-0.146780303030301</v>
       </c>
       <c r="AQ42" t="n">
-        <v>4.146853146853147</v>
-      </c>
-      <c r="AR42" t="inlineStr"/>
+        <v>-4</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>-2.977424242424235</v>
+      </c>
       <c r="AS42" t="n">
-        <v>2.546409868843135</v>
+        <v>2.625946969696969</v>
       </c>
       <c r="AT42" t="n">
-        <v>-3.057088366179272</v>
-      </c>
-      <c r="AU42" t="inlineStr"/>
-      <c r="AV42" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>2.375074302741297</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>-245</v>
+      </c>
       <c r="AW42" t="n">
-        <v>-0.02695486331849928</v>
+        <v>4.043636363636367</v>
       </c>
       <c r="AX42" t="n">
-        <v>-0.1087300351470391</v>
+        <v>-250</v>
       </c>
       <c r="AY42" t="n">
-        <v>529914.9512290233</v>
-      </c>
-      <c r="AZ42" t="inlineStr"/>
-      <c r="BA42" t="inlineStr"/>
+        <v>1.314835961448523</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>1035000</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>-3.5</v>
+      </c>
       <c r="BB42" t="n">
-        <v>2.73630811264605</v>
-      </c>
-      <c r="BC42" t="inlineStr"/>
+        <v>1671316.098484848</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>-0.1202282147676885</v>
+      </c>
       <c r="BD42" t="n">
-        <v>2.64696439923712</v>
-      </c>
-      <c r="BE42" t="inlineStr"/>
+        <v>483501.6170238415</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>0</v>
+      </c>
       <c r="BF42" t="n">
-        <v>-0.2933407501589294</v>
+        <v>2.494763986297258</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8066,7 +8182,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>b9cFuRmG</t>
+          <t>4nbBt7Y9</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -8074,24 +8190,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">ford t 
+          <t xml:space="preserve">fierro r 
   usa </t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">red bull arena
-  harrison  nj </t>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8118,127 +8234,141 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>rJ9D8rzj</t>
+          <t>roEEsq76</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>86yPt28f</t>
+          <t>jBBpU7Y0</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="P43" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="Q43" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="R43" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>1.1</v>
+        <v>-0.7678571428571432</v>
       </c>
       <c r="U43" t="n">
-        <v>-1</v>
+        <v>1.053571428571429</v>
       </c>
       <c r="V43" t="n">
-        <v>1.5</v>
+        <v>5.857142857142857</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>-1.800000000000001</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>-2.1</v>
-      </c>
+        <v>-3.732142857142858</v>
+      </c>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="n">
-        <v>-5.399999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AA43" t="n">
-        <v>5.399999999999999</v>
+        <v>0.1428571428571432</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.8</v>
+        <v>-7.303571428571431</v>
       </c>
       <c r="AC43" t="n">
-        <v>-0.7000000000000002</v>
+        <v>7.303571428571431</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.300000000000001</v>
+        <v>-0.4642857142857135</v>
       </c>
       <c r="AE43" t="n">
-        <v>-1.1</v>
+        <v>7.232142857142858</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>-0.4908333333333332</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.1111111111111107</v>
+        <v>0.5641666666666663</v>
       </c>
       <c r="AH43" t="n">
-        <v>-0.2228571428571429</v>
+        <v>-1.053571428571428</v>
       </c>
       <c r="AI43" t="n">
-        <v>-0.02857142857142891</v>
-      </c>
-      <c r="AJ43" t="inlineStr"/>
-      <c r="AK43" t="inlineStr"/>
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>-0.2678571428571428</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0.2678571428571429</v>
+      </c>
       <c r="AL43" t="n">
-        <v>67.83626262626262</v>
+        <v>68.47357954545456</v>
       </c>
       <c r="AM43" t="n">
-        <v>68.11545454545454</v>
+        <v>67.50227272727274</v>
       </c>
       <c r="AN43" t="n">
-        <v>1516578.512396694</v>
+        <v>1.372030077359824</v>
       </c>
       <c r="AO43" t="n">
-        <v>0.8281159900318471</v>
+        <v>0.09684343434343434</v>
       </c>
       <c r="AP43" t="n">
-        <v>-1.831380276471407</v>
+        <v>0.7053391053391067</v>
       </c>
       <c r="AQ43" t="n">
-        <v>3.996694214876044</v>
-      </c>
-      <c r="AR43" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>0.8393939393939149</v>
+      </c>
       <c r="AS43" t="n">
-        <v>-0.01647152816862274</v>
+        <v>-0.1049783549783712</v>
       </c>
       <c r="AT43" t="n">
-        <v>-5.238016528925613</v>
-      </c>
-      <c r="AU43" t="inlineStr"/>
-      <c r="AV43" t="inlineStr"/>
+        <v>-12</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>1.518589328150437</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>143</v>
+      </c>
       <c r="AW43" t="n">
-        <v>0.01735537190082637</v>
+        <v>-0.8510101010101039</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.05438137292601986</v>
+        <v>151</v>
       </c>
       <c r="AY43" t="n">
-        <v>826661.9968973692</v>
-      </c>
-      <c r="AZ43" t="inlineStr"/>
-      <c r="BA43" t="inlineStr"/>
+        <v>0.3485520072019597</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>9425000</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>-13.66666666666666</v>
+      </c>
       <c r="BB43" t="n">
-        <v>1.948098543149719</v>
-      </c>
-      <c r="BC43" t="inlineStr"/>
+        <v>-296803.751803752</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>0.1222343424549308</v>
+      </c>
       <c r="BD43" t="n">
-        <v>1.652066115702482</v>
-      </c>
-      <c r="BE43" t="inlineStr"/>
+        <v>-46141.19860597514</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>0</v>
+      </c>
       <c r="BF43" t="n">
-        <v>-3.336363636363636</v>
+        <v>1.795933309221127</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -8247,7 +8377,7 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>4nbBt7Y9</t>
+          <t>fiHVGBod</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -8255,24 +8385,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">de oliveira m 
+          <t xml:space="preserve">freemon j 
   usa </t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">gillette stadium
-  foxborough  ma </t>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>Szrwix67</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -8299,19 +8429,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>roEEsq76</t>
+          <t>lAVQ9RGh</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>jBBpU7Y0</t>
+          <t>022mBmSn</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>-8</v>
+        <v>1</v>
       </c>
       <c r="P44" t="n">
-        <v>-8</v>
+        <v>1</v>
       </c>
       <c r="Q44" t="n">
         <v>-1</v>
@@ -8323,103 +8453,117 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>-0.2678571428571428</v>
+        <v>-2.590909090909091</v>
       </c>
       <c r="U44" t="n">
-        <v>0.2678571428571429</v>
+        <v>2.654545454545454</v>
       </c>
       <c r="V44" t="n">
-        <v>-0.7678571428571432</v>
+        <v>1.554545454545455</v>
       </c>
       <c r="W44" t="n">
-        <v>1.053571428571429</v>
-      </c>
-      <c r="X44" t="n">
-        <v>5.857142857142857</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>-3.732142857142858</v>
-      </c>
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="n">
-        <v>-7.303571428571431</v>
+        <v>-0.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>7.303571428571431</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="AB44" t="n">
-        <v>-1.053571428571428</v>
+        <v>-4.418181818181822</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.3571428571428572</v>
+        <v>4.418181818181822</v>
       </c>
       <c r="AD44" t="n">
-        <v>-0.4642857142857135</v>
+        <v>-6.154545454545453</v>
       </c>
       <c r="AE44" t="n">
-        <v>7.232142857142858</v>
+        <v>4.081818181818182</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.5</v>
+        <v>-0.2269642857142857</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.1428571428571432</v>
+        <v>0.7108928571428572</v>
       </c>
       <c r="AH44" t="n">
-        <v>-0.4908333333333332</v>
+        <v>-0.05454545454545467</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.5641666666666663</v>
-      </c>
-      <c r="AJ44" t="inlineStr"/>
-      <c r="AK44" t="inlineStr"/>
+        <v>0.6818181818181819</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0.0636363636363636</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>-0.1000000000000001</v>
+      </c>
       <c r="AL44" t="n">
-        <v>68.47357954545456</v>
+        <v>68.36909090909091</v>
       </c>
       <c r="AM44" t="n">
-        <v>67.50227272727274</v>
+        <v>67.4854453627181</v>
       </c>
       <c r="AN44" t="n">
-        <v>-18406.63580246922</v>
+        <v>0.6252320305547272</v>
       </c>
       <c r="AO44" t="n">
-        <v>1.001967557895199</v>
+        <v>-0.0363636363636366</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.4697118745924911</v>
+        <v>-2.088888888888881</v>
       </c>
       <c r="AQ44" t="n">
-        <v>-0.8788019079685654</v>
-      </c>
-      <c r="AR44" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>-4.408631772268137</v>
+      </c>
       <c r="AS44" t="n">
-        <v>1.20542111508917</v>
+        <v>-3.540036730945815</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.5441077441076914</v>
-      </c>
-      <c r="AU44" t="inlineStr"/>
-      <c r="AV44" t="inlineStr"/>
+        <v>-3.800000000000001</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>-1.222280663125677</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>-233</v>
+      </c>
       <c r="AW44" t="n">
-        <v>0.09719416386083068</v>
+        <v>-1.329843893480273</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.1086527488488274</v>
+        <v>-232</v>
       </c>
       <c r="AY44" t="n">
-        <v>-451048.4717197607</v>
-      </c>
-      <c r="AZ44" t="inlineStr"/>
-      <c r="BA44" t="inlineStr"/>
+        <v>-0.4422169513409528</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>-14575000</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>3.5</v>
+      </c>
       <c r="BB44" t="n">
-        <v>1.187502740009677</v>
-      </c>
-      <c r="BC44" t="inlineStr"/>
+        <v>-1631741.046831956</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>0.02569634370824736</v>
+      </c>
       <c r="BD44" t="n">
-        <v>0.5061447811447692</v>
-      </c>
-      <c r="BE44" t="inlineStr"/>
+        <v>-236651.1420849033</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>-0.3999999999999999</v>
+      </c>
       <c r="BF44" t="n">
-        <v>1.212177328843996</v>
+        <v>-0.2849412696384377</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -8428,7 +8572,7 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>fiHVGBod</t>
+          <t>b9cFuRmG</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
@@ -8436,24 +8580,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">da silva a 
+          <t xml:space="preserve">badawi m 
   usa </t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">saputo stadium
-  montreal  qc </t>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>zV5YmQAr</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Szrwix67</t>
+          <t>O6hjfSXE</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -8480,127 +8624,141 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>lAVQ9RGh</t>
+          <t>rJ9D8rzj</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>022mBmSn</t>
+          <t>86yPt28f</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="P45" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="Q45" t="n">
+        <v>4</v>
+      </c>
+      <c r="R45" t="n">
+        <v>4</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>-1.800000000000001</v>
+      </c>
+      <c r="W45" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0.1111111111111107</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>-5.399999999999999</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>5.399999999999999</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>2.300000000000001</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>-0.2228571428571429</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>-0.02857142857142891</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>-0.7000000000000002</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK45" t="n">
         <v>-1</v>
       </c>
-      <c r="R45" t="n">
+      <c r="AL45" t="n">
+        <v>67.83626262626262</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>68.11545454545454</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>0.9178329598790071</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0.00818181818181829</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>-3.379999999999999</v>
+      </c>
+      <c r="AQ45" t="n">
         <v>-1</v>
       </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0.0636363636363636</v>
-      </c>
-      <c r="U45" t="n">
-        <v>-0.1000000000000001</v>
-      </c>
-      <c r="V45" t="n">
-        <v>-2.590909090909091</v>
-      </c>
-      <c r="W45" t="n">
-        <v>2.654545454545454</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.554545454545455</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>0.3000000000000007</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>-4.418181818181822</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>4.418181818181822</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>-0.05454545454545467</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0.6818181818181819</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>-6.154545454545453</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>4.081818181818182</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>-0.2269642857142857</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>0.7108928571428572</v>
-      </c>
-      <c r="AJ45" t="inlineStr"/>
-      <c r="AK45" t="inlineStr"/>
-      <c r="AL45" t="n">
-        <v>68.36909090909091</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>67.4854453627181</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>-1702994.031221304</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>0.6833117042514658</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>-0.6092034435808671</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>-1.67205387205388</v>
-      </c>
-      <c r="AR45" t="inlineStr"/>
+      <c r="AR45" t="n">
+        <v>-5.411818181818205</v>
+      </c>
       <c r="AS45" t="n">
-        <v>-1.281334343927124</v>
+        <v>1.575454545454548</v>
       </c>
       <c r="AT45" t="n">
-        <v>-4.368587389041977</v>
-      </c>
-      <c r="AU45" t="inlineStr"/>
-      <c r="AV45" t="inlineStr"/>
+        <v>-4.699999999999999</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>-0.02451254287807103</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>-73</v>
+      </c>
       <c r="AW45" t="n">
-        <v>-0.050137741046832</v>
+        <v>3.864545454545464</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.02656271197414184</v>
+        <v>-64</v>
       </c>
       <c r="AY45" t="n">
-        <v>-254493.1610636225</v>
-      </c>
-      <c r="AZ45" t="inlineStr"/>
-      <c r="BA45" t="inlineStr"/>
+        <v>-1.443930068824415</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>2525000</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>-7.966666666666669</v>
+      </c>
       <c r="BB45" t="n">
-        <v>-0.3815988276918176</v>
-      </c>
-      <c r="BC45" t="inlineStr"/>
+        <v>1450690.90909091</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>0.05112385804470865</v>
+      </c>
       <c r="BD45" t="n">
-        <v>-3.741727884909707</v>
-      </c>
-      <c r="BE45" t="inlineStr"/>
+        <v>775953.5162802008</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
       <c r="BF45" t="n">
-        <v>-2.070117845117842</v>
+        <v>1.733189727387973</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -8617,8 +8775,8 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">simon n 
-  usa </t>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -8685,34 +8843,30 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>0.4666666666666668</v>
+        <v>0.4333333333333331</v>
       </c>
       <c r="U46" t="n">
-        <v>-0.1666666666666667</v>
+        <v>0.9222222222222225</v>
       </c>
       <c r="V46" t="n">
-        <v>0.4333333333333331</v>
+        <v>2.300000000000001</v>
       </c>
       <c r="W46" t="n">
-        <v>0.9222222222222225</v>
-      </c>
-      <c r="X46" t="n">
-        <v>2.300000000000001</v>
-      </c>
-      <c r="Y46" t="n">
         <v>0.4777777777777779</v>
       </c>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AB46" t="n">
         <v>2.177777777777777</v>
       </c>
-      <c r="AA46" t="n">
+      <c r="AC46" t="n">
         <v>-2.177777777777777</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0.4666666666666668</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0.04444444444444451</v>
       </c>
       <c r="AD46" t="n">
         <v>1.477777777777778</v>
@@ -8721,19 +8875,23 @@
         <v>0.3777777777777782</v>
       </c>
       <c r="AF46" t="n">
-        <v>-0.5</v>
+        <v>0.6799999999999999</v>
       </c>
       <c r="AG46" t="n">
-        <v>-0.25</v>
+        <v>-0.3033333333333335</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.6799999999999999</v>
+        <v>0.4666666666666668</v>
       </c>
       <c r="AI46" t="n">
-        <v>-0.3033333333333335</v>
-      </c>
-      <c r="AJ46" t="inlineStr"/>
-      <c r="AK46" t="inlineStr"/>
+        <v>0.04444444444444451</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0.4666666666666668</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
       <c r="AL46" t="n">
         <v>68.17946127946128</v>
       </c>
@@ -8741,61 +8899,61 @@
         <v>69.49181818181816</v>
       </c>
       <c r="AN46" t="n">
-        <v>-1414782.407407407</v>
+        <v>2.270132167005897</v>
       </c>
       <c r="AO46" t="n">
-        <v>2.087320066669164</v>
+        <v>-0.2545454545454546</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.158425591996718</v>
+        <v>-3.645656565656569</v>
       </c>
       <c r="AQ46" t="n">
-        <v>-0.9163350678502127</v>
+        <v>-4</v>
       </c>
       <c r="AR46" t="n">
+        <v>2.905208333333348</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>-3.886919191919176</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>-1.199999999999999</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>-3.745100970282017</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>-259</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>-0.9991414141414054</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>-294</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>1.213378130671174</v>
+      </c>
+      <c r="AZ46" t="n">
         <v>-4390000</v>
       </c>
-      <c r="AS46" t="n">
-        <v>-3.853662739790018</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>2.976094276094273</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>-259</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>-294</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>-0.2314049586776861</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>-0.1537475799367158</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>-1274245.886599623</v>
-      </c>
-      <c r="AZ46" t="n">
+      <c r="BA46" t="n">
         <v>-0.4000000000000057</v>
       </c>
-      <c r="BA46" t="n">
-        <v>-4</v>
-      </c>
       <c r="BB46" t="n">
-        <v>-2.039403701492326</v>
+        <v>-1469180.208333333</v>
       </c>
       <c r="BC46" t="n">
-        <v>-1.199999999999999</v>
+        <v>-0.1262651950732445</v>
       </c>
       <c r="BD46" t="n">
-        <v>-3.805925415773885</v>
+        <v>-1215388.691299278</v>
       </c>
       <c r="BE46" t="n">
         <v>0</v>
       </c>
       <c r="BF46" t="n">
-        <v>-3.567291602897662</v>
+        <v>-1.853363287898901</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>

--- a/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
@@ -525,94 +525,94 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_interceptions</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -625,97 +625,97 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
@@ -727,32 +727,32 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>4MWOCVE5</t>
+          <t>p0lFJwSk</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45486.97916666666</v>
+        <v>45493.98958333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">da silva a 
+          <t xml:space="preserve">dickerson j 
   usa </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">paypal park
-  san jose  ca </t>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>U3ebh62R</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>bm8usLzB</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -779,145 +779,141 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>bFuhdIb3</t>
+          <t>2PIEeC7j</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>WWvwigh8</t>
+          <t>rXawJi8t</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>-11</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>-11</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
+        <v>-1.133333333333333</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-0.03333333333333321</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>-5.666666666666666</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>6.066666666666668</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.4166666666666665</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-3.600000000000001</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.600000000000001</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-3.333333333333333</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2.766666666666667</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-0.3999999999999999</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-2.066666666666666</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-2.366666666666665</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>67.61902356902357</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>67.35999999999999</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.2373737373737583</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>2.147619047619045</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>90088.6916100604</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-1.970479874218601</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>3725000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.2183747800486344</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.027994227994228</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.06088684277538747</v>
+      </c>
+      <c r="AX2" t="n">
         <v>2</v>
       </c>
-      <c r="U2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-0.8571428571428572</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.4047619047619051</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-0.07142857142857117</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-0.5952380952380958</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-7.142857142857142</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-0.1904761904761916</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-0.7857142857142858</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.7857142857142858</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-3.714285714285715</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>3.714285714285715</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.4761904761904763</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>6.523809523809526</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>69.59040404040404</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>66.52763347763347</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-0.06031149301826</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-66</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>3.563203463203465</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-0.04025974025974022</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>-0.5673160173160134</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1430729.437229438</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.654329004329</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>5.166666666666657</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>559504.4735285417</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3.032722722956457</v>
-      </c>
       <c r="AY2" t="n">
-        <v>-0.1666666666666679</v>
+        <v>0.2324235421926915</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-68</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.037709893263177</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-1275000</v>
+        <v>-0.3997113997114035</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.182021111266778</v>
+        <v>-2.404167455762575</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.6194136998811928</v>
+        <v>-5.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.07077922077922949</v>
+        <v>647337.6623376617</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>0.02857142857142847</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -926,32 +922,32 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CEEHEipg</t>
+          <t>MHXbihN8</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45486.97916666666</v>
+        <v>45493.97916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">szpala l 
+          <t xml:space="preserve">simon n 
   usa </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bmo stadium
-  los angeles  ca </t>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>txUJt9AR</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -978,12 +974,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>UL7r7duf</t>
+          <t>Sd7snoa0</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>xA45kovo</t>
+          <t>86yPt28f</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -1001,118 +997,118 @@
       <c r="S3" t="n">
         <v>0</v>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="n">
-        <v>-0.1666666666666665</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.1666666666666666</v>
-      </c>
+      <c r="T3" t="n">
+        <v>0.5333333333333334</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-6.199999999999999</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>5.133333333333335</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.666666666666667</v>
+        <v>0.4666666666666663</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.333333333333334</v>
+        <v>-14.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>-4.166666666666668</v>
+        <v>14.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-0.1333333333333329</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AF3" t="n">
         <v>0.1666666666666665</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.3333333333333334</v>
+        <v>-0.1333333333333334</v>
       </c>
       <c r="AH3" t="n">
-        <v>-8</v>
+        <v>-1.666666666666666</v>
       </c>
       <c r="AI3" t="n">
-        <v>8</v>
+        <v>-5.533333333333333</v>
       </c>
       <c r="AJ3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.833333333333332</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>68.39676767676767</v>
+        <v>65.75454545454545</v>
       </c>
       <c r="AM3" t="n">
-        <v>66.32420033670034</v>
+        <v>66.25999999999999</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.007246376811594013</v>
+        <v>-4.143939393939405</v>
       </c>
       <c r="AO3" t="n">
-        <v>66</v>
+        <v>0.0954545454545439</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.704545454545453</v>
+        <v>10</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.375757575757576</v>
+        <v>266676.5763149447</v>
       </c>
       <c r="AR3" t="n">
-        <v>1</v>
+        <v>-0.1558672508598491</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.580303030303021</v>
+        <v>425000</v>
       </c>
       <c r="AT3" t="n">
-        <v>-57878.78787878808</v>
+        <v>-1.060851148933352</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.010606060606051</v>
+        <v>0.09090909090909349</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AW3" t="n">
-        <v>-59617.18404972879</v>
+        <v>-0.02976190476190466</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.901667355567596</v>
+        <v>6</v>
       </c>
       <c r="AY3" t="n">
-        <v>-15.5</v>
+        <v>1.599816347036707</v>
       </c>
       <c r="AZ3" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.4975103919477313</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>3150000</v>
+        <v>-1.692424242424238</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.155067143238512</v>
+        <v>1.724847551530139</v>
       </c>
       <c r="BD3" t="n">
-        <v>-2.211562218211782</v>
+        <v>6</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.8863636363636545</v>
+        <v>593181.8181818181</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>-0.1818181818181821</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1121,32 +1117,32 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6yELDBaa</t>
+          <t>vNmJIcsd</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45486.97569444445</v>
+        <v>45493.97916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">dickerson j 
+          <t xml:space="preserve">gonzalez g  jr 
   usa </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">providence park
-  portland  or </t>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>bm8usLzB</t>
+          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>W0ealpQl</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1173,141 +1169,139 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>CfE5JcGF</t>
+          <t>tOpyQa24</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>l6eEjGlO</t>
+          <t>rXawJi8t</t>
         </is>
       </c>
       <c r="O4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="U4" t="n">
         <v>-1</v>
       </c>
-      <c r="P4" t="n">
+      <c r="V4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-6.666666666666668</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0.1666666666666665</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.333333333333336</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-2.333333333333336</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-1.833333333333334</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-0.666666666666667</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.8333333333333335</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-1.666666666666668</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>67.25818181818181</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>68.28767676767677</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-2.012590187590177</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-1.985750360750373</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>565857.9685826893</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0.1653769676513512</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-400000</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-1.246422982895382</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-3.102020202020199</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-68</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.125957556935818</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-58</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-0.557140372618079</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="n">
         <v>-1</v>
       </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>3</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="n">
-        <v>0.2000000000000002</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-0.2000000000000002</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.4000000000000004</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-2.199999999999999</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-2.800000000000001</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-0.2000000000000002</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.3999999999999999</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-0.2000000000000001</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>2.600000000000001</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>67.78</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>67.07818181818182</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>-63</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>-0.5054545454545405</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1.696363636363639</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>867945.4545454548</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.041818181818201</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>248960.5967259284</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>3.374640028164066</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>-66</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0.9108079563457174</v>
-      </c>
       <c r="BB4" t="n">
-        <v>75000</v>
+        <v>-1.683513708513704</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.4408801267382501</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>-0.07752508361207333</v>
-      </c>
+        <v>-0.52837107833912</v>
+      </c>
+      <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="n">
-        <v>-0.01636363636367832</v>
+        <v>-1873524.891774891</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>-0.1927128427128426</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1316,15 +1310,15 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YNFDFXUn</t>
+          <t>69kBKJCq</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45486.9375</v>
+        <v>45493.9375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ford t 
+          <t xml:space="preserve">gonzalez g  jr 
   usa </t>
         </is>
       </c>
@@ -1341,7 +1335,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>W0ealpQl</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1368,158 +1362,158 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lAVQ9RGh</t>
+          <t>2PIEeC7j</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>rJ9D8rzj</t>
+          <t>rXawJi8t</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>-12</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>-12</v>
       </c>
       <c r="Q5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.3666666666666665</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="n">
+        <v>-1.933333333333334</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.766666666666666</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-0.4666666666666663</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-3.566666666666663</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.566666666666663</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0.2000000000000002</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.2666666666666668</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-0.2333333333333332</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.3666666666666654</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>67.16632996632997</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>69.49636363636364</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.9035353535353465</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-2.422943722943714</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-731249.5467147724</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-4.310472699905521</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-8275000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.308867236972844</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-0.6921356421356393</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-278</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-266</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-0.2434049968047987</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-0.268398268398272</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>-5.279492049122638</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-4.399999999999999</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>-390134.5598845598</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
         <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-0.7000000000000002</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.7666666666666671</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-4.066666666666666</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-1.200000000000003</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.200000000000003</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-6.133333333333335</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>4.233333333333334</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>67.04966329966329</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>67.12949494949495</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-0.06000000000000005</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>-103</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-3.102424242424249</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.205454545454543</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>-125725.757575758</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0.4393939393939235</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>-933395.3284472467</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>-4.159996606595065</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>2.666666666666668</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-133</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>-1.579389098634625</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>500000</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>-2.322139812446707</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0.1531808278867004</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>-0.7263636363636579</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>nXtecjFI</t>
+          <t>h29zRLZF</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45486.89583333334</v>
+        <v>45493.89583333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">marrufo j 
+          <t xml:space="preserve">rivas v 
   usa </t>
         </is>
       </c>
@@ -1536,7 +1530,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>6P5S63Ah</t>
+          <t>QJF7WTFB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1563,128 +1557,142 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>KtuTuMN0</t>
+          <t>WWvwigh8</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>tOpyQa24</t>
+          <t>022mBmSn</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="n">
-        <v>-1.366666666666666</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="T6" t="n">
+        <v>-0.5999999999999999</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-4.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-5.800000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.5999999999999996</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.4</v>
+        <v>22</v>
       </c>
       <c r="AC6" t="n">
-        <v>-1.366666666666665</v>
+        <v>-22.00000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.5</v>
+        <v>-2.399999999999999</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.1499999999999999</v>
+        <v>-2.8</v>
       </c>
       <c r="AF6" t="n">
-        <v>-1.266666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.233333333333333</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="AH6" t="n">
-        <v>-5.033333333333339</v>
+        <v>4</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.033333333333339</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-7.433333333333334</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.866666666666665</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>67.09797979797979</v>
+        <v>66.87575757575758</v>
       </c>
       <c r="AM6" t="n">
-        <v>67.17636363636365</v>
+        <v>69.47353535353537</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.08726682702066313</v>
-      </c>
-      <c r="AO6" t="inlineStr"/>
+        <v>-1.421212121212108</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-3.516666666666666</v>
+      </c>
       <c r="AP6" t="n">
-        <v>-4.77882154882154</v>
+        <v>-1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.03626262626262622</v>
-      </c>
-      <c r="AR6" t="inlineStr"/>
+        <v>-947968.8040273878</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2.857060112734661</v>
+      </c>
       <c r="AS6" t="n">
-        <v>1.292289562289557</v>
+        <v>13850000</v>
       </c>
       <c r="AT6" t="n">
-        <v>-43064.8148148146</v>
+        <v>-1.247186663506994</v>
       </c>
       <c r="AU6" t="n">
-        <v>-2.1947138047138</v>
-      </c>
-      <c r="AV6" t="inlineStr"/>
+        <v>0.3545454545454447</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-57</v>
+      </c>
       <c r="AW6" t="n">
-        <v>-1391932.355732148</v>
+        <v>0.1258452491668605</v>
       </c>
       <c r="AX6" t="n">
-        <v>-1.881568001596776</v>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
+        <v>-57</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-3.922334139645514</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1</v>
+      </c>
       <c r="BA6" t="n">
-        <v>4.224470392021544</v>
-      </c>
-      <c r="BB6" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>2.515151515151505</v>
+      </c>
       <c r="BC6" t="n">
-        <v>-6.072003596124461</v>
+        <v>-0.9161483763465839</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.571442949160371</v>
+        <v>-5.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.7801010101009638</v>
-      </c>
-      <c r="BF6" t="inlineStr"/>
+        <v>164507.5757575759</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0.2000000000000002</v>
+      </c>
       <c r="BG6" t="n">
         <v>0</v>
       </c>
@@ -1692,32 +1700,32 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0zoadAUO</t>
+          <t>nP8vQukM</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45486.89583333334</v>
+        <v>45493.89583333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">mendoza r 
+          <t xml:space="preserve">da silva a 
   usa </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">soldier field
-  chicago  il </t>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1744,169 +1752,169 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>bFuhdIb3</t>
+          <t>Sd7snoa0</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>dp6AQn9c</t>
+          <t>WSL0wFD4</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-8</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>-8</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="n">
-        <v>0.7000000000000002</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.5333333333333334</v>
-      </c>
+      <c r="T7" t="n">
+        <v>0.2380952380952381</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.7857142857142858</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.261904761904763</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0.2619047619047628</v>
       </c>
       <c r="Z7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.4047619047619051</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-2.80952380952381</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.80952380952381</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-0.6904761904761898</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-1.619047619047619</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.047619047619047</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-0.8809523809523807</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.690476190476192</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.0952380952380949</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>67.26464646464646</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>66.60000000000001</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-1.724206349206327</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-1.864213564213571</v>
+      </c>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="n">
+        <v>-48028.0649067926</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.923746218375012</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>-1.32667707555251</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-1.500360750360741</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>137</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.03804916703523542</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>129</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-2.033776817363105</v>
+      </c>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="n">
         <v>2</v>
       </c>
-      <c r="AA7" t="n">
-        <v>-0.9666666666666668</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.933333333333334</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-0.2666666666666657</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0.7000000000000002</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-2.033333333333339</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>2.033333333333339</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>-1.333333333333334</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0.1333333333333346</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>67.85777777777777</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>68.28888888888889</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>337</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>-0.05353535353536643</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0.09090909090909105</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.101010101010097</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>697652.7777777778</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0.9666666666666686</v>
-      </c>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="n">
-        <v>119172.545836516</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>2.421486715898489</v>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="n">
-        <v>351</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>3.984228206434082</v>
-      </c>
       <c r="BB7" t="n">
-        <v>5575000</v>
+        <v>1.629599567099564</v>
       </c>
       <c r="BC7" t="n">
-        <v>-2.615075120957485</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0.05435468126646015</v>
-      </c>
+        <v>2.098175044929562</v>
+      </c>
+      <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="n">
-        <v>0.1381313131313107</v>
-      </c>
-      <c r="BF7" t="inlineStr"/>
+        <v>-897023.0880230882</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>-0.1274531024531023</v>
+      </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EwZtLg7P</t>
+          <t>QF7rPa4S</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45486.89583333334</v>
+        <v>45493.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">touchan r 
+          <t xml:space="preserve">simon n 
   usa </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">toyota stadium
-  frisco  tx </t>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>U3ebh62R</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1933,138 +1941,138 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>jBBpU7Y0</t>
+          <t>UFWZoX9L</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>UFWZoX9L</t>
+          <t>86yPt28f</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="P8" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="n">
-        <v>-0.02380952380952372</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.166666666666667</v>
-      </c>
+      <c r="T8" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.166666666666667</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.333333333333334</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>-4.666666666666666</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.2142857142857144</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.071428571428571</v>
+        <v>-0.166666666666667</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.261904761904763</v>
+        <v>-1.666666666666671</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.595238095238095</v>
+        <v>1.666666666666671</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.3333333333333335</v>
+        <v>-0.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>-1.214285714285714</v>
+        <v>-0.3333333333333334</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.214285714285714</v>
+        <v>0.1666666666666665</v>
       </c>
       <c r="AH8" t="n">
-        <v>-2.928571428571431</v>
+        <v>4.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.928571428571431</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>-1.047619047619047</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>67.62467532467532</v>
+        <v>68.64848484848484</v>
       </c>
       <c r="AM8" t="n">
-        <v>67.53030303030305</v>
+        <v>68.55404040404041</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.0248083443903877</v>
+        <v>1.2376623376623</v>
       </c>
       <c r="AO8" t="n">
-        <v>342</v>
+        <v>-2.007792207792193</v>
       </c>
       <c r="AP8" t="n">
-        <v>-3.823178210678208</v>
+        <v>0.75</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.03290043290043299</v>
+        <v>-342170.2870621935</v>
       </c>
       <c r="AR8" t="n">
-        <v>5</v>
+        <v>-1.931086539879111</v>
       </c>
       <c r="AS8" t="n">
-        <v>-0.1306577681577714</v>
+        <v>495000</v>
       </c>
       <c r="AT8" t="n">
-        <v>-946466.9011544003</v>
+        <v>-3.464827825867189</v>
       </c>
       <c r="AU8" t="n">
-        <v>-3.658814333814334</v>
+        <v>-3.585714285714275</v>
       </c>
       <c r="AV8" t="n">
-        <v>-2</v>
+        <v>126</v>
       </c>
       <c r="AW8" t="n">
-        <v>-578009.2817707483</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-2.007247178047415</v>
+        <v>128</v>
       </c>
       <c r="AY8" t="n">
-        <v>-7.833333333333332</v>
+        <v>0.5560359933447074</v>
       </c>
       <c r="AZ8" t="n">
-        <v>386</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.366044040874094</v>
+        <v>2</v>
       </c>
       <c r="BB8" t="n">
-        <v>24150000</v>
+        <v>-0.8350649350649348</v>
       </c>
       <c r="BC8" t="n">
-        <v>-2.527780790910086</v>
+        <v>-2.335666108548693</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.900646823114499</v>
+        <v>5.25</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.945141895141859</v>
+        <v>-1337584.415584416</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>
@@ -2076,32 +2084,32 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>GnL8GDFt</t>
+          <t>b3GRSs53</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45486.89583333334</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">freemon j 
+          <t xml:space="preserve">szpala l 
   usa </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">shell energy stadium
-  houston  tx </t>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2128,141 +2136,141 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>rXawJi8t</t>
+          <t>EgT3xN3S</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>UFWZoX9L</t>
+          <t>dp6AQn9c</t>
         </is>
       </c>
       <c r="O9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-3</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>-3</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>-5</v>
-      </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="n">
-        <v>1.033333333333333</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-1.066666666666666</v>
-      </c>
+      <c r="T9" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.1666666666666665</v>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.666666666666666</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.766666666666666</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.2666666666666666</v>
+        <v>0.4666666666666663</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.1333333333333346</v>
+        <v>-4.166666666666664</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.266666666666666</v>
+        <v>4.166666666666664</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.5</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.3500000000000001</v>
+        <v>-0.666666666666667</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.6</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AG9" t="n">
-        <v>-2</v>
+        <v>-0.8333333333333333</v>
       </c>
       <c r="AH9" t="n">
-        <v>9.100000000000001</v>
+        <v>-1.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>-9.100000000000001</v>
+        <v>-0.1666666666666679</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.266666666666666</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.8000000000000007</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>66.69070707070708</v>
+        <v>66.81868686868687</v>
       </c>
       <c r="AM9" t="n">
-        <v>69.23703703703704</v>
+        <v>67.85454545454546</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.03571428571428559</v>
+        <v>-2.742923280423298</v>
       </c>
       <c r="AO9" t="n">
-        <v>-54</v>
+        <v>0.2217592592592439</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.087878787878793</v>
+        <v>5.25</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.1818181818181821</v>
+        <v>1639632.975811181</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1</v>
+        <v>3.811251773436645</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.48030303030303</v>
+        <v>-2920000</v>
       </c>
       <c r="AT9" t="n">
-        <v>784356.060606061</v>
+        <v>-2.202058074674028</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.042424242424246</v>
+        <v>3.257341269841277</v>
       </c>
       <c r="AV9" t="n">
-        <v>-10.66666666666666</v>
+        <v>-202</v>
       </c>
       <c r="AW9" t="n">
-        <v>-14116.28121881862</v>
+        <v>0.2925099684142431</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.05910996587802231</v>
+        <v>-184</v>
       </c>
       <c r="AY9" t="n">
-        <v>-4.333333333333332</v>
+        <v>-1.115833356754095</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-51</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.7859597095894024</v>
+        <v>-3</v>
       </c>
       <c r="BB9" t="n">
-        <v>705000</v>
+        <v>3.213227513227508</v>
       </c>
       <c r="BC9" t="n">
-        <v>-1.438177562405585</v>
+        <v>2.74983246567097</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.9467315988180189</v>
+        <v>-1.25</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.04090909090911055</v>
+        <v>1029388.558201058</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>0.1142857142857143</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2271,32 +2279,32 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zPi4VA0k</t>
+          <t>jix3jCxF</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45486.89583333334</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">lauziere p 
-  can </t>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">citypark
-  st  louis  mo </t>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>K2dlua5N</t>
+          <t>zsdfgnmL</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2323,169 +2331,175 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lAVQ9RGh</t>
+          <t>rJ9D8rzj</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Sd7snoa0</t>
+          <t>xA45kovo</t>
         </is>
       </c>
       <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.8333333333333339</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-2.166666666666666</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-2.833333333333334</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>67.37563131313131</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>68.61060606060606</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-2.937662337662346</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>2.983116883116864</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-270682.9045015138</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.224515292560401</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-850000</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.5485862925712297</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.01298701298701133</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-71</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-0.06792875044754765</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-59</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>2.400941748310188</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
         <v>-1</v>
       </c>
-      <c r="P10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="n">
-        <v>-0.8333333333333333</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.3333333333333335</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0.5666666666666673</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.4000000000000004</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.766666666666666</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0.3000000000000007</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>-0.4500000000000002</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>-0.7333333333333333</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0.7666666666666666</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>4.200000000000003</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>-4.200000000000003</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>5.566666666666668</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>-2.733333333333334</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>65.93333333333334</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>66.52000000000001</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0.01960784313725483</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>-137</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>-0.3008417508417409</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0.174074074074074</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>-0.5991919191919202</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>-364867.0033670033</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>-1.653063973063979</v>
-      </c>
-      <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="n">
-        <v>-190250.1708817497</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>-3.036800155468875</v>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="n">
-        <v>-139</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>-1.268208355112375</v>
-      </c>
       <c r="BB10" t="n">
-        <v>-2600000</v>
+        <v>-3.040259740259742</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0.5945311138809615</v>
+        <v>2.375340407295283</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.335485036119707</v>
+        <v>6</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.422255892255862</v>
-      </c>
-      <c r="BF10" t="inlineStr"/>
+        <v>-1372480.519480519</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>-0.2363636363636363</v>
+      </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>GvBXzXxS</t>
+          <t>h6Py6Kcj</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45486.85416666666</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">unkel t 
-  usa </t>
+          <t xml:space="preserve">dujic f 
+  can </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">saputo stadium
-  montreal  qc </t>
+          <t xml:space="preserve">chase stadium
+  fort lauderdale  fl </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>0AheRyBg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2512,136 +2526,142 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>K4FYmLD9</t>
+          <t>6gpXy3vi</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>txm4BKVR</t>
+          <t>6LuGZiZI</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="P11" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="n">
-        <v>-0.09523809523809534</v>
-      </c>
-      <c r="W11" t="n">
-        <v>-0.02380952380952395</v>
-      </c>
+      <c r="T11" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.5833333333333333</v>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-3.833333333333334</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>-0.08333333333333393</v>
       </c>
       <c r="Z11" t="n">
-        <v>-1.976190476190477</v>
+        <v>-0.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>-3.261904761904763</v>
+        <v>-2.833333333333336</v>
       </c>
       <c r="AC11" t="n">
-        <v>-2.5</v>
+        <v>2.833333333333336</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.5</v>
+        <v>-1.416666666666667</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.08333333333333304</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.1428571428571428</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.0714285714285714</v>
+        <v>-0.9166666666666667</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.547619047619051</v>
+        <v>-1.333333333333334</v>
       </c>
       <c r="AI11" t="n">
-        <v>-1.547619047619051</v>
+        <v>0.08333333333333393</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-1.809523809523808</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.904761904761905</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>67.35593434343436</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="AM11" t="n">
-        <v>66.80151515151515</v>
+        <v>67.68552188552188</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.1316786283891547</v>
+        <v>0.5484848484848328</v>
       </c>
       <c r="AO11" t="n">
-        <v>-67</v>
+        <v>4.844242424242424</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.251948051948048</v>
+        <v>0.3499999999999943</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.08008658008658021</v>
+        <v>336986.0724029224</v>
       </c>
       <c r="AR11" t="n">
+        <v>-2.483369900036852</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>47750000</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.919455367716751</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3.047878787878801</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-45</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.09000000000000008</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-36</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>3.770812200617002</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="BA11" t="n">
         <v>-1</v>
       </c>
-      <c r="AS11" t="n">
-        <v>-2.629004329004328</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>-1387175.324675325</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>-0.1545454545454561</v>
-      </c>
-      <c r="AV11" t="inlineStr"/>
-      <c r="AW11" t="n">
-        <v>759289.877833111</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>2.119381787802837</v>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="n">
-        <v>-75</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>-1.195085251006308</v>
-      </c>
       <c r="BB11" t="n">
-        <v>-2300000</v>
+        <v>-0.3999999999999986</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.819430746780355</v>
+        <v>0.03227786003797917</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.8891534843602358</v>
+        <v>1.449999999999999</v>
       </c>
       <c r="BE11" t="n">
-        <v>-1.013419913419909</v>
-      </c>
-      <c r="BF11" t="inlineStr"/>
+        <v>1657545.454545455</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0.3090909090909089</v>
+      </c>
       <c r="BG11" t="n">
         <v>0</v>
       </c>
@@ -2649,27 +2669,27 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>QHhnaCp6</t>
+          <t>tS5WR1K9</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45486.85416666666</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dujic f 
+          <t xml:space="preserve">lauziere p 
   can </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi field
-  washington  dc </t>
+          <t xml:space="preserve">subaru park
+  chester  pa </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>Szrwix67</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2701,141 +2721,141 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
           <t>K4zRMgTN</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>EgT3xN3S</t>
-        </is>
-      </c>
       <c r="O12" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
+        <v>4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-2.333333333333332</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0.3333333333333357</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.3333333333333357</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0.3333333333333339</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.1666666666666666</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-0.1666666666666661</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>66.2530303030303</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>69.06727272727274</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-0.2492063492063608</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>2.993362193362202</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>179315.3140650892</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-3.404955270021468</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-2475000</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-1.039812670439545</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.195238095238096</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-205</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.04567906213868955</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-199</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>3.733927032431453</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
         <v>-3</v>
       </c>
-      <c r="R12" t="n">
-        <v>-3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0.3333333333333335</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0.3333333333333339</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0.3999999999999999</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0.9999999999999998</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.333333333333332</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>67.09696969696971</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>67.97818181818181</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>-0.02964426877470339</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>-58</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0.1000000000000085</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>-0.1181818181818184</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>-1.472727272727273</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>-2018227.272727273</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>-2.721212121212119</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>5.900000000000006</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>-196201.1048850294</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>-3.589359134382015</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>-0.6000000000000014</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>-49</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>-5.257177863241939</v>
-      </c>
       <c r="BB12" t="n">
-        <v>525000</v>
+        <v>-2.238528138528142</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.333570760115393</v>
+        <v>-1.320996290132456</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.2515921551962492</v>
+        <v>-5.75</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.3469696969697225</v>
+        <v>-266779.220779221</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>-0.1298701298701301</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2844,32 +2864,32 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>dYh0Wjoq</t>
+          <t>AszX60rp</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45486.85416666666</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapman a 
+          <t xml:space="preserve">rivas v 
   usa </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">bmo field
-  toronto  on </t>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
+          <t>EPngUvhk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Szrwix67</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2896,141 +2916,141 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>zoZ995af</t>
+          <t>l6eEjGlO</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>rJ9D8rzj</t>
+          <t>022mBmSn</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="R13" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="n">
-        <v>-0.8333333333333334</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.166666666666667</v>
-      </c>
+      <c r="T13" t="n">
+        <v>-2.214285714285714</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-5.071428571428571</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>3.261904761904763</v>
       </c>
       <c r="Z13" t="n">
-        <v>-1.833333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.666666666666667</v>
+        <v>-0.1666666666666665</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.333333333333334</v>
+        <v>-16.14285714285715</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.1666666666666661</v>
+        <v>16.14285714285715</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>-2.380952380952381</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.3999999999999999</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-1.952380952380952</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.3333333333333335</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="AH13" t="n">
-        <v>4.5</v>
+        <v>6.976190476190475</v>
       </c>
       <c r="AI13" t="n">
-        <v>-4.5</v>
+        <v>-4.095238095238095</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>-2.166666666666666</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>67.61212121212121</v>
+        <v>66.07929292929292</v>
       </c>
       <c r="AM13" t="n">
-        <v>67.80454545454546</v>
+        <v>66.66245791245791</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.1014411027568924</v>
+        <v>-0.8262987012987253</v>
       </c>
       <c r="AO13" t="n">
-        <v>-12</v>
+        <v>-2.081818181818164</v>
       </c>
       <c r="AP13" t="n">
-        <v>-4.057407407407396</v>
+        <v>-11.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.3166666666666667</v>
+        <v>-659556.9896220383</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.351843004848483</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.322222222222223</v>
+        <v>3750000</v>
       </c>
       <c r="AT13" t="n">
-        <v>165500</v>
+        <v>-1.590190691371163</v>
       </c>
       <c r="AU13" t="n">
-        <v>-2.87777777777778</v>
+        <v>-2.91720779220779</v>
       </c>
       <c r="AV13" t="n">
-        <v>-1</v>
+        <v>83</v>
       </c>
       <c r="AW13" t="n">
-        <v>335623.0847003874</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.145611345282404</v>
+        <v>72</v>
       </c>
       <c r="AY13" t="n">
-        <v>-2</v>
+        <v>-0.3806807515316279</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0.1219363117389385</v>
+        <v>1</v>
       </c>
       <c r="BB13" t="n">
-        <v>3115000</v>
+        <v>0.04464285714285765</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.6547615883142157</v>
+        <v>0.2319460820952344</v>
       </c>
       <c r="BD13" t="n">
-        <v>-1.824428653704899</v>
+        <v>-13.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>-2.009259259259295</v>
+        <v>-1844017.857142858</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3039,32 +3059,32 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>48ijbWaC</t>
+          <t>KCHNTNkc</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45486.85416666666</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
+          <t xml:space="preserve">dujic f 
+  can </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">gillette stadium
-  foxborough  ma </t>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
+          <t>zV5YmQAr</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>rsHkUNCo</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3091,138 +3111,138 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>tOpyQa24</t>
+          <t>rJ9D8rzj</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>nJ01AhXP</t>
+          <t>6LuGZiZI</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="n">
-        <v>-1.066666666666666</v>
-      </c>
-      <c r="W14" t="n">
+      <c r="T14" t="n">
+        <v>-0.3999999999999999</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="n">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-3.466666666666667</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA14" t="n">
         <v>0.2000000000000002</v>
       </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>-0.5999999999999996</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0.9333333333333327</v>
-      </c>
       <c r="AB14" t="n">
-        <v>1.6</v>
+        <v>-9.399999999999999</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.1666666666666661</v>
+        <v>9.399999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.5</v>
+        <v>-0.09999999999999964</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.4500000000000002</v>
+        <v>-1.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.03333333333333321</v>
+        <v>-0.7</v>
       </c>
       <c r="AH14" t="n">
-        <v>-4.966666666666661</v>
+        <v>-1</v>
       </c>
       <c r="AI14" t="n">
-        <v>4.966666666666661</v>
+        <v>-3.533333333333333</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-4.666666666666668</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>5.666666666666666</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>68.37090909090909</v>
+        <v>66.63313131313132</v>
       </c>
       <c r="AM14" t="n">
-        <v>67.5476430976431</v>
+        <v>67.63232323232323</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.07951681594904092</v>
+        <v>0.9099567099567309</v>
       </c>
       <c r="AO14" t="n">
-        <v>85</v>
+        <v>0.3809523809523938</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.7131313131313135</v>
+        <v>1.300000000000011</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0.1411111111111112</v>
+        <v>249557.6072534276</v>
       </c>
       <c r="AR14" t="n">
-        <v>1</v>
+        <v>-1.526916916652244</v>
       </c>
       <c r="AS14" t="n">
-        <v>-1.048888888888889</v>
+        <v>-555000</v>
       </c>
       <c r="AT14" t="n">
-        <v>-590106.0606060603</v>
+        <v>-0.9146376571223414</v>
       </c>
       <c r="AU14" t="n">
-        <v>-1.206565656565658</v>
+        <v>-2.655194805194796</v>
       </c>
       <c r="AV14" t="n">
-        <v>-11.5</v>
+        <v>-48</v>
       </c>
       <c r="AW14" t="n">
-        <v>-1517855.682325631</v>
+        <v>0.05000000000000004</v>
       </c>
       <c r="AX14" t="n">
-        <v>2.247691677461489</v>
+        <v>-81</v>
       </c>
       <c r="AY14" t="n">
-        <v>5.5</v>
+        <v>4.429968904037594</v>
       </c>
       <c r="AZ14" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.910573676110765</v>
+        <v>-1</v>
       </c>
       <c r="BB14" t="n">
-        <v>8325000</v>
+        <v>-2.422077922077925</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.7143859862785717</v>
+        <v>1.493680693101048</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.520908315895554</v>
+        <v>-6.800000000000001</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.110101010101005</v>
+        <v>-1459086.58008658</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
@@ -3234,32 +3254,32 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Iigr0hVa</t>
+          <t>WdOu5vDd</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45486.85416666666</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">gonzales g 
+          <t xml:space="preserve">villarreal a 
   usa </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">tql stadium
-  cincinnati  oh </t>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3286,19 +3306,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>roEEsq76</t>
+          <t>6BusaLE3</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>6gpXy3vi</t>
+          <t>KtuTuMN0</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>1</v>
@@ -3309,118 +3329,118 @@
       <c r="S15" t="n">
         <v>0</v>
       </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="n">
-        <v>1.966666666666667</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0.6666666666666667</v>
-      </c>
+      <c r="T15" t="n">
+        <v>-0.6904761904761905</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.119047619047619</v>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-4.88095238095238</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.547619047619046</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.1</v>
+        <v>-1</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.03333333333333321</v>
+        <v>-0.2380952380952381</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.966666666666667</v>
+        <v>-3.666666666666664</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.4</v>
+        <v>3.666666666666664</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.5</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.3500000000000001</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.1</v>
+        <v>-0.2857142857142858</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.8999999999999999</v>
+        <v>0.2857142857142858</v>
       </c>
       <c r="AH15" t="n">
-        <v>10.06666666666666</v>
+        <v>-5.904761904761905</v>
       </c>
       <c r="AI15" t="n">
-        <v>-10.06666666666666</v>
+        <v>-4.547619047619047</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.733333333333334</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0.8000000000000007</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>68.35959595959595</v>
+        <v>69.26666666666667</v>
       </c>
       <c r="AM15" t="n">
-        <v>68.42080808080809</v>
+        <v>67.87272727272727</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0.06750000000000012</v>
+        <v>-0.8989898989899245</v>
       </c>
       <c r="AO15" t="n">
-        <v>65</v>
+        <v>1.826557239057237</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.676363636363632</v>
+        <v>-3.166666666666657</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0.01818181818181808</v>
+        <v>-56778.98987307097</v>
       </c>
       <c r="AR15" t="n">
-        <v>1</v>
+        <v>0.703612624738664</v>
       </c>
       <c r="AS15" t="n">
-        <v>-0.788181818181819</v>
+        <v>-26350000</v>
       </c>
       <c r="AT15" t="n">
-        <v>1700734.848484848</v>
+        <v>0.1868072435125896</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.951515151515153</v>
+        <v>0.6569865319865329</v>
       </c>
       <c r="AV15" t="n">
-        <v>-5.166666666666657</v>
+        <v>-321</v>
       </c>
       <c r="AW15" t="n">
-        <v>-481764.3208844294</v>
+        <v>0.07716793129197241</v>
       </c>
       <c r="AX15" t="n">
-        <v>-3.225885194657572</v>
+        <v>-277</v>
       </c>
       <c r="AY15" t="n">
-        <v>-2.666666666666668</v>
+        <v>2.876361797709521</v>
       </c>
       <c r="AZ15" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-1.18414967101668</v>
+        <v>-4</v>
       </c>
       <c r="BB15" t="n">
-        <v>3630000</v>
+        <v>-0.2898989898989903</v>
       </c>
       <c r="BC15" t="n">
-        <v>-2.851425667256862</v>
+        <v>3.175401697760442</v>
       </c>
       <c r="BD15" t="n">
-        <v>-0.6096056025532164</v>
+        <v>3.833333333333332</v>
       </c>
       <c r="BE15" t="n">
-        <v>-2.123333333333363</v>
+        <v>-531295.244107744</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>-0.02390572390572387</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>

--- a/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_constructed.xlsx
@@ -460,44 +460,44 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>competition</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>h2h_27_segun_loc</t>
@@ -525,94 +525,94 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions_against</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -625,97 +625,97 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_hei_player_start</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
@@ -735,8 +735,8 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">dickerson j 
-  usa </t>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -755,36 +755,36 @@
           <t>bm8usLzB</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2PIEeC7j</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>167</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>1671</v>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>2024</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>mls</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2PIEeC7j</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>rXawJi8t</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -803,24 +803,28 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.133333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.03333333333333321</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+        <v>0.9500000000000002</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-0.3999999999999999</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.4</v>
+      </c>
       <c r="X2" t="n">
-        <v>-5.666666666666666</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.066666666666668</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.5</v>
+        <v>-2.066666666666666</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.4166666666666665</v>
+        <v>-2.366666666666665</v>
       </c>
       <c r="AB2" t="n">
         <v>-3.600000000000001</v>
@@ -828,29 +832,25 @@
       <c r="AC2" t="n">
         <v>3.600000000000001</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="n">
+        <v>-5.666666666666666</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>6.066666666666668</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-1.133333333333333</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-0.03333333333333321</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>-3.333333333333333</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AK2" t="n">
         <v>2.766666666666667</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-0.3999999999999999</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-2.066666666666666</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-2.366666666666665</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
       </c>
       <c r="AL2" t="n">
         <v>67.61902356902357</v>
@@ -859,61 +859,61 @@
         <v>67.35999999999999</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.2373737373737583</v>
+        <v>-5.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>2.147619047619045</v>
+        <v>772407.4074074072</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>0.3368733596112605</v>
       </c>
       <c r="AQ2" t="n">
-        <v>90088.6916100604</v>
+        <v>-2.285248505152936</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1.970479874218601</v>
+        <v>0.03333333333333344</v>
       </c>
       <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.3330918327620225</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>2.14680134680134</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>-0.3348484848484858</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.089225589225606</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.06270131657128553</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0.1772727272727366</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>-1.931658887071457</v>
+      </c>
+      <c r="BE2" t="n">
         <v>3725000</v>
       </c>
-      <c r="AT2" t="n">
-        <v>0.2183747800486344</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.027994227994228</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.06088684277538747</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0.2324235421926915</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>-0.3997113997114035</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>-2.404167455762575</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>647337.6623376617</v>
-      </c>
       <c r="BF2" t="n">
-        <v>0.02857142857142847</v>
+        <v>151685.7199218825</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -930,7 +930,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">simon n 
+          <t xml:space="preserve">bazakos f 
   usa </t>
         </is>
       </c>
@@ -950,36 +950,36 @@
           <t>2i4sdl32</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>167</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>1671</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>2024</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>mls</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Sd7snoa0</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>86yPt28f</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -998,24 +998,28 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+        <v>0.4500000000000002</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.1666666666666665</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-0.1333333333333334</v>
+      </c>
       <c r="X3" t="n">
-        <v>-6.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.133333333333335</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-1.666666666666666</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.4666666666666663</v>
+        <v>-5.533333333333333</v>
       </c>
       <c r="AB3" t="n">
         <v>-14.7</v>
@@ -1023,29 +1027,25 @@
       <c r="AC3" t="n">
         <v>14.7</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="n">
+        <v>-6.199999999999999</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>5.133333333333335</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.5333333333333334</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>-0.1333333333333329</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AK3" t="n">
         <v>1.333333333333333</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.1666666666666665</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-0.1333333333333334</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-1.666666666666666</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-5.533333333333333</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>65.75454545454545</v>
@@ -1054,61 +1054,61 @@
         <v>66.25999999999999</v>
       </c>
       <c r="AN3" t="n">
-        <v>-4.143939393939405</v>
+        <v>6</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.0954545454545439</v>
+        <v>582272.7272727271</v>
       </c>
       <c r="AP3" t="n">
+        <v>1.69159363766309</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.734740784185519</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-0.1818181818181821</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-0.8155212053617049</v>
+      </c>
+      <c r="AU3" t="n">
         <v>10</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>266676.5763149447</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-0.1558672508598491</v>
-      </c>
-      <c r="AS3" t="n">
+      <c r="AV3" t="n">
+        <v>0.04696969696969688</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-1.716666666666669</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0.07272727272727764</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-0.03571428571428559</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>-4.313636363636363</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>-0.1226110498287092</v>
+      </c>
+      <c r="BE3" t="n">
         <v>425000</v>
       </c>
-      <c r="AT3" t="n">
-        <v>-1.060851148933352</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0.09090909090909349</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>-0.02976190476190466</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.599816347036707</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>-1.692424242424238</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.724847551530139</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>593181.8181818181</v>
-      </c>
       <c r="BF3" t="n">
-        <v>-0.1818181818181821</v>
+        <v>241991.2532726842</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gonzalez g  jr 
+          <t xml:space="preserve">chapman a 
   usa </t>
         </is>
       </c>
@@ -1145,36 +1145,36 @@
           <t>txUJt9AR</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>167</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>1671</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>2024</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>mls</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>tOpyQa24</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>rXawJi8t</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -1193,28 +1193,28 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6666666666666665</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-1</v>
+        <v>0.2000000000000002</v>
       </c>
       <c r="V4" t="n">
-        <v>5.5</v>
+        <v>0.8333333333333335</v>
       </c>
       <c r="W4" t="n">
-        <v>-3</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="X4" t="n">
-        <v>-6.666666666666668</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-1.666666666666668</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.1666666666666665</v>
+        <v>5</v>
       </c>
       <c r="AB4" t="n">
         <v>2.333333333333336</v>
@@ -1223,28 +1223,28 @@
         <v>-2.333333333333336</v>
       </c>
       <c r="AD4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-6.666666666666668</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>-1.833333333333334</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AK4" t="n">
         <v>-0.666666666666667</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.8333333333333335</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-0.6666666666666666</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-1.666666666666668</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>67.25818181818181</v>
@@ -1252,56 +1252,56 @@
       <c r="AM4" t="n">
         <v>68.28767676767677</v>
       </c>
-      <c r="AN4" t="n">
-        <v>-2.012590187590177</v>
-      </c>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>-1.985750360750373</v>
-      </c>
-      <c r="AP4" t="inlineStr"/>
+        <v>-1783880.892255892</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-0.76352367143609</v>
+      </c>
       <c r="AQ4" t="n">
-        <v>565857.9685826893</v>
+        <v>-0.5812362373583682</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.1653769676513512</v>
+        <v>-0.1952020202020204</v>
       </c>
       <c r="AS4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-0.9955680142061283</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="n">
+        <v>-2.031523569023562</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-2.010395622895622</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-68</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-3.193097643097644</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.1179649758454109</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="n">
+        <v>-58</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-2.638762626262633</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.1027813914322877</v>
+      </c>
+      <c r="BE4" t="n">
         <v>-400000</v>
       </c>
-      <c r="AT4" t="n">
-        <v>-1.246422982895382</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>-3.102020202020199</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>-68</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.125957556935818</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>-58</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>-0.557140372618079</v>
-      </c>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>-1.683513708513704</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>-0.52837107833912</v>
-      </c>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="n">
-        <v>-1873524.891774891</v>
-      </c>
       <c r="BF4" t="n">
-        <v>-0.1927128427128426</v>
+        <v>573754.5865348768</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">gonzalez g  jr 
+          <t xml:space="preserve">touchan r 
   usa </t>
         </is>
       </c>
@@ -1338,36 +1338,36 @@
           <t>W0ealpQl</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2PIEeC7j</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>167</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>1671</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>2024</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>mls</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2PIEeC7j</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>rXawJi8t</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -1386,24 +1386,28 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3666666666666665</v>
+        <v>0.5</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1333333333333333</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+        <v>-0.7000000000000002</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.2666666666666668</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0.2333333333333332</v>
+      </c>
       <c r="X5" t="n">
-        <v>-1.933333333333334</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.766666666666666</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.5</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.4666666666666663</v>
+        <v>-0.3666666666666654</v>
       </c>
       <c r="AB5" t="n">
         <v>-3.566666666666663</v>
@@ -1411,29 +1415,25 @@
       <c r="AC5" t="n">
         <v>3.566666666666663</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="n">
+        <v>-1.933333333333334</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.766666666666666</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.3666666666666665</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>-0.2000000000000002</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AK5" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0.2666666666666668</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-0.2333333333333332</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-0.3666666666666654</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>67.16632996632997</v>
@@ -1442,61 +1442,61 @@
         <v>69.49636363636364</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9035353535353465</v>
+        <v>-4.399999999999999</v>
       </c>
       <c r="AO5" t="n">
-        <v>-2.422943722943714</v>
+        <v>-530803.7037037036</v>
       </c>
       <c r="AP5" t="n">
+        <v>-0.3093279743394106</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-5.282423021507682</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.306836368140694</v>
+      </c>
+      <c r="AU5" t="n">
         <v>4</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>-731249.5467147724</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>-4.310472699905521</v>
-      </c>
-      <c r="AS5" t="n">
+      <c r="AV5" t="n">
+        <v>-2.515555555555537</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-0.5355555555555576</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-278</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-1.18703703703703</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-266</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.8618518518518101</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-4.211324460351921</v>
+      </c>
+      <c r="BE5" t="n">
         <v>-8275000</v>
       </c>
-      <c r="AT5" t="n">
-        <v>1.308867236972844</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>-0.6921356421356393</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-278</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>-266</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>-0.2434049968047987</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>-4</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>-0.268398268398272</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>-5.279492049122638</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>-4.399999999999999</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>-390134.5598845598</v>
-      </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>-654430.7881371955</v>
       </c>
       <c r="BG5" t="n">
         <v>1</v>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">rivas v 
+          <t xml:space="preserve">freemon j 
   usa </t>
         </is>
       </c>
@@ -1533,36 +1533,36 @@
           <t>QJF7WTFB</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>167</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>1671</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>2024</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>mls</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>WWvwigh8</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>022mBmSn</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -1581,24 +1581,28 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5999999999999999</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3999999999999999</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+        <v>0.75</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.4000000000000001</v>
+      </c>
       <c r="X6" t="n">
-        <v>-4.6</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>-5.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5999999999999996</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="AB6" t="n">
         <v>22</v>
@@ -1606,29 +1610,25 @@
       <c r="AC6" t="n">
         <v>-22.00000000000001</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-5.800000000000001</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.5999999999999999</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>-2.399999999999999</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AK6" t="n">
         <v>-2.8</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.4000000000000001</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>5.199999999999999</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>66.87575757575758</v>
@@ -1637,61 +1637,61 @@
         <v>69.47353535353537</v>
       </c>
       <c r="AN6" t="n">
-        <v>-1.421212121212108</v>
+        <v>-5.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>-3.516666666666666</v>
+        <v>126045.4545454546</v>
       </c>
       <c r="AP6" t="n">
+        <v>-4.259742144045205</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-1.311142757498246</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.2400000000000002</v>
+      </c>
+      <c r="AS6" t="n">
         <v>-1</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>-947968.8040273878</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>2.857060112734661</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>13850000</v>
-      </c>
       <c r="AT6" t="n">
-        <v>-1.247186663506994</v>
+        <v>-1.955447525620144</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.3545454545454447</v>
+        <v>-1</v>
       </c>
       <c r="AV6" t="n">
-        <v>-57</v>
+        <v>-3.510909090909095</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.1258452491668605</v>
+        <v>2.61818181818181</v>
       </c>
       <c r="AX6" t="n">
         <v>-57</v>
       </c>
       <c r="AY6" t="n">
-        <v>-3.922334139645514</v>
+        <v>0.3527272727272646</v>
       </c>
       <c r="AZ6" t="n">
+        <v>0.06866135782376181</v>
+      </c>
+      <c r="BA6" t="n">
         <v>1</v>
       </c>
-      <c r="BA6" t="n">
-        <v>-1</v>
-      </c>
       <c r="BB6" t="n">
-        <v>2.515151515151505</v>
+        <v>-57</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.9161483763465839</v>
+        <v>-1.069090909090903</v>
       </c>
       <c r="BD6" t="n">
-        <v>-5.5</v>
+        <v>2.640236841163951</v>
       </c>
       <c r="BE6" t="n">
-        <v>164507.5757575759</v>
+        <v>13850000</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.2000000000000002</v>
+        <v>-1135621.388362277</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1700,7 +1700,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>nP8vQukM</t>
+          <t>QF7rPa4S</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1708,188 +1708,194 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">da silva a 
+          <t xml:space="preserve">pekmic i 
   usa </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">children s mercy park
-  kansas city  ks </t>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>167</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>1671</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>2024</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Sd7snoa0</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>WSL0wFD4</t>
-        </is>
-      </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2380952380952381</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7857142857142858</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+        <v>-0.2000000000000002</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.1666666666666665</v>
+      </c>
       <c r="X7" t="n">
-        <v>-2.261904761904763</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.2619047619047628</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4047619047619051</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-2.80952380952381</v>
+        <v>-1.666666666666671</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.80952380952381</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-0.6904761904761898</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-1.619047619047619</v>
-      </c>
+        <v>1.666666666666671</v>
+      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="n">
-        <v>1.047619047619047</v>
+        <v>-2.333333333333334</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.8809523809523807</v>
+        <v>-4.666666666666666</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.690476190476192</v>
+        <v>0.5000000000000001</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0952380952380949</v>
+        <v>-0.166666666666667</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>67.26464646464646</v>
+        <v>68.64848484848484</v>
       </c>
       <c r="AM7" t="n">
-        <v>66.60000000000001</v>
+        <v>68.55404040404041</v>
       </c>
       <c r="AN7" t="n">
-        <v>-1.724206349206327</v>
+        <v>5.25</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1.864213564213571</v>
-      </c>
-      <c r="AP7" t="inlineStr"/>
+        <v>-1283015.151515151</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.4806531033466115</v>
+      </c>
       <c r="AQ7" t="n">
-        <v>-48028.0649067926</v>
+        <v>-2.324943793306801</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.923746218375012</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>2000000</v>
+        <v>2</v>
       </c>
       <c r="AT7" t="n">
-        <v>-1.32667707555251</v>
+        <v>-3.729799130178407</v>
       </c>
       <c r="AU7" t="n">
-        <v>-1.500360750360741</v>
+        <v>0.75</v>
       </c>
       <c r="AV7" t="n">
-        <v>137</v>
+        <v>-1.907575757575742</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.03804916703523542</v>
+        <v>-0.9727272727272762</v>
       </c>
       <c r="AX7" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AY7" t="n">
-        <v>-2.033776817363105</v>
-      </c>
-      <c r="AZ7" t="inlineStr"/>
+        <v>-3.627272727272725</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
       <c r="BA7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.629599567099564</v>
+        <v>128</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.098175044929562</v>
-      </c>
-      <c r="BD7" t="inlineStr"/>
+        <v>1.059090909090912</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-1.837656518747849</v>
+      </c>
       <c r="BE7" t="n">
-        <v>-897023.0880230882</v>
+        <v>495000</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.1274531024531023</v>
+        <v>-384962.5571281144</v>
       </c>
       <c r="BG7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>QF7rPa4S</t>
+          <t>nP8vQukM</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1897,194 +1903,188 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">simon n 
+          <t xml:space="preserve">vazquez r 
   usa </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz field
-  saint paul  mn </t>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>WSL0wFD4</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>167</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>1671</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>2024</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>UFWZoX9L</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>86yPt28f</t>
-        </is>
-      </c>
       <c r="O8" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.166666666666667</v>
-      </c>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
+        <v>0.1666666666666665</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.047619047619047</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.8809523809523807</v>
+      </c>
       <c r="X8" t="n">
-        <v>-2.333333333333334</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>-4.666666666666666</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.690476190476192</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.166666666666667</v>
+        <v>0.0952380952380949</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1.666666666666671</v>
+        <v>-2.80952380952381</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.666666666666671</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0.6666666666666665</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>-0.5</v>
-      </c>
+        <v>2.80952380952381</v>
+      </c>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="n">
-        <v>-0.3333333333333334</v>
+        <v>-2.261904761904763</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.1666666666666665</v>
+        <v>-0.2619047619047628</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.5</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-0.7857142857142858</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>-0.6904761904761898</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>-1.619047619047619</v>
       </c>
       <c r="AL8" t="n">
-        <v>68.64848484848484</v>
+        <v>67.26464646464646</v>
       </c>
       <c r="AM8" t="n">
-        <v>68.55404040404041</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.2376623376623</v>
-      </c>
+        <v>66.60000000000001</v>
+      </c>
+      <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>-2.007792207792193</v>
+        <v>-827002.0442520443</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.75</v>
+        <v>-1.680352110333061</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-342170.2870621935</v>
+        <v>2.792413088944052</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.931086539879111</v>
+        <v>-0.1164983164983164</v>
       </c>
       <c r="AS8" t="n">
-        <v>495000</v>
+        <v>2</v>
       </c>
       <c r="AT8" t="n">
-        <v>-3.464827825867189</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>-3.585714285714275</v>
-      </c>
+        <v>-2.054922145683747</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
       <c r="AV8" t="n">
-        <v>126</v>
+        <v>-1.88530543530544</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.680230880230887</v>
       </c>
       <c r="AX8" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.5560359933447074</v>
+        <v>-1.315031265031251</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>2</v>
-      </c>
+        <v>0.04308460226195776</v>
+      </c>
+      <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="n">
-        <v>-0.8350649350649348</v>
+        <v>129</v>
       </c>
       <c r="BC8" t="n">
-        <v>-2.335666108548693</v>
+        <v>-1.462818662818677</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.25</v>
+        <v>3.091819645825186</v>
       </c>
       <c r="BE8" t="n">
-        <v>-1337584.415584416</v>
+        <v>2000000</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>113766.6834190859</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>b3GRSs53</t>
+          <t>AszX60rp</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2092,185 +2092,179 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">szpala l 
+          <t xml:space="preserve">mendoza r 
   usa </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">inter co stadium
-  orlando  fl </t>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>rsHkUNCo</t>
+          <t>EPngUvhk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>167</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>1671</v>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>2024</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>EgT3xN3S</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>dp6AQn9c</t>
-        </is>
-      </c>
       <c r="O9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-1.952380952380952</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6.976190476190475</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-4.095238095238095</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-16.14285714285715</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>16.14285714285715</v>
+      </c>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="n">
+        <v>-5.071428571428571</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3.261904761904763</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-2.214285714285714</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-2.380952380952381</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>66.07929292929292</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>66.66245791245791</v>
+      </c>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="n">
+        <v>-2395909.090909091</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-0.7619047619047592</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.023809523809533</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.09090909090909083</v>
+      </c>
+      <c r="AS9" t="n">
         <v>-1</v>
       </c>
-      <c r="P9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="n">
+        <v>-2.390909090909091</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-63</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-0.8727272727272606</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="n">
+        <v>-63</v>
+      </c>
+      <c r="BC9" t="n">
         <v>-3</v>
       </c>
-      <c r="R9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.1666666666666665</v>
-      </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="n">
-        <v>1.666666666666666</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.4666666666666663</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>-4.166666666666664</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>4.166666666666664</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.333333333333334</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>-0.666666666666667</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>-0.8333333333333333</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>-0.1666666666666679</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>66.81868686868687</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>67.85454545454546</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>-2.742923280423298</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0.2217592592592439</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1639632.975811181</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>3.811251773436645</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>-2920000</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>-2.202058074674028</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.257341269841277</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>-202</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.2925099684142431</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>-184</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>-1.115833356754095</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>3.213227513227508</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2.74983246567097</v>
-      </c>
       <c r="BD9" t="n">
-        <v>-1.25</v>
+        <v>2.595238095238095</v>
       </c>
       <c r="BE9" t="n">
-        <v>1029388.558201058</v>
+        <v>-50000</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.1142857142857143</v>
+        <v>-269642.857142857</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2287,7 +2281,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">marrufo j 
+          <t xml:space="preserve">villarreal a 
   usa </t>
         </is>
       </c>
@@ -2307,36 +2301,36 @@
           <t>zsdfgnmL</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>167</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>1671</v>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>2024</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>mls</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>rJ9D8rzj</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>xA45kovo</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -2355,24 +2349,28 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6666666666666667</v>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-1.166666666666667</v>
+      </c>
       <c r="X10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-2.166666666666666</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.166666666666667</v>
+        <v>-2.833333333333334</v>
       </c>
       <c r="AB10" t="n">
         <v>1.5</v>
@@ -2380,29 +2378,25 @@
       <c r="AC10" t="n">
         <v>-1.5</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.333333333333333</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AK10" t="n">
         <v>0.8333333333333339</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0.8333333333333333</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>-1.166666666666667</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-2.166666666666666</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>-2.833333333333334</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>67.37563131313131</v>
@@ -2411,61 +2405,61 @@
         <v>68.61060606060606</v>
       </c>
       <c r="AN10" t="n">
-        <v>-2.937662337662346</v>
+        <v>3.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>2.983116883116864</v>
+        <v>-1917727.272727273</v>
       </c>
       <c r="AP10" t="n">
-        <v>9.5</v>
+        <v>3.625</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-270682.9045015138</v>
+        <v>2.902777777777771</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.224515292560401</v>
+        <v>-0.2727272727272727</v>
       </c>
       <c r="AS10" t="n">
-        <v>-850000</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.5485862925712297</v>
+        <v>-5.888888888888886</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.01298701298701133</v>
+        <v>5.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>-71</v>
+        <v>1.181818181818173</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.06792875044754765</v>
+        <v>-2.272727272727273</v>
       </c>
       <c r="AX10" t="n">
-        <v>-59</v>
+        <v>-2</v>
       </c>
       <c r="AY10" t="n">
-        <v>2.400941748310188</v>
+        <v>-1.181818181818187</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>0.1111111111111112</v>
       </c>
       <c r="BA10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>-3.040259740259742</v>
+        <v>7</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.375340407295283</v>
+        <v>-0.3636363636363455</v>
       </c>
       <c r="BD10" t="n">
-        <v>6</v>
+        <v>-0.9027777777777786</v>
       </c>
       <c r="BE10" t="n">
-        <v>-1372480.519480519</v>
+        <v>350000</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.2363636363636363</v>
+        <v>903472.2222222222</v>
       </c>
       <c r="BG10" t="n">
         <v>1</v>
@@ -2474,7 +2468,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>h6Py6Kcj</t>
+          <t>tS5WR1K9</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2482,185 +2476,185 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">dujic f 
-  can </t>
+          <t xml:space="preserve">penso c 
+  usa </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">chase stadium
-  fort lauderdale  fl </t>
+          <t xml:space="preserve">subaru park
+  chester  pa </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0AheRyBg</t>
+          <t>Szrwix67</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>63fk89be</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>167</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>1671</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>2024</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>6gpXy3vi</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>6LuGZiZI</t>
-        </is>
-      </c>
       <c r="O11" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
+        <v>4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.7000000000000002</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.1666666666666666</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.1666666666666661</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0.3333333333333357</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.3333333333333357</v>
+      </c>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-2.333333333333332</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0.3333333333333339</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>66.2530303030303</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>69.06727272727274</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-3.666666666666668</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>649545.4545454541</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-1.666666666666657</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
         <v>-2</v>
       </c>
-      <c r="R11" t="n">
-        <v>-2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.6666666666666667</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.5833333333333333</v>
-      </c>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="n">
-        <v>-3.833333333333334</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>-0.08333333333333393</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>-2.833333333333336</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.833333333333336</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>-1.416666666666667</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0.08333333333333304</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.083333333333333</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>-0.9166666666666667</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>-1.333333333333334</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0.08333333333333393</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>68.65000000000001</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>67.68552188552188</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0.5484848484848328</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>4.844242424242424</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0.3499999999999943</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>336986.0724029224</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>-2.483369900036852</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>47750000</v>
-      </c>
       <c r="AT11" t="n">
-        <v>3.919455367716751</v>
+        <v>0.8333333333333428</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.047878787878801</v>
+        <v>-3.333333333333343</v>
       </c>
       <c r="AV11" t="n">
-        <v>-45</v>
+        <v>6.454545454545467</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.09000000000000008</v>
+        <v>-0.8181818181818201</v>
       </c>
       <c r="AX11" t="n">
-        <v>-36</v>
+        <v>-135</v>
       </c>
       <c r="AY11" t="n">
-        <v>3.770812200617002</v>
+        <v>5.545454545454533</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="BA11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>-0.3999999999999986</v>
+        <v>-129</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.03227786003797917</v>
+        <v>-0.454545454545439</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.449999999999999</v>
+        <v>-2.666666666666668</v>
       </c>
       <c r="BE11" t="n">
-        <v>1657545.454545455</v>
+        <v>-1675000</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.3090909090909089</v>
+        <v>161666.6666666666</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2669,7 +2663,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>tS5WR1K9</t>
+          <t>KCHNTNkc</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2677,185 +2671,185 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">lauziere p 
-  can </t>
+          <t xml:space="preserve">unkel t 
+  usa </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">subaru park
-  chester  pa </t>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Szrwix67</t>
+          <t>zV5YmQAr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>84yIDQMe</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>167</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>1671</v>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>2024</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>6BusaLE3</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>K4zRMgTN</t>
-        </is>
-      </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="R12" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.166666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
+        <v>0.6499999999999999</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.1000000000000001</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.7</v>
+      </c>
       <c r="X12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-2.333333333333332</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.3333333333333335</v>
+        <v>-3.533333333333333</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.3333333333333357</v>
+        <v>-9.399999999999999</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.3333333333333357</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>-0.3333333333333339</v>
-      </c>
+        <v>9.399999999999999</v>
+      </c>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="n">
-        <v>0.1666666666666666</v>
+        <v>0.3000000000000007</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.3333333333333335</v>
+        <v>-3.466666666666667</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.1666666666666661</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="AI12" t="n">
         <v>-0.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>-0.09999999999999964</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-1.7</v>
       </c>
       <c r="AL12" t="n">
-        <v>66.2530303030303</v>
+        <v>66.63313131313132</v>
       </c>
       <c r="AM12" t="n">
-        <v>69.06727272727274</v>
+        <v>67.63232323232323</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.2492063492063608</v>
+        <v>-7</v>
       </c>
       <c r="AO12" t="n">
-        <v>2.993362193362202</v>
+        <v>91545.45454545459</v>
       </c>
       <c r="AP12" t="n">
-        <v>-4.5</v>
+        <v>1.984126984126988</v>
       </c>
       <c r="AQ12" t="n">
-        <v>179315.3140650892</v>
+        <v>-3.38095238095238</v>
       </c>
       <c r="AR12" t="n">
-        <v>-3.404955270021468</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>-2475000</v>
+        <v>2</v>
       </c>
       <c r="AT12" t="n">
-        <v>-1.039812670439545</v>
+        <v>2.841269841269821</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.195238095238096</v>
+        <v>-4.466666666666669</v>
       </c>
       <c r="AV12" t="n">
-        <v>-205</v>
+        <v>2.154545454545456</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.04567906213868955</v>
+        <v>-2.109090909090909</v>
       </c>
       <c r="AX12" t="n">
-        <v>-199</v>
+        <v>162</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.733927032431453</v>
+        <v>0.1363636363636402</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-3</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="BB12" t="n">
-        <v>-2.238528138528142</v>
+        <v>120</v>
       </c>
       <c r="BC12" t="n">
-        <v>-1.320996290132456</v>
+        <v>-1.863636363636374</v>
       </c>
       <c r="BD12" t="n">
-        <v>-5.75</v>
+        <v>-1.238095238095241</v>
       </c>
       <c r="BE12" t="n">
-        <v>-266779.220779221</v>
+        <v>15675000</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.1298701298701301</v>
+        <v>-2626428.571428571</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2864,7 +2858,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>AszX60rp</t>
+          <t>WdOu5vDd</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2872,185 +2866,185 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">rivas v 
+          <t xml:space="preserve">allatin m 
   usa </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">mercedes benz stadium
-  atlanta  ga </t>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>167</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>1671</v>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>2024</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>l6eEjGlO</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>022mBmSn</t>
-        </is>
-      </c>
       <c r="O13" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.214285714285714</v>
+        <v>-0.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
+        <v>-0.2000000000000002</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.2857142857142858</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.2857142857142858</v>
+      </c>
       <c r="X13" t="n">
-        <v>-5.071428571428571</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.261904761904763</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.5</v>
+        <v>-5.904761904761905</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.1666666666666665</v>
+        <v>-4.547619047619047</v>
       </c>
       <c r="AB13" t="n">
-        <v>-16.14285714285715</v>
+        <v>-3.666666666666664</v>
       </c>
       <c r="AC13" t="n">
-        <v>16.14285714285715</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>-2.380952380952381</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.166666666666667</v>
-      </c>
+        <v>3.666666666666664</v>
+      </c>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="n">
-        <v>-1.952380952380952</v>
+        <v>-4.88095238095238</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.833333333333333</v>
+        <v>2.547619047619046</v>
       </c>
       <c r="AH13" t="n">
-        <v>6.976190476190475</v>
+        <v>-0.6904761904761905</v>
       </c>
       <c r="AI13" t="n">
-        <v>-4.095238095238095</v>
+        <v>1.119047619047619</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="AL13" t="n">
-        <v>66.07929292929292</v>
+        <v>69.26666666666667</v>
       </c>
       <c r="AM13" t="n">
-        <v>66.66245791245791</v>
+        <v>67.87272727272727</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.8262987012987253</v>
+        <v>0.7857142857142847</v>
       </c>
       <c r="AO13" t="n">
-        <v>-2.081818181818164</v>
+        <v>204722.2222222222</v>
       </c>
       <c r="AP13" t="n">
-        <v>-11.5</v>
+        <v>3.571428571428569</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-659556.9896220383</v>
+        <v>6.571428571428569</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.351843004848483</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>3750000</v>
+        <v>-1</v>
       </c>
       <c r="AT13" t="n">
-        <v>-1.590190691371163</v>
+        <v>-6.142857142857167</v>
       </c>
       <c r="AU13" t="n">
-        <v>-2.91720779220779</v>
+        <v>-0.2857142857142776</v>
       </c>
       <c r="AV13" t="n">
-        <v>83</v>
+        <v>1.700000000000003</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.300000000000001</v>
       </c>
       <c r="AX13" t="n">
-        <v>72</v>
+        <v>-81</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.3806807515316279</v>
+        <v>2.644444444444446</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="BA13" t="n">
-        <v>1</v>
+        <v>0.01785714285714279</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.04464285714285765</v>
+        <v>-68</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.2319460820952344</v>
+        <v>2.244444444444468</v>
       </c>
       <c r="BD13" t="n">
-        <v>-13.5</v>
+        <v>3</v>
       </c>
       <c r="BE13" t="n">
-        <v>-1844017.857142858</v>
+        <v>-8250000</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.125</v>
+        <v>348571.4285714286</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3059,7 +3053,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>KCHNTNkc</t>
+          <t>h6Py6Kcj</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -3067,63 +3061,63 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">dujic f 
-  can </t>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">red bull arena
-  harrison  nj </t>
+          <t xml:space="preserve">chase stadium
+  fort lauderdale  fl </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>0AheRyBg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>8btog05R</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>6gpXy3vi</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>167</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>1671</v>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>2024</v>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>rJ9D8rzj</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>6LuGZiZI</t>
-        </is>
-      </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="Q14" t="n">
         <v>-2</v>
@@ -3135,117 +3129,117 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3999999999999999</v>
+        <v>-1</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
+        <v>-0.25</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.9166666666666667</v>
+      </c>
       <c r="X14" t="n">
-        <v>0.3000000000000007</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>-3.466666666666667</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.5</v>
+        <v>-1.333333333333334</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.2000000000000002</v>
+        <v>0.08333333333333393</v>
       </c>
       <c r="AB14" t="n">
-        <v>-9.399999999999999</v>
+        <v>-2.833333333333336</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.399999999999999</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>-0.09999999999999964</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>-1.7</v>
-      </c>
+        <v>2.833333333333336</v>
+      </c>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="n">
-        <v>-0.1000000000000001</v>
+        <v>-3.833333333333334</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.7</v>
+        <v>-0.08333333333333393</v>
       </c>
       <c r="AH14" t="n">
-        <v>-1</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="AI14" t="n">
-        <v>-3.533333333333333</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>-1.416666666666667</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>0.08333333333333304</v>
       </c>
       <c r="AL14" t="n">
-        <v>66.63313131313132</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="AM14" t="n">
-        <v>67.63232323232323</v>
+        <v>67.68552188552188</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.9099567099567309</v>
+        <v>2.399999999999999</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.3809523809523938</v>
+        <v>3693181.818181819</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.300000000000011</v>
+        <v>5.063492063492063</v>
       </c>
       <c r="AQ14" t="n">
-        <v>249557.6072534276</v>
+        <v>1.412698412698411</v>
       </c>
       <c r="AR14" t="n">
-        <v>-1.526916916652244</v>
+        <v>0.6363636363636365</v>
       </c>
       <c r="AS14" t="n">
-        <v>-555000</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>-0.9146376571223414</v>
+        <v>4.349206349206355</v>
       </c>
       <c r="AU14" t="n">
-        <v>-2.655194805194796</v>
+        <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>-48</v>
+        <v>5.818181818181827</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.05000000000000004</v>
+        <v>0.4545454545454568</v>
       </c>
       <c r="AX14" t="n">
-        <v>-81</v>
+        <v>26</v>
       </c>
       <c r="AY14" t="n">
-        <v>4.429968904037594</v>
+        <v>5.454545454545453</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-1</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="BB14" t="n">
-        <v>-2.422077922077925</v>
+        <v>35</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.493680693101048</v>
+        <v>-0.454545454545439</v>
       </c>
       <c r="BD14" t="n">
-        <v>-6.800000000000001</v>
+        <v>-2.555555555555557</v>
       </c>
       <c r="BE14" t="n">
-        <v>-1459086.58008658</v>
+        <v>48950000</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>203968.253968254</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3254,7 +3248,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WdOu5vDd</t>
+          <t>b3GRSs53</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -3262,185 +3256,185 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">villarreal a 
+          <t xml:space="preserve">dickerson j 
   usa </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">gillette stadium
-  foxborough  ma </t>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>167</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>1671</v>
       </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>2024</v>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>6BusaLE3</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>KtuTuMN0</t>
-        </is>
-      </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6904761904761905</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.119047619047619</v>
-      </c>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.8333333333333333</v>
+      </c>
       <c r="X15" t="n">
-        <v>-4.88095238095238</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.547619047619046</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.1666666666666679</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-4.166666666666664</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.166666666666664</v>
+      </c>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="n">
+        <v>1.666666666666666</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.1666666666666665</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-0.666666666666667</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>66.81868686868687</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>67.85454545454546</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>636944.4444444445</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.9107142857142847</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AS15" t="n">
         <v>-1</v>
       </c>
-      <c r="AA15" t="n">
-        <v>-0.2380952380952381</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>-3.666666666666664</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.666666666666664</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>-1.714285714285714</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.380952380952381</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>-0.2857142857142858</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0.2857142857142858</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>-5.904761904761905</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>-4.547619047619047</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>69.26666666666667</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>67.87272727272727</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>-0.8989898989899245</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1.826557239057237</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>-3.166666666666657</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>-56778.98987307097</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0.703612624738664</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>-26350000</v>
-      </c>
       <c r="AT15" t="n">
-        <v>0.1868072435125896</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.6569865319865329</v>
+        <v>4.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>-321</v>
+        <v>-1.777777777777771</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.07716793129197241</v>
+        <v>4.344444444444441</v>
       </c>
       <c r="AX15" t="n">
-        <v>-277</v>
+        <v>-66</v>
       </c>
       <c r="AY15" t="n">
-        <v>2.876361797709521</v>
+        <v>3.711111111111109</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="BA15" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>-0.2898989898989903</v>
+        <v>-60</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.175401697760442</v>
+        <v>-4.811111111111103</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.833333333333332</v>
+        <v>3.428571428571427</v>
       </c>
       <c r="BE15" t="n">
-        <v>-531295.244107744</v>
+        <v>-1145000</v>
       </c>
       <c r="BF15" t="n">
-        <v>-0.02390572390572387</v>
+        <v>972946.4285714286</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
